--- a/Result/checksun_type/電信.xlsx
+++ b/Result/checksun_type/電信.xlsx
@@ -641,62 +641,62 @@
       </c>
       <c r="AQ1" s="1" t="inlineStr">
         <is>
-          <t>my_signal</t>
+          <t>up_up</t>
         </is>
       </c>
       <c r="AR1" s="1" t="inlineStr">
         <is>
-          <t>my_signal_3d</t>
+          <t>up_up_3d</t>
         </is>
       </c>
       <c r="AS1" s="1" t="inlineStr">
         <is>
-          <t>my_signal_5d</t>
+          <t>up_up_5d</t>
         </is>
       </c>
       <c r="AT1" s="1" t="inlineStr">
         <is>
-          <t>my_signal_10d</t>
+          <t>up_up_10d</t>
         </is>
       </c>
       <c r="AU1" s="1" t="inlineStr">
         <is>
-          <t>up_up</t>
+          <t>bbw_cross</t>
         </is>
       </c>
       <c r="AV1" s="1" t="inlineStr">
         <is>
-          <t>up_up_3d</t>
+          <t>MA_UP_d</t>
         </is>
       </c>
       <c r="AW1" s="1" t="inlineStr">
         <is>
-          <t>up_up_5d</t>
+          <t>MA_UP_3d</t>
         </is>
       </c>
       <c r="AX1" s="1" t="inlineStr">
         <is>
-          <t>up_up_10d</t>
+          <t>MA_UP_5d</t>
         </is>
       </c>
       <c r="AY1" s="1" t="inlineStr">
         <is>
-          <t>bbw_cross</t>
+          <t>MA_UP_10d</t>
         </is>
       </c>
       <c r="AZ1" s="1" t="inlineStr">
         <is>
-          <t>MA_UP_3d</t>
+          <t>MA_UP_20d</t>
         </is>
       </c>
       <c r="BA1" s="1" t="inlineStr">
         <is>
-          <t>MA_UP_5d</t>
+          <t>MA_UP_30d</t>
         </is>
       </c>
       <c r="BB1" s="1" t="inlineStr">
         <is>
-          <t>MA_UP_10d</t>
+          <t>MA_UP_40d</t>
         </is>
       </c>
       <c r="BC1" s="1" t="inlineStr">
@@ -1653,52 +1653,52 @@
       </c>
       <c r="AS2" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
         <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="AV2" t="inlineStr">
+        <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AV2" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>16.0</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>16.0</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>7.0</t>
+          <t>16.0</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
@@ -1893,11 +1893,15 @@
           <t>144.95</t>
         </is>
       </c>
-      <c r="CQ2" t="n">
-        <v>142.55</v>
-      </c>
-      <c r="CR2" t="n">
-        <v>139.36</v>
+      <c r="CQ2" t="inlineStr">
+        <is>
+          <t>142.55</t>
+        </is>
+      </c>
+      <c r="CR2" t="inlineStr">
+        <is>
+          <t>139.36</t>
+        </is>
       </c>
       <c r="CS2" t="inlineStr">
         <is>
@@ -2635,52 +2639,52 @@
       </c>
       <c r="AS3" t="inlineStr">
         <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AU3" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="AV3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
           <t>2.0</t>
         </is>
       </c>
-      <c r="AT3" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
-      </c>
-      <c r="AU3" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AV3" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AW3" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AX3" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>15.0</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>15.0</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>7.0</t>
+          <t>15.0</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
@@ -2875,11 +2879,15 @@
           <t>144.7</t>
         </is>
       </c>
-      <c r="CQ3" t="n">
-        <v>142.12</v>
-      </c>
-      <c r="CR3" t="n">
-        <v>139.21</v>
+      <c r="CQ3" t="inlineStr">
+        <is>
+          <t>142.12</t>
+        </is>
+      </c>
+      <c r="CR3" t="inlineStr">
+        <is>
+          <t>139.21</t>
+        </is>
       </c>
       <c r="CS3" t="inlineStr">
         <is>
@@ -3612,57 +3620,57 @@
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
         <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="AV4" t="inlineStr">
+        <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AV4" t="inlineStr">
+      <c r="AW4" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="AW4" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>14.0</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>14.0</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>7.0</t>
+          <t>14.0</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
@@ -3857,11 +3865,15 @@
           <t>144.5</t>
         </is>
       </c>
-      <c r="CQ4" t="n">
-        <v>141.65</v>
-      </c>
-      <c r="CR4" t="n">
-        <v>139.08</v>
+      <c r="CQ4" t="inlineStr">
+        <is>
+          <t>141.65</t>
+        </is>
+      </c>
+      <c r="CR4" t="inlineStr">
+        <is>
+          <t>139.08</t>
+        </is>
       </c>
       <c r="CS4" t="inlineStr">
         <is>
@@ -4594,57 +4606,57 @@
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
         <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="AV5" t="inlineStr">
+        <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AV5" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>14.0</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>14.0</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>8.0</t>
+          <t>14.0</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
@@ -4839,11 +4851,15 @@
           <t>144.4</t>
         </is>
       </c>
-      <c r="CQ5" t="n">
-        <v>141.28</v>
-      </c>
-      <c r="CR5" t="n">
-        <v>138.99</v>
+      <c r="CQ5" t="inlineStr">
+        <is>
+          <t>141.28</t>
+        </is>
+      </c>
+      <c r="CR5" t="inlineStr">
+        <is>
+          <t>138.99</t>
+        </is>
       </c>
       <c r="CS5" t="inlineStr">
         <is>
@@ -5571,62 +5587,62 @@
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AR6" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AS6" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AU6" t="inlineStr">
+        <is>
           <t>True</t>
         </is>
       </c>
-      <c r="AR6" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
-      </c>
-      <c r="AS6" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
-      </c>
-      <c r="AT6" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
-      </c>
-      <c r="AU6" t="inlineStr">
+      <c r="AV6" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AV6" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>9.0</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>14.0</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>14.0</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>9.0</t>
+          <t>14.0</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
@@ -5821,11 +5837,15 @@
           <t>144.05</t>
         </is>
       </c>
-      <c r="CQ6" t="n">
-        <v>140.85</v>
-      </c>
-      <c r="CR6" t="n">
-        <v>138.87</v>
+      <c r="CQ6" t="inlineStr">
+        <is>
+          <t>140.85</t>
+        </is>
+      </c>
+      <c r="CR6" t="inlineStr">
+        <is>
+          <t>138.87</t>
+        </is>
       </c>
       <c r="CS6" t="inlineStr">
         <is>
@@ -6553,62 +6573,62 @@
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AR7" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AS7" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AU7" t="inlineStr">
+        <is>
           <t>True</t>
         </is>
       </c>
-      <c r="AR7" t="inlineStr">
+      <c r="AV7" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="AW7" t="inlineStr">
         <is>
           <t>3.0</t>
         </is>
       </c>
-      <c r="AS7" t="inlineStr">
-        <is>
-          <t>4.0</t>
-        </is>
-      </c>
-      <c r="AT7" t="inlineStr">
-        <is>
-          <t>4.0</t>
-        </is>
-      </c>
-      <c r="AU7" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AV7" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AW7" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>14.0</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>14.0</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>14.0</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
@@ -6803,11 +6823,15 @@
           <t>143.5</t>
         </is>
       </c>
-      <c r="CQ7" t="n">
-        <v>140.38</v>
-      </c>
-      <c r="CR7" t="n">
-        <v>138.69</v>
+      <c r="CQ7" t="inlineStr">
+        <is>
+          <t>140.38</t>
+        </is>
+      </c>
+      <c r="CR7" t="inlineStr">
+        <is>
+          <t>138.69</t>
+        </is>
       </c>
       <c r="CS7" t="inlineStr">
         <is>
@@ -7535,62 +7559,62 @@
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AR8" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AS8" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AU8" t="inlineStr">
+        <is>
           <t>True</t>
         </is>
       </c>
-      <c r="AR8" t="inlineStr">
+      <c r="AV8" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="AW8" t="inlineStr">
         <is>
           <t>3.0</t>
         </is>
       </c>
-      <c r="AS8" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
-      </c>
-      <c r="AT8" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
-      </c>
-      <c r="AU8" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AV8" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AW8" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>13.0</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>13.0</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>13.0</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
@@ -7785,11 +7809,15 @@
           <t>142.9</t>
         </is>
       </c>
-      <c r="CQ8" t="n">
-        <v>139.9</v>
-      </c>
-      <c r="CR8" t="n">
-        <v>138.44</v>
+      <c r="CQ8" t="inlineStr">
+        <is>
+          <t>139.9</t>
+        </is>
+      </c>
+      <c r="CR8" t="inlineStr">
+        <is>
+          <t>138.44</t>
+        </is>
       </c>
       <c r="CS8" t="inlineStr">
         <is>
@@ -8517,62 +8545,62 @@
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AR9" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AS9" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="AU9" t="inlineStr">
+        <is>
           <t>True</t>
         </is>
       </c>
-      <c r="AR9" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
-      </c>
-      <c r="AS9" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
-      </c>
-      <c r="AT9" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
-      </c>
-      <c r="AU9" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
@@ -8767,11 +8795,15 @@
           <t>142.3</t>
         </is>
       </c>
-      <c r="CQ9" t="n">
-        <v>139.48</v>
-      </c>
-      <c r="CR9" t="n">
-        <v>138.2</v>
+      <c r="CQ9" t="inlineStr">
+        <is>
+          <t>139.48</t>
+        </is>
+      </c>
+      <c r="CR9" t="inlineStr">
+        <is>
+          <t>138.2</t>
+        </is>
       </c>
       <c r="CS9" t="inlineStr">
         <is>
@@ -9499,62 +9531,62 @@
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AR10" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AS10" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="AU10" t="inlineStr">
+        <is>
           <t>True</t>
         </is>
       </c>
-      <c r="AR10" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="AS10" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="AT10" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="AU10" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>11.0</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>11.0</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>11.0</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
@@ -9749,11 +9781,15 @@
           <t>141.65</t>
         </is>
       </c>
-      <c r="CQ10" t="n">
-        <v>139.07</v>
-      </c>
-      <c r="CR10" t="n">
-        <v>137.98</v>
+      <c r="CQ10" t="inlineStr">
+        <is>
+          <t>139.07</t>
+        </is>
+      </c>
+      <c r="CR10" t="inlineStr">
+        <is>
+          <t>137.98</t>
+        </is>
       </c>
       <c r="CS10" t="inlineStr">
         <is>

--- a/Result/checksun_type/電信.xlsx
+++ b/Result/checksun_type/電信.xlsx
@@ -1443,12 +1443,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0.34</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>10009.961</t>
+          <t>8515.486</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -1458,7 +1458,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>146.0</t>
+          <t>145.5</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -1478,7 +1478,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-0.16786321196452753</t>
+          <t>-0.07440392378152937</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -1488,7 +1488,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>99.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -1523,7 +1523,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>60.0</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -1538,47 +1538,47 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>142.55</t>
+          <t>142.925</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>148.4785216050076</t>
+          <t>148.5844122811866</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>136.6214783949924</t>
+          <t>137.2655877188134</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>0.08317813546134833</t>
+          <t>0.07919415471312412</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>0.002990325417766115</t>
+          <t>0.002630655910206947</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>0.001688232507605081</t>
+          <t>0.000713171676491875</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>-0.03152921474358805</t>
+          <t>-0.0478969710749888</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>0.05111568461276083</t>
+          <t>0.04785629426595885</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>1.23096372806679</t>
+          <t>1.123964812126325</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
@@ -1593,7 +1593,7 @@
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>35.0</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
@@ -1623,162 +1623,162 @@
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
+          <t>3.0</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
           <t>2.0</t>
         </is>
       </c>
-      <c r="AO2" t="inlineStr">
+      <c r="AP2" t="inlineStr">
         <is>
           <t>2.0</t>
         </is>
       </c>
-      <c r="AP2" t="inlineStr">
+      <c r="AQ2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AR2" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AS2" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AT2" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AU2" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="AV2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AW2" t="inlineStr">
         <is>
           <t>3.0</t>
         </is>
       </c>
-      <c r="AQ2" t="inlineStr">
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>7.0</t>
+        </is>
+      </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>16.0</t>
+        </is>
+      </c>
+      <c r="BA2" t="inlineStr">
+        <is>
+          <t>17.0</t>
+        </is>
+      </c>
+      <c r="BB2" t="inlineStr">
+        <is>
+          <t>17.0</t>
+        </is>
+      </c>
+      <c r="BC2" t="inlineStr">
+        <is>
+          <t>盤整</t>
+        </is>
+      </c>
+      <c r="BD2" t="inlineStr">
+        <is>
+          <t>盤整</t>
+        </is>
+      </c>
+      <c r="BE2" t="inlineStr">
+        <is>
+          <t>58.3</t>
+        </is>
+      </c>
+      <c r="BF2" t="inlineStr">
+        <is>
+          <t>15010110.0</t>
+        </is>
+      </c>
+      <c r="BG2" t="inlineStr">
+        <is>
+          <t>1050416.0</t>
+        </is>
+      </c>
+      <c r="BH2" t="inlineStr">
+        <is>
+          <t>4036399.0</t>
+        </is>
+      </c>
+      <c r="BI2" t="inlineStr">
+        <is>
+          <t>-2985983.0</t>
+        </is>
+      </c>
+      <c r="BJ2" t="inlineStr">
+        <is>
+          <t>-213000.0</t>
+        </is>
+      </c>
+      <c r="BK2" t="inlineStr">
+        <is>
+          <t>11811127.0</t>
+        </is>
+      </c>
+      <c r="BL2" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="BM2" t="inlineStr">
+        <is>
+          <t>4.0</t>
+        </is>
+      </c>
+      <c r="BN2" t="inlineStr">
+        <is>
+          <t>-2.0</t>
+        </is>
+      </c>
+      <c r="BO2" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AR2" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AS2" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AT2" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AU2" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="AV2" t="inlineStr">
+      <c r="BP2" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AW2" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
-      </c>
-      <c r="AX2" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>7.0</t>
-        </is>
-      </c>
-      <c r="AZ2" t="inlineStr">
-        <is>
-          <t>16.0</t>
-        </is>
-      </c>
-      <c r="BA2" t="inlineStr">
-        <is>
-          <t>16.0</t>
-        </is>
-      </c>
-      <c r="BB2" t="inlineStr">
-        <is>
-          <t>16.0</t>
-        </is>
-      </c>
-      <c r="BC2" t="inlineStr">
-        <is>
-          <t>盤整</t>
-        </is>
-      </c>
-      <c r="BD2" t="inlineStr">
-        <is>
-          <t>盤整</t>
-        </is>
-      </c>
-      <c r="BE2" t="inlineStr">
-        <is>
-          <t>58.3</t>
-        </is>
-      </c>
-      <c r="BF2" t="inlineStr">
-        <is>
-          <t>13104436.0</t>
-        </is>
-      </c>
-      <c r="BG2" t="inlineStr">
-        <is>
-          <t>1124316.0</t>
-        </is>
-      </c>
-      <c r="BH2" t="inlineStr">
-        <is>
-          <t>2157000.0</t>
-        </is>
-      </c>
-      <c r="BI2" t="inlineStr">
-        <is>
-          <t>-1032684.0</t>
-        </is>
-      </c>
-      <c r="BJ2" t="inlineStr">
-        <is>
-          <t>-452020.0</t>
-        </is>
-      </c>
-      <c r="BK2" t="inlineStr">
-        <is>
-          <t>11619732.0</t>
-        </is>
-      </c>
-      <c r="BL2" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
-      </c>
-      <c r="BM2" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
-      </c>
-      <c r="BN2" t="inlineStr">
-        <is>
-          <t>-1.0</t>
-        </is>
-      </c>
-      <c r="BO2" t="inlineStr">
+      <c r="BQ2" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="BP2" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="BQ2" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-0.05</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
@@ -1828,17 +1828,17 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="CC2" t="inlineStr">
         <is>
-          <t>16.71</t>
+          <t>14.21</t>
         </is>
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
@@ -1849,177 +1849,177 @@
       <c r="CF2" t="inlineStr"/>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>86</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
         <is>
-          <t>10010</t>
+          <t>8515</t>
         </is>
       </c>
       <c r="CI2" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="CJ2" t="inlineStr">
         <is>
-          <t>66.67</t>
+          <t>93.33</t>
         </is>
       </c>
       <c r="CK2" t="n">
-        <v>0.83</v>
+        <v>0.41</v>
       </c>
       <c r="CL2" t="n">
-        <v>1.58</v>
+        <v>1.38</v>
       </c>
       <c r="CM2" t="inlineStr">
         <is>
-          <t>2.29</t>
+          <t>2.45</t>
         </is>
       </c>
       <c r="CN2" t="inlineStr">
         <is>
-          <t>-0.43</t>
+          <t>-0.35</t>
         </is>
       </c>
       <c r="CO2" t="inlineStr">
         <is>
-          <t>144.8</t>
+          <t>144.9</t>
         </is>
       </c>
       <c r="CP2" t="inlineStr">
         <is>
-          <t>144.95</t>
+          <t>145.0</t>
         </is>
       </c>
       <c r="CQ2" t="inlineStr">
         <is>
-          <t>142.55</t>
+          <t>142.93</t>
         </is>
       </c>
       <c r="CR2" t="inlineStr">
         <is>
-          <t>139.36</t>
+          <t>139.51</t>
         </is>
       </c>
       <c r="CS2" t="inlineStr">
         <is>
-          <t>139.96</t>
+          <t>140.01</t>
         </is>
       </c>
       <c r="CT2" t="inlineStr">
         <is>
+          <t>136.0104166666667</t>
+        </is>
+      </c>
+      <c r="CU2" t="inlineStr">
+        <is>
+          <t>0.0006906077348065587</t>
+        </is>
+      </c>
+      <c r="CV2" t="inlineStr">
+        <is>
+          <t>0.0003449465332874269</t>
+        </is>
+      </c>
+      <c r="CW2" t="inlineStr">
+        <is>
+          <t>0.002630655910206947</t>
+        </is>
+      </c>
+      <c r="CX2" t="inlineStr">
+        <is>
+          <t>0.001076349024110135</t>
+        </is>
+      </c>
+      <c r="CY2" t="inlineStr">
+        <is>
+          <t>0.0003125837277841992</t>
+        </is>
+      </c>
+      <c r="CZ2" t="inlineStr">
+        <is>
+          <t>0.0003830830524056417</t>
+        </is>
+      </c>
+      <c r="DA2" t="inlineStr">
+        <is>
+          <t>4.21</t>
+        </is>
+      </c>
+      <c r="DB2" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="DC2" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="DD2" t="inlineStr">
+        <is>
+          <t>1.9</t>
+        </is>
+      </c>
+      <c r="DE2" t="inlineStr">
+        <is>
+          <t>-2.49</t>
+        </is>
+      </c>
+      <c r="DF2" t="inlineStr">
+        <is>
+          <t>2026/08/21</t>
+        </is>
+      </c>
+      <c r="DG2" t="inlineStr">
+        <is>
+          <t>2218439785.568572</t>
+        </is>
+      </c>
+      <c r="DH2" t="inlineStr">
+        <is>
+          <t>1239700787.0</t>
+        </is>
+      </c>
+      <c r="DI2" t="n">
+        <v>1429392742.2</v>
+      </c>
+      <c r="DJ2" t="inlineStr">
+        <is>
+          <t>1544294297.4</t>
+        </is>
+      </c>
+      <c r="DK2" t="inlineStr">
+        <is>
+          <t>1502594940.533333</t>
+        </is>
+      </c>
+      <c r="DL2" t="n">
+        <v>1654145469.66</v>
+      </c>
+      <c r="DM2" t="inlineStr">
+        <is>
+          <t>1987286590.375</t>
+        </is>
+      </c>
+      <c r="DN2" t="inlineStr">
+        <is>
+          <t>-8184469.60354781</t>
+        </is>
+      </c>
+      <c r="DO2" t="inlineStr">
+        <is>
+          <t>-74321546.88150048</t>
+        </is>
+      </c>
+      <c r="DP2" t="inlineStr">
+        <is>
+          <t>1239700787.0</t>
+        </is>
+      </c>
+      <c r="DQ2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="CU2" t="inlineStr">
-        <is>
-          <t>0.0006910850034556049</t>
-        </is>
-      </c>
-      <c r="CV2" t="inlineStr">
-        <is>
-          <t>0.001727712508638568</t>
-        </is>
-      </c>
-      <c r="CW2" t="inlineStr">
-        <is>
-          <t>0.002990325417766115</t>
-        </is>
-      </c>
-      <c r="CX2" t="inlineStr">
-        <is>
-          <t>0.001077508799655291</t>
-        </is>
-      </c>
-      <c r="CY2" t="inlineStr">
-        <is>
-          <t>0.0006702712364270447</t>
-        </is>
-      </c>
-      <c r="CZ2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="DA2" t="inlineStr">
-        <is>
-          <t>7.12</t>
-        </is>
-      </c>
-      <c r="DB2" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="DC2" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="DD2" t="inlineStr">
-        <is>
-          <t>1.9</t>
-        </is>
-      </c>
-      <c r="DE2" t="inlineStr">
-        <is>
-          <t>-3.52</t>
-        </is>
-      </c>
-      <c r="DF2" t="inlineStr">
-        <is>
-          <t>2026/08/21</t>
-        </is>
-      </c>
-      <c r="DG2" t="inlineStr">
-        <is>
-          <t>2525520667.780788</t>
-        </is>
-      </c>
-      <c r="DH2" t="inlineStr">
-        <is>
-          <t>1458318100.0</t>
-        </is>
-      </c>
-      <c r="DI2" t="n">
-        <v>1365056504.4</v>
-      </c>
-      <c r="DJ2" t="inlineStr">
-        <is>
-          <t>1640423214.1</t>
-        </is>
-      </c>
-      <c r="DK2" t="inlineStr">
-        <is>
-          <t>1485353753.433333</t>
-        </is>
-      </c>
-      <c r="DL2" t="n">
-        <v>1659414895.68</v>
-      </c>
-      <c r="DM2" t="inlineStr">
-        <is>
-          <t>2004348026.1375</t>
-        </is>
-      </c>
-      <c r="DN2" t="inlineStr">
-        <is>
-          <t>3840453.53609038</t>
-        </is>
-      </c>
-      <c r="DO2" t="inlineStr">
-        <is>
-          <t>-62046440.25567794</t>
-        </is>
-      </c>
-      <c r="DP2" t="inlineStr">
-        <is>
-          <t>1458318100.0</t>
-        </is>
-      </c>
-      <c r="DQ2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="DR2" t="inlineStr">
         <is>
           <t>143.5</t>
@@ -2032,7 +2032,7 @@
       </c>
       <c r="DT2" t="inlineStr">
         <is>
-          <t>1.74</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="DU2" t="inlineStr">
@@ -2087,12 +2087,12 @@
       </c>
       <c r="EE2" t="inlineStr">
         <is>
-          <t>3.09</t>
+          <t>3.08</t>
         </is>
       </c>
       <c r="EF2" t="inlineStr">
         <is>
-          <t>3.56</t>
+          <t>3.57</t>
         </is>
       </c>
       <c r="EG2" t="inlineStr">
@@ -2102,7 +2102,7 @@
       </c>
       <c r="EH2" t="inlineStr">
         <is>
-          <t>28.68</t>
+          <t>28.59</t>
         </is>
       </c>
       <c r="EI2" t="inlineStr">
@@ -2117,12 +2117,12 @@
       </c>
       <c r="EK2" t="inlineStr">
         <is>
-          <t>86.5</t>
+          <t>85.28</t>
         </is>
       </c>
       <c r="EL2" t="inlineStr">
         <is>
-          <t>1132587</t>
+          <t>1128708</t>
         </is>
       </c>
       <c r="EM2" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="EP2" t="inlineStr">
         <is>
-          <t>145.0</t>
+          <t>147.0</t>
         </is>
       </c>
       <c r="EQ2" t="inlineStr">
         <is>
-          <t>146.5</t>
+          <t>147.0</t>
         </is>
       </c>
       <c r="ER2" t="inlineStr">
@@ -2157,12 +2157,12 @@
       </c>
       <c r="ES2" t="inlineStr">
         <is>
-          <t>146.0</t>
+          <t>145.5</t>
         </is>
       </c>
       <c r="ET2" t="inlineStr">
         <is>
-          <t>129.5</t>
+          <t>128.0</t>
         </is>
       </c>
       <c r="EU2" t="inlineStr">
@@ -2182,42 +2182,42 @@
       </c>
       <c r="EX2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="EY2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="EZ2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FA2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FB2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FC2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FD2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="FE2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FF2" t="inlineStr">
@@ -2227,22 +2227,22 @@
       </c>
       <c r="FG2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="FH2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FI2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FJ2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FK2" t="inlineStr">
@@ -2429,12 +2429,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>0.34</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>8628.434</t>
+          <t>10009.961</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -2444,7 +2444,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>145.5</t>
+          <t>146.0</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -2454,7 +2454,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>0.34</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-0.22942768703039035</t>
+          <t>-0.16786321196452753</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -2474,7 +2474,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>99.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -2509,7 +2509,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>60.0</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -2524,47 +2524,47 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>142.125</t>
+          <t>142.55</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>148.228277807866</t>
+          <t>148.4785216050106</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>136.021722192134</t>
+          <t>136.6214783949895</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>0.08588605534376148</t>
+          <t>0.0831781354613898</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>0.003353335686551384</t>
+          <t>0.002990325417766115</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>0.0007628237184782449</t>
+          <t>0.001688232507606857</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>-0.05914846279594743</t>
+          <t>-0.03152921474353376</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>0.05111568461276083</t>
+          <t>0.04785629426595885</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>1.334686942343627</t>
+          <t>1.230963728066852</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
@@ -2609,7 +2609,7 @@
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
@@ -2619,152 +2619,152 @@
       </c>
       <c r="AO3" t="inlineStr">
         <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="AP3" t="inlineStr">
+        <is>
           <t>3.0</t>
         </is>
       </c>
-      <c r="AP3" t="inlineStr">
+      <c r="AQ3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AR3" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AS3" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AU3" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="AV3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
         <is>
           <t>2.0</t>
         </is>
       </c>
-      <c r="AQ3" t="inlineStr">
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>7.0</t>
+        </is>
+      </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>16.0</t>
+        </is>
+      </c>
+      <c r="BA3" t="inlineStr">
+        <is>
+          <t>16.0</t>
+        </is>
+      </c>
+      <c r="BB3" t="inlineStr">
+        <is>
+          <t>16.0</t>
+        </is>
+      </c>
+      <c r="BC3" t="inlineStr">
+        <is>
+          <t>盤整</t>
+        </is>
+      </c>
+      <c r="BD3" t="inlineStr">
+        <is>
+          <t>盤整</t>
+        </is>
+      </c>
+      <c r="BE3" t="inlineStr">
+        <is>
+          <t>58.3</t>
+        </is>
+      </c>
+      <c r="BF3" t="inlineStr">
+        <is>
+          <t>15010110.0</t>
+        </is>
+      </c>
+      <c r="BG3" t="inlineStr">
+        <is>
+          <t>1050416.0</t>
+        </is>
+      </c>
+      <c r="BH3" t="inlineStr">
+        <is>
+          <t>4036399.0</t>
+        </is>
+      </c>
+      <c r="BI3" t="inlineStr">
+        <is>
+          <t>-2985983.0</t>
+        </is>
+      </c>
+      <c r="BJ3" t="inlineStr">
+        <is>
+          <t>-213000.0</t>
+        </is>
+      </c>
+      <c r="BK3" t="inlineStr">
+        <is>
+          <t>11811127.0</t>
+        </is>
+      </c>
+      <c r="BL3" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="BM3" t="inlineStr">
+        <is>
+          <t>4.0</t>
+        </is>
+      </c>
+      <c r="BN3" t="inlineStr">
+        <is>
+          <t>-2.0</t>
+        </is>
+      </c>
+      <c r="BO3" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AR3" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AS3" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AT3" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AU3" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="AV3" t="inlineStr">
+      <c r="BP3" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AW3" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="AX3" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr">
-        <is>
-          <t>7.0</t>
-        </is>
-      </c>
-      <c r="AZ3" t="inlineStr">
-        <is>
-          <t>15.0</t>
-        </is>
-      </c>
-      <c r="BA3" t="inlineStr">
-        <is>
-          <t>15.0</t>
-        </is>
-      </c>
-      <c r="BB3" t="inlineStr">
-        <is>
-          <t>15.0</t>
-        </is>
-      </c>
-      <c r="BC3" t="inlineStr">
-        <is>
-          <t>盤整</t>
-        </is>
-      </c>
-      <c r="BD3" t="inlineStr">
-        <is>
-          <t>盤整</t>
-        </is>
-      </c>
-      <c r="BE3" t="inlineStr">
-        <is>
-          <t>58.3</t>
-        </is>
-      </c>
-      <c r="BF3" t="inlineStr">
-        <is>
-          <t>13104436.0</t>
-        </is>
-      </c>
-      <c r="BG3" t="inlineStr">
-        <is>
-          <t>1124316.0</t>
-        </is>
-      </c>
-      <c r="BH3" t="inlineStr">
-        <is>
-          <t>2157000.0</t>
-        </is>
-      </c>
-      <c r="BI3" t="inlineStr">
-        <is>
-          <t>-1032684.0</t>
-        </is>
-      </c>
-      <c r="BJ3" t="inlineStr">
-        <is>
-          <t>-452020.0</t>
-        </is>
-      </c>
-      <c r="BK3" t="inlineStr">
-        <is>
-          <t>11619732.0</t>
-        </is>
-      </c>
-      <c r="BL3" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
-      </c>
-      <c r="BM3" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
-      </c>
-      <c r="BN3" t="inlineStr">
-        <is>
-          <t>-1.0</t>
-        </is>
-      </c>
-      <c r="BO3" t="inlineStr">
+      <c r="BQ3" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="BP3" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="BQ3" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>-0.01</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
@@ -2814,17 +2814,17 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="CC3" t="inlineStr">
         <is>
-          <t>14.40</t>
+          <t>16.71</t>
         </is>
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>1.40</t>
+          <t>1.05</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
@@ -2835,12 +2835,12 @@
       <c r="CF3" t="inlineStr"/>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>86</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
         <is>
-          <t>10010</t>
+          <t>8515</t>
         </is>
       </c>
       <c r="CI3" t="inlineStr">
@@ -2850,162 +2850,162 @@
       </c>
       <c r="CJ3" t="inlineStr">
         <is>
-          <t>41.67</t>
+          <t>66.67</t>
         </is>
       </c>
       <c r="CK3" t="n">
-        <v>0.55</v>
+        <v>0.83</v>
       </c>
       <c r="CL3" t="n">
-        <v>1.81</v>
+        <v>1.58</v>
       </c>
       <c r="CM3" t="inlineStr">
         <is>
-          <t>2.09</t>
+          <t>2.29</t>
         </is>
       </c>
       <c r="CN3" t="inlineStr">
         <is>
-          <t>-0.47</t>
+          <t>-0.43</t>
         </is>
       </c>
       <c r="CO3" t="inlineStr">
         <is>
-          <t>144.7</t>
+          <t>144.8</t>
         </is>
       </c>
       <c r="CP3" t="inlineStr">
         <is>
-          <t>144.7</t>
+          <t>144.95</t>
         </is>
       </c>
       <c r="CQ3" t="inlineStr">
         <is>
-          <t>142.12</t>
+          <t>142.55</t>
         </is>
       </c>
       <c r="CR3" t="inlineStr">
         <is>
-          <t>139.21</t>
+          <t>139.36</t>
         </is>
       </c>
       <c r="CS3" t="inlineStr">
         <is>
-          <t>139.87</t>
+          <t>139.96</t>
         </is>
       </c>
       <c r="CT3" t="inlineStr">
         <is>
+          <t>135.9583333333333</t>
+        </is>
+      </c>
+      <c r="CU3" t="inlineStr">
+        <is>
+          <t>0.0006910850034556049</t>
+        </is>
+      </c>
+      <c r="CV3" t="inlineStr">
+        <is>
+          <t>0.001727712508638568</t>
+        </is>
+      </c>
+      <c r="CW3" t="inlineStr">
+        <is>
+          <t>0.002990325417766115</t>
+        </is>
+      </c>
+      <c r="CX3" t="inlineStr">
+        <is>
+          <t>0.001077508799655291</t>
+        </is>
+      </c>
+      <c r="CY3" t="inlineStr">
+        <is>
+          <t>0.0006702712364270447</t>
+        </is>
+      </c>
+      <c r="CZ3" t="inlineStr">
+        <is>
+          <t>0.0003985651654045963</t>
+        </is>
+      </c>
+      <c r="DA3" t="inlineStr">
+        <is>
+          <t>7.12</t>
+        </is>
+      </c>
+      <c r="DB3" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="DC3" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="DD3" t="inlineStr">
+        <is>
+          <t>1.9</t>
+        </is>
+      </c>
+      <c r="DE3" t="inlineStr">
+        <is>
+          <t>-3.52</t>
+        </is>
+      </c>
+      <c r="DF3" t="inlineStr">
+        <is>
+          <t>2026/08/21</t>
+        </is>
+      </c>
+      <c r="DG3" t="inlineStr">
+        <is>
+          <t>2218439785.568572</t>
+        </is>
+      </c>
+      <c r="DH3" t="inlineStr">
+        <is>
+          <t>1458318100.0</t>
+        </is>
+      </c>
+      <c r="DI3" t="n">
+        <v>1365056504.4</v>
+      </c>
+      <c r="DJ3" t="inlineStr">
+        <is>
+          <t>1640423214.1</t>
+        </is>
+      </c>
+      <c r="DK3" t="inlineStr">
+        <is>
+          <t>1485353753.433333</t>
+        </is>
+      </c>
+      <c r="DL3" t="n">
+        <v>1659414895.68</v>
+      </c>
+      <c r="DM3" t="inlineStr">
+        <is>
+          <t>2004348026.1375</t>
+        </is>
+      </c>
+      <c r="DN3" t="inlineStr">
+        <is>
+          <t>3840453.537898131</t>
+        </is>
+      </c>
+      <c r="DO3" t="inlineStr">
+        <is>
+          <t>-62046440.25528979</t>
+        </is>
+      </c>
+      <c r="DP3" t="inlineStr">
+        <is>
+          <t>1458318100.0</t>
+        </is>
+      </c>
+      <c r="DQ3" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="CU3" t="inlineStr">
-        <is>
-          <t>0.0006915629322268302</t>
-        </is>
-      </c>
-      <c r="CV3" t="inlineStr">
-        <is>
-          <t>0.00138408304498272</t>
-        </is>
-      </c>
-      <c r="CW3" t="inlineStr">
-        <is>
-          <t>0.003353335686551384</t>
-        </is>
-      </c>
-      <c r="CX3" t="inlineStr">
-        <is>
-          <t>0.0009347138337647554</t>
-        </is>
-      </c>
-      <c r="CY3" t="inlineStr">
-        <is>
-          <t>0.0004023245417970056</t>
-        </is>
-      </c>
-      <c r="CZ3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="DA3" t="inlineStr">
-        <is>
-          <t>6.98</t>
-        </is>
-      </c>
-      <c r="DB3" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="DC3" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="DD3" t="inlineStr">
-        <is>
-          <t>1.9</t>
-        </is>
-      </c>
-      <c r="DE3" t="inlineStr">
-        <is>
-          <t>-5.24</t>
-        </is>
-      </c>
-      <c r="DF3" t="inlineStr">
-        <is>
-          <t>2026/08/21</t>
-        </is>
-      </c>
-      <c r="DG3" t="inlineStr">
-        <is>
-          <t>2525520667.780788</t>
-        </is>
-      </c>
-      <c r="DH3" t="inlineStr">
-        <is>
-          <t>1248190797.0</t>
-        </is>
-      </c>
-      <c r="DI3" t="n">
-        <v>1315071112.6</v>
-      </c>
-      <c r="DJ3" t="inlineStr">
-        <is>
-          <t>1706616096.2</t>
-        </is>
-      </c>
-      <c r="DK3" t="inlineStr">
-        <is>
-          <t>1469076947.433333</t>
-        </is>
-      </c>
-      <c r="DL3" t="n">
-        <v>1667394181.32</v>
-      </c>
-      <c r="DM3" t="inlineStr">
-        <is>
-          <t>2016079760.0875</t>
-        </is>
-      </c>
-      <c r="DN3" t="inlineStr">
-        <is>
-          <t>15819888.77095735</t>
-        </is>
-      </c>
-      <c r="DO3" t="inlineStr">
-        <is>
-          <t>-65717912.88774347</t>
-        </is>
-      </c>
-      <c r="DP3" t="inlineStr">
-        <is>
-          <t>1248190797.0</t>
-        </is>
-      </c>
-      <c r="DQ3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="DR3" t="inlineStr">
         <is>
           <t>143.5</t>
@@ -3018,7 +3018,7 @@
       </c>
       <c r="DT3" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>1.74</t>
         </is>
       </c>
       <c r="DU3" t="inlineStr">
@@ -3068,17 +3068,17 @@
       </c>
       <c r="ED3" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="EE3" t="inlineStr">
         <is>
-          <t>3.08</t>
+          <t>3.09</t>
         </is>
       </c>
       <c r="EF3" t="inlineStr">
         <is>
-          <t>3.56</t>
+          <t>3.57</t>
         </is>
       </c>
       <c r="EG3" t="inlineStr">
@@ -3088,7 +3088,7 @@
       </c>
       <c r="EH3" t="inlineStr">
         <is>
-          <t>28.68</t>
+          <t>28.59</t>
         </is>
       </c>
       <c r="EI3" t="inlineStr">
@@ -3103,12 +3103,12 @@
       </c>
       <c r="EK3" t="inlineStr">
         <is>
-          <t>86.5</t>
+          <t>85.28</t>
         </is>
       </c>
       <c r="EL3" t="inlineStr">
         <is>
-          <t>1132587</t>
+          <t>1128708</t>
         </is>
       </c>
       <c r="EM3" t="inlineStr">
@@ -3128,27 +3128,27 @@
       </c>
       <c r="EP3" t="inlineStr">
         <is>
+          <t>145.0</t>
+        </is>
+      </c>
+      <c r="EQ3" t="inlineStr">
+        <is>
+          <t>146.5</t>
+        </is>
+      </c>
+      <c r="ER3" t="inlineStr">
+        <is>
           <t>144.0</t>
         </is>
       </c>
-      <c r="EQ3" t="inlineStr">
+      <c r="ES3" t="inlineStr">
         <is>
           <t>146.0</t>
         </is>
       </c>
-      <c r="ER3" t="inlineStr">
-        <is>
-          <t>143.0</t>
-        </is>
-      </c>
-      <c r="ES3" t="inlineStr">
-        <is>
-          <t>145.5</t>
-        </is>
-      </c>
       <c r="ET3" t="inlineStr">
         <is>
-          <t>129.5</t>
+          <t>128.0</t>
         </is>
       </c>
       <c r="EU3" t="inlineStr">
@@ -3168,42 +3168,42 @@
       </c>
       <c r="EX3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="EY3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="EZ3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FA3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FB3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FC3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FD3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="FE3" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FF3" t="inlineStr">
@@ -3213,22 +3213,22 @@
       </c>
       <c r="FG3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="FH3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FI3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FJ3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FK3" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>10607.859</t>
+          <t>8628.434</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -3430,369 +3430,369 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
+          <t>145.5</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>-0.22942768703039035</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>60.0</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>轉強</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>TrendType : 轉強&lt;br&gt;TrendScore : 60&lt;br&gt;HH : True&lt;br&gt;HL : False&lt;br&gt;MA : True&lt;br&gt;VOL : False</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>142.125</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>148.2282778078687</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>136.0217221921313</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>0.08588605534379948</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>0.003353335686551384</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>0.0007628237184804654</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>-0.0591484627958786</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>0.04785629426595885</t>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t>1.334686942343584</t>
+        </is>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>2026-09-02 00:00:00</t>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="AG4" t="inlineStr">
+        <is>
+          <t>40.0</t>
+        </is>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>2026-09-03 00:00:00</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AL4" t="inlineStr">
+        <is>
+          <t>2026-09-08 00:00:00</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="AN4" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
+      </c>
+      <c r="AP4" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="AQ4" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AR4" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AS4" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AU4" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="AV4" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>7.0</t>
+        </is>
+      </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>15.0</t>
+        </is>
+      </c>
+      <c r="BA4" t="inlineStr">
+        <is>
+          <t>15.0</t>
+        </is>
+      </c>
+      <c r="BB4" t="inlineStr">
+        <is>
+          <t>15.0</t>
+        </is>
+      </c>
+      <c r="BC4" t="inlineStr">
+        <is>
+          <t>盤整</t>
+        </is>
+      </c>
+      <c r="BD4" t="inlineStr">
+        <is>
+          <t>盤整</t>
+        </is>
+      </c>
+      <c r="BE4" t="inlineStr">
+        <is>
+          <t>58.3</t>
+        </is>
+      </c>
+      <c r="BF4" t="inlineStr">
+        <is>
+          <t>15010110.0</t>
+        </is>
+      </c>
+      <c r="BG4" t="inlineStr">
+        <is>
+          <t>1050416.0</t>
+        </is>
+      </c>
+      <c r="BH4" t="inlineStr">
+        <is>
+          <t>4036399.0</t>
+        </is>
+      </c>
+      <c r="BI4" t="inlineStr">
+        <is>
+          <t>-2985983.0</t>
+        </is>
+      </c>
+      <c r="BJ4" t="inlineStr">
+        <is>
+          <t>-213000.0</t>
+        </is>
+      </c>
+      <c r="BK4" t="inlineStr">
+        <is>
+          <t>11811127.0</t>
+        </is>
+      </c>
+      <c r="BL4" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="BM4" t="inlineStr">
+        <is>
+          <t>4.0</t>
+        </is>
+      </c>
+      <c r="BN4" t="inlineStr">
+        <is>
+          <t>-2.0</t>
+        </is>
+      </c>
+      <c r="BO4" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="BP4" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="BQ4" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="BR4" t="inlineStr">
+        <is>
+          <t>-0.01</t>
+        </is>
+      </c>
+      <c r="BS4" t="inlineStr">
+        <is>
+          <t>2026/07/20</t>
+        </is>
+      </c>
+      <c r="BT4" t="inlineStr">
+        <is>
+          <t>139.0</t>
+        </is>
+      </c>
+      <c r="BU4" t="inlineStr">
+        <is>
+          <t>2026/04/16</t>
+        </is>
+      </c>
+      <c r="BV4" t="inlineStr">
+        <is>
+          <t>136.5</t>
+        </is>
+      </c>
+      <c r="BW4" t="inlineStr">
+        <is>
+          <t>2026/08/05</t>
+        </is>
+      </c>
+      <c r="BX4" t="inlineStr">
+        <is>
+          <t>137.0</t>
+        </is>
+      </c>
+      <c r="BY4" t="inlineStr">
+        <is>
+          <t>2026/06/24</t>
+        </is>
+      </c>
+      <c r="BZ4" t="inlineStr">
+        <is>
           <t>143.5</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>1.71</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>-0.3292751984432931</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>90.0</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>盤整偏多</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>TrendType : 盤整偏多&lt;br&gt;TrendScore : 40&lt;br&gt;HH : True&lt;br&gt;HL : False&lt;br&gt;MA : False&lt;br&gt;VOL : False</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>141.65</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>148.1152919500972</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>135.1847080499028</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>0.09128544934835393</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>0.002654397451778534</t>
-        </is>
-      </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>-0.0002059336306642345</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>-0.06151019020493131</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>0.05111568461276083</t>
-        </is>
-      </c>
-      <c r="AD4" t="inlineStr">
-        <is>
-          <t>1.49820616914414</t>
-        </is>
-      </c>
-      <c r="AE4" t="inlineStr">
-        <is>
-          <t>2026-09-02 00:00:00</t>
-        </is>
-      </c>
-      <c r="AF4" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="AG4" t="inlineStr">
-        <is>
-          <t>40.0</t>
-        </is>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>2026-09-03 00:00:00</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AL4" t="inlineStr">
-        <is>
-          <t>2026-09-08 00:00:00</t>
-        </is>
-      </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AN4" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
-      </c>
-      <c r="AP4" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
-      </c>
-      <c r="AQ4" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AR4" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AS4" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AT4" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AU4" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="AV4" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AW4" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr">
-        <is>
-          <t>7.0</t>
-        </is>
-      </c>
-      <c r="AZ4" t="inlineStr">
-        <is>
-          <t>14.0</t>
-        </is>
-      </c>
-      <c r="BA4" t="inlineStr">
-        <is>
-          <t>14.0</t>
-        </is>
-      </c>
-      <c r="BB4" t="inlineStr">
-        <is>
-          <t>14.0</t>
-        </is>
-      </c>
-      <c r="BC4" t="inlineStr">
-        <is>
-          <t>盤整</t>
-        </is>
-      </c>
-      <c r="BD4" t="inlineStr">
-        <is>
-          <t>盤整</t>
-        </is>
-      </c>
-      <c r="BE4" t="inlineStr">
-        <is>
-          <t>58.3</t>
-        </is>
-      </c>
-      <c r="BF4" t="inlineStr">
-        <is>
-          <t>13104436.0</t>
-        </is>
-      </c>
-      <c r="BG4" t="inlineStr">
-        <is>
-          <t>1124316.0</t>
-        </is>
-      </c>
-      <c r="BH4" t="inlineStr">
-        <is>
-          <t>2157000.0</t>
-        </is>
-      </c>
-      <c r="BI4" t="inlineStr">
-        <is>
-          <t>-1032684.0</t>
-        </is>
-      </c>
-      <c r="BJ4" t="inlineStr">
-        <is>
-          <t>-452020.0</t>
-        </is>
-      </c>
-      <c r="BK4" t="inlineStr">
-        <is>
-          <t>11619732.0</t>
-        </is>
-      </c>
-      <c r="BL4" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
-      </c>
-      <c r="BM4" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
-      </c>
-      <c r="BN4" t="inlineStr">
-        <is>
-          <t>-1.0</t>
-        </is>
-      </c>
-      <c r="BO4" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="BP4" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="BQ4" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="BR4" t="inlineStr">
-        <is>
-          <t>-0.18</t>
-        </is>
-      </c>
-      <c r="BS4" t="inlineStr">
-        <is>
-          <t>2026/07/20</t>
-        </is>
-      </c>
-      <c r="BT4" t="inlineStr">
-        <is>
-          <t>139.0</t>
-        </is>
-      </c>
-      <c r="BU4" t="inlineStr">
-        <is>
-          <t>2026/04/16</t>
-        </is>
-      </c>
-      <c r="BV4" t="inlineStr">
-        <is>
-          <t>136.5</t>
-        </is>
-      </c>
-      <c r="BW4" t="inlineStr">
-        <is>
-          <t>2026/08/05</t>
-        </is>
-      </c>
-      <c r="BX4" t="inlineStr">
-        <is>
-          <t>137.0</t>
-        </is>
-      </c>
-      <c r="BY4" t="inlineStr">
-        <is>
-          <t>2026/06/24</t>
-        </is>
-      </c>
-      <c r="BZ4" t="inlineStr">
-        <is>
-          <t>143.5</t>
-        </is>
-      </c>
       <c r="CA4" t="inlineStr">
         <is>
           <t>2026-09-18 00:00:00</t>
@@ -3800,17 +3800,17 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="CC4" t="inlineStr">
         <is>
-          <t>17.70</t>
+          <t>14.40</t>
         </is>
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>-0.70</t>
+          <t>1.40</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
@@ -3821,177 +3821,177 @@
       <c r="CF4" t="inlineStr"/>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>86</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
         <is>
-          <t>10010</t>
+          <t>8515</t>
         </is>
       </c>
       <c r="CI4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="CJ4" t="inlineStr">
         <is>
-          <t>36.11</t>
+          <t>41.67</t>
         </is>
       </c>
       <c r="CK4" t="n">
-        <v>-0.76</v>
+        <v>0.55</v>
       </c>
       <c r="CL4" t="n">
-        <v>2.08</v>
+        <v>1.81</v>
       </c>
       <c r="CM4" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>2.09</t>
         </is>
       </c>
       <c r="CN4" t="inlineStr">
         <is>
-          <t>-0.52</t>
+          <t>-0.47</t>
         </is>
       </c>
       <c r="CO4" t="inlineStr">
         <is>
-          <t>144.6</t>
+          <t>144.7</t>
         </is>
       </c>
       <c r="CP4" t="inlineStr">
         <is>
-          <t>144.5</t>
+          <t>144.7</t>
         </is>
       </c>
       <c r="CQ4" t="inlineStr">
         <is>
-          <t>141.65</t>
+          <t>142.12</t>
         </is>
       </c>
       <c r="CR4" t="inlineStr">
         <is>
-          <t>139.08</t>
+          <t>139.21</t>
         </is>
       </c>
       <c r="CS4" t="inlineStr">
         <is>
-          <t>139.81</t>
+          <t>139.87</t>
         </is>
       </c>
       <c r="CT4" t="inlineStr">
         <is>
+          <t>135.9041666666667</t>
+        </is>
+      </c>
+      <c r="CU4" t="inlineStr">
+        <is>
+          <t>0.0006915629322268302</t>
+        </is>
+      </c>
+      <c r="CV4" t="inlineStr">
+        <is>
+          <t>0.00138408304498272</t>
+        </is>
+      </c>
+      <c r="CW4" t="inlineStr">
+        <is>
+          <t>0.003353335686551384</t>
+        </is>
+      </c>
+      <c r="CX4" t="inlineStr">
+        <is>
+          <t>0.0009347138337647554</t>
+        </is>
+      </c>
+      <c r="CY4" t="inlineStr">
+        <is>
+          <t>0.0004023245417970056</t>
+        </is>
+      </c>
+      <c r="CZ4" t="inlineStr">
+        <is>
+          <t>0.0003833826619026315</t>
+        </is>
+      </c>
+      <c r="DA4" t="inlineStr">
+        <is>
+          <t>6.98</t>
+        </is>
+      </c>
+      <c r="DB4" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="DC4" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="DD4" t="inlineStr">
+        <is>
+          <t>1.9</t>
+        </is>
+      </c>
+      <c r="DE4" t="inlineStr">
+        <is>
+          <t>-5.24</t>
+        </is>
+      </c>
+      <c r="DF4" t="inlineStr">
+        <is>
+          <t>2026/08/21</t>
+        </is>
+      </c>
+      <c r="DG4" t="inlineStr">
+        <is>
+          <t>2218439785.568572</t>
+        </is>
+      </c>
+      <c r="DH4" t="inlineStr">
+        <is>
+          <t>1248190797.0</t>
+        </is>
+      </c>
+      <c r="DI4" t="n">
+        <v>1315071112.6</v>
+      </c>
+      <c r="DJ4" t="inlineStr">
+        <is>
+          <t>1706616096.2</t>
+        </is>
+      </c>
+      <c r="DK4" t="inlineStr">
+        <is>
+          <t>1469076947.433333</t>
+        </is>
+      </c>
+      <c r="DL4" t="n">
+        <v>1667394181.32</v>
+      </c>
+      <c r="DM4" t="inlineStr">
+        <is>
+          <t>2016079760.0875</t>
+        </is>
+      </c>
+      <c r="DN4" t="inlineStr">
+        <is>
+          <t>15819888.77302321</t>
+        </is>
+      </c>
+      <c r="DO4" t="inlineStr">
+        <is>
+          <t>-65717912.88730001</t>
+        </is>
+      </c>
+      <c r="DP4" t="inlineStr">
+        <is>
+          <t>1248190797.0</t>
+        </is>
+      </c>
+      <c r="DQ4" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="CU4" t="inlineStr">
-        <is>
-          <t>-0.001381215469613339</t>
-        </is>
-      </c>
-      <c r="CV4" t="inlineStr">
-        <is>
-          <t>0.0006925207756232066</t>
-        </is>
-      </c>
-      <c r="CW4" t="inlineStr">
-        <is>
-          <t>0.002654397451778534</t>
-        </is>
-      </c>
-      <c r="CX4" t="inlineStr">
-        <is>
-          <t>0.0006475285991798252</t>
-        </is>
-      </c>
-      <c r="CY4" t="inlineStr">
-        <is>
-          <t>0.0001788428865241443</t>
-        </is>
-      </c>
-      <c r="CZ4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="DA4" t="inlineStr">
-        <is>
-          <t>7.47</t>
-        </is>
-      </c>
-      <c r="DB4" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="DC4" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="DD4" t="inlineStr">
-        <is>
-          <t>1.9</t>
-        </is>
-      </c>
-      <c r="DE4" t="inlineStr">
-        <is>
-          <t>-6.89</t>
-        </is>
-      </c>
-      <c r="DF4" t="inlineStr">
-        <is>
-          <t>2026/08/21</t>
-        </is>
-      </c>
-      <c r="DG4" t="inlineStr">
-        <is>
-          <t>2525520667.780788</t>
-        </is>
-      </c>
-      <c r="DH4" t="inlineStr">
-        <is>
-          <t>1524028999.0</t>
-        </is>
-      </c>
-      <c r="DI4" t="n">
-        <v>1223386087.6</v>
-      </c>
-      <c r="DJ4" t="inlineStr">
-        <is>
-          <t>1823976219.1</t>
-        </is>
-      </c>
-      <c r="DK4" t="inlineStr">
-        <is>
-          <t>1490856706.633333</t>
-        </is>
-      </c>
-      <c r="DL4" t="n">
-        <v>1693335182.06</v>
-      </c>
-      <c r="DM4" t="inlineStr">
-        <is>
-          <t>2020913533.8875</t>
-        </is>
-      </c>
-      <c r="DN4" t="inlineStr">
-        <is>
-          <t>30644943.61799386</t>
-        </is>
-      </c>
-      <c r="DO4" t="inlineStr">
-        <is>
-          <t>-46102165.86613226</t>
-        </is>
-      </c>
-      <c r="DP4" t="inlineStr">
-        <is>
-          <t>1524028999.0</t>
-        </is>
-      </c>
-      <c r="DQ4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="DR4" t="inlineStr">
         <is>
           <t>143.5</t>
@@ -4004,7 +4004,7 @@
       </c>
       <c r="DT4" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="DU4" t="inlineStr">
@@ -4049,7 +4049,7 @@
       </c>
       <c r="EC4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="ED4" t="inlineStr">
@@ -4059,12 +4059,12 @@
       </c>
       <c r="EE4" t="inlineStr">
         <is>
-          <t>3.04</t>
+          <t>3.08</t>
         </is>
       </c>
       <c r="EF4" t="inlineStr">
         <is>
-          <t>3.56</t>
+          <t>3.57</t>
         </is>
       </c>
       <c r="EG4" t="inlineStr">
@@ -4074,7 +4074,7 @@
       </c>
       <c r="EH4" t="inlineStr">
         <is>
-          <t>28.68</t>
+          <t>28.59</t>
         </is>
       </c>
       <c r="EI4" t="inlineStr">
@@ -4089,12 +4089,12 @@
       </c>
       <c r="EK4" t="inlineStr">
         <is>
-          <t>86.5</t>
+          <t>85.28</t>
         </is>
       </c>
       <c r="EL4" t="inlineStr">
         <is>
-          <t>1132587</t>
+          <t>1128708</t>
         </is>
       </c>
       <c r="EM4" t="inlineStr">
@@ -4114,12 +4114,12 @@
       </c>
       <c r="EP4" t="inlineStr">
         <is>
-          <t>145.0</t>
+          <t>144.0</t>
         </is>
       </c>
       <c r="EQ4" t="inlineStr">
         <is>
-          <t>145.0</t>
+          <t>146.0</t>
         </is>
       </c>
       <c r="ER4" t="inlineStr">
@@ -4129,12 +4129,12 @@
       </c>
       <c r="ES4" t="inlineStr">
         <is>
-          <t>143.5</t>
+          <t>145.5</t>
         </is>
       </c>
       <c r="ET4" t="inlineStr">
         <is>
-          <t>129.5</t>
+          <t>128.0</t>
         </is>
       </c>
       <c r="EU4" t="inlineStr">
@@ -4154,42 +4154,42 @@
       </c>
       <c r="EX4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="EY4" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="EZ4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FA4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FB4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FC4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FD4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="FE4" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="FF4" t="inlineStr">
@@ -4199,22 +4199,22 @@
       </c>
       <c r="FG4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="FH4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="FI4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FJ4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FK4" t="inlineStr">
@@ -4401,12 +4401,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-0.68</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>11652.18</t>
+          <t>10607.859</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -4416,7 +4416,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>144.0</t>
+          <t>143.5</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -4436,7 +4436,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-0.39166013609889294</t>
+          <t>-0.3292751984432931</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -4481,7 +4481,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -4496,47 +4496,47 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>141.275</t>
+          <t>141.65</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>148.1458001525903</t>
+          <t>148.1152919500996</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>134.4041998474098</t>
+          <t>135.1847080499005</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>0.09726845022247742</t>
+          <t>0.09128544934838764</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>0.003017394391196415</t>
+          <t>0.002654397451778534</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>0.0006164580977021661</t>
+          <t>-0.0002059336306624582</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>-0.04919128589699406</t>
+          <t>-0.06151019020487603</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>0.05111568461276083</t>
+          <t>0.04785629426595885</t>
         </is>
       </c>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>1.699323642510904</t>
+          <t>1.498206169143926</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
@@ -4581,159 +4581,159 @@
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
+          <t>3.0</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
           <t>2.0</t>
         </is>
       </c>
-      <c r="AO5" t="inlineStr">
+      <c r="AP5" t="inlineStr">
         <is>
           <t>5.0</t>
         </is>
       </c>
-      <c r="AP5" t="inlineStr">
+      <c r="AQ5" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AR5" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AS5" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AU5" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="AV5" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
         <is>
           <t>7.0</t>
         </is>
       </c>
-      <c r="AQ5" t="inlineStr">
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>14.0</t>
+        </is>
+      </c>
+      <c r="BA5" t="inlineStr">
+        <is>
+          <t>14.0</t>
+        </is>
+      </c>
+      <c r="BB5" t="inlineStr">
+        <is>
+          <t>14.0</t>
+        </is>
+      </c>
+      <c r="BC5" t="inlineStr">
+        <is>
+          <t>盤整</t>
+        </is>
+      </c>
+      <c r="BD5" t="inlineStr">
+        <is>
+          <t>盤整</t>
+        </is>
+      </c>
+      <c r="BE5" t="inlineStr">
+        <is>
+          <t>58.3</t>
+        </is>
+      </c>
+      <c r="BF5" t="inlineStr">
+        <is>
+          <t>15010110.0</t>
+        </is>
+      </c>
+      <c r="BG5" t="inlineStr">
+        <is>
+          <t>1050416.0</t>
+        </is>
+      </c>
+      <c r="BH5" t="inlineStr">
+        <is>
+          <t>4036399.0</t>
+        </is>
+      </c>
+      <c r="BI5" t="inlineStr">
+        <is>
+          <t>-2985983.0</t>
+        </is>
+      </c>
+      <c r="BJ5" t="inlineStr">
+        <is>
+          <t>-213000.0</t>
+        </is>
+      </c>
+      <c r="BK5" t="inlineStr">
+        <is>
+          <t>11811127.0</t>
+        </is>
+      </c>
+      <c r="BL5" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="BM5" t="inlineStr">
+        <is>
+          <t>4.0</t>
+        </is>
+      </c>
+      <c r="BN5" t="inlineStr">
+        <is>
+          <t>-2.0</t>
+        </is>
+      </c>
+      <c r="BO5" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AR5" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AS5" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AT5" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AU5" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="AV5" t="inlineStr">
+      <c r="BP5" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AW5" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr">
-        <is>
-          <t>8.0</t>
-        </is>
-      </c>
-      <c r="AZ5" t="inlineStr">
-        <is>
-          <t>14.0</t>
-        </is>
-      </c>
-      <c r="BA5" t="inlineStr">
-        <is>
-          <t>14.0</t>
-        </is>
-      </c>
-      <c r="BB5" t="inlineStr">
-        <is>
-          <t>14.0</t>
-        </is>
-      </c>
-      <c r="BC5" t="inlineStr">
-        <is>
-          <t>盤整</t>
-        </is>
-      </c>
-      <c r="BD5" t="inlineStr">
-        <is>
-          <t>強勢</t>
-        </is>
-      </c>
-      <c r="BE5" t="inlineStr">
-        <is>
-          <t>58.3</t>
-        </is>
-      </c>
-      <c r="BF5" t="inlineStr">
-        <is>
-          <t>13104436.0</t>
-        </is>
-      </c>
-      <c r="BG5" t="inlineStr">
-        <is>
-          <t>1124316.0</t>
-        </is>
-      </c>
-      <c r="BH5" t="inlineStr">
-        <is>
-          <t>2157000.0</t>
-        </is>
-      </c>
-      <c r="BI5" t="inlineStr">
-        <is>
-          <t>-1032684.0</t>
-        </is>
-      </c>
-      <c r="BJ5" t="inlineStr">
-        <is>
-          <t>-452020.0</t>
-        </is>
-      </c>
-      <c r="BK5" t="inlineStr">
-        <is>
-          <t>11619732.0</t>
-        </is>
-      </c>
-      <c r="BL5" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
-      </c>
-      <c r="BM5" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
-      </c>
-      <c r="BN5" t="inlineStr">
-        <is>
-          <t>-1.0</t>
-        </is>
-      </c>
-      <c r="BO5" t="inlineStr">
+      <c r="BQ5" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="BP5" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="BQ5" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
       <c r="BR5" t="inlineStr">
         <is>
           <t>-0.18</t>
@@ -4786,17 +4786,17 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="CC5" t="inlineStr">
         <is>
-          <t>19.45</t>
+          <t>17.70</t>
         </is>
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>-0.69</t>
+          <t>-0.70</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
@@ -4807,177 +4807,177 @@
       <c r="CF5" t="inlineStr"/>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>86</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
         <is>
-          <t>10010</t>
+          <t>8515</t>
         </is>
       </c>
       <c r="CI5" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="CJ5" t="inlineStr">
         <is>
-          <t>69.44</t>
+          <t>36.11</t>
         </is>
       </c>
       <c r="CK5" t="n">
-        <v>-0.55</v>
+        <v>-0.76</v>
       </c>
       <c r="CL5" t="n">
-        <v>2.5</v>
+        <v>2.08</v>
       </c>
       <c r="CM5" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="CN5" t="inlineStr">
         <is>
-          <t>-0.57</t>
+          <t>-0.52</t>
         </is>
       </c>
       <c r="CO5" t="inlineStr">
         <is>
-          <t>144.8</t>
+          <t>144.6</t>
         </is>
       </c>
       <c r="CP5" t="inlineStr">
         <is>
-          <t>144.4</t>
+          <t>144.5</t>
         </is>
       </c>
       <c r="CQ5" t="inlineStr">
         <is>
-          <t>141.28</t>
+          <t>141.65</t>
         </is>
       </c>
       <c r="CR5" t="inlineStr">
         <is>
-          <t>138.99</t>
+          <t>139.08</t>
         </is>
       </c>
       <c r="CS5" t="inlineStr">
         <is>
-          <t>139.79</t>
+          <t>139.81</t>
         </is>
       </c>
       <c r="CT5" t="inlineStr">
         <is>
+          <t>135.8520833333333</t>
+        </is>
+      </c>
+      <c r="CU5" t="inlineStr">
+        <is>
+          <t>-0.001381215469613339</t>
+        </is>
+      </c>
+      <c r="CV5" t="inlineStr">
+        <is>
+          <t>0.0006925207756232066</t>
+        </is>
+      </c>
+      <c r="CW5" t="inlineStr">
+        <is>
+          <t>0.002654397451778534</t>
+        </is>
+      </c>
+      <c r="CX5" t="inlineStr">
+        <is>
+          <t>0.0006475285991798252</t>
+        </is>
+      </c>
+      <c r="CY5" t="inlineStr">
+        <is>
+          <t>0.0001788428865241443</t>
+        </is>
+      </c>
+      <c r="CZ5" t="inlineStr">
+        <is>
+          <t>0.0002761117332146235</t>
+        </is>
+      </c>
+      <c r="DA5" t="inlineStr">
+        <is>
+          <t>7.47</t>
+        </is>
+      </c>
+      <c r="DB5" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="DC5" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="DD5" t="inlineStr">
+        <is>
+          <t>1.9</t>
+        </is>
+      </c>
+      <c r="DE5" t="inlineStr">
+        <is>
+          <t>-6.89</t>
+        </is>
+      </c>
+      <c r="DF5" t="inlineStr">
+        <is>
+          <t>2026/08/21</t>
+        </is>
+      </c>
+      <c r="DG5" t="inlineStr">
+        <is>
+          <t>2218439785.568572</t>
+        </is>
+      </c>
+      <c r="DH5" t="inlineStr">
+        <is>
+          <t>1524028999.0</t>
+        </is>
+      </c>
+      <c r="DI5" t="n">
+        <v>1223386087.6</v>
+      </c>
+      <c r="DJ5" t="inlineStr">
+        <is>
+          <t>1823976219.1</t>
+        </is>
+      </c>
+      <c r="DK5" t="inlineStr">
+        <is>
+          <t>1490856706.633333</t>
+        </is>
+      </c>
+      <c r="DL5" t="n">
+        <v>1693335182.06</v>
+      </c>
+      <c r="DM5" t="inlineStr">
+        <is>
+          <t>2020913533.8875</t>
+        </is>
+      </c>
+      <c r="DN5" t="inlineStr">
+        <is>
+          <t>30644943.6203547</t>
+        </is>
+      </c>
+      <c r="DO5" t="inlineStr">
+        <is>
+          <t>-46102165.86562538</t>
+        </is>
+      </c>
+      <c r="DP5" t="inlineStr">
+        <is>
+          <t>1524028999.0</t>
+        </is>
+      </c>
+      <c r="DQ5" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="CU5" t="inlineStr">
-        <is>
-          <t>-0.002067539627842785</t>
-        </is>
-      </c>
-      <c r="CV5" t="inlineStr">
-        <is>
-          <t>0.002429711905588272</t>
-        </is>
-      </c>
-      <c r="CW5" t="inlineStr">
-        <is>
-          <t>0.003017394391196415</t>
-        </is>
-      </c>
-      <c r="CX5" t="inlineStr">
-        <is>
-          <t>0.0008641175199828321</t>
-        </is>
-      </c>
-      <c r="CY5" t="inlineStr">
-        <is>
-          <t>0.0002683363148479057</t>
-        </is>
-      </c>
-      <c r="CZ5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="DA5" t="inlineStr">
-        <is>
-          <t>17.86</t>
-        </is>
-      </c>
-      <c r="DB5" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="DC5" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="DD5" t="inlineStr">
-        <is>
-          <t>1.9</t>
-        </is>
-      </c>
-      <c r="DE5" t="inlineStr">
-        <is>
-          <t>-8.63</t>
-        </is>
-      </c>
-      <c r="DF5" t="inlineStr">
-        <is>
-          <t>2026/08/21</t>
-        </is>
-      </c>
-      <c r="DG5" t="inlineStr">
-        <is>
-          <t>2525520667.780788</t>
-        </is>
-      </c>
-      <c r="DH5" t="inlineStr">
-        <is>
-          <t>1676725028.0</t>
-        </is>
-      </c>
-      <c r="DI5" t="n">
-        <v>1178675636.2</v>
-      </c>
-      <c r="DJ5" t="inlineStr">
-        <is>
-          <t>1937528191.3</t>
-        </is>
-      </c>
-      <c r="DK5" t="inlineStr">
-        <is>
-          <t>1486546014.1</t>
-        </is>
-      </c>
-      <c r="DL5" t="n">
-        <v>1735471199.16</v>
-      </c>
-      <c r="DM5" t="inlineStr">
-        <is>
-          <t>2026673727.9875</t>
-        </is>
-      </c>
-      <c r="DN5" t="inlineStr">
-        <is>
-          <t>44598963.52419861</t>
-        </is>
-      </c>
-      <c r="DO5" t="inlineStr">
-        <is>
-          <t>-45987257.26861119</t>
-        </is>
-      </c>
-      <c r="DP5" t="inlineStr">
-        <is>
-          <t>1676725028.0</t>
-        </is>
-      </c>
-      <c r="DQ5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="DR5" t="inlineStr">
         <is>
           <t>143.5</t>
@@ -4990,7 +4990,7 @@
       </c>
       <c r="DT5" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="DU5" t="inlineStr">
@@ -5035,7 +5035,7 @@
       </c>
       <c r="EC5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="ED5" t="inlineStr">
@@ -5045,12 +5045,12 @@
       </c>
       <c r="EE5" t="inlineStr">
         <is>
-          <t>3.05</t>
+          <t>3.04</t>
         </is>
       </c>
       <c r="EF5" t="inlineStr">
         <is>
-          <t>3.56</t>
+          <t>3.57</t>
         </is>
       </c>
       <c r="EG5" t="inlineStr">
@@ -5060,7 +5060,7 @@
       </c>
       <c r="EH5" t="inlineStr">
         <is>
-          <t>28.68</t>
+          <t>28.59</t>
         </is>
       </c>
       <c r="EI5" t="inlineStr">
@@ -5075,12 +5075,12 @@
       </c>
       <c r="EK5" t="inlineStr">
         <is>
-          <t>86.5</t>
+          <t>85.28</t>
         </is>
       </c>
       <c r="EL5" t="inlineStr">
         <is>
-          <t>1132587</t>
+          <t>1128708</t>
         </is>
       </c>
       <c r="EM5" t="inlineStr">
@@ -5100,12 +5100,12 @@
       </c>
       <c r="EP5" t="inlineStr">
         <is>
-          <t>146.0</t>
+          <t>145.0</t>
         </is>
       </c>
       <c r="EQ5" t="inlineStr">
         <is>
-          <t>146.0</t>
+          <t>145.0</t>
         </is>
       </c>
       <c r="ER5" t="inlineStr">
@@ -5115,12 +5115,12 @@
       </c>
       <c r="ES5" t="inlineStr">
         <is>
-          <t>144.0</t>
+          <t>143.5</t>
         </is>
       </c>
       <c r="ET5" t="inlineStr">
         <is>
-          <t>129.5</t>
+          <t>128.0</t>
         </is>
       </c>
       <c r="EU5" t="inlineStr">
@@ -5140,42 +5140,42 @@
       </c>
       <c r="EX5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="EY5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="EZ5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FA5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FB5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FC5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FD5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="FE5" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="FF5" t="inlineStr">
@@ -5185,22 +5185,22 @@
       </c>
       <c r="FG5" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="FH5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="FI5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FJ5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FK5" t="inlineStr">
@@ -5387,12 +5387,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>-0.68</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>6311.915</t>
+          <t>11652.18</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -5402,7 +5402,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>145.0</t>
+          <t>144.0</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -5412,7 +5412,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>0.68</t>
+          <t>1.03</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -5422,7 +5422,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-0.15933593107033336</t>
+          <t>-0.39166013609889294</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -5467,7 +5467,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -5482,47 +5482,47 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>140.85</t>
+          <t>141.275</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>148.0545307382152</t>
+          <t>148.1458001525924</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>133.6454692617848</t>
+          <t>134.4041998474076</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>0.1023007559561973</t>
+          <t>0.0972684502225076</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>0.00338379341050743</t>
+          <t>0.003017394391196415</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>0.002539703250194592</t>
+          <t>0.0006164580977034984</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>-0.01700799986583423</t>
+          <t>-0.0491912858969541</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>0.05111568461276083</t>
+          <t>0.04785629426595885</t>
         </is>
       </c>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>1.907951888344739</t>
+          <t>1.699323642510481</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
@@ -5567,24 +5567,24 @@
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
           <t>5.0</t>
         </is>
       </c>
-      <c r="AO6" t="inlineStr">
+      <c r="AP6" t="inlineStr">
         <is>
           <t>7.0</t>
         </is>
       </c>
-      <c r="AP6" t="inlineStr">
-        <is>
-          <t>7.0</t>
-        </is>
-      </c>
       <c r="AQ6" t="inlineStr">
         <is>
           <t>False</t>
@@ -5617,92 +5617,92 @@
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
+          <t>3.0</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>8.0</t>
+        </is>
+      </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>14.0</t>
+        </is>
+      </c>
+      <c r="BA6" t="inlineStr">
+        <is>
+          <t>14.0</t>
+        </is>
+      </c>
+      <c r="BB6" t="inlineStr">
+        <is>
+          <t>14.0</t>
+        </is>
+      </c>
+      <c r="BC6" t="inlineStr">
+        <is>
+          <t>盤整</t>
+        </is>
+      </c>
+      <c r="BD6" t="inlineStr">
+        <is>
+          <t>強勢</t>
+        </is>
+      </c>
+      <c r="BE6" t="inlineStr">
+        <is>
+          <t>58.3</t>
+        </is>
+      </c>
+      <c r="BF6" t="inlineStr">
+        <is>
+          <t>15010110.0</t>
+        </is>
+      </c>
+      <c r="BG6" t="inlineStr">
+        <is>
+          <t>1050416.0</t>
+        </is>
+      </c>
+      <c r="BH6" t="inlineStr">
+        <is>
+          <t>4036399.0</t>
+        </is>
+      </c>
+      <c r="BI6" t="inlineStr">
+        <is>
+          <t>-2985983.0</t>
+        </is>
+      </c>
+      <c r="BJ6" t="inlineStr">
+        <is>
+          <t>-213000.0</t>
+        </is>
+      </c>
+      <c r="BK6" t="inlineStr">
+        <is>
+          <t>11811127.0</t>
+        </is>
+      </c>
+      <c r="BL6" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="BM6" t="inlineStr">
+        <is>
           <t>4.0</t>
         </is>
       </c>
-      <c r="AY6" t="inlineStr">
-        <is>
-          <t>9.0</t>
-        </is>
-      </c>
-      <c r="AZ6" t="inlineStr">
-        <is>
-          <t>14.0</t>
-        </is>
-      </c>
-      <c r="BA6" t="inlineStr">
-        <is>
-          <t>14.0</t>
-        </is>
-      </c>
-      <c r="BB6" t="inlineStr">
-        <is>
-          <t>14.0</t>
-        </is>
-      </c>
-      <c r="BC6" t="inlineStr">
-        <is>
-          <t>強勢</t>
-        </is>
-      </c>
-      <c r="BD6" t="inlineStr">
-        <is>
-          <t>強勢</t>
-        </is>
-      </c>
-      <c r="BE6" t="inlineStr">
-        <is>
-          <t>58.3</t>
-        </is>
-      </c>
-      <c r="BF6" t="inlineStr">
-        <is>
-          <t>13104436.0</t>
-        </is>
-      </c>
-      <c r="BG6" t="inlineStr">
-        <is>
-          <t>1124316.0</t>
-        </is>
-      </c>
-      <c r="BH6" t="inlineStr">
-        <is>
-          <t>2157000.0</t>
-        </is>
-      </c>
-      <c r="BI6" t="inlineStr">
-        <is>
-          <t>-1032684.0</t>
-        </is>
-      </c>
-      <c r="BJ6" t="inlineStr">
-        <is>
-          <t>-452020.0</t>
-        </is>
-      </c>
-      <c r="BK6" t="inlineStr">
-        <is>
-          <t>11619732.0</t>
-        </is>
-      </c>
-      <c r="BL6" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
-      </c>
-      <c r="BM6" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
-      </c>
       <c r="BN6" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-2.0</t>
         </is>
       </c>
       <c r="BO6" t="inlineStr">
@@ -5722,7 +5722,7 @@
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>-0.18</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
@@ -5772,12 +5772,12 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="CC6" t="inlineStr">
         <is>
-          <t>10.53</t>
+          <t>19.45</t>
         </is>
       </c>
       <c r="CD6" t="inlineStr">
@@ -5793,177 +5793,177 @@
       <c r="CF6" t="inlineStr"/>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>86</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
         <is>
-          <t>10010</t>
+          <t>8515</t>
         </is>
       </c>
       <c r="CI6" t="inlineStr">
         <is>
-          <t>83.33</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="CJ6" t="inlineStr">
         <is>
-          <t>91.67</t>
+          <t>69.44</t>
         </is>
       </c>
       <c r="CK6" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.55</v>
       </c>
       <c r="CL6" t="n">
-        <v>3.02</v>
+        <v>2.5</v>
       </c>
       <c r="CM6" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="CN6" t="inlineStr">
         <is>
-          <t>-0.63</t>
+          <t>-0.57</t>
         </is>
       </c>
       <c r="CO6" t="inlineStr">
         <is>
-          <t>145.1</t>
+          <t>144.8</t>
         </is>
       </c>
       <c r="CP6" t="inlineStr">
         <is>
-          <t>144.05</t>
+          <t>144.4</t>
         </is>
       </c>
       <c r="CQ6" t="inlineStr">
         <is>
-          <t>140.85</t>
+          <t>141.28</t>
         </is>
       </c>
       <c r="CR6" t="inlineStr">
         <is>
-          <t>138.87</t>
+          <t>138.99</t>
         </is>
       </c>
       <c r="CS6" t="inlineStr">
         <is>
-          <t>139.75</t>
+          <t>139.79</t>
         </is>
       </c>
       <c r="CT6" t="inlineStr">
         <is>
+          <t>135.8145833333333</t>
+        </is>
+      </c>
+      <c r="CU6" t="inlineStr">
+        <is>
+          <t>-0.002067539627842785</t>
+        </is>
+      </c>
+      <c r="CV6" t="inlineStr">
+        <is>
+          <t>0.002429711905588272</t>
+        </is>
+      </c>
+      <c r="CW6" t="inlineStr">
+        <is>
+          <t>0.003017394391196415</t>
+        </is>
+      </c>
+      <c r="CX6" t="inlineStr">
+        <is>
+          <t>0.0008641175199828321</t>
+        </is>
+      </c>
+      <c r="CY6" t="inlineStr">
+        <is>
+          <t>0.0002683363148479057</t>
+        </is>
+      </c>
+      <c r="CZ6" t="inlineStr">
+        <is>
+          <t>0.0003222341568205334</t>
+        </is>
+      </c>
+      <c r="DA6" t="inlineStr">
+        <is>
+          <t>17.86</t>
+        </is>
+      </c>
+      <c r="DB6" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="DC6" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="DD6" t="inlineStr">
+        <is>
+          <t>1.9</t>
+        </is>
+      </c>
+      <c r="DE6" t="inlineStr">
+        <is>
+          <t>-8.63</t>
+        </is>
+      </c>
+      <c r="DF6" t="inlineStr">
+        <is>
+          <t>2026/08/21</t>
+        </is>
+      </c>
+      <c r="DG6" t="inlineStr">
+        <is>
+          <t>2218439785.568572</t>
+        </is>
+      </c>
+      <c r="DH6" t="inlineStr">
+        <is>
+          <t>1676725028.0</t>
+        </is>
+      </c>
+      <c r="DI6" t="n">
+        <v>1178675636.2</v>
+      </c>
+      <c r="DJ6" t="inlineStr">
+        <is>
+          <t>1937528191.3</t>
+        </is>
+      </c>
+      <c r="DK6" t="inlineStr">
+        <is>
+          <t>1486546014.1</t>
+        </is>
+      </c>
+      <c r="DL6" t="n">
+        <v>1735471199.16</v>
+      </c>
+      <c r="DM6" t="inlineStr">
+        <is>
+          <t>2026673727.9875</t>
+        </is>
+      </c>
+      <c r="DN6" t="inlineStr">
+        <is>
+          <t>44598963.52689654</t>
+        </is>
+      </c>
+      <c r="DO6" t="inlineStr">
+        <is>
+          <t>-45987257.26803184</t>
+        </is>
+      </c>
+      <c r="DP6" t="inlineStr">
+        <is>
+          <t>1676725028.0</t>
+        </is>
+      </c>
+      <c r="DQ6" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="CU6" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="CV6" t="inlineStr">
-        <is>
-          <t>0.003832752613240453</t>
-        </is>
-      </c>
-      <c r="CW6" t="inlineStr">
-        <is>
-          <t>0.00338379341050743</t>
-        </is>
-      </c>
-      <c r="CX6" t="inlineStr">
-        <is>
-          <t>0.001297858533420015</t>
-        </is>
-      </c>
-      <c r="CY6" t="inlineStr">
-        <is>
-          <t>0.0002684083385522396</t>
-        </is>
-      </c>
-      <c r="CZ6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="DA6" t="inlineStr">
-        <is>
-          <t>29.64</t>
-        </is>
-      </c>
-      <c r="DB6" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="DC6" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="DD6" t="inlineStr">
-        <is>
-          <t>1.9</t>
-        </is>
-      </c>
-      <c r="DE6" t="inlineStr">
-        <is>
-          <t>-12.71</t>
-        </is>
-      </c>
-      <c r="DF6" t="inlineStr">
-        <is>
-          <t>2026/08/21</t>
-        </is>
-      </c>
-      <c r="DG6" t="inlineStr">
-        <is>
-          <t>2525520667.780788</t>
-        </is>
-      </c>
-      <c r="DH6" t="inlineStr">
-        <is>
-          <t>918019598.0</t>
-        </is>
-      </c>
-      <c r="DI6" t="n">
-        <v>1659195852.6</v>
-      </c>
-      <c r="DJ6" t="inlineStr">
-        <is>
-          <t>1973672854.5</t>
-        </is>
-      </c>
-      <c r="DK6" t="inlineStr">
-        <is>
-          <t>1482010386.8</t>
-        </is>
-      </c>
-      <c r="DL6" t="n">
-        <v>1806077677.02</v>
-      </c>
-      <c r="DM6" t="inlineStr">
-        <is>
-          <t>2030537576.35</t>
-        </is>
-      </c>
-      <c r="DN6" t="inlineStr">
-        <is>
-          <t>61069185.48652767</t>
-        </is>
-      </c>
-      <c r="DO6" t="inlineStr">
-        <is>
-          <t>-60540988.90541673</t>
-        </is>
-      </c>
-      <c r="DP6" t="inlineStr">
-        <is>
-          <t>918019598.0</t>
-        </is>
-      </c>
-      <c r="DQ6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="DR6" t="inlineStr">
         <is>
           <t>143.5</t>
@@ -5976,7 +5976,7 @@
       </c>
       <c r="DT6" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>0.35</t>
         </is>
       </c>
       <c r="DU6" t="inlineStr">
@@ -6026,17 +6026,17 @@
       </c>
       <c r="ED6" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="EE6" t="inlineStr">
         <is>
-          <t>3.07</t>
+          <t>3.05</t>
         </is>
       </c>
       <c r="EF6" t="inlineStr">
         <is>
-          <t>3.56</t>
+          <t>3.57</t>
         </is>
       </c>
       <c r="EG6" t="inlineStr">
@@ -6046,7 +6046,7 @@
       </c>
       <c r="EH6" t="inlineStr">
         <is>
-          <t>28.68</t>
+          <t>28.59</t>
         </is>
       </c>
       <c r="EI6" t="inlineStr">
@@ -6061,12 +6061,12 @@
       </c>
       <c r="EK6" t="inlineStr">
         <is>
-          <t>86.5</t>
+          <t>85.28</t>
         </is>
       </c>
       <c r="EL6" t="inlineStr">
         <is>
-          <t>1132587</t>
+          <t>1128708</t>
         </is>
       </c>
       <c r="EM6" t="inlineStr">
@@ -6086,7 +6086,7 @@
       </c>
       <c r="EP6" t="inlineStr">
         <is>
-          <t>145.5</t>
+          <t>146.0</t>
         </is>
       </c>
       <c r="EQ6" t="inlineStr">
@@ -6096,17 +6096,17 @@
       </c>
       <c r="ER6" t="inlineStr">
         <is>
-          <t>145.0</t>
+          <t>143.0</t>
         </is>
       </c>
       <c r="ES6" t="inlineStr">
         <is>
-          <t>145.0</t>
+          <t>144.0</t>
         </is>
       </c>
       <c r="ET6" t="inlineStr">
         <is>
-          <t>129.5</t>
+          <t>128.0</t>
         </is>
       </c>
       <c r="EU6" t="inlineStr">
@@ -6126,67 +6126,67 @@
       </c>
       <c r="EX6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="EY6" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="EZ6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FA6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FB6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FC6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FD6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="FE6" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>13.0</t>
         </is>
       </c>
       <c r="FF6" t="inlineStr">
         <is>
-          <t>1.119557506059444</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FG6" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="FH6" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="FI6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FJ6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FK6" t="inlineStr">
@@ -6373,342 +6373,342 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
+          <t>-0.34</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>6311.915</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>145.0</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
           <t>0.34</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>8326.189</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>-0.15933593107033336</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>145.5</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>99.0</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>0.34</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>-0.03295367443261963</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>99.0</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="O7" t="inlineStr">
         <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
           <t>False</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
+      <c r="Q7" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr">
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>40.0</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>盤整偏多</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>TrendType : 盤整偏多&lt;br&gt;TrendScore : 40&lt;br&gt;HH : True&lt;br&gt;HL : False&lt;br&gt;MA : False&lt;br&gt;VOL : False</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>140.85</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>148.0545307382171</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>133.6454692617829</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>0.1023007559562248</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>0.00338379341050743</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>0.002539703250195702</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>-0.01700799986580759</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>0.04785629426595885</t>
+        </is>
+      </c>
+      <c r="AD7" t="inlineStr">
+        <is>
+          <t>1.907951888344097</t>
+        </is>
+      </c>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t>2026-09-02 00:00:00</t>
+        </is>
+      </c>
+      <c r="AF7" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="R7" t="inlineStr">
+      <c r="AG7" t="inlineStr">
+        <is>
+          <t>40.0</t>
+        </is>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>2026-09-03 00:00:00</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AL7" t="inlineStr">
+        <is>
+          <t>2026-09-08 00:00:00</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="AN7" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>7.0</t>
+        </is>
+      </c>
+      <c r="AP7" t="inlineStr">
+        <is>
+          <t>7.0</t>
+        </is>
+      </c>
+      <c r="AQ7" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AR7" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AS7" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AU7" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>弱勢整理</t>
-        </is>
-      </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>TrendType : 弱勢整理&lt;br&gt;TrendScore : 30&lt;br&gt;HH : False&lt;br&gt;HL : False&lt;br&gt;MA : True&lt;br&gt;VOL : True</t>
-        </is>
-      </c>
-      <c r="V7" t="inlineStr">
-        <is>
-          <t>140.375</t>
-        </is>
-      </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>147.6794687115415</t>
-        </is>
-      </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>133.0705312884585</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>0.104070791972096</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>0.003395282344531791</t>
-        </is>
-      </c>
-      <c r="AA7" t="inlineStr">
-        <is>
-          <t>0.004384515128182942</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>0.02031726359982433</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>0.05111568461276083</t>
-        </is>
-      </c>
-      <c r="AD7" t="inlineStr">
-        <is>
-          <t>2.079004612848601</t>
-        </is>
-      </c>
-      <c r="AE7" t="inlineStr">
-        <is>
-          <t>2026-09-02 00:00:00</t>
-        </is>
-      </c>
-      <c r="AF7" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="AG7" t="inlineStr">
-        <is>
-          <t>40.0</t>
-        </is>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>20.0</t>
-        </is>
-      </c>
-      <c r="AI7" t="inlineStr">
+      <c r="AV7" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>2026-09-03 00:00:00</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>4.0</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>9.0</t>
+        </is>
+      </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>14.0</t>
+        </is>
+      </c>
+      <c r="BA7" t="inlineStr">
+        <is>
+          <t>14.0</t>
+        </is>
+      </c>
+      <c r="BB7" t="inlineStr">
+        <is>
+          <t>14.0</t>
+        </is>
+      </c>
+      <c r="BC7" t="inlineStr">
+        <is>
+          <t>強勢</t>
+        </is>
+      </c>
+      <c r="BD7" t="inlineStr">
+        <is>
+          <t>強勢</t>
+        </is>
+      </c>
+      <c r="BE7" t="inlineStr">
+        <is>
+          <t>58.3</t>
+        </is>
+      </c>
+      <c r="BF7" t="inlineStr">
+        <is>
+          <t>15010110.0</t>
+        </is>
+      </c>
+      <c r="BG7" t="inlineStr">
+        <is>
+          <t>1050416.0</t>
+        </is>
+      </c>
+      <c r="BH7" t="inlineStr">
+        <is>
+          <t>4036399.0</t>
+        </is>
+      </c>
+      <c r="BI7" t="inlineStr">
+        <is>
+          <t>-2985983.0</t>
+        </is>
+      </c>
+      <c r="BJ7" t="inlineStr">
+        <is>
+          <t>-213000.0</t>
+        </is>
+      </c>
+      <c r="BK7" t="inlineStr">
+        <is>
+          <t>11811127.0</t>
+        </is>
+      </c>
+      <c r="BL7" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="BM7" t="inlineStr">
+        <is>
+          <t>4.0</t>
+        </is>
+      </c>
+      <c r="BN7" t="inlineStr">
+        <is>
+          <t>-2.0</t>
+        </is>
+      </c>
+      <c r="BO7" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AL7" t="inlineStr">
-        <is>
-          <t>2026-09-08 00:00:00</t>
-        </is>
-      </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AN7" t="inlineStr">
-        <is>
-          <t>7.0</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>7.0</t>
-        </is>
-      </c>
-      <c r="AP7" t="inlineStr">
-        <is>
-          <t>8.0</t>
-        </is>
-      </c>
-      <c r="AQ7" t="inlineStr">
+      <c r="BP7" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AR7" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AS7" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AT7" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AU7" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="AV7" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="AW7" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
-      </c>
-      <c r="AX7" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr">
-        <is>
-          <t>10.0</t>
-        </is>
-      </c>
-      <c r="AZ7" t="inlineStr">
-        <is>
-          <t>14.0</t>
-        </is>
-      </c>
-      <c r="BA7" t="inlineStr">
-        <is>
-          <t>14.0</t>
-        </is>
-      </c>
-      <c r="BB7" t="inlineStr">
-        <is>
-          <t>14.0</t>
-        </is>
-      </c>
-      <c r="BC7" t="inlineStr">
-        <is>
-          <t>強勢</t>
-        </is>
-      </c>
-      <c r="BD7" t="inlineStr">
-        <is>
-          <t>強勢</t>
-        </is>
-      </c>
-      <c r="BE7" t="inlineStr">
-        <is>
-          <t>58.3</t>
-        </is>
-      </c>
-      <c r="BF7" t="inlineStr">
-        <is>
-          <t>13104436.0</t>
-        </is>
-      </c>
-      <c r="BG7" t="inlineStr">
-        <is>
-          <t>1124316.0</t>
-        </is>
-      </c>
-      <c r="BH7" t="inlineStr">
-        <is>
-          <t>2157000.0</t>
-        </is>
-      </c>
-      <c r="BI7" t="inlineStr">
-        <is>
-          <t>-1032684.0</t>
-        </is>
-      </c>
-      <c r="BJ7" t="inlineStr">
-        <is>
-          <t>-452020.0</t>
-        </is>
-      </c>
-      <c r="BK7" t="inlineStr">
-        <is>
-          <t>11619732.0</t>
-        </is>
-      </c>
-      <c r="BL7" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
-      </c>
-      <c r="BM7" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
-      </c>
-      <c r="BN7" t="inlineStr">
-        <is>
-          <t>-1.0</t>
-        </is>
-      </c>
-      <c r="BO7" t="inlineStr">
+      <c r="BQ7" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="BP7" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="BQ7" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>-0.07</t>
+          <t>-0.12</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
@@ -6758,17 +6758,17 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="CC7" t="inlineStr">
         <is>
-          <t>13.90</t>
+          <t>10.53</t>
         </is>
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>0.69</t>
+          <t>-0.69</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
@@ -6779,17 +6779,17 @@
       <c r="CF7" t="inlineStr"/>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>86</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
         <is>
-          <t>10010</t>
+          <t>8515</t>
         </is>
       </c>
       <c r="CI7" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>83.33</t>
         </is>
       </c>
       <c r="CJ7" t="inlineStr">
@@ -6798,19 +6798,19 @@
         </is>
       </c>
       <c r="CK7" t="n">
-        <v>0.28</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="CL7" t="n">
-        <v>3.37</v>
+        <v>3.02</v>
       </c>
       <c r="CM7" t="inlineStr">
         <is>
-          <t>1.21</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="CN7" t="inlineStr">
         <is>
-          <t>-0.73</t>
+          <t>-0.63</t>
         </is>
       </c>
       <c r="CO7" t="inlineStr">
@@ -6820,69 +6820,69 @@
       </c>
       <c r="CP7" t="inlineStr">
         <is>
-          <t>143.5</t>
+          <t>144.05</t>
         </is>
       </c>
       <c r="CQ7" t="inlineStr">
         <is>
-          <t>140.38</t>
+          <t>140.85</t>
         </is>
       </c>
       <c r="CR7" t="inlineStr">
         <is>
-          <t>138.69</t>
+          <t>138.87</t>
         </is>
       </c>
       <c r="CS7" t="inlineStr">
         <is>
-          <t>139.71</t>
+          <t>139.75</t>
         </is>
       </c>
       <c r="CT7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>135.7708333333333</t>
         </is>
       </c>
       <c r="CU7" t="inlineStr">
         <is>
-          <t>0.002764340013821753</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="CV7" t="inlineStr">
         <is>
-          <t>0.004198740377886701</t>
+          <t>0.003832752613240453</t>
         </is>
       </c>
       <c r="CW7" t="inlineStr">
         <is>
-          <t>0.003395282344531791</t>
+          <t>0.00338379341050743</t>
         </is>
       </c>
       <c r="CX7" t="inlineStr">
         <is>
-          <t>0.001805836463449895</t>
+          <t>0.001297858533420015</t>
         </is>
       </c>
       <c r="CY7" t="inlineStr">
         <is>
-          <t>0.0004475474400287283</t>
+          <t>0.0002684083385522396</t>
         </is>
       </c>
       <c r="CZ7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0003223380251424768</t>
         </is>
       </c>
       <c r="DA7" t="inlineStr">
         <is>
-          <t>39.98</t>
+          <t>29.64</t>
         </is>
       </c>
       <c r="DB7" t="n">
         <v>2.14</v>
       </c>
       <c r="DC7" t="n">
-        <v>1.53</v>
+        <v>1.65</v>
       </c>
       <c r="DD7" t="inlineStr">
         <is>
@@ -6891,7 +6891,7 @@
       </c>
       <c r="DE7" t="inlineStr">
         <is>
-          <t>-19.18</t>
+          <t>-12.71</t>
         </is>
       </c>
       <c r="DF7" t="inlineStr">
@@ -6901,48 +6901,48 @@
       </c>
       <c r="DG7" t="inlineStr">
         <is>
-          <t>2525520667.780788</t>
+          <t>2218439785.568572</t>
         </is>
       </c>
       <c r="DH7" t="inlineStr">
         <is>
-          <t>1208391141.0</t>
+          <t>918019598.0</t>
         </is>
       </c>
       <c r="DI7" t="n">
-        <v>1915789923.8</v>
+        <v>1659195852.6</v>
       </c>
       <c r="DJ7" t="inlineStr">
         <is>
-          <t>1981073577.5</t>
+          <t>1973672854.5</t>
         </is>
       </c>
       <c r="DK7" t="inlineStr">
         <is>
-          <t>1491726965.1</t>
+          <t>1482010386.8</t>
         </is>
       </c>
       <c r="DL7" t="n">
-        <v>1845563731.54</v>
+        <v>1806077677.02</v>
       </c>
       <c r="DM7" t="inlineStr">
         <is>
-          <t>2053704109.375</t>
+          <t>2030537576.35</t>
         </is>
       </c>
       <c r="DN7" t="inlineStr">
         <is>
-          <t>83180126.28506301</t>
+          <t>61069185.48961079</t>
         </is>
       </c>
       <c r="DO7" t="inlineStr">
         <is>
-          <t>2120011.574340582</t>
+          <t>-60540988.90475464</t>
         </is>
       </c>
       <c r="DP7" t="inlineStr">
         <is>
-          <t>1208391141.0</t>
+          <t>918019598.0</t>
         </is>
       </c>
       <c r="DQ7" t="inlineStr">
@@ -6962,7 +6962,7 @@
       </c>
       <c r="DT7" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>1.05</t>
         </is>
       </c>
       <c r="DU7" t="inlineStr">
@@ -7007,22 +7007,22 @@
       </c>
       <c r="EC7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="ED7" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="EE7" t="inlineStr">
         <is>
-          <t>3.08</t>
+          <t>3.07</t>
         </is>
       </c>
       <c r="EF7" t="inlineStr">
         <is>
-          <t>3.56</t>
+          <t>3.57</t>
         </is>
       </c>
       <c r="EG7" t="inlineStr">
@@ -7032,7 +7032,7 @@
       </c>
       <c r="EH7" t="inlineStr">
         <is>
-          <t>28.68</t>
+          <t>28.59</t>
         </is>
       </c>
       <c r="EI7" t="inlineStr">
@@ -7047,12 +7047,12 @@
       </c>
       <c r="EK7" t="inlineStr">
         <is>
-          <t>86.5</t>
+          <t>85.28</t>
         </is>
       </c>
       <c r="EL7" t="inlineStr">
         <is>
-          <t>1132587</t>
+          <t>1128708</t>
         </is>
       </c>
       <c r="EM7" t="inlineStr">
@@ -7072,27 +7072,27 @@
       </c>
       <c r="EP7" t="inlineStr">
         <is>
+          <t>145.5</t>
+        </is>
+      </c>
+      <c r="EQ7" t="inlineStr">
+        <is>
+          <t>146.0</t>
+        </is>
+      </c>
+      <c r="ER7" t="inlineStr">
+        <is>
           <t>145.0</t>
         </is>
       </c>
-      <c r="EQ7" t="inlineStr">
-        <is>
-          <t>145.5</t>
-        </is>
-      </c>
-      <c r="ER7" t="inlineStr">
-        <is>
-          <t>144.5</t>
-        </is>
-      </c>
       <c r="ES7" t="inlineStr">
         <is>
-          <t>145.5</t>
+          <t>145.0</t>
         </is>
       </c>
       <c r="ET7" t="inlineStr">
         <is>
-          <t>129.5</t>
+          <t>128.0</t>
         </is>
       </c>
       <c r="EU7" t="inlineStr">
@@ -7112,67 +7112,67 @@
       </c>
       <c r="EX7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="EY7" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="EZ7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FA7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FB7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FC7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FD7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="FE7" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14.0</t>
         </is>
       </c>
       <c r="FF7" t="inlineStr">
         <is>
-          <t>1.284276525544721</t>
+          <t>1.119557506059444</t>
         </is>
       </c>
       <c r="FG7" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="FH7" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="FI7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="FJ7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FK7" t="inlineStr">
@@ -7364,7 +7364,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>5469.034</t>
+          <t>8326.189</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -7374,7 +7374,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>145.0</t>
+          <t>145.5</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -7384,7 +7384,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>0.68</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -7394,7 +7394,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>0.05100096628122345</t>
+          <t>-0.03295367443261963</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -7404,7 +7404,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>99.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -7439,7 +7439,7 @@
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>30.0</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
@@ -7454,47 +7454,47 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>139.9</t>
+          <t>140.375</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>147.0347924397203</t>
+          <t>147.6794687115433</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>132.7652075602797</t>
+          <t>133.0705312884567</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>0.1019984623262371</t>
+          <t>0.1040707919721211</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>0.003047141064707048</t>
+          <t>0.003395282344531791</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>0.004760596003286599</t>
+          <t>0.004384515128183608</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>0.03642388578015932</t>
+          <t>0.02031726359983477</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>0.05111568461276083</t>
+          <t>0.04785629426595885</t>
         </is>
       </c>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>2.179114382213557</t>
+          <t>2.079004612847744</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
@@ -7514,7 +7514,7 @@
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
@@ -7539,7 +7539,7 @@
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
@@ -7549,14 +7549,14 @@
       </c>
       <c r="AO8" t="inlineStr">
         <is>
+          <t>7.0</t>
+        </is>
+      </c>
+      <c r="AP8" t="inlineStr">
+        <is>
           <t>8.0</t>
         </is>
       </c>
-      <c r="AP8" t="inlineStr">
-        <is>
-          <t>7.0</t>
-        </is>
-      </c>
       <c r="AQ8" t="inlineStr">
         <is>
           <t>False</t>
@@ -7604,17 +7604,17 @@
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>13.0</t>
+          <t>14.0</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>13.0</t>
+          <t>14.0</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>13.0</t>
+          <t>14.0</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
@@ -7634,32 +7634,32 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>13104436.0</t>
+          <t>15010110.0</t>
         </is>
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>1124316.0</t>
+          <t>1050416.0</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2157000.0</t>
+          <t>4036399.0</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
         <is>
-          <t>-1032684.0</t>
+          <t>-2985983.0</t>
         </is>
       </c>
       <c r="BJ8" t="inlineStr">
         <is>
-          <t>-452020.0</t>
+          <t>-213000.0</t>
         </is>
       </c>
       <c r="BK8" t="inlineStr">
         <is>
-          <t>11619732.0</t>
+          <t>11811127.0</t>
         </is>
       </c>
       <c r="BL8" t="inlineStr">
@@ -7669,12 +7669,12 @@
       </c>
       <c r="BM8" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="BN8" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-2.0</t>
         </is>
       </c>
       <c r="BO8" t="inlineStr">
@@ -7694,7 +7694,7 @@
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>-0.09</t>
+          <t>-0.07</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
@@ -7744,17 +7744,17 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="CC8" t="inlineStr">
         <is>
-          <t>9.13</t>
+          <t>13.90</t>
         </is>
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>1.40</t>
+          <t>0.69</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
@@ -7765,177 +7765,177 @@
       <c r="CF8" t="inlineStr"/>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>86</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
         <is>
-          <t>10010</t>
+          <t>8515</t>
         </is>
       </c>
       <c r="CI8" t="inlineStr">
         <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="CJ8" t="inlineStr">
+        <is>
           <t>91.67</t>
         </is>
       </c>
-      <c r="CJ8" t="inlineStr">
-        <is>
-          <t>91.67</t>
-        </is>
-      </c>
       <c r="CK8" t="n">
-        <v>0.21</v>
+        <v>0.28</v>
       </c>
       <c r="CL8" t="n">
-        <v>3.43</v>
+        <v>3.37</v>
       </c>
       <c r="CM8" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>1.21</t>
         </is>
       </c>
       <c r="CN8" t="inlineStr">
         <is>
-          <t>-0.87</t>
+          <t>-0.73</t>
         </is>
       </c>
       <c r="CO8" t="inlineStr">
         <is>
-          <t>144.7</t>
+          <t>145.1</t>
         </is>
       </c>
       <c r="CP8" t="inlineStr">
         <is>
-          <t>142.9</t>
+          <t>143.5</t>
         </is>
       </c>
       <c r="CQ8" t="inlineStr">
         <is>
-          <t>139.9</t>
+          <t>140.38</t>
         </is>
       </c>
       <c r="CR8" t="inlineStr">
         <is>
-          <t>138.44</t>
+          <t>138.69</t>
         </is>
       </c>
       <c r="CS8" t="inlineStr">
         <is>
-          <t>139.65</t>
+          <t>139.71</t>
         </is>
       </c>
       <c r="CT8" t="inlineStr">
         <is>
+          <t>135.7270833333333</t>
+        </is>
+      </c>
+      <c r="CU8" t="inlineStr">
+        <is>
+          <t>0.002764340013821753</t>
+        </is>
+      </c>
+      <c r="CV8" t="inlineStr">
+        <is>
+          <t>0.004198740377886701</t>
+        </is>
+      </c>
+      <c r="CW8" t="inlineStr">
+        <is>
+          <t>0.003395282344531791</t>
+        </is>
+      </c>
+      <c r="CX8" t="inlineStr">
+        <is>
+          <t>0.001805836463449895</t>
+        </is>
+      </c>
+      <c r="CY8" t="inlineStr">
+        <is>
+          <t>0.0004475474400287283</t>
+        </is>
+      </c>
+      <c r="CZ8" t="inlineStr">
+        <is>
+          <t>0.0003685220729365835</t>
+        </is>
+      </c>
+      <c r="DA8" t="inlineStr">
+        <is>
+          <t>39.98</t>
+        </is>
+      </c>
+      <c r="DB8" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="DC8" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="DD8" t="inlineStr">
+        <is>
+          <t>1.9</t>
+        </is>
+      </c>
+      <c r="DE8" t="inlineStr">
+        <is>
+          <t>-19.18</t>
+        </is>
+      </c>
+      <c r="DF8" t="inlineStr">
+        <is>
+          <t>2026/08/21</t>
+        </is>
+      </c>
+      <c r="DG8" t="inlineStr">
+        <is>
+          <t>2218439785.568572</t>
+        </is>
+      </c>
+      <c r="DH8" t="inlineStr">
+        <is>
+          <t>1208391141.0</t>
+        </is>
+      </c>
+      <c r="DI8" t="n">
+        <v>1915789923.8</v>
+      </c>
+      <c r="DJ8" t="inlineStr">
+        <is>
+          <t>1981073577.5</t>
+        </is>
+      </c>
+      <c r="DK8" t="inlineStr">
+        <is>
+          <t>1491726965.1</t>
+        </is>
+      </c>
+      <c r="DL8" t="n">
+        <v>1845563731.54</v>
+      </c>
+      <c r="DM8" t="inlineStr">
+        <is>
+          <t>2053704109.375</t>
+        </is>
+      </c>
+      <c r="DN8" t="inlineStr">
+        <is>
+          <t>83180126.28858632</t>
+        </is>
+      </c>
+      <c r="DO8" t="inlineStr">
+        <is>
+          <t>2120011.575097084</t>
+        </is>
+      </c>
+      <c r="DP8" t="inlineStr">
+        <is>
+          <t>1208391141.0</t>
+        </is>
+      </c>
+      <c r="DQ8" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="CU8" t="inlineStr">
-        <is>
-          <t>0.00207756232686962</t>
-        </is>
-      </c>
-      <c r="CV8" t="inlineStr">
-        <is>
-          <t>0.004216444132115305</t>
-        </is>
-      </c>
-      <c r="CW8" t="inlineStr">
-        <is>
-          <t>0.003047141064707048</t>
-        </is>
-      </c>
-      <c r="CX8" t="inlineStr">
-        <is>
-          <t>0.001736613603473325</t>
-        </is>
-      </c>
-      <c r="CY8" t="inlineStr">
-        <is>
-          <t>0.0007165890361877647</t>
-        </is>
-      </c>
-      <c r="CZ8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="DA8" t="inlineStr">
-        <is>
-          <t>49.52</t>
-        </is>
-      </c>
-      <c r="DB8" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="DC8" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="DD8" t="inlineStr">
-        <is>
-          <t>1.9</t>
-        </is>
-      </c>
-      <c r="DE8" t="inlineStr">
-        <is>
-          <t>-27.26</t>
-        </is>
-      </c>
-      <c r="DF8" t="inlineStr">
-        <is>
-          <t>2026/08/21</t>
-        </is>
-      </c>
-      <c r="DG8" t="inlineStr">
-        <is>
-          <t>2525520667.780788</t>
-        </is>
-      </c>
-      <c r="DH8" t="inlineStr">
-        <is>
-          <t>789765672.0</t>
-        </is>
-      </c>
-      <c r="DI8" t="n">
-        <v>2098161079.8</v>
-      </c>
-      <c r="DJ8" t="inlineStr">
-        <is>
-          <t>1996345528.8</t>
-        </is>
-      </c>
-      <c r="DK8" t="inlineStr">
-        <is>
-          <t>1491758387.733333</t>
-        </is>
-      </c>
-      <c r="DL8" t="n">
-        <v>1849876216.36</v>
-      </c>
-      <c r="DM8" t="inlineStr">
-        <is>
-          <t>2086692476.8625</t>
-        </is>
-      </c>
-      <c r="DN8" t="inlineStr">
-        <is>
-          <t>97918328.95973982</t>
-        </is>
-      </c>
-      <c r="DO8" t="inlineStr">
-        <is>
-          <t>60448775.09633851</t>
-        </is>
-      </c>
-      <c r="DP8" t="inlineStr">
-        <is>
-          <t>789765672.0</t>
-        </is>
-      </c>
-      <c r="DQ8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="DR8" t="inlineStr">
         <is>
           <t>143.5</t>
@@ -7948,7 +7948,7 @@
       </c>
       <c r="DT8" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="DU8" t="inlineStr">
@@ -7993,7 +7993,7 @@
       </c>
       <c r="EC8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
         </is>
       </c>
       <c r="ED8" t="inlineStr">
@@ -8003,12 +8003,12 @@
       </c>
       <c r="EE8" t="inlineStr">
         <is>
-          <t>3.07</t>
+          <t>3.08</t>
         </is>
       </c>
       <c r="EF8" t="inlineStr">
         <is>
-          <t>3.56</t>
+          <t>3.57</t>
         </is>
       </c>
       <c r="EG8" t="inlineStr">
@@ -8018,7 +8018,7 @@
       </c>
       <c r="EH8" t="inlineStr">
         <is>
-          <t>28.68</t>
+          <t>28.59</t>
         </is>
       </c>
       <c r="EI8" t="inlineStr">
@@ -8033,12 +8033,12 @@
       </c>
       <c r="EK8" t="inlineStr">
         <is>
-          <t>86.5</t>
+          <t>85.28</t>
         </is>
       </c>
       <c r="EL8" t="inlineStr">
         <is>
-          <t>1132587</t>
+          <t>1128708</t>
         </is>
       </c>
       <c r="EM8" t="inlineStr">
@@ -8063,22 +8063,22 @@
       </c>
       <c r="EQ8" t="inlineStr">
         <is>
-          <t>145.0</t>
+          <t>145.5</t>
         </is>
       </c>
       <c r="ER8" t="inlineStr">
         <is>
-          <t>143.0</t>
+          <t>144.5</t>
         </is>
       </c>
       <c r="ES8" t="inlineStr">
         <is>
-          <t>145.0</t>
+          <t>145.5</t>
         </is>
       </c>
       <c r="ET8" t="inlineStr">
         <is>
-          <t>129.5</t>
+          <t>128.0</t>
         </is>
       </c>
       <c r="EU8" t="inlineStr">
@@ -8098,67 +8098,67 @@
       </c>
       <c r="EX8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="EY8" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="EZ8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FA8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FB8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FC8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FD8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="FE8" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>15.0</t>
         </is>
       </c>
       <c r="FF8" t="inlineStr">
         <is>
-          <t>1.406501949010705</t>
+          <t>1.284276525544721</t>
         </is>
       </c>
       <c r="FG8" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="FH8" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="FI8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="FJ8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="FK8" t="inlineStr">
@@ -8345,12 +8345,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-0.69</t>
+          <t>0.34</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>9034.372</t>
+          <t>5469.034</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -8360,7 +8360,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>144.5</t>
+          <t>145.0</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -8370,7 +8370,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>1.03</t>
+          <t>0.34</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -8380,7 +8380,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>0.17008176547467793</t>
+          <t>0.05100096628122345</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -8425,7 +8425,7 @@
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>30.0</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
@@ -8440,47 +8440,47 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>139.475</t>
+          <t>139.9</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>146.3381356957985</t>
+          <t>147.0347924397219</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>132.6118643042015</t>
+          <t>132.7652075602781</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>0.09841384758269887</t>
+          <t>0.1019984623262607</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>0.002876145964407772</t>
+          <t>0.003047141064707048</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>0.004858204025057544</t>
+          <t>0.004760596003287043</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>0.04390431594303235</t>
+          <t>0.03642388578015843</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>0.05111568461276083</t>
+          <t>0.04785629426595885</t>
         </is>
       </c>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>2.238719767301117</t>
+          <t>2.179114382212529</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
@@ -8500,7 +8500,7 @@
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>60.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
@@ -8525,24 +8525,24 @@
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
+          <t>7.0</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
           <t>8.0</t>
         </is>
       </c>
-      <c r="AO9" t="inlineStr">
+      <c r="AP9" t="inlineStr">
         <is>
           <t>7.0</t>
         </is>
       </c>
-      <c r="AP9" t="inlineStr">
-        <is>
-          <t>7.0</t>
-        </is>
-      </c>
       <c r="AQ9" t="inlineStr">
         <is>
           <t>False</t>
@@ -8560,7 +8560,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -8590,17 +8590,17 @@
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>12.0</t>
+          <t>13.0</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>12.0</t>
+          <t>13.0</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>12.0</t>
+          <t>13.0</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
@@ -8620,32 +8620,32 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>13104436.0</t>
+          <t>15010110.0</t>
         </is>
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>1124316.0</t>
+          <t>1050416.0</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2157000.0</t>
+          <t>4036399.0</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
         <is>
-          <t>-1032684.0</t>
+          <t>-2985983.0</t>
         </is>
       </c>
       <c r="BJ9" t="inlineStr">
         <is>
-          <t>-452020.0</t>
+          <t>-213000.0</t>
         </is>
       </c>
       <c r="BK9" t="inlineStr">
         <is>
-          <t>11619732.0</t>
+          <t>11811127.0</t>
         </is>
       </c>
       <c r="BL9" t="inlineStr">
@@ -8655,12 +8655,12 @@
       </c>
       <c r="BM9" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="BN9" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-2.0</t>
         </is>
       </c>
       <c r="BO9" t="inlineStr">
@@ -8680,7 +8680,7 @@
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>-0.11</t>
+          <t>-0.09</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
@@ -8730,17 +8730,17 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="CC9" t="inlineStr">
         <is>
-          <t>15.08</t>
+          <t>9.13</t>
         </is>
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>0.70</t>
+          <t>1.40</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
@@ -8751,177 +8751,177 @@
       <c r="CF9" t="inlineStr"/>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>86</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
         <is>
-          <t>10010</t>
+          <t>8515</t>
         </is>
       </c>
       <c r="CI9" t="inlineStr">
         <is>
-          <t>83.33</t>
+          <t>91.67</t>
         </is>
       </c>
       <c r="CJ9" t="inlineStr">
         <is>
-          <t>94.44</t>
+          <t>91.67</t>
         </is>
       </c>
       <c r="CK9" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.21</v>
       </c>
       <c r="CL9" t="n">
-        <v>3.53</v>
+        <v>3.43</v>
       </c>
       <c r="CM9" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>1.05</t>
         </is>
       </c>
       <c r="CN9" t="inlineStr">
         <is>
-          <t>-0.97</t>
+          <t>-0.87</t>
         </is>
       </c>
       <c r="CO9" t="inlineStr">
         <is>
-          <t>144.4</t>
+          <t>144.7</t>
         </is>
       </c>
       <c r="CP9" t="inlineStr">
         <is>
-          <t>142.3</t>
+          <t>142.9</t>
         </is>
       </c>
       <c r="CQ9" t="inlineStr">
         <is>
-          <t>139.48</t>
+          <t>139.9</t>
         </is>
       </c>
       <c r="CR9" t="inlineStr">
         <is>
-          <t>138.2</t>
+          <t>138.44</t>
         </is>
       </c>
       <c r="CS9" t="inlineStr">
         <is>
-          <t>139.55</t>
+          <t>139.65</t>
         </is>
       </c>
       <c r="CT9" t="inlineStr">
         <is>
+          <t>135.6770833333333</t>
+        </is>
+      </c>
+      <c r="CU9" t="inlineStr">
+        <is>
+          <t>0.00207756232686962</t>
+        </is>
+      </c>
+      <c r="CV9" t="inlineStr">
+        <is>
+          <t>0.004216444132115305</t>
+        </is>
+      </c>
+      <c r="CW9" t="inlineStr">
+        <is>
+          <t>0.003047141064707048</t>
+        </is>
+      </c>
+      <c r="CX9" t="inlineStr">
+        <is>
+          <t>0.001736613603473325</t>
+        </is>
+      </c>
+      <c r="CY9" t="inlineStr">
+        <is>
+          <t>0.0007165890361877647</t>
+        </is>
+      </c>
+      <c r="CZ9" t="inlineStr">
+        <is>
+          <t>0.0003225608257557688</t>
+        </is>
+      </c>
+      <c r="DA9" t="inlineStr">
+        <is>
+          <t>49.52</t>
+        </is>
+      </c>
+      <c r="DB9" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="DC9" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="DD9" t="inlineStr">
+        <is>
+          <t>1.9</t>
+        </is>
+      </c>
+      <c r="DE9" t="inlineStr">
+        <is>
+          <t>-27.26</t>
+        </is>
+      </c>
+      <c r="DF9" t="inlineStr">
+        <is>
+          <t>2026/08/21</t>
+        </is>
+      </c>
+      <c r="DG9" t="inlineStr">
+        <is>
+          <t>2218439785.568572</t>
+        </is>
+      </c>
+      <c r="DH9" t="inlineStr">
+        <is>
+          <t>789765672.0</t>
+        </is>
+      </c>
+      <c r="DI9" t="n">
+        <v>2098161079.8</v>
+      </c>
+      <c r="DJ9" t="inlineStr">
+        <is>
+          <t>1996345528.8</t>
+        </is>
+      </c>
+      <c r="DK9" t="inlineStr">
+        <is>
+          <t>1491758387.733333</t>
+        </is>
+      </c>
+      <c r="DL9" t="n">
+        <v>1849876216.36</v>
+      </c>
+      <c r="DM9" t="inlineStr">
+        <is>
+          <t>2086692476.8625</t>
+        </is>
+      </c>
+      <c r="DN9" t="inlineStr">
+        <is>
+          <t>97918328.96376617</t>
+        </is>
+      </c>
+      <c r="DO9" t="inlineStr">
+        <is>
+          <t>60448775.09720325</t>
+        </is>
+      </c>
+      <c r="DP9" t="inlineStr">
+        <is>
+          <t>789765672.0</t>
+        </is>
+      </c>
+      <c r="DQ9" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="CU9" t="inlineStr">
-        <is>
-          <t>0.002777777777777768</t>
-        </is>
-      </c>
-      <c r="CV9" t="inlineStr">
-        <is>
-          <t>0.004588775150017765</t>
-        </is>
-      </c>
-      <c r="CW9" t="inlineStr">
-        <is>
-          <t>0.002876145964407772</t>
-        </is>
-      </c>
-      <c r="CX9" t="inlineStr">
-        <is>
-          <t>0.001594433975938614</t>
-        </is>
-      </c>
-      <c r="CY9" t="inlineStr">
-        <is>
-          <t>0.0007171029042669641</t>
-        </is>
-      </c>
-      <c r="CZ9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="DA9" t="inlineStr">
-        <is>
-          <t>63.63</t>
-        </is>
-      </c>
-      <c r="DB9" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="DC9" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="DD9" t="inlineStr">
-        <is>
-          <t>1.9</t>
-        </is>
-      </c>
-      <c r="DE9" t="inlineStr">
-        <is>
-          <t>-36.27</t>
-        </is>
-      </c>
-      <c r="DF9" t="inlineStr">
-        <is>
-          <t>2026/08/21</t>
-        </is>
-      </c>
-      <c r="DG9" t="inlineStr">
-        <is>
-          <t>2525520667.780788</t>
-        </is>
-      </c>
-      <c r="DH9" t="inlineStr">
-        <is>
-          <t>1300476742.0</t>
-        </is>
-      </c>
-      <c r="DI9" t="n">
-        <v>2424566350.6</v>
-      </c>
-      <c r="DJ9" t="inlineStr">
-        <is>
-          <t>2072134121.0</t>
-        </is>
-      </c>
-      <c r="DK9" t="inlineStr">
-        <is>
-          <t>1501977696.5</t>
-        </is>
-      </c>
-      <c r="DL9" t="n">
-        <v>1909506330.54</v>
-      </c>
-      <c r="DM9" t="inlineStr">
-        <is>
-          <t>2125272163.8375</t>
-        </is>
-      </c>
-      <c r="DN9" t="inlineStr">
-        <is>
-          <t>104730975.1167219</t>
-        </is>
-      </c>
-      <c r="DO9" t="inlineStr">
-        <is>
-          <t>186469424.1243234</t>
-        </is>
-      </c>
-      <c r="DP9" t="inlineStr">
-        <is>
-          <t>1300476742.0</t>
-        </is>
-      </c>
-      <c r="DQ9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="DR9" t="inlineStr">
         <is>
           <t>143.5</t>
@@ -8934,7 +8934,7 @@
       </c>
       <c r="DT9" t="inlineStr">
         <is>
-          <t>0.70</t>
+          <t>1.05</t>
         </is>
       </c>
       <c r="DU9" t="inlineStr">
@@ -8979,7 +8979,7 @@
       </c>
       <c r="EC9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="ED9" t="inlineStr">
@@ -8989,12 +8989,12 @@
       </c>
       <c r="EE9" t="inlineStr">
         <is>
-          <t>3.06</t>
+          <t>3.07</t>
         </is>
       </c>
       <c r="EF9" t="inlineStr">
         <is>
-          <t>3.56</t>
+          <t>3.57</t>
         </is>
       </c>
       <c r="EG9" t="inlineStr">
@@ -9004,7 +9004,7 @@
       </c>
       <c r="EH9" t="inlineStr">
         <is>
-          <t>28.68</t>
+          <t>28.59</t>
         </is>
       </c>
       <c r="EI9" t="inlineStr">
@@ -9019,12 +9019,12 @@
       </c>
       <c r="EK9" t="inlineStr">
         <is>
-          <t>86.5</t>
+          <t>85.28</t>
         </is>
       </c>
       <c r="EL9" t="inlineStr">
         <is>
-          <t>1132587</t>
+          <t>1128708</t>
         </is>
       </c>
       <c r="EM9" t="inlineStr">
@@ -9059,12 +9059,12 @@
       </c>
       <c r="ES9" t="inlineStr">
         <is>
-          <t>144.5</t>
+          <t>145.0</t>
         </is>
       </c>
       <c r="ET9" t="inlineStr">
         <is>
-          <t>129.5</t>
+          <t>128.0</t>
         </is>
       </c>
       <c r="EU9" t="inlineStr">
@@ -9084,67 +9084,67 @@
       </c>
       <c r="EX9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="EY9" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="EZ9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FA9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FB9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FC9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FD9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="FE9" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>15.0</t>
         </is>
       </c>
       <c r="FF9" t="inlineStr">
         <is>
-          <t>1.614249237022542</t>
+          <t>1.406501949010705</t>
         </is>
       </c>
       <c r="FG9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="FH9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="FI9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="FJ9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="FK9" t="inlineStr">
@@ -9321,7 +9321,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>價_量;【b1】</t>
+          <t>【b1】</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -9331,12 +9331,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>0.34</t>
+          <t>-0.69</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>28080.563</t>
+          <t>9034.372</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -9346,7 +9346,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>145.5</t>
+          <t>144.5</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -9356,7 +9356,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>0.34</t>
+          <t>0.69</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -9366,7 +9366,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>0.3056706822272381</t>
+          <t>0.17008176547467793</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -9411,7 +9411,7 @@
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>30.0</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
@@ -9426,47 +9426,47 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>139.075</t>
+          <t>139.475</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>145.6306323714398</t>
+          <t>146.3381356958</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>132.5193676285601</t>
+          <t>132.6118643041999</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>0.09427477794628591</t>
+          <t>0.09841384758272169</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>0.003246167718665482</t>
+          <t>0.002876145964407772</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>0.007638917948316726</t>
+          <t>0.004858204025057988</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>0.1072276106301613</t>
+          <t>0.04390431594303013</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>0.05111568461276083</t>
+          <t>0.04785629426595885</t>
         </is>
       </c>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>2.265751933747335</t>
+          <t>2.238719767299949</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
@@ -9486,7 +9486,7 @@
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>60.0</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
@@ -9511,24 +9511,24 @@
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
+          <t>8.0</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
           <t>7.0</t>
         </is>
       </c>
-      <c r="AO10" t="inlineStr">
+      <c r="AP10" t="inlineStr">
         <is>
           <t>7.0</t>
         </is>
       </c>
-      <c r="AP10" t="inlineStr">
-        <is>
-          <t>7.0</t>
-        </is>
-      </c>
       <c r="AQ10" t="inlineStr">
         <is>
           <t>False</t>
@@ -9576,17 +9576,17 @@
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>11.0</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>11.0</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>11.0</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
@@ -9606,32 +9606,32 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>13104436.0</t>
+          <t>15010110.0</t>
         </is>
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>1124316.0</t>
+          <t>1050416.0</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2157000.0</t>
+          <t>4036399.0</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
         <is>
-          <t>-1032684.0</t>
+          <t>-2985983.0</t>
         </is>
       </c>
       <c r="BJ10" t="inlineStr">
         <is>
-          <t>-452020.0</t>
+          <t>-213000.0</t>
         </is>
       </c>
       <c r="BK10" t="inlineStr">
         <is>
-          <t>11619732.0</t>
+          <t>11811127.0</t>
         </is>
       </c>
       <c r="BL10" t="inlineStr">
@@ -9641,12 +9641,12 @@
       </c>
       <c r="BM10" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="BN10" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-2.0</t>
         </is>
       </c>
       <c r="BO10" t="inlineStr">
@@ -9666,7 +9666,7 @@
       </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>-0.11</t>
         </is>
       </c>
       <c r="BS10" t="inlineStr">
@@ -9716,17 +9716,17 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="CC10" t="inlineStr">
         <is>
-          <t>46.86</t>
+          <t>15.08</t>
         </is>
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>1.04</t>
+          <t>0.70</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
@@ -9737,177 +9737,177 @@
       <c r="CF10" t="inlineStr"/>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>86</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
         <is>
-          <t>10010</t>
+          <t>8515</t>
         </is>
       </c>
       <c r="CI10" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>83.33</t>
         </is>
       </c>
       <c r="CJ10" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>94.44</t>
         </is>
       </c>
       <c r="CK10" t="n">
-        <v>1.04</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="CL10" t="n">
-        <v>3.54</v>
+        <v>3.53</v>
       </c>
       <c r="CM10" t="inlineStr">
         <is>
-          <t>0.79</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="CN10" t="inlineStr">
         <is>
-          <t>-1.05</t>
+          <t>-0.97</t>
         </is>
       </c>
       <c r="CO10" t="inlineStr">
         <is>
-          <t>144.0</t>
+          <t>144.4</t>
         </is>
       </c>
       <c r="CP10" t="inlineStr">
         <is>
-          <t>141.65</t>
+          <t>142.3</t>
         </is>
       </c>
       <c r="CQ10" t="inlineStr">
         <is>
-          <t>139.07</t>
+          <t>139.48</t>
         </is>
       </c>
       <c r="CR10" t="inlineStr">
         <is>
-          <t>137.98</t>
+          <t>138.2</t>
         </is>
       </c>
       <c r="CS10" t="inlineStr">
         <is>
-          <t>139.45</t>
+          <t>139.55</t>
         </is>
       </c>
       <c r="CT10" t="inlineStr">
         <is>
+          <t>135.6333333333333</t>
+        </is>
+      </c>
+      <c r="CU10" t="inlineStr">
+        <is>
+          <t>0.002777777777777768</t>
+        </is>
+      </c>
+      <c r="CV10" t="inlineStr">
+        <is>
+          <t>0.004588775150017765</t>
+        </is>
+      </c>
+      <c r="CW10" t="inlineStr">
+        <is>
+          <t>0.002876145964407772</t>
+        </is>
+      </c>
+      <c r="CX10" t="inlineStr">
+        <is>
+          <t>0.001594433975938614</t>
+        </is>
+      </c>
+      <c r="CY10" t="inlineStr">
+        <is>
+          <t>0.0007171029042669641</t>
+        </is>
+      </c>
+      <c r="CZ10" t="inlineStr">
+        <is>
+          <t>0.0003380350941888377</t>
+        </is>
+      </c>
+      <c r="DA10" t="inlineStr">
+        <is>
+          <t>63.63</t>
+        </is>
+      </c>
+      <c r="DB10" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="DC10" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="DD10" t="inlineStr">
+        <is>
+          <t>1.9</t>
+        </is>
+      </c>
+      <c r="DE10" t="inlineStr">
+        <is>
+          <t>-36.26</t>
+        </is>
+      </c>
+      <c r="DF10" t="inlineStr">
+        <is>
+          <t>2026/08/21</t>
+        </is>
+      </c>
+      <c r="DG10" t="inlineStr">
+        <is>
+          <t>2218439785.568572</t>
+        </is>
+      </c>
+      <c r="DH10" t="inlineStr">
+        <is>
+          <t>1300476742.0</t>
+        </is>
+      </c>
+      <c r="DI10" t="n">
+        <v>2424566350.6</v>
+      </c>
+      <c r="DJ10" t="inlineStr">
+        <is>
+          <t>2072134121.0</t>
+        </is>
+      </c>
+      <c r="DK10" t="inlineStr">
+        <is>
+          <t>1501977696.5</t>
+        </is>
+      </c>
+      <c r="DL10" t="n">
+        <v>1909506330.54</v>
+      </c>
+      <c r="DM10" t="inlineStr">
+        <is>
+          <t>2125272163.8375</t>
+        </is>
+      </c>
+      <c r="DN10" t="inlineStr">
+        <is>
+          <t>104730975.1213231</t>
+        </is>
+      </c>
+      <c r="DO10" t="inlineStr">
+        <is>
+          <t>186469424.1253116</t>
+        </is>
+      </c>
+      <c r="DP10" t="inlineStr">
+        <is>
+          <t>1300476742.0</t>
+        </is>
+      </c>
+      <c r="DQ10" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="CU10" t="inlineStr">
-        <is>
-          <t>0.006993006993007089</t>
-        </is>
-      </c>
-      <c r="CV10" t="inlineStr">
-        <is>
-          <t>0.00567980120695788</t>
-        </is>
-      </c>
-      <c r="CW10" t="inlineStr">
-        <is>
-          <t>0.003246167718665482</t>
-        </is>
-      </c>
-      <c r="CX10" t="inlineStr">
-        <is>
-          <t>0.001742413242340479</t>
-        </is>
-      </c>
-      <c r="CY10" t="inlineStr">
-        <is>
-          <t>0.0007625028033191317</t>
-        </is>
-      </c>
-      <c r="CZ10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="DA10" t="inlineStr">
-        <is>
-          <t>86.11</t>
-        </is>
-      </c>
-      <c r="DB10" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="DC10" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="DD10" t="inlineStr">
-        <is>
-          <t>1.9</t>
-        </is>
-      </c>
-      <c r="DE10" t="inlineStr">
-        <is>
-          <t>-46.40</t>
-        </is>
-      </c>
-      <c r="DF10" t="inlineStr">
-        <is>
-          <t>2026/08/21</t>
-        </is>
-      </c>
-      <c r="DG10" t="inlineStr">
-        <is>
-          <t>2525520667.780788</t>
-        </is>
-      </c>
-      <c r="DH10" t="inlineStr">
-        <is>
-          <t>4079326110.0</t>
-        </is>
-      </c>
-      <c r="DI10" t="n">
-        <v>2696380746.4</v>
-      </c>
-      <c r="DJ10" t="inlineStr">
-        <is>
-          <t>2065130804.5</t>
-        </is>
-      </c>
-      <c r="DK10" t="inlineStr">
-        <is>
-          <t>1502038517.366667</t>
-        </is>
-      </c>
-      <c r="DL10" t="n">
-        <v>1937116325.58</v>
-      </c>
-      <c r="DM10" t="inlineStr">
-        <is>
-          <t>2138184347.15</t>
-        </is>
-      </c>
-      <c r="DN10" t="inlineStr">
-        <is>
-          <t>89869438.93352161</t>
-        </is>
-      </c>
-      <c r="DO10" t="inlineStr">
-        <is>
-          <t>305120257.2312903</t>
-        </is>
-      </c>
-      <c r="DP10" t="inlineStr">
-        <is>
-          <t>4079326110.0</t>
-        </is>
-      </c>
-      <c r="DQ10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="DR10" t="inlineStr">
         <is>
           <t>143.5</t>
@@ -9920,7 +9920,7 @@
       </c>
       <c r="DT10" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>0.70</t>
         </is>
       </c>
       <c r="DU10" t="inlineStr">
@@ -9965,7 +9965,7 @@
       </c>
       <c r="EC10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="ED10" t="inlineStr">
@@ -9975,12 +9975,12 @@
       </c>
       <c r="EE10" t="inlineStr">
         <is>
-          <t>3.08</t>
+          <t>3.06</t>
         </is>
       </c>
       <c r="EF10" t="inlineStr">
         <is>
-          <t>3.56</t>
+          <t>3.57</t>
         </is>
       </c>
       <c r="EG10" t="inlineStr">
@@ -9990,7 +9990,7 @@
       </c>
       <c r="EH10" t="inlineStr">
         <is>
-          <t>28.68</t>
+          <t>28.59</t>
         </is>
       </c>
       <c r="EI10" t="inlineStr">
@@ -10005,12 +10005,12 @@
       </c>
       <c r="EK10" t="inlineStr">
         <is>
-          <t>86.5</t>
+          <t>85.28</t>
         </is>
       </c>
       <c r="EL10" t="inlineStr">
         <is>
-          <t>1132587</t>
+          <t>1128708</t>
         </is>
       </c>
       <c r="EM10" t="inlineStr">
@@ -10035,22 +10035,22 @@
       </c>
       <c r="EQ10" t="inlineStr">
         <is>
-          <t>145.5</t>
+          <t>145.0</t>
         </is>
       </c>
       <c r="ER10" t="inlineStr">
         <is>
-          <t>144.0</t>
+          <t>143.0</t>
         </is>
       </c>
       <c r="ES10" t="inlineStr">
         <is>
-          <t>145.5</t>
+          <t>144.5</t>
         </is>
       </c>
       <c r="ET10" t="inlineStr">
         <is>
-          <t>129.5</t>
+          <t>128.0</t>
         </is>
       </c>
       <c r="EU10" t="inlineStr">
@@ -10070,67 +10070,67 @@
       </c>
       <c r="EX10" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="EY10" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="EZ10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FA10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FB10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FC10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FD10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="FE10" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>15.0</t>
         </is>
       </c>
       <c r="FF10" t="inlineStr">
         <is>
-          <t>1.795147537978734</t>
+          <t>1.614249237022542</t>
         </is>
       </c>
       <c r="FG10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="FH10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="FI10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="FJ10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="FK10" t="inlineStr">

--- a/Result/checksun_type/電信.xlsx
+++ b/Result/checksun_type/電信.xlsx
@@ -1443,12 +1443,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>8515.486</t>
+          <t>7052.714</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -1478,7 +1478,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-0.07440392378152937</t>
+          <t>0.04819550174243172</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -1488,7 +1488,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>99.0</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -1523,7 +1523,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>60.0</t>
+          <t>60</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -1538,47 +1538,47 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>142.925</t>
+          <t>143.325</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>148.5844122811866</t>
+          <t>148.4781799073856</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>137.2655877188134</t>
+          <t>138.1718200926144</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>0.07919415471312412</t>
+          <t>0.07190901667379143</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>0.002630655910206947</t>
+          <t>0.002798670631450006</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>0.000713171676491875</t>
+          <t>-0.0007149631119904853</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>-0.0478969710749888</t>
+          <t>-0.09199085545746999</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>0.04785629426595885</t>
+          <t>0.05137843623728422</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>1.123964812126325</t>
+          <t>0.9852782093293254</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
@@ -1588,7 +1588,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
@@ -1623,24 +1623,24 @@
       </c>
       <c r="AM2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AN2" t="inlineStr">
+        <is>
           <t>2.0</t>
         </is>
       </c>
-      <c r="AN2" t="inlineStr">
+      <c r="AO2" t="inlineStr">
         <is>
           <t>3.0</t>
         </is>
       </c>
-      <c r="AO2" t="inlineStr">
+      <c r="AP2" t="inlineStr">
         <is>
           <t>2.0</t>
         </is>
       </c>
-      <c r="AP2" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
-      </c>
       <c r="AQ2" t="inlineStr">
         <is>
           <t>False</t>
@@ -1663,7 +1663,7 @@
       </c>
       <c r="AU2" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AV2" t="inlineStr">
@@ -1678,7 +1678,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -1688,17 +1688,17 @@
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>16.0</t>
+          <t>17.0</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>17.0</t>
+          <t>18.0</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>17.0</t>
+          <t>18.0</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
@@ -1718,32 +1718,32 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>15010110.0</t>
+          <t>18108850.0</t>
         </is>
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>1050416.0</t>
+          <t>1199596.0</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>4036399.0</t>
+          <t>4011399.0</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
         <is>
-          <t>-2985983.0</t>
+          <t>-2811803.0</t>
         </is>
       </c>
       <c r="BJ2" t="inlineStr">
         <is>
-          <t>-213000.0</t>
+          <t>-248002.0</t>
         </is>
       </c>
       <c r="BK2" t="inlineStr">
         <is>
-          <t>11811127.0</t>
+          <t>15049045.0</t>
         </is>
       </c>
       <c r="BL2" t="inlineStr">
@@ -1753,12 +1753,12 @@
       </c>
       <c r="BM2" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="BN2" t="inlineStr">
         <is>
-          <t>-2.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="BO2" t="inlineStr">
@@ -1828,17 +1828,17 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="CC2" t="inlineStr">
         <is>
-          <t>14.21</t>
+          <t>11.77</t>
         </is>
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>1.04</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
@@ -1849,12 +1849,12 @@
       <c r="CF2" t="inlineStr"/>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>86</t>
+          <t>54</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
         <is>
-          <t>8515</t>
+          <t>7053</t>
         </is>
       </c>
       <c r="CI2" t="inlineStr">
@@ -1864,28 +1864,28 @@
       </c>
       <c r="CJ2" t="inlineStr">
         <is>
-          <t>93.33</t>
+          <t>86.67</t>
         </is>
       </c>
       <c r="CK2" t="n">
-        <v>0.41</v>
+        <v>0.21</v>
       </c>
       <c r="CL2" t="n">
-        <v>1.38</v>
+        <v>1.31</v>
       </c>
       <c r="CM2" t="inlineStr">
         <is>
-          <t>2.45</t>
+          <t>2.64</t>
         </is>
       </c>
       <c r="CN2" t="inlineStr">
         <is>
-          <t>-0.35</t>
+          <t>-0.27</t>
         </is>
       </c>
       <c r="CO2" t="inlineStr">
         <is>
-          <t>144.9</t>
+          <t>145.2</t>
         </is>
       </c>
       <c r="CP2" t="inlineStr">
@@ -1895,61 +1895,61 @@
       </c>
       <c r="CQ2" t="inlineStr">
         <is>
-          <t>142.93</t>
+          <t>143.32</t>
         </is>
       </c>
       <c r="CR2" t="inlineStr">
         <is>
-          <t>139.51</t>
+          <t>139.64</t>
         </is>
       </c>
       <c r="CS2" t="inlineStr">
         <is>
-          <t>140.01</t>
+          <t>140.02</t>
         </is>
       </c>
       <c r="CT2" t="inlineStr">
         <is>
-          <t>136.0104166666667</t>
+          <t>0</t>
         </is>
       </c>
       <c r="CU2" t="inlineStr">
         <is>
-          <t>0.0006906077348065587</t>
+          <t>0.00207039337474102</t>
         </is>
       </c>
       <c r="CV2" t="inlineStr">
         <is>
-          <t>0.0003449465332874269</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="CW2" t="inlineStr">
         <is>
-          <t>0.002630655910206947</t>
+          <t>0.002798670631450006</t>
         </is>
       </c>
       <c r="CX2" t="inlineStr">
         <is>
-          <t>0.001076349024110135</t>
+          <t>0.0009318328435237166</t>
         </is>
       </c>
       <c r="CY2" t="inlineStr">
         <is>
-          <t>0.0003125837277841992</t>
+          <t>0.0001339225927414756</t>
         </is>
       </c>
       <c r="CZ2" t="inlineStr">
         <is>
-          <t>0.0003830830524056417</t>
+          <t>0</t>
         </is>
       </c>
       <c r="DA2" t="inlineStr">
         <is>
-          <t>4.21</t>
+          <t>1.30</t>
         </is>
       </c>
       <c r="DB2" t="n">
-        <v>1.93</v>
+        <v>1.88</v>
       </c>
       <c r="DC2" t="n">
         <v>1.85</v>
@@ -1961,7 +1961,7 @@
       </c>
       <c r="DE2" t="inlineStr">
         <is>
-          <t>-2.49</t>
+          <t>-2.18</t>
         </is>
       </c>
       <c r="DF2" t="inlineStr">
@@ -1971,48 +1971,48 @@
       </c>
       <c r="DG2" t="inlineStr">
         <is>
-          <t>2218439785.568572</t>
+          <t>2517415638.848781</t>
         </is>
       </c>
       <c r="DH2" t="inlineStr">
         <is>
-          <t>1239700787.0</t>
+          <t>1019972816.0</t>
         </is>
       </c>
       <c r="DI2" t="n">
-        <v>1429392742.2</v>
+        <v>1298042299.8</v>
       </c>
       <c r="DJ2" t="inlineStr">
         <is>
-          <t>1544294297.4</t>
+          <t>1238358968.0</t>
         </is>
       </c>
       <c r="DK2" t="inlineStr">
         <is>
-          <t>1502594940.533333</t>
+          <t>1512402699.433333</t>
         </is>
       </c>
       <c r="DL2" t="n">
-        <v>1654145469.66</v>
+        <v>1630284122.58</v>
       </c>
       <c r="DM2" t="inlineStr">
         <is>
-          <t>1987286590.375</t>
+          <t>1973713221.6375</t>
         </is>
       </c>
       <c r="DN2" t="inlineStr">
         <is>
-          <t>-8184469.60354781</t>
+          <t>-21930809.76943394</t>
         </is>
       </c>
       <c r="DO2" t="inlineStr">
         <is>
-          <t>-74321546.88150048</t>
+          <t>-97535680.67310739</t>
         </is>
       </c>
       <c r="DP2" t="inlineStr">
         <is>
-          <t>1239700787.0</t>
+          <t>1019972816.0</t>
         </is>
       </c>
       <c r="DQ2" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="EC2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="ED2" t="inlineStr">
@@ -2117,7 +2117,7 @@
       </c>
       <c r="EK2" t="inlineStr">
         <is>
-          <t>85.28</t>
+          <t>84.97</t>
         </is>
       </c>
       <c r="EL2" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="EP2" t="inlineStr">
         <is>
-          <t>147.0</t>
+          <t>145.5</t>
         </is>
       </c>
       <c r="EQ2" t="inlineStr">
         <is>
-          <t>147.0</t>
+          <t>145.5</t>
         </is>
       </c>
       <c r="ER2" t="inlineStr">
@@ -2162,7 +2162,7 @@
       </c>
       <c r="ET2" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>129.5</t>
         </is>
       </c>
       <c r="EU2" t="inlineStr">
@@ -2182,67 +2182,67 @@
       </c>
       <c r="EX2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="EY2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="EZ2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="FA2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="FB2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="FC2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="FD2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="FE2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="FF2" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="EY2" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
-      </c>
-      <c r="EZ2" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="FA2" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="FB2" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="FC2" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="FD2" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="FE2" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="FF2" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="FG2" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="FH2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FI2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FJ2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FK2" t="inlineStr">
@@ -2429,12 +2429,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.34</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>10009.961</t>
+          <t>8515.486</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -2444,7 +2444,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>146.0</t>
+          <t>145.5</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -2454,7 +2454,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-0.16786321196452753</t>
+          <t>-0.07440392378152937</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -2474,7 +2474,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>99.0</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -2509,7 +2509,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>60.0</t>
+          <t>60</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -2524,47 +2524,47 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>142.55</t>
+          <t>142.925</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>148.4785216050106</t>
+          <t>148.5844122811834</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>136.6214783949895</t>
+          <t>137.2655877188166</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>0.0831781354613898</t>
+          <t>0.07919415471307878</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>0.002990325417766115</t>
+          <t>0.002630655910206947</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>0.001688232507606857</t>
+          <t>0.0007131716764898766</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>-0.03152921474353376</t>
+          <t>-0.04789697107505919</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>0.04785629426595885</t>
+          <t>0.05137843623728422</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>1.230963728066852</t>
+          <t>1.123964812126167</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
@@ -2579,7 +2579,7 @@
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>35.0</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
@@ -2609,162 +2609,162 @@
       </c>
       <c r="AM3" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AN3" t="inlineStr">
+        <is>
           <t>3.0</t>
         </is>
       </c>
-      <c r="AN3" t="inlineStr">
+      <c r="AO3" t="inlineStr">
         <is>
           <t>2.0</t>
         </is>
       </c>
-      <c r="AO3" t="inlineStr">
+      <c r="AP3" t="inlineStr">
         <is>
           <t>2.0</t>
         </is>
       </c>
-      <c r="AP3" t="inlineStr">
+      <c r="AQ3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AR3" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AS3" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AU3" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="AV3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
         <is>
           <t>3.0</t>
         </is>
       </c>
-      <c r="AQ3" t="inlineStr">
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>7.0</t>
+        </is>
+      </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>16.0</t>
+        </is>
+      </c>
+      <c r="BA3" t="inlineStr">
+        <is>
+          <t>17.0</t>
+        </is>
+      </c>
+      <c r="BB3" t="inlineStr">
+        <is>
+          <t>17.0</t>
+        </is>
+      </c>
+      <c r="BC3" t="inlineStr">
+        <is>
+          <t>盤整</t>
+        </is>
+      </c>
+      <c r="BD3" t="inlineStr">
+        <is>
+          <t>盤整</t>
+        </is>
+      </c>
+      <c r="BE3" t="inlineStr">
+        <is>
+          <t>58.3</t>
+        </is>
+      </c>
+      <c r="BF3" t="inlineStr">
+        <is>
+          <t>18108850.0</t>
+        </is>
+      </c>
+      <c r="BG3" t="inlineStr">
+        <is>
+          <t>1199596.0</t>
+        </is>
+      </c>
+      <c r="BH3" t="inlineStr">
+        <is>
+          <t>4011399.0</t>
+        </is>
+      </c>
+      <c r="BI3" t="inlineStr">
+        <is>
+          <t>-2811803.0</t>
+        </is>
+      </c>
+      <c r="BJ3" t="inlineStr">
+        <is>
+          <t>-248002.0</t>
+        </is>
+      </c>
+      <c r="BK3" t="inlineStr">
+        <is>
+          <t>15049045.0</t>
+        </is>
+      </c>
+      <c r="BL3" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="BM3" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="BN3" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="BO3" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AR3" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AS3" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AT3" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AU3" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="AV3" t="inlineStr">
+      <c r="BP3" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AW3" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
-      </c>
-      <c r="AX3" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr">
-        <is>
-          <t>7.0</t>
-        </is>
-      </c>
-      <c r="AZ3" t="inlineStr">
-        <is>
-          <t>16.0</t>
-        </is>
-      </c>
-      <c r="BA3" t="inlineStr">
-        <is>
-          <t>16.0</t>
-        </is>
-      </c>
-      <c r="BB3" t="inlineStr">
-        <is>
-          <t>16.0</t>
-        </is>
-      </c>
-      <c r="BC3" t="inlineStr">
-        <is>
-          <t>盤整</t>
-        </is>
-      </c>
-      <c r="BD3" t="inlineStr">
-        <is>
-          <t>盤整</t>
-        </is>
-      </c>
-      <c r="BE3" t="inlineStr">
-        <is>
-          <t>58.3</t>
-        </is>
-      </c>
-      <c r="BF3" t="inlineStr">
-        <is>
-          <t>15010110.0</t>
-        </is>
-      </c>
-      <c r="BG3" t="inlineStr">
-        <is>
-          <t>1050416.0</t>
-        </is>
-      </c>
-      <c r="BH3" t="inlineStr">
-        <is>
-          <t>4036399.0</t>
-        </is>
-      </c>
-      <c r="BI3" t="inlineStr">
-        <is>
-          <t>-2985983.0</t>
-        </is>
-      </c>
-      <c r="BJ3" t="inlineStr">
-        <is>
-          <t>-213000.0</t>
-        </is>
-      </c>
-      <c r="BK3" t="inlineStr">
-        <is>
-          <t>11811127.0</t>
-        </is>
-      </c>
-      <c r="BL3" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
-      </c>
-      <c r="BM3" t="inlineStr">
-        <is>
-          <t>4.0</t>
-        </is>
-      </c>
-      <c r="BN3" t="inlineStr">
-        <is>
-          <t>-2.0</t>
-        </is>
-      </c>
-      <c r="BO3" t="inlineStr">
+      <c r="BQ3" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="BP3" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="BQ3" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-0.05</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
@@ -2814,17 +2814,17 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="CC3" t="inlineStr">
         <is>
-          <t>16.71</t>
+          <t>14.21</t>
         </is>
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
@@ -2835,110 +2835,110 @@
       <c r="CF3" t="inlineStr"/>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>86</t>
+          <t>54</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
         <is>
-          <t>8515</t>
+          <t>7053</t>
         </is>
       </c>
       <c r="CI3" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="CJ3" t="inlineStr">
         <is>
-          <t>66.67</t>
+          <t>93.33</t>
         </is>
       </c>
       <c r="CK3" t="n">
-        <v>0.83</v>
+        <v>0.41</v>
       </c>
       <c r="CL3" t="n">
-        <v>1.58</v>
+        <v>1.38</v>
       </c>
       <c r="CM3" t="inlineStr">
         <is>
-          <t>2.29</t>
+          <t>2.45</t>
         </is>
       </c>
       <c r="CN3" t="inlineStr">
         <is>
-          <t>-0.43</t>
+          <t>-0.35</t>
         </is>
       </c>
       <c r="CO3" t="inlineStr">
         <is>
-          <t>144.8</t>
+          <t>144.9</t>
         </is>
       </c>
       <c r="CP3" t="inlineStr">
         <is>
-          <t>144.95</t>
+          <t>145.0</t>
         </is>
       </c>
       <c r="CQ3" t="inlineStr">
         <is>
-          <t>142.55</t>
+          <t>142.93</t>
         </is>
       </c>
       <c r="CR3" t="inlineStr">
         <is>
-          <t>139.36</t>
+          <t>139.51</t>
         </is>
       </c>
       <c r="CS3" t="inlineStr">
         <is>
-          <t>139.96</t>
+          <t>140.01</t>
         </is>
       </c>
       <c r="CT3" t="inlineStr">
         <is>
-          <t>135.9583333333333</t>
+          <t>0</t>
         </is>
       </c>
       <c r="CU3" t="inlineStr">
         <is>
-          <t>0.0006910850034556049</t>
+          <t>0.0006906077348065587</t>
         </is>
       </c>
       <c r="CV3" t="inlineStr">
         <is>
-          <t>0.001727712508638568</t>
+          <t>0.0003449465332874269</t>
         </is>
       </c>
       <c r="CW3" t="inlineStr">
         <is>
-          <t>0.002990325417766115</t>
+          <t>0.002630655910206947</t>
         </is>
       </c>
       <c r="CX3" t="inlineStr">
         <is>
-          <t>0.001077508799655291</t>
+          <t>0.001076349024110135</t>
         </is>
       </c>
       <c r="CY3" t="inlineStr">
         <is>
-          <t>0.0006702712364270447</t>
+          <t>0.0003125837277841992</t>
         </is>
       </c>
       <c r="CZ3" t="inlineStr">
         <is>
-          <t>0.0003985651654045963</t>
+          <t>0</t>
         </is>
       </c>
       <c r="DA3" t="inlineStr">
         <is>
-          <t>7.12</t>
+          <t>4.21</t>
         </is>
       </c>
       <c r="DB3" t="n">
-        <v>1.96</v>
+        <v>1.93</v>
       </c>
       <c r="DC3" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="DD3" t="inlineStr">
         <is>
@@ -2947,7 +2947,7 @@
       </c>
       <c r="DE3" t="inlineStr">
         <is>
-          <t>-3.52</t>
+          <t>-2.50</t>
         </is>
       </c>
       <c r="DF3" t="inlineStr">
@@ -2957,48 +2957,48 @@
       </c>
       <c r="DG3" t="inlineStr">
         <is>
-          <t>2218439785.568572</t>
+          <t>2517415638.848781</t>
         </is>
       </c>
       <c r="DH3" t="inlineStr">
         <is>
-          <t>1458318100.0</t>
+          <t>1239700787.0</t>
         </is>
       </c>
       <c r="DI3" t="n">
-        <v>1365056504.4</v>
+        <v>1429392742.2</v>
       </c>
       <c r="DJ3" t="inlineStr">
         <is>
-          <t>1640423214.1</t>
+          <t>1544294297.4</t>
         </is>
       </c>
       <c r="DK3" t="inlineStr">
         <is>
-          <t>1485353753.433333</t>
+          <t>1502594940.533333</t>
         </is>
       </c>
       <c r="DL3" t="n">
-        <v>1659414895.68</v>
+        <v>1654145469.66</v>
       </c>
       <c r="DM3" t="inlineStr">
         <is>
-          <t>2004348026.1375</t>
+          <t>1987286590.375</t>
         </is>
       </c>
       <c r="DN3" t="inlineStr">
         <is>
-          <t>3840453.537898131</t>
+          <t>-8184469.605129678</t>
         </is>
       </c>
       <c r="DO3" t="inlineStr">
         <is>
-          <t>-62046440.25528979</t>
+          <t>-74321546.88183999</t>
         </is>
       </c>
       <c r="DP3" t="inlineStr">
         <is>
-          <t>1458318100.0</t>
+          <t>1239700787.0</t>
         </is>
       </c>
       <c r="DQ3" t="inlineStr">
@@ -3018,7 +3018,7 @@
       </c>
       <c r="DT3" t="inlineStr">
         <is>
-          <t>1.74</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="DU3" t="inlineStr">
@@ -3073,7 +3073,7 @@
       </c>
       <c r="EE3" t="inlineStr">
         <is>
-          <t>3.09</t>
+          <t>3.08</t>
         </is>
       </c>
       <c r="EF3" t="inlineStr">
@@ -3103,7 +3103,7 @@
       </c>
       <c r="EK3" t="inlineStr">
         <is>
-          <t>85.28</t>
+          <t>84.97</t>
         </is>
       </c>
       <c r="EL3" t="inlineStr">
@@ -3128,12 +3128,12 @@
       </c>
       <c r="EP3" t="inlineStr">
         <is>
-          <t>145.0</t>
+          <t>147.0</t>
         </is>
       </c>
       <c r="EQ3" t="inlineStr">
         <is>
-          <t>146.5</t>
+          <t>147.0</t>
         </is>
       </c>
       <c r="ER3" t="inlineStr">
@@ -3143,12 +3143,12 @@
       </c>
       <c r="ES3" t="inlineStr">
         <is>
-          <t>146.0</t>
+          <t>145.5</t>
         </is>
       </c>
       <c r="ET3" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>129.5</t>
         </is>
       </c>
       <c r="EU3" t="inlineStr">
@@ -3168,67 +3168,67 @@
       </c>
       <c r="EX3" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="EY3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="EZ3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="FA3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="FB3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="FC3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="FD3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="FE3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="FF3" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="EY3" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
-      </c>
-      <c r="EZ3" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="FA3" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="FB3" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="FC3" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="FD3" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="FE3" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="FF3" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="FG3" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>4</t>
         </is>
       </c>
       <c r="FH3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FI3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FJ3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FK3" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>0.34</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>8628.434</t>
+          <t>10009.961</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -3430,7 +3430,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>145.5</t>
+          <t>146.0</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -3440,319 +3440,319 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
+          <t>-0.34</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>-0.16786321196452753</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>99.0</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>轉強</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>TrendType : 轉強&lt;br&gt;TrendScore : 60&lt;br&gt;HH : True&lt;br&gt;HL : False&lt;br&gt;MA : True&lt;br&gt;VOL : False</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>142.55</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>148.4785216050076</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>136.6214783949924</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>0.08317813546134833</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>0.002990325417766115</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>0.001688232507605081</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>-0.03152921474358805</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>0.05137843623728422</t>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t>1.23096372806679</t>
+        </is>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>2026-09-02 00:00:00</t>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="AG4" t="inlineStr">
+        <is>
+          <t>40.0</t>
+        </is>
+      </c>
+      <c r="AH4" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>-0.22942768703039035</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>100.0</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>2026-09-03 00:00:00</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AL4" t="inlineStr">
+        <is>
+          <t>2026-09-08 00:00:00</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AN4" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="AP4" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
+      </c>
+      <c r="AQ4" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AR4" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AS4" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AU4" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="AV4" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="R4" t="inlineStr">
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>7.0</t>
+        </is>
+      </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>16.0</t>
+        </is>
+      </c>
+      <c r="BA4" t="inlineStr">
+        <is>
+          <t>16.0</t>
+        </is>
+      </c>
+      <c r="BB4" t="inlineStr">
+        <is>
+          <t>16.0</t>
+        </is>
+      </c>
+      <c r="BC4" t="inlineStr">
+        <is>
+          <t>盤整</t>
+        </is>
+      </c>
+      <c r="BD4" t="inlineStr">
+        <is>
+          <t>盤整</t>
+        </is>
+      </c>
+      <c r="BE4" t="inlineStr">
+        <is>
+          <t>58.3</t>
+        </is>
+      </c>
+      <c r="BF4" t="inlineStr">
+        <is>
+          <t>18108850.0</t>
+        </is>
+      </c>
+      <c r="BG4" t="inlineStr">
+        <is>
+          <t>1199596.0</t>
+        </is>
+      </c>
+      <c r="BH4" t="inlineStr">
+        <is>
+          <t>4011399.0</t>
+        </is>
+      </c>
+      <c r="BI4" t="inlineStr">
+        <is>
+          <t>-2811803.0</t>
+        </is>
+      </c>
+      <c r="BJ4" t="inlineStr">
+        <is>
+          <t>-248002.0</t>
+        </is>
+      </c>
+      <c r="BK4" t="inlineStr">
+        <is>
+          <t>15049045.0</t>
+        </is>
+      </c>
+      <c r="BL4" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="BM4" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="BN4" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="BO4" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>60.0</t>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>轉強</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>TrendType : 轉強&lt;br&gt;TrendScore : 60&lt;br&gt;HH : True&lt;br&gt;HL : False&lt;br&gt;MA : True&lt;br&gt;VOL : False</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>142.125</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>148.2282778078687</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>136.0217221921313</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>0.08588605534379948</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>0.003353335686551384</t>
-        </is>
-      </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>0.0007628237184804654</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>-0.0591484627958786</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>0.04785629426595885</t>
-        </is>
-      </c>
-      <c r="AD4" t="inlineStr">
-        <is>
-          <t>1.334686942343584</t>
-        </is>
-      </c>
-      <c r="AE4" t="inlineStr">
-        <is>
-          <t>2026-09-02 00:00:00</t>
-        </is>
-      </c>
-      <c r="AF4" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="AG4" t="inlineStr">
-        <is>
-          <t>40.0</t>
-        </is>
-      </c>
-      <c r="AH4" t="inlineStr">
+      <c r="BP4" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="BQ4" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="BR4" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>2026-09-03 00:00:00</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AL4" t="inlineStr">
-        <is>
-          <t>2026-09-08 00:00:00</t>
-        </is>
-      </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
-      </c>
-      <c r="AN4" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
-      </c>
-      <c r="AP4" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
-      </c>
-      <c r="AQ4" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AR4" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AS4" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AT4" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AU4" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="AV4" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AW4" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr">
-        <is>
-          <t>7.0</t>
-        </is>
-      </c>
-      <c r="AZ4" t="inlineStr">
-        <is>
-          <t>15.0</t>
-        </is>
-      </c>
-      <c r="BA4" t="inlineStr">
-        <is>
-          <t>15.0</t>
-        </is>
-      </c>
-      <c r="BB4" t="inlineStr">
-        <is>
-          <t>15.0</t>
-        </is>
-      </c>
-      <c r="BC4" t="inlineStr">
-        <is>
-          <t>盤整</t>
-        </is>
-      </c>
-      <c r="BD4" t="inlineStr">
-        <is>
-          <t>盤整</t>
-        </is>
-      </c>
-      <c r="BE4" t="inlineStr">
-        <is>
-          <t>58.3</t>
-        </is>
-      </c>
-      <c r="BF4" t="inlineStr">
-        <is>
-          <t>15010110.0</t>
-        </is>
-      </c>
-      <c r="BG4" t="inlineStr">
-        <is>
-          <t>1050416.0</t>
-        </is>
-      </c>
-      <c r="BH4" t="inlineStr">
-        <is>
-          <t>4036399.0</t>
-        </is>
-      </c>
-      <c r="BI4" t="inlineStr">
-        <is>
-          <t>-2985983.0</t>
-        </is>
-      </c>
-      <c r="BJ4" t="inlineStr">
-        <is>
-          <t>-213000.0</t>
-        </is>
-      </c>
-      <c r="BK4" t="inlineStr">
-        <is>
-          <t>11811127.0</t>
-        </is>
-      </c>
-      <c r="BL4" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
-      </c>
-      <c r="BM4" t="inlineStr">
-        <is>
-          <t>4.0</t>
-        </is>
-      </c>
-      <c r="BN4" t="inlineStr">
-        <is>
-          <t>-2.0</t>
-        </is>
-      </c>
-      <c r="BO4" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="BP4" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="BQ4" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="BR4" t="inlineStr">
-        <is>
-          <t>-0.01</t>
-        </is>
-      </c>
       <c r="BS4" t="inlineStr">
         <is>
           <t>2026/07/20</t>
@@ -3800,17 +3800,17 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="CC4" t="inlineStr">
         <is>
-          <t>14.40</t>
+          <t>16.71</t>
         </is>
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>1.40</t>
+          <t>1.05</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
@@ -3821,12 +3821,12 @@
       <c r="CF4" t="inlineStr"/>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>86</t>
+          <t>54</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
         <is>
-          <t>8515</t>
+          <t>7053</t>
         </is>
       </c>
       <c r="CI4" t="inlineStr">
@@ -3836,95 +3836,95 @@
       </c>
       <c r="CJ4" t="inlineStr">
         <is>
-          <t>41.67</t>
+          <t>66.67</t>
         </is>
       </c>
       <c r="CK4" t="n">
-        <v>0.55</v>
+        <v>0.83</v>
       </c>
       <c r="CL4" t="n">
-        <v>1.81</v>
+        <v>1.58</v>
       </c>
       <c r="CM4" t="inlineStr">
         <is>
-          <t>2.09</t>
+          <t>2.29</t>
         </is>
       </c>
       <c r="CN4" t="inlineStr">
         <is>
-          <t>-0.47</t>
+          <t>-0.43</t>
         </is>
       </c>
       <c r="CO4" t="inlineStr">
         <is>
-          <t>144.7</t>
+          <t>144.8</t>
         </is>
       </c>
       <c r="CP4" t="inlineStr">
         <is>
-          <t>144.7</t>
+          <t>144.95</t>
         </is>
       </c>
       <c r="CQ4" t="inlineStr">
         <is>
-          <t>142.12</t>
+          <t>142.55</t>
         </is>
       </c>
       <c r="CR4" t="inlineStr">
         <is>
-          <t>139.21</t>
+          <t>139.36</t>
         </is>
       </c>
       <c r="CS4" t="inlineStr">
         <is>
-          <t>139.87</t>
+          <t>139.96</t>
         </is>
       </c>
       <c r="CT4" t="inlineStr">
         <is>
-          <t>135.9041666666667</t>
+          <t>0</t>
         </is>
       </c>
       <c r="CU4" t="inlineStr">
         <is>
-          <t>0.0006915629322268302</t>
+          <t>0.0006910850034556049</t>
         </is>
       </c>
       <c r="CV4" t="inlineStr">
         <is>
-          <t>0.00138408304498272</t>
+          <t>0.001727712508638568</t>
         </is>
       </c>
       <c r="CW4" t="inlineStr">
         <is>
-          <t>0.003353335686551384</t>
+          <t>0.002990325417766115</t>
         </is>
       </c>
       <c r="CX4" t="inlineStr">
         <is>
-          <t>0.0009347138337647554</t>
+          <t>0.001077508799655291</t>
         </is>
       </c>
       <c r="CY4" t="inlineStr">
         <is>
-          <t>0.0004023245417970056</t>
+          <t>0.0006702712364270447</t>
         </is>
       </c>
       <c r="CZ4" t="inlineStr">
         <is>
-          <t>0.0003833826619026315</t>
+          <t>0</t>
         </is>
       </c>
       <c r="DA4" t="inlineStr">
         <is>
-          <t>6.98</t>
+          <t>7.12</t>
         </is>
       </c>
       <c r="DB4" t="n">
-        <v>1.92</v>
+        <v>1.96</v>
       </c>
       <c r="DC4" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="DD4" t="inlineStr">
         <is>
@@ -3933,7 +3933,7 @@
       </c>
       <c r="DE4" t="inlineStr">
         <is>
-          <t>-5.24</t>
+          <t>-3.52</t>
         </is>
       </c>
       <c r="DF4" t="inlineStr">
@@ -3943,48 +3943,48 @@
       </c>
       <c r="DG4" t="inlineStr">
         <is>
-          <t>2218439785.568572</t>
+          <t>2517415638.848781</t>
         </is>
       </c>
       <c r="DH4" t="inlineStr">
         <is>
-          <t>1248190797.0</t>
+          <t>1458318100.0</t>
         </is>
       </c>
       <c r="DI4" t="n">
-        <v>1315071112.6</v>
+        <v>1365056504.4</v>
       </c>
       <c r="DJ4" t="inlineStr">
         <is>
-          <t>1706616096.2</t>
+          <t>1640423214.1</t>
         </is>
       </c>
       <c r="DK4" t="inlineStr">
         <is>
-          <t>1469076947.433333</t>
+          <t>1485353753.433333</t>
         </is>
       </c>
       <c r="DL4" t="n">
-        <v>1667394181.32</v>
+        <v>1659414895.68</v>
       </c>
       <c r="DM4" t="inlineStr">
         <is>
-          <t>2016079760.0875</t>
+          <t>2004348026.1375</t>
         </is>
       </c>
       <c r="DN4" t="inlineStr">
         <is>
-          <t>15819888.77302321</t>
+          <t>3840453.53609038</t>
         </is>
       </c>
       <c r="DO4" t="inlineStr">
         <is>
-          <t>-65717912.88730001</t>
+          <t>-62046440.25567794</t>
         </is>
       </c>
       <c r="DP4" t="inlineStr">
         <is>
-          <t>1248190797.0</t>
+          <t>1458318100.0</t>
         </is>
       </c>
       <c r="DQ4" t="inlineStr">
@@ -4004,7 +4004,7 @@
       </c>
       <c r="DT4" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>1.74</t>
         </is>
       </c>
       <c r="DU4" t="inlineStr">
@@ -4054,12 +4054,12 @@
       </c>
       <c r="ED4" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="EE4" t="inlineStr">
         <is>
-          <t>3.08</t>
+          <t>3.09</t>
         </is>
       </c>
       <c r="EF4" t="inlineStr">
@@ -4089,7 +4089,7 @@
       </c>
       <c r="EK4" t="inlineStr">
         <is>
-          <t>85.28</t>
+          <t>84.97</t>
         </is>
       </c>
       <c r="EL4" t="inlineStr">
@@ -4114,27 +4114,27 @@
       </c>
       <c r="EP4" t="inlineStr">
         <is>
+          <t>145.0</t>
+        </is>
+      </c>
+      <c r="EQ4" t="inlineStr">
+        <is>
+          <t>146.5</t>
+        </is>
+      </c>
+      <c r="ER4" t="inlineStr">
+        <is>
           <t>144.0</t>
         </is>
       </c>
-      <c r="EQ4" t="inlineStr">
+      <c r="ES4" t="inlineStr">
         <is>
           <t>146.0</t>
         </is>
       </c>
-      <c r="ER4" t="inlineStr">
-        <is>
-          <t>143.0</t>
-        </is>
-      </c>
-      <c r="ES4" t="inlineStr">
-        <is>
-          <t>145.5</t>
-        </is>
-      </c>
       <c r="ET4" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>129.5</t>
         </is>
       </c>
       <c r="EU4" t="inlineStr">
@@ -4154,67 +4154,67 @@
       </c>
       <c r="EX4" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="EY4" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="EZ4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="FA4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="FB4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="FC4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="FD4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="FE4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="FF4" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="EY4" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
-      </c>
-      <c r="EZ4" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="FA4" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="FB4" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="FC4" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="FD4" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="FE4" t="inlineStr">
-        <is>
-          <t>12.0</t>
-        </is>
-      </c>
-      <c r="FF4" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="FG4" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>4</t>
         </is>
       </c>
       <c r="FH4" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FI4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FJ4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FK4" t="inlineStr">
@@ -4401,12 +4401,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>10607.859</t>
+          <t>8628.434</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -4416,369 +4416,369 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
+          <t>145.5</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>-0.22942768703039035</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>99.0</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>轉強</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>TrendType : 轉強&lt;br&gt;TrendScore : 60&lt;br&gt;HH : True&lt;br&gt;HL : False&lt;br&gt;MA : True&lt;br&gt;VOL : False</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>142.125</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>148.228277807866</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>136.021722192134</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>0.08588605534376148</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>0.003353335686551384</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>0.0007628237184782449</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>-0.05914846279594743</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>0.05137843623728422</t>
+        </is>
+      </c>
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t>1.334686942343627</t>
+        </is>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>2026-09-02 00:00:00</t>
+        </is>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="AG5" t="inlineStr">
+        <is>
+          <t>40.0</t>
+        </is>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>2026-09-03 00:00:00</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AL5" t="inlineStr">
+        <is>
+          <t>2026-09-08 00:00:00</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AN5" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
+      </c>
+      <c r="AP5" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="AQ5" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AR5" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AS5" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AU5" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="AV5" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>7.0</t>
+        </is>
+      </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>15.0</t>
+        </is>
+      </c>
+      <c r="BA5" t="inlineStr">
+        <is>
+          <t>15.0</t>
+        </is>
+      </c>
+      <c r="BB5" t="inlineStr">
+        <is>
+          <t>15.0</t>
+        </is>
+      </c>
+      <c r="BC5" t="inlineStr">
+        <is>
+          <t>盤整</t>
+        </is>
+      </c>
+      <c r="BD5" t="inlineStr">
+        <is>
+          <t>盤整</t>
+        </is>
+      </c>
+      <c r="BE5" t="inlineStr">
+        <is>
+          <t>58.3</t>
+        </is>
+      </c>
+      <c r="BF5" t="inlineStr">
+        <is>
+          <t>18108850.0</t>
+        </is>
+      </c>
+      <c r="BG5" t="inlineStr">
+        <is>
+          <t>1199596.0</t>
+        </is>
+      </c>
+      <c r="BH5" t="inlineStr">
+        <is>
+          <t>4011399.0</t>
+        </is>
+      </c>
+      <c r="BI5" t="inlineStr">
+        <is>
+          <t>-2811803.0</t>
+        </is>
+      </c>
+      <c r="BJ5" t="inlineStr">
+        <is>
+          <t>-248002.0</t>
+        </is>
+      </c>
+      <c r="BK5" t="inlineStr">
+        <is>
+          <t>15049045.0</t>
+        </is>
+      </c>
+      <c r="BL5" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="BM5" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="BN5" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="BO5" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="BP5" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="BQ5" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="BR5" t="inlineStr">
+        <is>
+          <t>-0.01</t>
+        </is>
+      </c>
+      <c r="BS5" t="inlineStr">
+        <is>
+          <t>2026/07/20</t>
+        </is>
+      </c>
+      <c r="BT5" t="inlineStr">
+        <is>
+          <t>139.0</t>
+        </is>
+      </c>
+      <c r="BU5" t="inlineStr">
+        <is>
+          <t>2026/04/16</t>
+        </is>
+      </c>
+      <c r="BV5" t="inlineStr">
+        <is>
+          <t>136.5</t>
+        </is>
+      </c>
+      <c r="BW5" t="inlineStr">
+        <is>
+          <t>2026/08/05</t>
+        </is>
+      </c>
+      <c r="BX5" t="inlineStr">
+        <is>
+          <t>137.0</t>
+        </is>
+      </c>
+      <c r="BY5" t="inlineStr">
+        <is>
+          <t>2026/06/24</t>
+        </is>
+      </c>
+      <c r="BZ5" t="inlineStr">
+        <is>
           <t>143.5</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>1.37</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>-0.3292751984432931</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>99.0</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="R5" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>40.0</t>
-        </is>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>盤整偏多</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>TrendType : 盤整偏多&lt;br&gt;TrendScore : 40&lt;br&gt;HH : True&lt;br&gt;HL : False&lt;br&gt;MA : False&lt;br&gt;VOL : False</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>141.65</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>148.1152919500996</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>135.1847080499005</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>0.09128544934838764</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>0.002654397451778534</t>
-        </is>
-      </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>-0.0002059336306624582</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>-0.06151019020487603</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>0.04785629426595885</t>
-        </is>
-      </c>
-      <c r="AD5" t="inlineStr">
-        <is>
-          <t>1.498206169143926</t>
-        </is>
-      </c>
-      <c r="AE5" t="inlineStr">
-        <is>
-          <t>2026-09-02 00:00:00</t>
-        </is>
-      </c>
-      <c r="AF5" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="AG5" t="inlineStr">
-        <is>
-          <t>40.0</t>
-        </is>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>2026-09-03 00:00:00</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AL5" t="inlineStr">
-        <is>
-          <t>2026-09-08 00:00:00</t>
-        </is>
-      </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
-      </c>
-      <c r="AN5" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
-      </c>
-      <c r="AP5" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
-      </c>
-      <c r="AQ5" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AR5" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AS5" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AT5" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AU5" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="AV5" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AW5" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr">
-        <is>
-          <t>7.0</t>
-        </is>
-      </c>
-      <c r="AZ5" t="inlineStr">
-        <is>
-          <t>14.0</t>
-        </is>
-      </c>
-      <c r="BA5" t="inlineStr">
-        <is>
-          <t>14.0</t>
-        </is>
-      </c>
-      <c r="BB5" t="inlineStr">
-        <is>
-          <t>14.0</t>
-        </is>
-      </c>
-      <c r="BC5" t="inlineStr">
-        <is>
-          <t>盤整</t>
-        </is>
-      </c>
-      <c r="BD5" t="inlineStr">
-        <is>
-          <t>盤整</t>
-        </is>
-      </c>
-      <c r="BE5" t="inlineStr">
-        <is>
-          <t>58.3</t>
-        </is>
-      </c>
-      <c r="BF5" t="inlineStr">
-        <is>
-          <t>15010110.0</t>
-        </is>
-      </c>
-      <c r="BG5" t="inlineStr">
-        <is>
-          <t>1050416.0</t>
-        </is>
-      </c>
-      <c r="BH5" t="inlineStr">
-        <is>
-          <t>4036399.0</t>
-        </is>
-      </c>
-      <c r="BI5" t="inlineStr">
-        <is>
-          <t>-2985983.0</t>
-        </is>
-      </c>
-      <c r="BJ5" t="inlineStr">
-        <is>
-          <t>-213000.0</t>
-        </is>
-      </c>
-      <c r="BK5" t="inlineStr">
-        <is>
-          <t>11811127.0</t>
-        </is>
-      </c>
-      <c r="BL5" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
-      </c>
-      <c r="BM5" t="inlineStr">
-        <is>
-          <t>4.0</t>
-        </is>
-      </c>
-      <c r="BN5" t="inlineStr">
-        <is>
-          <t>-2.0</t>
-        </is>
-      </c>
-      <c r="BO5" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="BP5" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="BQ5" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="BR5" t="inlineStr">
-        <is>
-          <t>-0.18</t>
-        </is>
-      </c>
-      <c r="BS5" t="inlineStr">
-        <is>
-          <t>2026/07/20</t>
-        </is>
-      </c>
-      <c r="BT5" t="inlineStr">
-        <is>
-          <t>139.0</t>
-        </is>
-      </c>
-      <c r="BU5" t="inlineStr">
-        <is>
-          <t>2026/04/16</t>
-        </is>
-      </c>
-      <c r="BV5" t="inlineStr">
-        <is>
-          <t>136.5</t>
-        </is>
-      </c>
-      <c r="BW5" t="inlineStr">
-        <is>
-          <t>2026/08/05</t>
-        </is>
-      </c>
-      <c r="BX5" t="inlineStr">
-        <is>
-          <t>137.0</t>
-        </is>
-      </c>
-      <c r="BY5" t="inlineStr">
-        <is>
-          <t>2026/06/24</t>
-        </is>
-      </c>
-      <c r="BZ5" t="inlineStr">
-        <is>
-          <t>143.5</t>
-        </is>
-      </c>
       <c r="CA5" t="inlineStr">
         <is>
           <t>2026-09-18 00:00:00</t>
@@ -4786,17 +4786,17 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="CC5" t="inlineStr">
         <is>
-          <t>17.70</t>
+          <t>14.40</t>
         </is>
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>-0.70</t>
+          <t>1.40</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
@@ -4807,400 +4807,400 @@
       <c r="CF5" t="inlineStr"/>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>86</t>
+          <t>54</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
         <is>
-          <t>8515</t>
+          <t>7053</t>
         </is>
       </c>
       <c r="CI5" t="inlineStr">
         <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="CJ5" t="inlineStr">
+        <is>
+          <t>41.67</t>
+        </is>
+      </c>
+      <c r="CK5" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="CL5" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="CM5" t="inlineStr">
+        <is>
+          <t>2.09</t>
+        </is>
+      </c>
+      <c r="CN5" t="inlineStr">
+        <is>
+          <t>-0.47</t>
+        </is>
+      </c>
+      <c r="CO5" t="inlineStr">
+        <is>
+          <t>144.7</t>
+        </is>
+      </c>
+      <c r="CP5" t="inlineStr">
+        <is>
+          <t>144.7</t>
+        </is>
+      </c>
+      <c r="CQ5" t="inlineStr">
+        <is>
+          <t>142.12</t>
+        </is>
+      </c>
+      <c r="CR5" t="inlineStr">
+        <is>
+          <t>139.21</t>
+        </is>
+      </c>
+      <c r="CS5" t="inlineStr">
+        <is>
+          <t>139.87</t>
+        </is>
+      </c>
+      <c r="CT5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CU5" t="inlineStr">
+        <is>
+          <t>0.0006915629322268302</t>
+        </is>
+      </c>
+      <c r="CV5" t="inlineStr">
+        <is>
+          <t>0.00138408304498272</t>
+        </is>
+      </c>
+      <c r="CW5" t="inlineStr">
+        <is>
+          <t>0.003353335686551384</t>
+        </is>
+      </c>
+      <c r="CX5" t="inlineStr">
+        <is>
+          <t>0.0009347138337647554</t>
+        </is>
+      </c>
+      <c r="CY5" t="inlineStr">
+        <is>
+          <t>0.0004023245417970056</t>
+        </is>
+      </c>
+      <c r="CZ5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="DA5" t="inlineStr">
+        <is>
+          <t>6.98</t>
+        </is>
+      </c>
+      <c r="DB5" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="DC5" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="DD5" t="inlineStr">
+        <is>
+          <t>1.9</t>
+        </is>
+      </c>
+      <c r="DE5" t="inlineStr">
+        <is>
+          <t>-5.24</t>
+        </is>
+      </c>
+      <c r="DF5" t="inlineStr">
+        <is>
+          <t>2026/08/21</t>
+        </is>
+      </c>
+      <c r="DG5" t="inlineStr">
+        <is>
+          <t>2517415638.848781</t>
+        </is>
+      </c>
+      <c r="DH5" t="inlineStr">
+        <is>
+          <t>1248190797.0</t>
+        </is>
+      </c>
+      <c r="DI5" t="n">
+        <v>1315071112.6</v>
+      </c>
+      <c r="DJ5" t="inlineStr">
+        <is>
+          <t>1706616096.2</t>
+        </is>
+      </c>
+      <c r="DK5" t="inlineStr">
+        <is>
+          <t>1469076947.433333</t>
+        </is>
+      </c>
+      <c r="DL5" t="n">
+        <v>1667394181.32</v>
+      </c>
+      <c r="DM5" t="inlineStr">
+        <is>
+          <t>2016079760.0875</t>
+        </is>
+      </c>
+      <c r="DN5" t="inlineStr">
+        <is>
+          <t>15819888.77095735</t>
+        </is>
+      </c>
+      <c r="DO5" t="inlineStr">
+        <is>
+          <t>-65717912.88774347</t>
+        </is>
+      </c>
+      <c r="DP5" t="inlineStr">
+        <is>
+          <t>1248190797.0</t>
+        </is>
+      </c>
+      <c r="DQ5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="DR5" t="inlineStr">
+        <is>
+          <t>143.5</t>
+        </is>
+      </c>
+      <c r="DS5" t="inlineStr">
+        <is>
+          <t>2026/09/15</t>
+        </is>
+      </c>
+      <c r="DT5" t="inlineStr">
+        <is>
+          <t>1.39</t>
+        </is>
+      </c>
+      <c r="DU5" t="inlineStr">
+        <is>
+          <t>中華電</t>
+        </is>
+      </c>
+      <c r="DV5" t="inlineStr">
+        <is>
+          <t>中華電</t>
+        </is>
+      </c>
+      <c r="DW5" t="inlineStr">
+        <is>
+          <t>通信網路業</t>
+        </is>
+      </c>
+      <c r="DX5" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="DY5" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="DZ5" t="inlineStr">
+        <is>
+          <t>-1.398042523039787</t>
+        </is>
+      </c>
+      <c r="EA5" t="inlineStr">
+        <is>
+          <t>7.608984617555596</t>
+        </is>
+      </c>
+      <c r="EB5" t="inlineStr">
+        <is>
+          <t>7.52024426560034</t>
+        </is>
+      </c>
+      <c r="EC5" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="ED5" t="inlineStr">
+        <is>
+          <t>價-量增</t>
+        </is>
+      </c>
+      <c r="EE5" t="inlineStr">
+        <is>
+          <t>3.08</t>
+        </is>
+      </c>
+      <c r="EF5" t="inlineStr">
+        <is>
+          <t>3.57</t>
+        </is>
+      </c>
+      <c r="EG5" t="inlineStr">
+        <is>
+          <t>7.91</t>
+        </is>
+      </c>
+      <c r="EH5" t="inlineStr">
+        <is>
+          <t>28.59</t>
+        </is>
+      </c>
+      <c r="EI5" t="inlineStr">
+        <is>
+          <t>37.54%</t>
+        </is>
+      </c>
+      <c r="EJ5" t="inlineStr">
+        <is>
+          <t>21.61%</t>
+        </is>
+      </c>
+      <c r="EK5" t="inlineStr">
+        <is>
+          <t>84.97</t>
+        </is>
+      </c>
+      <c r="EL5" t="inlineStr">
+        <is>
+          <t>1128708</t>
+        </is>
+      </c>
+      <c r="EM5" t="inlineStr">
+        <is>
+          <t>個人家庭60.70%、企業客戶32.70%、國際客戶4.00%、其他2.60% (2025年)</t>
+        </is>
+      </c>
+      <c r="EN5" t="inlineStr">
+        <is>
+          <t>中華電-通信網路業-上市</t>
+        </is>
+      </c>
+      <c r="EO5" t="inlineStr">
+        <is>
+          <t>通信網路業右上上市</t>
+        </is>
+      </c>
+      <c r="EP5" t="inlineStr">
+        <is>
+          <t>144.0</t>
+        </is>
+      </c>
+      <c r="EQ5" t="inlineStr">
+        <is>
+          <t>146.0</t>
+        </is>
+      </c>
+      <c r="ER5" t="inlineStr">
+        <is>
+          <t>143.0</t>
+        </is>
+      </c>
+      <c r="ES5" t="inlineStr">
+        <is>
+          <t>145.5</t>
+        </is>
+      </c>
+      <c r="ET5" t="inlineStr">
+        <is>
+          <t>129.5</t>
+        </is>
+      </c>
+      <c r="EU5" t="inlineStr">
+        <is>
+          <t>47.26</t>
+        </is>
+      </c>
+      <c r="EV5" t="inlineStr">
+        <is>
+          <t>** 通信網路 - 電信服務業** 智慧電網 - 能源管理服務、系統整合服務</t>
+        </is>
+      </c>
+      <c r="EW5" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="EX5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="EY5" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="EZ5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="FA5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="FB5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="FC5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="FD5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="FE5" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="FF5" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="CJ5" t="inlineStr">
-        <is>
-          <t>36.11</t>
-        </is>
-      </c>
-      <c r="CK5" t="n">
-        <v>-0.76</v>
-      </c>
-      <c r="CL5" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="CM5" t="inlineStr">
-        <is>
-          <t>1.85</t>
-        </is>
-      </c>
-      <c r="CN5" t="inlineStr">
-        <is>
-          <t>-0.52</t>
-        </is>
-      </c>
-      <c r="CO5" t="inlineStr">
-        <is>
-          <t>144.6</t>
-        </is>
-      </c>
-      <c r="CP5" t="inlineStr">
-        <is>
-          <t>144.5</t>
-        </is>
-      </c>
-      <c r="CQ5" t="inlineStr">
-        <is>
-          <t>141.65</t>
-        </is>
-      </c>
-      <c r="CR5" t="inlineStr">
-        <is>
-          <t>139.08</t>
-        </is>
-      </c>
-      <c r="CS5" t="inlineStr">
-        <is>
-          <t>139.81</t>
-        </is>
-      </c>
-      <c r="CT5" t="inlineStr">
-        <is>
-          <t>135.8520833333333</t>
-        </is>
-      </c>
-      <c r="CU5" t="inlineStr">
-        <is>
-          <t>-0.001381215469613339</t>
-        </is>
-      </c>
-      <c r="CV5" t="inlineStr">
-        <is>
-          <t>0.0006925207756232066</t>
-        </is>
-      </c>
-      <c r="CW5" t="inlineStr">
-        <is>
-          <t>0.002654397451778534</t>
-        </is>
-      </c>
-      <c r="CX5" t="inlineStr">
-        <is>
-          <t>0.0006475285991798252</t>
-        </is>
-      </c>
-      <c r="CY5" t="inlineStr">
-        <is>
-          <t>0.0001788428865241443</t>
-        </is>
-      </c>
-      <c r="CZ5" t="inlineStr">
-        <is>
-          <t>0.0002761117332146235</t>
-        </is>
-      </c>
-      <c r="DA5" t="inlineStr">
-        <is>
-          <t>7.47</t>
-        </is>
-      </c>
-      <c r="DB5" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="DC5" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="DD5" t="inlineStr">
-        <is>
-          <t>1.9</t>
-        </is>
-      </c>
-      <c r="DE5" t="inlineStr">
-        <is>
-          <t>-6.89</t>
-        </is>
-      </c>
-      <c r="DF5" t="inlineStr">
-        <is>
-          <t>2026/08/21</t>
-        </is>
-      </c>
-      <c r="DG5" t="inlineStr">
-        <is>
-          <t>2218439785.568572</t>
-        </is>
-      </c>
-      <c r="DH5" t="inlineStr">
-        <is>
-          <t>1524028999.0</t>
-        </is>
-      </c>
-      <c r="DI5" t="n">
-        <v>1223386087.6</v>
-      </c>
-      <c r="DJ5" t="inlineStr">
-        <is>
-          <t>1823976219.1</t>
-        </is>
-      </c>
-      <c r="DK5" t="inlineStr">
-        <is>
-          <t>1490856706.633333</t>
-        </is>
-      </c>
-      <c r="DL5" t="n">
-        <v>1693335182.06</v>
-      </c>
-      <c r="DM5" t="inlineStr">
-        <is>
-          <t>2020913533.8875</t>
-        </is>
-      </c>
-      <c r="DN5" t="inlineStr">
-        <is>
-          <t>30644943.6203547</t>
-        </is>
-      </c>
-      <c r="DO5" t="inlineStr">
-        <is>
-          <t>-46102165.86562538</t>
-        </is>
-      </c>
-      <c r="DP5" t="inlineStr">
-        <is>
-          <t>1524028999.0</t>
-        </is>
-      </c>
-      <c r="DQ5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="DR5" t="inlineStr">
-        <is>
-          <t>143.5</t>
-        </is>
-      </c>
-      <c r="DS5" t="inlineStr">
-        <is>
-          <t>2026/09/15</t>
-        </is>
-      </c>
-      <c r="DT5" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="DU5" t="inlineStr">
-        <is>
-          <t>中華電</t>
-        </is>
-      </c>
-      <c r="DV5" t="inlineStr">
-        <is>
-          <t>中華電</t>
-        </is>
-      </c>
-      <c r="DW5" t="inlineStr">
-        <is>
-          <t>通信網路業</t>
-        </is>
-      </c>
-      <c r="DX5" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="DY5" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="DZ5" t="inlineStr">
-        <is>
-          <t>-1.398042523039787</t>
-        </is>
-      </c>
-      <c r="EA5" t="inlineStr">
-        <is>
-          <t>7.608984617555596</t>
-        </is>
-      </c>
-      <c r="EB5" t="inlineStr">
-        <is>
-          <t>7.52024426560034</t>
-        </is>
-      </c>
-      <c r="EC5" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
-        </is>
-      </c>
-      <c r="ED5" t="inlineStr">
-        <is>
-          <t>價-量增</t>
-        </is>
-      </c>
-      <c r="EE5" t="inlineStr">
-        <is>
-          <t>3.04</t>
-        </is>
-      </c>
-      <c r="EF5" t="inlineStr">
-        <is>
-          <t>3.57</t>
-        </is>
-      </c>
-      <c r="EG5" t="inlineStr">
-        <is>
-          <t>7.91</t>
-        </is>
-      </c>
-      <c r="EH5" t="inlineStr">
-        <is>
-          <t>28.59</t>
-        </is>
-      </c>
-      <c r="EI5" t="inlineStr">
-        <is>
-          <t>37.54%</t>
-        </is>
-      </c>
-      <c r="EJ5" t="inlineStr">
-        <is>
-          <t>21.61%</t>
-        </is>
-      </c>
-      <c r="EK5" t="inlineStr">
-        <is>
-          <t>85.28</t>
-        </is>
-      </c>
-      <c r="EL5" t="inlineStr">
-        <is>
-          <t>1128708</t>
-        </is>
-      </c>
-      <c r="EM5" t="inlineStr">
-        <is>
-          <t>個人家庭60.70%、企業客戶32.70%、國際客戶4.00%、其他2.60% (2025年)</t>
-        </is>
-      </c>
-      <c r="EN5" t="inlineStr">
-        <is>
-          <t>中華電-通信網路業-上市</t>
-        </is>
-      </c>
-      <c r="EO5" t="inlineStr">
-        <is>
-          <t>通信網路業右上上市</t>
-        </is>
-      </c>
-      <c r="EP5" t="inlineStr">
-        <is>
-          <t>145.0</t>
-        </is>
-      </c>
-      <c r="EQ5" t="inlineStr">
-        <is>
-          <t>145.0</t>
-        </is>
-      </c>
-      <c r="ER5" t="inlineStr">
-        <is>
-          <t>143.0</t>
-        </is>
-      </c>
-      <c r="ES5" t="inlineStr">
-        <is>
-          <t>143.5</t>
-        </is>
-      </c>
-      <c r="ET5" t="inlineStr">
-        <is>
-          <t>128.0</t>
-        </is>
-      </c>
-      <c r="EU5" t="inlineStr">
-        <is>
-          <t>47.26</t>
-        </is>
-      </c>
-      <c r="EV5" t="inlineStr">
-        <is>
-          <t>** 通信網路 - 電信服務業** 智慧電網 - 能源管理服務、系統整合服務</t>
-        </is>
-      </c>
-      <c r="EW5" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="EX5" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="EY5" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
-      </c>
-      <c r="EZ5" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="FA5" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="FB5" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="FC5" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="FD5" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="FE5" t="inlineStr">
-        <is>
-          <t>12.0</t>
-        </is>
-      </c>
-      <c r="FF5" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="FG5" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>4</t>
         </is>
       </c>
       <c r="FH5" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="FI5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FJ5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FK5" t="inlineStr">
@@ -5387,12 +5387,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-0.68</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>11652.18</t>
+          <t>10607.859</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -5402,7 +5402,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>144.0</t>
+          <t>143.5</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -5412,7 +5412,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>1.03</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -5422,7 +5422,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-0.39166013609889294</t>
+          <t>-0.3292751984432931</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -5432,7 +5432,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>99.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -5467,259 +5467,259 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>盤整偏多</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>TrendType : 盤整偏多&lt;br&gt;TrendScore : 40&lt;br&gt;HH : True&lt;br&gt;HL : False&lt;br&gt;MA : False&lt;br&gt;VOL : False</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>141.65</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>148.1152919500972</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>135.1847080499028</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>0.09128544934835393</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>0.002654397451778534</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>-0.0002059336306642345</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>-0.06151019020493131</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>0.05137843623728422</t>
+        </is>
+      </c>
+      <c r="AD6" t="inlineStr">
+        <is>
+          <t>1.49820616914414</t>
+        </is>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t>2026-09-02 00:00:00</t>
+        </is>
+      </c>
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="AG6" t="inlineStr">
+        <is>
           <t>40.0</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>盤整偏多</t>
-        </is>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>TrendType : 盤整偏多&lt;br&gt;TrendScore : 40&lt;br&gt;HH : True&lt;br&gt;HL : False&lt;br&gt;MA : False&lt;br&gt;VOL : False</t>
-        </is>
-      </c>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>141.275</t>
-        </is>
-      </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>148.1458001525924</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>134.4041998474076</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>0.0972684502225076</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>0.003017394391196415</t>
-        </is>
-      </c>
-      <c r="AA6" t="inlineStr">
-        <is>
-          <t>0.0006164580977034984</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>-0.0491912858969541</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>0.04785629426595885</t>
-        </is>
-      </c>
-      <c r="AD6" t="inlineStr">
-        <is>
-          <t>1.699323642510481</t>
-        </is>
-      </c>
-      <c r="AE6" t="inlineStr">
-        <is>
-          <t>2026-09-02 00:00:00</t>
-        </is>
-      </c>
-      <c r="AF6" t="inlineStr">
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>2026-09-03 00:00:00</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AL6" t="inlineStr">
+        <is>
+          <t>2026-09-08 00:00:00</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AN6" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="AP6" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="AQ6" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AR6" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AS6" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AU6" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="AG6" t="inlineStr">
-        <is>
-          <t>40.0</t>
-        </is>
-      </c>
-      <c r="AH6" t="inlineStr">
+      <c r="AV6" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AW6" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="AI6" t="inlineStr">
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>7.0</t>
+        </is>
+      </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>14.0</t>
+        </is>
+      </c>
+      <c r="BA6" t="inlineStr">
+        <is>
+          <t>14.0</t>
+        </is>
+      </c>
+      <c r="BB6" t="inlineStr">
+        <is>
+          <t>14.0</t>
+        </is>
+      </c>
+      <c r="BC6" t="inlineStr">
+        <is>
+          <t>盤整</t>
+        </is>
+      </c>
+      <c r="BD6" t="inlineStr">
+        <is>
+          <t>盤整</t>
+        </is>
+      </c>
+      <c r="BE6" t="inlineStr">
+        <is>
+          <t>58.3</t>
+        </is>
+      </c>
+      <c r="BF6" t="inlineStr">
+        <is>
+          <t>18108850.0</t>
+        </is>
+      </c>
+      <c r="BG6" t="inlineStr">
+        <is>
+          <t>1199596.0</t>
+        </is>
+      </c>
+      <c r="BH6" t="inlineStr">
+        <is>
+          <t>4011399.0</t>
+        </is>
+      </c>
+      <c r="BI6" t="inlineStr">
+        <is>
+          <t>-2811803.0</t>
+        </is>
+      </c>
+      <c r="BJ6" t="inlineStr">
+        <is>
+          <t>-248002.0</t>
+        </is>
+      </c>
+      <c r="BK6" t="inlineStr">
+        <is>
+          <t>15049045.0</t>
+        </is>
+      </c>
+      <c r="BL6" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="BM6" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="BN6" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="BO6" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>2026-09-03 00:00:00</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
+      <c r="BP6" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AL6" t="inlineStr">
-        <is>
-          <t>2026-09-08 00:00:00</t>
-        </is>
-      </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
-      </c>
-      <c r="AN6" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
-      </c>
-      <c r="AP6" t="inlineStr">
-        <is>
-          <t>7.0</t>
-        </is>
-      </c>
-      <c r="AQ6" t="inlineStr">
+      <c r="BQ6" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AR6" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AS6" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AT6" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AU6" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="AV6" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AW6" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr">
-        <is>
-          <t>8.0</t>
-        </is>
-      </c>
-      <c r="AZ6" t="inlineStr">
-        <is>
-          <t>14.0</t>
-        </is>
-      </c>
-      <c r="BA6" t="inlineStr">
-        <is>
-          <t>14.0</t>
-        </is>
-      </c>
-      <c r="BB6" t="inlineStr">
-        <is>
-          <t>14.0</t>
-        </is>
-      </c>
-      <c r="BC6" t="inlineStr">
-        <is>
-          <t>盤整</t>
-        </is>
-      </c>
-      <c r="BD6" t="inlineStr">
-        <is>
-          <t>強勢</t>
-        </is>
-      </c>
-      <c r="BE6" t="inlineStr">
-        <is>
-          <t>58.3</t>
-        </is>
-      </c>
-      <c r="BF6" t="inlineStr">
-        <is>
-          <t>15010110.0</t>
-        </is>
-      </c>
-      <c r="BG6" t="inlineStr">
-        <is>
-          <t>1050416.0</t>
-        </is>
-      </c>
-      <c r="BH6" t="inlineStr">
-        <is>
-          <t>4036399.0</t>
-        </is>
-      </c>
-      <c r="BI6" t="inlineStr">
-        <is>
-          <t>-2985983.0</t>
-        </is>
-      </c>
-      <c r="BJ6" t="inlineStr">
-        <is>
-          <t>-213000.0</t>
-        </is>
-      </c>
-      <c r="BK6" t="inlineStr">
-        <is>
-          <t>11811127.0</t>
-        </is>
-      </c>
-      <c r="BL6" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
-      </c>
-      <c r="BM6" t="inlineStr">
-        <is>
-          <t>4.0</t>
-        </is>
-      </c>
-      <c r="BN6" t="inlineStr">
-        <is>
-          <t>-2.0</t>
-        </is>
-      </c>
-      <c r="BO6" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="BP6" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="BQ6" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
       <c r="BR6" t="inlineStr">
         <is>
           <t>-0.18</t>
@@ -5772,17 +5772,17 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="CC6" t="inlineStr">
         <is>
-          <t>19.45</t>
+          <t>17.70</t>
         </is>
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>-0.69</t>
+          <t>-0.70</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
@@ -5793,110 +5793,110 @@
       <c r="CF6" t="inlineStr"/>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>86</t>
+          <t>54</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
         <is>
-          <t>8515</t>
+          <t>7053</t>
         </is>
       </c>
       <c r="CI6" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="CJ6" t="inlineStr">
         <is>
-          <t>69.44</t>
+          <t>36.11</t>
         </is>
       </c>
       <c r="CK6" t="n">
-        <v>-0.55</v>
+        <v>-0.76</v>
       </c>
       <c r="CL6" t="n">
-        <v>2.5</v>
+        <v>2.08</v>
       </c>
       <c r="CM6" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="CN6" t="inlineStr">
         <is>
-          <t>-0.57</t>
+          <t>-0.52</t>
         </is>
       </c>
       <c r="CO6" t="inlineStr">
         <is>
-          <t>144.8</t>
+          <t>144.6</t>
         </is>
       </c>
       <c r="CP6" t="inlineStr">
         <is>
-          <t>144.4</t>
+          <t>144.5</t>
         </is>
       </c>
       <c r="CQ6" t="inlineStr">
         <is>
-          <t>141.28</t>
+          <t>141.65</t>
         </is>
       </c>
       <c r="CR6" t="inlineStr">
         <is>
-          <t>138.99</t>
+          <t>139.08</t>
         </is>
       </c>
       <c r="CS6" t="inlineStr">
         <is>
-          <t>139.79</t>
+          <t>139.81</t>
         </is>
       </c>
       <c r="CT6" t="inlineStr">
         <is>
-          <t>135.8145833333333</t>
+          <t>0</t>
         </is>
       </c>
       <c r="CU6" t="inlineStr">
         <is>
-          <t>-0.002067539627842785</t>
+          <t>-0.001381215469613339</t>
         </is>
       </c>
       <c r="CV6" t="inlineStr">
         <is>
-          <t>0.002429711905588272</t>
+          <t>0.0006925207756232066</t>
         </is>
       </c>
       <c r="CW6" t="inlineStr">
         <is>
-          <t>0.003017394391196415</t>
+          <t>0.002654397451778534</t>
         </is>
       </c>
       <c r="CX6" t="inlineStr">
         <is>
-          <t>0.0008641175199828321</t>
+          <t>0.0006475285991798252</t>
         </is>
       </c>
       <c r="CY6" t="inlineStr">
         <is>
-          <t>0.0002683363148479057</t>
+          <t>0.0001788428865241443</t>
         </is>
       </c>
       <c r="CZ6" t="inlineStr">
         <is>
-          <t>0.0003222341568205334</t>
+          <t>0</t>
         </is>
       </c>
       <c r="DA6" t="inlineStr">
         <is>
-          <t>17.86</t>
+          <t>7.47</t>
         </is>
       </c>
       <c r="DB6" t="n">
-        <v>2.04</v>
+        <v>1.9</v>
       </c>
       <c r="DC6" t="n">
-        <v>1.73</v>
+        <v>1.76</v>
       </c>
       <c r="DD6" t="inlineStr">
         <is>
@@ -5905,7 +5905,7 @@
       </c>
       <c r="DE6" t="inlineStr">
         <is>
-          <t>-8.63</t>
+          <t>-6.89</t>
         </is>
       </c>
       <c r="DF6" t="inlineStr">
@@ -5915,48 +5915,48 @@
       </c>
       <c r="DG6" t="inlineStr">
         <is>
-          <t>2218439785.568572</t>
+          <t>2517415638.848781</t>
         </is>
       </c>
       <c r="DH6" t="inlineStr">
         <is>
-          <t>1676725028.0</t>
+          <t>1524028999.0</t>
         </is>
       </c>
       <c r="DI6" t="n">
-        <v>1178675636.2</v>
+        <v>1223386087.6</v>
       </c>
       <c r="DJ6" t="inlineStr">
         <is>
-          <t>1937528191.3</t>
+          <t>1823976219.1</t>
         </is>
       </c>
       <c r="DK6" t="inlineStr">
         <is>
-          <t>1486546014.1</t>
+          <t>1490856706.633333</t>
         </is>
       </c>
       <c r="DL6" t="n">
-        <v>1735471199.16</v>
+        <v>1693335182.06</v>
       </c>
       <c r="DM6" t="inlineStr">
         <is>
-          <t>2026673727.9875</t>
+          <t>2020913533.8875</t>
         </is>
       </c>
       <c r="DN6" t="inlineStr">
         <is>
-          <t>44598963.52689654</t>
+          <t>30644943.61799386</t>
         </is>
       </c>
       <c r="DO6" t="inlineStr">
         <is>
-          <t>-45987257.26803184</t>
+          <t>-46102165.86613226</t>
         </is>
       </c>
       <c r="DP6" t="inlineStr">
         <is>
-          <t>1676725028.0</t>
+          <t>1524028999.0</t>
         </is>
       </c>
       <c r="DQ6" t="inlineStr">
@@ -5976,7 +5976,7 @@
       </c>
       <c r="DT6" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="DU6" t="inlineStr">
@@ -6021,7 +6021,7 @@
       </c>
       <c r="EC6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="ED6" t="inlineStr">
@@ -6031,7 +6031,7 @@
       </c>
       <c r="EE6" t="inlineStr">
         <is>
-          <t>3.05</t>
+          <t>3.04</t>
         </is>
       </c>
       <c r="EF6" t="inlineStr">
@@ -6061,7 +6061,7 @@
       </c>
       <c r="EK6" t="inlineStr">
         <is>
-          <t>85.28</t>
+          <t>84.97</t>
         </is>
       </c>
       <c r="EL6" t="inlineStr">
@@ -6086,12 +6086,12 @@
       </c>
       <c r="EP6" t="inlineStr">
         <is>
-          <t>146.0</t>
+          <t>145.0</t>
         </is>
       </c>
       <c r="EQ6" t="inlineStr">
         <is>
-          <t>146.0</t>
+          <t>145.0</t>
         </is>
       </c>
       <c r="ER6" t="inlineStr">
@@ -6101,12 +6101,12 @@
       </c>
       <c r="ES6" t="inlineStr">
         <is>
-          <t>144.0</t>
+          <t>143.5</t>
         </is>
       </c>
       <c r="ET6" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>129.5</t>
         </is>
       </c>
       <c r="EU6" t="inlineStr">
@@ -6126,67 +6126,67 @@
       </c>
       <c r="EX6" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="EY6" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="EZ6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="FA6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="FB6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="FC6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="FD6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="FE6" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="FF6" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="EY6" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
-      </c>
-      <c r="EZ6" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="FA6" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="FB6" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="FC6" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="FD6" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="FE6" t="inlineStr">
-        <is>
-          <t>13.0</t>
-        </is>
-      </c>
-      <c r="FF6" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="FG6" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>4</t>
         </is>
       </c>
       <c r="FH6" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="FI6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FJ6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FK6" t="inlineStr">
@@ -6373,12 +6373,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>-0.68</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>6311.915</t>
+          <t>11652.18</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -6388,7 +6388,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>145.0</t>
+          <t>144.0</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -6398,7 +6398,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>0.34</t>
+          <t>1.03</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -6408,7 +6408,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-0.15933593107033336</t>
+          <t>-0.39166013609889294</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -6453,262 +6453,262 @@
       </c>
       <c r="S7" t="inlineStr">
         <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>盤整偏多</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>TrendType : 盤整偏多&lt;br&gt;TrendScore : 40&lt;br&gt;HH : True&lt;br&gt;HL : False&lt;br&gt;MA : False&lt;br&gt;VOL : False</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>141.275</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>148.1458001525903</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>134.4041998474098</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>0.09726845022247742</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>0.003017394391196415</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>0.0006164580977021661</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>-0.04919128589699406</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>0.05137843623728422</t>
+        </is>
+      </c>
+      <c r="AD7" t="inlineStr">
+        <is>
+          <t>1.699323642510904</t>
+        </is>
+      </c>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t>2026-09-02 00:00:00</t>
+        </is>
+      </c>
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="AG7" t="inlineStr">
+        <is>
           <t>40.0</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>盤整偏多</t>
-        </is>
-      </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>TrendType : 盤整偏多&lt;br&gt;TrendScore : 40&lt;br&gt;HH : True&lt;br&gt;HL : False&lt;br&gt;MA : False&lt;br&gt;VOL : False</t>
-        </is>
-      </c>
-      <c r="V7" t="inlineStr">
-        <is>
-          <t>140.85</t>
-        </is>
-      </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>148.0545307382171</t>
-        </is>
-      </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>133.6454692617829</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>0.1023007559562248</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>0.00338379341050743</t>
-        </is>
-      </c>
-      <c r="AA7" t="inlineStr">
-        <is>
-          <t>0.002539703250195702</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>-0.01700799986580759</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>0.04785629426595885</t>
-        </is>
-      </c>
-      <c r="AD7" t="inlineStr">
-        <is>
-          <t>1.907951888344097</t>
-        </is>
-      </c>
-      <c r="AE7" t="inlineStr">
-        <is>
-          <t>2026-09-02 00:00:00</t>
-        </is>
-      </c>
-      <c r="AF7" t="inlineStr">
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>2026-09-03 00:00:00</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AL7" t="inlineStr">
+        <is>
+          <t>2026-09-08 00:00:00</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AN7" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="AP7" t="inlineStr">
+        <is>
+          <t>7.0</t>
+        </is>
+      </c>
+      <c r="AQ7" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AR7" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AS7" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AU7" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="AG7" t="inlineStr">
-        <is>
-          <t>40.0</t>
-        </is>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AI7" t="inlineStr">
+      <c r="AV7" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>2026-09-03 00:00:00</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>8.0</t>
+        </is>
+      </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>14.0</t>
+        </is>
+      </c>
+      <c r="BA7" t="inlineStr">
+        <is>
+          <t>14.0</t>
+        </is>
+      </c>
+      <c r="BB7" t="inlineStr">
+        <is>
+          <t>14.0</t>
+        </is>
+      </c>
+      <c r="BC7" t="inlineStr">
+        <is>
+          <t>盤整</t>
+        </is>
+      </c>
+      <c r="BD7" t="inlineStr">
+        <is>
+          <t>強勢</t>
+        </is>
+      </c>
+      <c r="BE7" t="inlineStr">
+        <is>
+          <t>58.3</t>
+        </is>
+      </c>
+      <c r="BF7" t="inlineStr">
+        <is>
+          <t>18108850.0</t>
+        </is>
+      </c>
+      <c r="BG7" t="inlineStr">
+        <is>
+          <t>1199596.0</t>
+        </is>
+      </c>
+      <c r="BH7" t="inlineStr">
+        <is>
+          <t>4011399.0</t>
+        </is>
+      </c>
+      <c r="BI7" t="inlineStr">
+        <is>
+          <t>-2811803.0</t>
+        </is>
+      </c>
+      <c r="BJ7" t="inlineStr">
+        <is>
+          <t>-248002.0</t>
+        </is>
+      </c>
+      <c r="BK7" t="inlineStr">
+        <is>
+          <t>15049045.0</t>
+        </is>
+      </c>
+      <c r="BL7" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="BM7" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="BN7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="BO7" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AL7" t="inlineStr">
-        <is>
-          <t>2026-09-08 00:00:00</t>
-        </is>
-      </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
-      </c>
-      <c r="AN7" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>7.0</t>
-        </is>
-      </c>
-      <c r="AP7" t="inlineStr">
-        <is>
-          <t>7.0</t>
-        </is>
-      </c>
-      <c r="AQ7" t="inlineStr">
+      <c r="BP7" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AR7" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AS7" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AT7" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AU7" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="AV7" t="inlineStr">
+      <c r="BQ7" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AW7" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
-      </c>
-      <c r="AX7" t="inlineStr">
-        <is>
-          <t>4.0</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr">
-        <is>
-          <t>9.0</t>
-        </is>
-      </c>
-      <c r="AZ7" t="inlineStr">
-        <is>
-          <t>14.0</t>
-        </is>
-      </c>
-      <c r="BA7" t="inlineStr">
-        <is>
-          <t>14.0</t>
-        </is>
-      </c>
-      <c r="BB7" t="inlineStr">
-        <is>
-          <t>14.0</t>
-        </is>
-      </c>
-      <c r="BC7" t="inlineStr">
-        <is>
-          <t>強勢</t>
-        </is>
-      </c>
-      <c r="BD7" t="inlineStr">
-        <is>
-          <t>強勢</t>
-        </is>
-      </c>
-      <c r="BE7" t="inlineStr">
-        <is>
-          <t>58.3</t>
-        </is>
-      </c>
-      <c r="BF7" t="inlineStr">
-        <is>
-          <t>15010110.0</t>
-        </is>
-      </c>
-      <c r="BG7" t="inlineStr">
-        <is>
-          <t>1050416.0</t>
-        </is>
-      </c>
-      <c r="BH7" t="inlineStr">
-        <is>
-          <t>4036399.0</t>
-        </is>
-      </c>
-      <c r="BI7" t="inlineStr">
-        <is>
-          <t>-2985983.0</t>
-        </is>
-      </c>
-      <c r="BJ7" t="inlineStr">
-        <is>
-          <t>-213000.0</t>
-        </is>
-      </c>
-      <c r="BK7" t="inlineStr">
-        <is>
-          <t>11811127.0</t>
-        </is>
-      </c>
-      <c r="BL7" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
-      </c>
-      <c r="BM7" t="inlineStr">
-        <is>
-          <t>4.0</t>
-        </is>
-      </c>
-      <c r="BN7" t="inlineStr">
-        <is>
-          <t>-2.0</t>
-        </is>
-      </c>
-      <c r="BO7" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="BP7" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="BQ7" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>-0.18</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
@@ -6758,12 +6758,12 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="CC7" t="inlineStr">
         <is>
-          <t>10.53</t>
+          <t>19.45</t>
         </is>
       </c>
       <c r="CD7" t="inlineStr">
@@ -6779,400 +6779,400 @@
       <c r="CF7" t="inlineStr"/>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>86</t>
+          <t>54</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
         <is>
-          <t>8515</t>
+          <t>7053</t>
         </is>
       </c>
       <c r="CI7" t="inlineStr">
         <is>
-          <t>83.33</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="CJ7" t="inlineStr">
         <is>
-          <t>91.67</t>
+          <t>69.44</t>
         </is>
       </c>
       <c r="CK7" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.55</v>
       </c>
       <c r="CL7" t="n">
-        <v>3.02</v>
+        <v>2.5</v>
       </c>
       <c r="CM7" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="CN7" t="inlineStr">
         <is>
-          <t>-0.63</t>
+          <t>-0.57</t>
         </is>
       </c>
       <c r="CO7" t="inlineStr">
         <is>
-          <t>145.1</t>
+          <t>144.8</t>
         </is>
       </c>
       <c r="CP7" t="inlineStr">
         <is>
-          <t>144.05</t>
+          <t>144.4</t>
         </is>
       </c>
       <c r="CQ7" t="inlineStr">
         <is>
-          <t>140.85</t>
+          <t>141.28</t>
         </is>
       </c>
       <c r="CR7" t="inlineStr">
         <is>
-          <t>138.87</t>
+          <t>138.99</t>
         </is>
       </c>
       <c r="CS7" t="inlineStr">
         <is>
-          <t>139.75</t>
+          <t>139.79</t>
         </is>
       </c>
       <c r="CT7" t="inlineStr">
         <is>
-          <t>135.7708333333333</t>
+          <t>0</t>
         </is>
       </c>
       <c r="CU7" t="inlineStr">
         <is>
+          <t>-0.002067539627842785</t>
+        </is>
+      </c>
+      <c r="CV7" t="inlineStr">
+        <is>
+          <t>0.002429711905588272</t>
+        </is>
+      </c>
+      <c r="CW7" t="inlineStr">
+        <is>
+          <t>0.003017394391196415</t>
+        </is>
+      </c>
+      <c r="CX7" t="inlineStr">
+        <is>
+          <t>0.0008641175199828321</t>
+        </is>
+      </c>
+      <c r="CY7" t="inlineStr">
+        <is>
+          <t>0.0002683363148479057</t>
+        </is>
+      </c>
+      <c r="CZ7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="DA7" t="inlineStr">
+        <is>
+          <t>17.86</t>
+        </is>
+      </c>
+      <c r="DB7" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="DC7" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="DD7" t="inlineStr">
+        <is>
+          <t>1.9</t>
+        </is>
+      </c>
+      <c r="DE7" t="inlineStr">
+        <is>
+          <t>-8.63</t>
+        </is>
+      </c>
+      <c r="DF7" t="inlineStr">
+        <is>
+          <t>2026/08/21</t>
+        </is>
+      </c>
+      <c r="DG7" t="inlineStr">
+        <is>
+          <t>2517415638.848781</t>
+        </is>
+      </c>
+      <c r="DH7" t="inlineStr">
+        <is>
+          <t>1676725028.0</t>
+        </is>
+      </c>
+      <c r="DI7" t="n">
+        <v>1178675636.2</v>
+      </c>
+      <c r="DJ7" t="inlineStr">
+        <is>
+          <t>1937528191.3</t>
+        </is>
+      </c>
+      <c r="DK7" t="inlineStr">
+        <is>
+          <t>1486546014.1</t>
+        </is>
+      </c>
+      <c r="DL7" t="n">
+        <v>1735471199.16</v>
+      </c>
+      <c r="DM7" t="inlineStr">
+        <is>
+          <t>2026673727.9875</t>
+        </is>
+      </c>
+      <c r="DN7" t="inlineStr">
+        <is>
+          <t>44598963.52419861</t>
+        </is>
+      </c>
+      <c r="DO7" t="inlineStr">
+        <is>
+          <t>-45987257.26861119</t>
+        </is>
+      </c>
+      <c r="DP7" t="inlineStr">
+        <is>
+          <t>1676725028.0</t>
+        </is>
+      </c>
+      <c r="DQ7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="DR7" t="inlineStr">
+        <is>
+          <t>143.5</t>
+        </is>
+      </c>
+      <c r="DS7" t="inlineStr">
+        <is>
+          <t>2026/09/15</t>
+        </is>
+      </c>
+      <c r="DT7" t="inlineStr">
+        <is>
+          <t>0.35</t>
+        </is>
+      </c>
+      <c r="DU7" t="inlineStr">
+        <is>
+          <t>中華電</t>
+        </is>
+      </c>
+      <c r="DV7" t="inlineStr">
+        <is>
+          <t>中華電</t>
+        </is>
+      </c>
+      <c r="DW7" t="inlineStr">
+        <is>
+          <t>通信網路業</t>
+        </is>
+      </c>
+      <c r="DX7" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="DY7" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="DZ7" t="inlineStr">
+        <is>
+          <t>-1.398042523039787</t>
+        </is>
+      </c>
+      <c r="EA7" t="inlineStr">
+        <is>
+          <t>7.608984617555596</t>
+        </is>
+      </c>
+      <c r="EB7" t="inlineStr">
+        <is>
+          <t>7.52024426560034</t>
+        </is>
+      </c>
+      <c r="EC7" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="ED7" t="inlineStr">
+        <is>
+          <t>價-量增</t>
+        </is>
+      </c>
+      <c r="EE7" t="inlineStr">
+        <is>
+          <t>3.05</t>
+        </is>
+      </c>
+      <c r="EF7" t="inlineStr">
+        <is>
+          <t>3.57</t>
+        </is>
+      </c>
+      <c r="EG7" t="inlineStr">
+        <is>
+          <t>7.91</t>
+        </is>
+      </c>
+      <c r="EH7" t="inlineStr">
+        <is>
+          <t>28.59</t>
+        </is>
+      </c>
+      <c r="EI7" t="inlineStr">
+        <is>
+          <t>37.54%</t>
+        </is>
+      </c>
+      <c r="EJ7" t="inlineStr">
+        <is>
+          <t>21.61%</t>
+        </is>
+      </c>
+      <c r="EK7" t="inlineStr">
+        <is>
+          <t>84.97</t>
+        </is>
+      </c>
+      <c r="EL7" t="inlineStr">
+        <is>
+          <t>1128708</t>
+        </is>
+      </c>
+      <c r="EM7" t="inlineStr">
+        <is>
+          <t>個人家庭60.70%、企業客戶32.70%、國際客戶4.00%、其他2.60% (2025年)</t>
+        </is>
+      </c>
+      <c r="EN7" t="inlineStr">
+        <is>
+          <t>中華電-通信網路業-上市</t>
+        </is>
+      </c>
+      <c r="EO7" t="inlineStr">
+        <is>
+          <t>通信網路業右上上市</t>
+        </is>
+      </c>
+      <c r="EP7" t="inlineStr">
+        <is>
+          <t>146.0</t>
+        </is>
+      </c>
+      <c r="EQ7" t="inlineStr">
+        <is>
+          <t>146.0</t>
+        </is>
+      </c>
+      <c r="ER7" t="inlineStr">
+        <is>
+          <t>143.0</t>
+        </is>
+      </c>
+      <c r="ES7" t="inlineStr">
+        <is>
+          <t>144.0</t>
+        </is>
+      </c>
+      <c r="ET7" t="inlineStr">
+        <is>
+          <t>129.5</t>
+        </is>
+      </c>
+      <c r="EU7" t="inlineStr">
+        <is>
+          <t>47.26</t>
+        </is>
+      </c>
+      <c r="EV7" t="inlineStr">
+        <is>
+          <t>** 通信網路 - 電信服務業** 智慧電網 - 能源管理服務、系統整合服務</t>
+        </is>
+      </c>
+      <c r="EW7" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="EX7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="EY7" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="EZ7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="FA7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="FB7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="FC7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="FD7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="FE7" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="FF7" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="CV7" t="inlineStr">
-        <is>
-          <t>0.003832752613240453</t>
-        </is>
-      </c>
-      <c r="CW7" t="inlineStr">
-        <is>
-          <t>0.00338379341050743</t>
-        </is>
-      </c>
-      <c r="CX7" t="inlineStr">
-        <is>
-          <t>0.001297858533420015</t>
-        </is>
-      </c>
-      <c r="CY7" t="inlineStr">
-        <is>
-          <t>0.0002684083385522396</t>
-        </is>
-      </c>
-      <c r="CZ7" t="inlineStr">
-        <is>
-          <t>0.0003223380251424768</t>
-        </is>
-      </c>
-      <c r="DA7" t="inlineStr">
-        <is>
-          <t>29.64</t>
-        </is>
-      </c>
-      <c r="DB7" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="DC7" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="DD7" t="inlineStr">
-        <is>
-          <t>1.9</t>
-        </is>
-      </c>
-      <c r="DE7" t="inlineStr">
-        <is>
-          <t>-12.71</t>
-        </is>
-      </c>
-      <c r="DF7" t="inlineStr">
-        <is>
-          <t>2026/08/21</t>
-        </is>
-      </c>
-      <c r="DG7" t="inlineStr">
-        <is>
-          <t>2218439785.568572</t>
-        </is>
-      </c>
-      <c r="DH7" t="inlineStr">
-        <is>
-          <t>918019598.0</t>
-        </is>
-      </c>
-      <c r="DI7" t="n">
-        <v>1659195852.6</v>
-      </c>
-      <c r="DJ7" t="inlineStr">
-        <is>
-          <t>1973672854.5</t>
-        </is>
-      </c>
-      <c r="DK7" t="inlineStr">
-        <is>
-          <t>1482010386.8</t>
-        </is>
-      </c>
-      <c r="DL7" t="n">
-        <v>1806077677.02</v>
-      </c>
-      <c r="DM7" t="inlineStr">
-        <is>
-          <t>2030537576.35</t>
-        </is>
-      </c>
-      <c r="DN7" t="inlineStr">
-        <is>
-          <t>61069185.48961079</t>
-        </is>
-      </c>
-      <c r="DO7" t="inlineStr">
-        <is>
-          <t>-60540988.90475464</t>
-        </is>
-      </c>
-      <c r="DP7" t="inlineStr">
-        <is>
-          <t>918019598.0</t>
-        </is>
-      </c>
-      <c r="DQ7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="DR7" t="inlineStr">
-        <is>
-          <t>143.5</t>
-        </is>
-      </c>
-      <c r="DS7" t="inlineStr">
-        <is>
-          <t>2026/09/15</t>
-        </is>
-      </c>
-      <c r="DT7" t="inlineStr">
-        <is>
-          <t>1.05</t>
-        </is>
-      </c>
-      <c r="DU7" t="inlineStr">
-        <is>
-          <t>中華電</t>
-        </is>
-      </c>
-      <c r="DV7" t="inlineStr">
-        <is>
-          <t>中華電</t>
-        </is>
-      </c>
-      <c r="DW7" t="inlineStr">
-        <is>
-          <t>通信網路業</t>
-        </is>
-      </c>
-      <c r="DX7" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="DY7" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="DZ7" t="inlineStr">
-        <is>
-          <t>-1.398042523039787</t>
-        </is>
-      </c>
-      <c r="EA7" t="inlineStr">
-        <is>
-          <t>7.608984617555596</t>
-        </is>
-      </c>
-      <c r="EB7" t="inlineStr">
-        <is>
-          <t>7.52024426560034</t>
-        </is>
-      </c>
-      <c r="EC7" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="ED7" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="EE7" t="inlineStr">
-        <is>
-          <t>3.07</t>
-        </is>
-      </c>
-      <c r="EF7" t="inlineStr">
-        <is>
-          <t>3.57</t>
-        </is>
-      </c>
-      <c r="EG7" t="inlineStr">
-        <is>
-          <t>7.91</t>
-        </is>
-      </c>
-      <c r="EH7" t="inlineStr">
-        <is>
-          <t>28.59</t>
-        </is>
-      </c>
-      <c r="EI7" t="inlineStr">
-        <is>
-          <t>37.54%</t>
-        </is>
-      </c>
-      <c r="EJ7" t="inlineStr">
-        <is>
-          <t>21.61%</t>
-        </is>
-      </c>
-      <c r="EK7" t="inlineStr">
-        <is>
-          <t>85.28</t>
-        </is>
-      </c>
-      <c r="EL7" t="inlineStr">
-        <is>
-          <t>1128708</t>
-        </is>
-      </c>
-      <c r="EM7" t="inlineStr">
-        <is>
-          <t>個人家庭60.70%、企業客戶32.70%、國際客戶4.00%、其他2.60% (2025年)</t>
-        </is>
-      </c>
-      <c r="EN7" t="inlineStr">
-        <is>
-          <t>中華電-通信網路業-上市</t>
-        </is>
-      </c>
-      <c r="EO7" t="inlineStr">
-        <is>
-          <t>通信網路業右上上市</t>
-        </is>
-      </c>
-      <c r="EP7" t="inlineStr">
-        <is>
-          <t>145.5</t>
-        </is>
-      </c>
-      <c r="EQ7" t="inlineStr">
-        <is>
-          <t>146.0</t>
-        </is>
-      </c>
-      <c r="ER7" t="inlineStr">
-        <is>
-          <t>145.0</t>
-        </is>
-      </c>
-      <c r="ES7" t="inlineStr">
-        <is>
-          <t>145.0</t>
-        </is>
-      </c>
-      <c r="ET7" t="inlineStr">
-        <is>
-          <t>128.0</t>
-        </is>
-      </c>
-      <c r="EU7" t="inlineStr">
-        <is>
-          <t>47.26</t>
-        </is>
-      </c>
-      <c r="EV7" t="inlineStr">
-        <is>
-          <t>** 通信網路 - 電信服務業** 智慧電網 - 能源管理服務、系統整合服務</t>
-        </is>
-      </c>
-      <c r="EW7" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="EX7" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="EY7" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
-      </c>
-      <c r="EZ7" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="FA7" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="FB7" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="FC7" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="FD7" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="FE7" t="inlineStr">
-        <is>
-          <t>14.0</t>
-        </is>
-      </c>
-      <c r="FF7" t="inlineStr">
-        <is>
-          <t>1.119557506059444</t>
-        </is>
-      </c>
       <c r="FG7" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>4</t>
         </is>
       </c>
       <c r="FH7" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="FI7" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FJ7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FK7" t="inlineStr">
@@ -7359,342 +7359,342 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
+          <t>-0.34</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>6311.915</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>145.0</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
           <t>0.34</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>8326.189</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>145.5</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
+      <c r="I8" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>-0.15933593107033336</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>99.0</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>盤整偏多</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>TrendType : 盤整偏多&lt;br&gt;TrendScore : 40&lt;br&gt;HH : True&lt;br&gt;HL : False&lt;br&gt;MA : False&lt;br&gt;VOL : False</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>140.85</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>148.0545307382152</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>133.6454692617848</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>0.1023007559561973</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>0.00338379341050743</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>0.002539703250194592</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>-0.01700799986583423</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>0.05137843623728422</t>
+        </is>
+      </c>
+      <c r="AD8" t="inlineStr">
+        <is>
+          <t>1.907951888344739</t>
+        </is>
+      </c>
+      <c r="AE8" t="inlineStr">
+        <is>
+          <t>2026-09-02 00:00:00</t>
+        </is>
+      </c>
+      <c r="AF8" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="AG8" t="inlineStr">
+        <is>
+          <t>40.0</t>
+        </is>
+      </c>
+      <c r="AH8" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>-0.03295367443261963</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>100.0</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
+      <c r="AI8" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr">
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>2026-09-03 00:00:00</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr">
+      <c r="AL8" t="inlineStr">
+        <is>
+          <t>2026-09-08 00:00:00</t>
+        </is>
+      </c>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AN8" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>7.0</t>
+        </is>
+      </c>
+      <c r="AP8" t="inlineStr">
+        <is>
+          <t>7.0</t>
+        </is>
+      </c>
+      <c r="AQ8" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AR8" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AS8" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AU8" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="R8" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>30.0</t>
-        </is>
-      </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>弱勢整理</t>
-        </is>
-      </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>TrendType : 弱勢整理&lt;br&gt;TrendScore : 30&lt;br&gt;HH : False&lt;br&gt;HL : False&lt;br&gt;MA : True&lt;br&gt;VOL : True</t>
-        </is>
-      </c>
-      <c r="V8" t="inlineStr">
-        <is>
-          <t>140.375</t>
-        </is>
-      </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>147.6794687115433</t>
-        </is>
-      </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>133.0705312884567</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>0.1040707919721211</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>0.003395282344531791</t>
-        </is>
-      </c>
-      <c r="AA8" t="inlineStr">
-        <is>
-          <t>0.004384515128183608</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>0.02031726359983477</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>0.04785629426595885</t>
-        </is>
-      </c>
-      <c r="AD8" t="inlineStr">
-        <is>
-          <t>2.079004612847744</t>
-        </is>
-      </c>
-      <c r="AE8" t="inlineStr">
-        <is>
-          <t>2026-09-02 00:00:00</t>
-        </is>
-      </c>
-      <c r="AF8" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="AG8" t="inlineStr">
-        <is>
-          <t>40.0</t>
-        </is>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>20.0</t>
-        </is>
-      </c>
-      <c r="AI8" t="inlineStr">
+      <c r="AV8" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>2026-09-03 00:00:00</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>4.0</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>9.0</t>
+        </is>
+      </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>14.0</t>
+        </is>
+      </c>
+      <c r="BA8" t="inlineStr">
+        <is>
+          <t>14.0</t>
+        </is>
+      </c>
+      <c r="BB8" t="inlineStr">
+        <is>
+          <t>14.0</t>
+        </is>
+      </c>
+      <c r="BC8" t="inlineStr">
+        <is>
+          <t>強勢</t>
+        </is>
+      </c>
+      <c r="BD8" t="inlineStr">
+        <is>
+          <t>強勢</t>
+        </is>
+      </c>
+      <c r="BE8" t="inlineStr">
+        <is>
+          <t>58.3</t>
+        </is>
+      </c>
+      <c r="BF8" t="inlineStr">
+        <is>
+          <t>18108850.0</t>
+        </is>
+      </c>
+      <c r="BG8" t="inlineStr">
+        <is>
+          <t>1199596.0</t>
+        </is>
+      </c>
+      <c r="BH8" t="inlineStr">
+        <is>
+          <t>4011399.0</t>
+        </is>
+      </c>
+      <c r="BI8" t="inlineStr">
+        <is>
+          <t>-2811803.0</t>
+        </is>
+      </c>
+      <c r="BJ8" t="inlineStr">
+        <is>
+          <t>-248002.0</t>
+        </is>
+      </c>
+      <c r="BK8" t="inlineStr">
+        <is>
+          <t>15049045.0</t>
+        </is>
+      </c>
+      <c r="BL8" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="BM8" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="BN8" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="BO8" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AL8" t="inlineStr">
-        <is>
-          <t>2026-09-08 00:00:00</t>
-        </is>
-      </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
-      </c>
-      <c r="AN8" t="inlineStr">
-        <is>
-          <t>7.0</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>7.0</t>
-        </is>
-      </c>
-      <c r="AP8" t="inlineStr">
-        <is>
-          <t>8.0</t>
-        </is>
-      </c>
-      <c r="AQ8" t="inlineStr">
+      <c r="BP8" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AR8" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AS8" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AT8" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AU8" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="AV8" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="AW8" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
-      </c>
-      <c r="AX8" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr">
-        <is>
-          <t>10.0</t>
-        </is>
-      </c>
-      <c r="AZ8" t="inlineStr">
-        <is>
-          <t>14.0</t>
-        </is>
-      </c>
-      <c r="BA8" t="inlineStr">
-        <is>
-          <t>14.0</t>
-        </is>
-      </c>
-      <c r="BB8" t="inlineStr">
-        <is>
-          <t>14.0</t>
-        </is>
-      </c>
-      <c r="BC8" t="inlineStr">
-        <is>
-          <t>強勢</t>
-        </is>
-      </c>
-      <c r="BD8" t="inlineStr">
-        <is>
-          <t>強勢</t>
-        </is>
-      </c>
-      <c r="BE8" t="inlineStr">
-        <is>
-          <t>58.3</t>
-        </is>
-      </c>
-      <c r="BF8" t="inlineStr">
-        <is>
-          <t>15010110.0</t>
-        </is>
-      </c>
-      <c r="BG8" t="inlineStr">
-        <is>
-          <t>1050416.0</t>
-        </is>
-      </c>
-      <c r="BH8" t="inlineStr">
-        <is>
-          <t>4036399.0</t>
-        </is>
-      </c>
-      <c r="BI8" t="inlineStr">
-        <is>
-          <t>-2985983.0</t>
-        </is>
-      </c>
-      <c r="BJ8" t="inlineStr">
-        <is>
-          <t>-213000.0</t>
-        </is>
-      </c>
-      <c r="BK8" t="inlineStr">
-        <is>
-          <t>11811127.0</t>
-        </is>
-      </c>
-      <c r="BL8" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
-      </c>
-      <c r="BM8" t="inlineStr">
-        <is>
-          <t>4.0</t>
-        </is>
-      </c>
-      <c r="BN8" t="inlineStr">
-        <is>
-          <t>-2.0</t>
-        </is>
-      </c>
-      <c r="BO8" t="inlineStr">
+      <c r="BQ8" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="BP8" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="BQ8" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>-0.07</t>
+          <t>-0.12</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
@@ -7744,17 +7744,17 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="CC8" t="inlineStr">
         <is>
-          <t>13.90</t>
+          <t>10.53</t>
         </is>
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>0.69</t>
+          <t>-0.69</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
@@ -7765,17 +7765,17 @@
       <c r="CF8" t="inlineStr"/>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>86</t>
+          <t>54</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
         <is>
-          <t>8515</t>
+          <t>7053</t>
         </is>
       </c>
       <c r="CI8" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>83.33</t>
         </is>
       </c>
       <c r="CJ8" t="inlineStr">
@@ -7784,19 +7784,19 @@
         </is>
       </c>
       <c r="CK8" t="n">
-        <v>0.28</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="CL8" t="n">
-        <v>3.37</v>
+        <v>3.02</v>
       </c>
       <c r="CM8" t="inlineStr">
         <is>
-          <t>1.21</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="CN8" t="inlineStr">
         <is>
-          <t>-0.73</t>
+          <t>-0.63</t>
         </is>
       </c>
       <c r="CO8" t="inlineStr">
@@ -7806,69 +7806,69 @@
       </c>
       <c r="CP8" t="inlineStr">
         <is>
-          <t>143.5</t>
+          <t>144.05</t>
         </is>
       </c>
       <c r="CQ8" t="inlineStr">
         <is>
-          <t>140.38</t>
+          <t>140.85</t>
         </is>
       </c>
       <c r="CR8" t="inlineStr">
         <is>
-          <t>138.69</t>
+          <t>138.87</t>
         </is>
       </c>
       <c r="CS8" t="inlineStr">
         <is>
-          <t>139.71</t>
+          <t>139.75</t>
         </is>
       </c>
       <c r="CT8" t="inlineStr">
         <is>
-          <t>135.7270833333333</t>
+          <t>0</t>
         </is>
       </c>
       <c r="CU8" t="inlineStr">
         <is>
-          <t>0.002764340013821753</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="CV8" t="inlineStr">
         <is>
-          <t>0.004198740377886701</t>
+          <t>0.003832752613240453</t>
         </is>
       </c>
       <c r="CW8" t="inlineStr">
         <is>
-          <t>0.003395282344531791</t>
+          <t>0.00338379341050743</t>
         </is>
       </c>
       <c r="CX8" t="inlineStr">
         <is>
-          <t>0.001805836463449895</t>
+          <t>0.001297858533420015</t>
         </is>
       </c>
       <c r="CY8" t="inlineStr">
         <is>
-          <t>0.0004475474400287283</t>
+          <t>0.0002684083385522396</t>
         </is>
       </c>
       <c r="CZ8" t="inlineStr">
         <is>
-          <t>0.0003685220729365835</t>
+          <t>0</t>
         </is>
       </c>
       <c r="DA8" t="inlineStr">
         <is>
-          <t>39.98</t>
+          <t>29.64</t>
         </is>
       </c>
       <c r="DB8" t="n">
         <v>2.14</v>
       </c>
       <c r="DC8" t="n">
-        <v>1.53</v>
+        <v>1.65</v>
       </c>
       <c r="DD8" t="inlineStr">
         <is>
@@ -7877,7 +7877,7 @@
       </c>
       <c r="DE8" t="inlineStr">
         <is>
-          <t>-19.18</t>
+          <t>-12.71</t>
         </is>
       </c>
       <c r="DF8" t="inlineStr">
@@ -7887,48 +7887,48 @@
       </c>
       <c r="DG8" t="inlineStr">
         <is>
-          <t>2218439785.568572</t>
+          <t>2517415638.848781</t>
         </is>
       </c>
       <c r="DH8" t="inlineStr">
         <is>
-          <t>1208391141.0</t>
+          <t>918019598.0</t>
         </is>
       </c>
       <c r="DI8" t="n">
-        <v>1915789923.8</v>
+        <v>1659195852.6</v>
       </c>
       <c r="DJ8" t="inlineStr">
         <is>
-          <t>1981073577.5</t>
+          <t>1973672854.5</t>
         </is>
       </c>
       <c r="DK8" t="inlineStr">
         <is>
-          <t>1491726965.1</t>
+          <t>1482010386.8</t>
         </is>
       </c>
       <c r="DL8" t="n">
-        <v>1845563731.54</v>
+        <v>1806077677.02</v>
       </c>
       <c r="DM8" t="inlineStr">
         <is>
-          <t>2053704109.375</t>
+          <t>2030537576.35</t>
         </is>
       </c>
       <c r="DN8" t="inlineStr">
         <is>
-          <t>83180126.28858632</t>
+          <t>61069185.48652767</t>
         </is>
       </c>
       <c r="DO8" t="inlineStr">
         <is>
-          <t>2120011.575097084</t>
+          <t>-60540988.90541673</t>
         </is>
       </c>
       <c r="DP8" t="inlineStr">
         <is>
-          <t>1208391141.0</t>
+          <t>918019598.0</t>
         </is>
       </c>
       <c r="DQ8" t="inlineStr">
@@ -7948,7 +7948,7 @@
       </c>
       <c r="DT8" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>1.05</t>
         </is>
       </c>
       <c r="DU8" t="inlineStr">
@@ -7993,7 +7993,7 @@
       </c>
       <c r="EC8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="ED8" t="inlineStr">
@@ -8003,7 +8003,7 @@
       </c>
       <c r="EE8" t="inlineStr">
         <is>
-          <t>3.08</t>
+          <t>3.07</t>
         </is>
       </c>
       <c r="EF8" t="inlineStr">
@@ -8033,7 +8033,7 @@
       </c>
       <c r="EK8" t="inlineStr">
         <is>
-          <t>85.28</t>
+          <t>84.97</t>
         </is>
       </c>
       <c r="EL8" t="inlineStr">
@@ -8058,27 +8058,27 @@
       </c>
       <c r="EP8" t="inlineStr">
         <is>
+          <t>145.5</t>
+        </is>
+      </c>
+      <c r="EQ8" t="inlineStr">
+        <is>
+          <t>146.0</t>
+        </is>
+      </c>
+      <c r="ER8" t="inlineStr">
+        <is>
           <t>145.0</t>
         </is>
       </c>
-      <c r="EQ8" t="inlineStr">
-        <is>
-          <t>145.5</t>
-        </is>
-      </c>
-      <c r="ER8" t="inlineStr">
-        <is>
-          <t>144.5</t>
-        </is>
-      </c>
       <c r="ES8" t="inlineStr">
         <is>
-          <t>145.5</t>
+          <t>145.0</t>
         </is>
       </c>
       <c r="ET8" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>129.5</t>
         </is>
       </c>
       <c r="EU8" t="inlineStr">
@@ -8098,67 +8098,67 @@
       </c>
       <c r="EX8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="EY8" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>5</t>
         </is>
       </c>
       <c r="EZ8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FA8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FB8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FC8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FD8" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="FE8" t="inlineStr">
         <is>
-          <t>15.0</t>
+          <t>14</t>
         </is>
       </c>
       <c r="FF8" t="inlineStr">
         <is>
-          <t>1.284276525544721</t>
+          <t>1.119557506059444</t>
         </is>
       </c>
       <c r="FG8" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>4</t>
         </is>
       </c>
       <c r="FH8" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>4</t>
         </is>
       </c>
       <c r="FI8" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="FJ8" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FK8" t="inlineStr">
@@ -8350,7 +8350,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>5469.034</t>
+          <t>8326.189</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -8360,7 +8360,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>145.0</t>
+          <t>145.5</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -8370,7 +8370,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0.34</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -8380,7 +8380,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>0.05100096628122345</t>
+          <t>-0.03295367443261963</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -8425,7 +8425,7 @@
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>30.0</t>
+          <t>30</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
@@ -8440,47 +8440,47 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>139.9</t>
+          <t>140.375</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>147.0347924397219</t>
+          <t>147.6794687115415</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>132.7652075602781</t>
+          <t>133.0705312884585</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>0.1019984623262607</t>
+          <t>0.104070791972096</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>0.003047141064707048</t>
+          <t>0.003395282344531791</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>0.004760596003287043</t>
+          <t>0.004384515128182942</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>0.03642388578015843</t>
+          <t>0.02031726359982433</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>0.04785629426595885</t>
+          <t>0.05137843623728422</t>
         </is>
       </c>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>2.179114382212529</t>
+          <t>2.079004612848601</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
@@ -8500,7 +8500,7 @@
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
@@ -8525,24 +8525,24 @@
       </c>
       <c r="AM9" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AN9" t="inlineStr">
+        <is>
           <t>7.0</t>
         </is>
       </c>
-      <c r="AN9" t="inlineStr">
+      <c r="AO9" t="inlineStr">
         <is>
           <t>7.0</t>
         </is>
       </c>
-      <c r="AO9" t="inlineStr">
+      <c r="AP9" t="inlineStr">
         <is>
           <t>8.0</t>
         </is>
       </c>
-      <c r="AP9" t="inlineStr">
-        <is>
-          <t>7.0</t>
-        </is>
-      </c>
       <c r="AQ9" t="inlineStr">
         <is>
           <t>False</t>
@@ -8590,17 +8590,17 @@
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>13.0</t>
+          <t>14.0</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>13.0</t>
+          <t>14.0</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>13.0</t>
+          <t>14.0</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
@@ -8620,32 +8620,32 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>15010110.0</t>
+          <t>18108850.0</t>
         </is>
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>1050416.0</t>
+          <t>1199596.0</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>4036399.0</t>
+          <t>4011399.0</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
         <is>
-          <t>-2985983.0</t>
+          <t>-2811803.0</t>
         </is>
       </c>
       <c r="BJ9" t="inlineStr">
         <is>
-          <t>-213000.0</t>
+          <t>-248002.0</t>
         </is>
       </c>
       <c r="BK9" t="inlineStr">
         <is>
-          <t>11811127.0</t>
+          <t>15049045.0</t>
         </is>
       </c>
       <c r="BL9" t="inlineStr">
@@ -8655,12 +8655,12 @@
       </c>
       <c r="BM9" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="BN9" t="inlineStr">
         <is>
-          <t>-2.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="BO9" t="inlineStr">
@@ -8680,7 +8680,7 @@
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>-0.09</t>
+          <t>-0.07</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
@@ -8730,17 +8730,17 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="CC9" t="inlineStr">
         <is>
-          <t>9.13</t>
+          <t>13.90</t>
         </is>
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>1.40</t>
+          <t>0.69</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
@@ -8751,110 +8751,110 @@
       <c r="CF9" t="inlineStr"/>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>86</t>
+          <t>54</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
         <is>
-          <t>8515</t>
+          <t>7053</t>
         </is>
       </c>
       <c r="CI9" t="inlineStr">
         <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="CJ9" t="inlineStr">
+        <is>
           <t>91.67</t>
         </is>
       </c>
-      <c r="CJ9" t="inlineStr">
-        <is>
-          <t>91.67</t>
-        </is>
-      </c>
       <c r="CK9" t="n">
-        <v>0.21</v>
+        <v>0.28</v>
       </c>
       <c r="CL9" t="n">
-        <v>3.43</v>
+        <v>3.37</v>
       </c>
       <c r="CM9" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>1.21</t>
         </is>
       </c>
       <c r="CN9" t="inlineStr">
         <is>
-          <t>-0.87</t>
+          <t>-0.73</t>
         </is>
       </c>
       <c r="CO9" t="inlineStr">
         <is>
-          <t>144.7</t>
+          <t>145.1</t>
         </is>
       </c>
       <c r="CP9" t="inlineStr">
         <is>
-          <t>142.9</t>
+          <t>143.5</t>
         </is>
       </c>
       <c r="CQ9" t="inlineStr">
         <is>
-          <t>139.9</t>
+          <t>140.38</t>
         </is>
       </c>
       <c r="CR9" t="inlineStr">
         <is>
-          <t>138.44</t>
+          <t>138.69</t>
         </is>
       </c>
       <c r="CS9" t="inlineStr">
         <is>
-          <t>139.65</t>
+          <t>139.71</t>
         </is>
       </c>
       <c r="CT9" t="inlineStr">
         <is>
-          <t>135.6770833333333</t>
+          <t>0</t>
         </is>
       </c>
       <c r="CU9" t="inlineStr">
         <is>
-          <t>0.00207756232686962</t>
+          <t>0.002764340013821753</t>
         </is>
       </c>
       <c r="CV9" t="inlineStr">
         <is>
-          <t>0.004216444132115305</t>
+          <t>0.004198740377886701</t>
         </is>
       </c>
       <c r="CW9" t="inlineStr">
         <is>
-          <t>0.003047141064707048</t>
+          <t>0.003395282344531791</t>
         </is>
       </c>
       <c r="CX9" t="inlineStr">
         <is>
-          <t>0.001736613603473325</t>
+          <t>0.001805836463449895</t>
         </is>
       </c>
       <c r="CY9" t="inlineStr">
         <is>
-          <t>0.0007165890361877647</t>
+          <t>0.0004475474400287283</t>
         </is>
       </c>
       <c r="CZ9" t="inlineStr">
         <is>
-          <t>0.0003225608257557688</t>
+          <t>0</t>
         </is>
       </c>
       <c r="DA9" t="inlineStr">
         <is>
-          <t>49.52</t>
+          <t>39.98</t>
         </is>
       </c>
       <c r="DB9" t="n">
-        <v>2.06</v>
+        <v>2.14</v>
       </c>
       <c r="DC9" t="n">
-        <v>1.38</v>
+        <v>1.53</v>
       </c>
       <c r="DD9" t="inlineStr">
         <is>
@@ -8863,7 +8863,7 @@
       </c>
       <c r="DE9" t="inlineStr">
         <is>
-          <t>-27.26</t>
+          <t>-19.18</t>
         </is>
       </c>
       <c r="DF9" t="inlineStr">
@@ -8873,48 +8873,48 @@
       </c>
       <c r="DG9" t="inlineStr">
         <is>
-          <t>2218439785.568572</t>
+          <t>2517415638.848781</t>
         </is>
       </c>
       <c r="DH9" t="inlineStr">
         <is>
-          <t>789765672.0</t>
+          <t>1208391141.0</t>
         </is>
       </c>
       <c r="DI9" t="n">
-        <v>2098161079.8</v>
+        <v>1915789923.8</v>
       </c>
       <c r="DJ9" t="inlineStr">
         <is>
-          <t>1996345528.8</t>
+          <t>1981073577.5</t>
         </is>
       </c>
       <c r="DK9" t="inlineStr">
         <is>
-          <t>1491758387.733333</t>
+          <t>1491726965.1</t>
         </is>
       </c>
       <c r="DL9" t="n">
-        <v>1849876216.36</v>
+        <v>1845563731.54</v>
       </c>
       <c r="DM9" t="inlineStr">
         <is>
-          <t>2086692476.8625</t>
+          <t>2053704109.375</t>
         </is>
       </c>
       <c r="DN9" t="inlineStr">
         <is>
-          <t>97918328.96376617</t>
+          <t>83180126.28506301</t>
         </is>
       </c>
       <c r="DO9" t="inlineStr">
         <is>
-          <t>60448775.09720325</t>
+          <t>2120011.574340582</t>
         </is>
       </c>
       <c r="DP9" t="inlineStr">
         <is>
-          <t>789765672.0</t>
+          <t>1208391141.0</t>
         </is>
       </c>
       <c r="DQ9" t="inlineStr">
@@ -8934,7 +8934,7 @@
       </c>
       <c r="DT9" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="DU9" t="inlineStr">
@@ -8979,7 +8979,7 @@
       </c>
       <c r="EC9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
         </is>
       </c>
       <c r="ED9" t="inlineStr">
@@ -8989,7 +8989,7 @@
       </c>
       <c r="EE9" t="inlineStr">
         <is>
-          <t>3.07</t>
+          <t>3.08</t>
         </is>
       </c>
       <c r="EF9" t="inlineStr">
@@ -9019,7 +9019,7 @@
       </c>
       <c r="EK9" t="inlineStr">
         <is>
-          <t>85.28</t>
+          <t>84.97</t>
         </is>
       </c>
       <c r="EL9" t="inlineStr">
@@ -9049,22 +9049,22 @@
       </c>
       <c r="EQ9" t="inlineStr">
         <is>
-          <t>145.0</t>
+          <t>145.5</t>
         </is>
       </c>
       <c r="ER9" t="inlineStr">
         <is>
-          <t>143.0</t>
+          <t>144.5</t>
         </is>
       </c>
       <c r="ES9" t="inlineStr">
         <is>
-          <t>145.0</t>
+          <t>145.5</t>
         </is>
       </c>
       <c r="ET9" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>129.5</t>
         </is>
       </c>
       <c r="EU9" t="inlineStr">
@@ -9084,67 +9084,67 @@
       </c>
       <c r="EX9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="EY9" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>5</t>
         </is>
       </c>
       <c r="EZ9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FA9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FB9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FC9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FD9" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="FE9" t="inlineStr">
         <is>
-          <t>15.0</t>
+          <t>15</t>
         </is>
       </c>
       <c r="FF9" t="inlineStr">
         <is>
-          <t>1.406501949010705</t>
+          <t>1.284276525544721</t>
         </is>
       </c>
       <c r="FG9" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>4</t>
         </is>
       </c>
       <c r="FH9" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>4</t>
         </is>
       </c>
       <c r="FI9" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="FJ9" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="FK9" t="inlineStr">
@@ -9331,12 +9331,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-0.69</t>
+          <t>0.34</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>9034.372</t>
+          <t>5469.034</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -9346,7 +9346,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>144.5</t>
+          <t>145.0</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -9356,7 +9356,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>0.69</t>
+          <t>0.34</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -9366,7 +9366,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>0.17008176547467793</t>
+          <t>0.05100096628122345</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -9411,7 +9411,7 @@
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>30.0</t>
+          <t>30</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
@@ -9426,47 +9426,47 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>139.475</t>
+          <t>139.9</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>146.3381356958</t>
+          <t>147.0347924397203</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>132.6118643041999</t>
+          <t>132.7652075602797</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>0.09841384758272169</t>
+          <t>0.1019984623262371</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>0.002876145964407772</t>
+          <t>0.003047141064707048</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>0.004858204025057988</t>
+          <t>0.004760596003286599</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>0.04390431594303013</t>
+          <t>0.03642388578015932</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>0.04785629426595885</t>
+          <t>0.05137843623728422</t>
         </is>
       </c>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>2.238719767299949</t>
+          <t>2.179114382213557</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
@@ -9486,7 +9486,7 @@
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>60.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
@@ -9511,24 +9511,24 @@
       </c>
       <c r="AM10" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AN10" t="inlineStr">
+        <is>
           <t>7.0</t>
         </is>
       </c>
-      <c r="AN10" t="inlineStr">
+      <c r="AO10" t="inlineStr">
         <is>
           <t>8.0</t>
         </is>
       </c>
-      <c r="AO10" t="inlineStr">
+      <c r="AP10" t="inlineStr">
         <is>
           <t>7.0</t>
         </is>
       </c>
-      <c r="AP10" t="inlineStr">
-        <is>
-          <t>7.0</t>
-        </is>
-      </c>
       <c r="AQ10" t="inlineStr">
         <is>
           <t>False</t>
@@ -9546,109 +9546,109 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AU10" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="AV10" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>10.0</t>
+        </is>
+      </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>13.0</t>
+        </is>
+      </c>
+      <c r="BA10" t="inlineStr">
+        <is>
+          <t>13.0</t>
+        </is>
+      </c>
+      <c r="BB10" t="inlineStr">
+        <is>
+          <t>13.0</t>
+        </is>
+      </c>
+      <c r="BC10" t="inlineStr">
+        <is>
+          <t>強勢</t>
+        </is>
+      </c>
+      <c r="BD10" t="inlineStr">
+        <is>
+          <t>強勢</t>
+        </is>
+      </c>
+      <c r="BE10" t="inlineStr">
+        <is>
+          <t>58.3</t>
+        </is>
+      </c>
+      <c r="BF10" t="inlineStr">
+        <is>
+          <t>18108850.0</t>
+        </is>
+      </c>
+      <c r="BG10" t="inlineStr">
+        <is>
+          <t>1199596.0</t>
+        </is>
+      </c>
+      <c r="BH10" t="inlineStr">
+        <is>
+          <t>4011399.0</t>
+        </is>
+      </c>
+      <c r="BI10" t="inlineStr">
+        <is>
+          <t>-2811803.0</t>
+        </is>
+      </c>
+      <c r="BJ10" t="inlineStr">
+        <is>
+          <t>-248002.0</t>
+        </is>
+      </c>
+      <c r="BK10" t="inlineStr">
+        <is>
+          <t>15049045.0</t>
+        </is>
+      </c>
+      <c r="BL10" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="BM10" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="BN10" t="inlineStr">
+        <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="AU10" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="AV10" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="AW10" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
-      </c>
-      <c r="AX10" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
-      </c>
-      <c r="AY10" t="inlineStr">
-        <is>
-          <t>10.0</t>
-        </is>
-      </c>
-      <c r="AZ10" t="inlineStr">
-        <is>
-          <t>12.0</t>
-        </is>
-      </c>
-      <c r="BA10" t="inlineStr">
-        <is>
-          <t>12.0</t>
-        </is>
-      </c>
-      <c r="BB10" t="inlineStr">
-        <is>
-          <t>12.0</t>
-        </is>
-      </c>
-      <c r="BC10" t="inlineStr">
-        <is>
-          <t>強勢</t>
-        </is>
-      </c>
-      <c r="BD10" t="inlineStr">
-        <is>
-          <t>強勢</t>
-        </is>
-      </c>
-      <c r="BE10" t="inlineStr">
-        <is>
-          <t>58.3</t>
-        </is>
-      </c>
-      <c r="BF10" t="inlineStr">
-        <is>
-          <t>15010110.0</t>
-        </is>
-      </c>
-      <c r="BG10" t="inlineStr">
-        <is>
-          <t>1050416.0</t>
-        </is>
-      </c>
-      <c r="BH10" t="inlineStr">
-        <is>
-          <t>4036399.0</t>
-        </is>
-      </c>
-      <c r="BI10" t="inlineStr">
-        <is>
-          <t>-2985983.0</t>
-        </is>
-      </c>
-      <c r="BJ10" t="inlineStr">
-        <is>
-          <t>-213000.0</t>
-        </is>
-      </c>
-      <c r="BK10" t="inlineStr">
-        <is>
-          <t>11811127.0</t>
-        </is>
-      </c>
-      <c r="BL10" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
-      </c>
-      <c r="BM10" t="inlineStr">
-        <is>
-          <t>4.0</t>
-        </is>
-      </c>
-      <c r="BN10" t="inlineStr">
-        <is>
-          <t>-2.0</t>
-        </is>
-      </c>
       <c r="BO10" t="inlineStr">
         <is>
           <t>False</t>
@@ -9666,7 +9666,7 @@
       </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>-0.11</t>
+          <t>-0.09</t>
         </is>
       </c>
       <c r="BS10" t="inlineStr">
@@ -9716,17 +9716,17 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="CC10" t="inlineStr">
         <is>
-          <t>15.08</t>
+          <t>9.13</t>
         </is>
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>0.70</t>
+          <t>1.40</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
@@ -9737,110 +9737,110 @@
       <c r="CF10" t="inlineStr"/>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>86</t>
+          <t>54</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
         <is>
-          <t>8515</t>
+          <t>7053</t>
         </is>
       </c>
       <c r="CI10" t="inlineStr">
         <is>
-          <t>83.33</t>
+          <t>91.67</t>
         </is>
       </c>
       <c r="CJ10" t="inlineStr">
         <is>
-          <t>94.44</t>
+          <t>91.67</t>
         </is>
       </c>
       <c r="CK10" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.21</v>
       </c>
       <c r="CL10" t="n">
-        <v>3.53</v>
+        <v>3.43</v>
       </c>
       <c r="CM10" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>1.05</t>
         </is>
       </c>
       <c r="CN10" t="inlineStr">
         <is>
-          <t>-0.97</t>
+          <t>-0.87</t>
         </is>
       </c>
       <c r="CO10" t="inlineStr">
         <is>
-          <t>144.4</t>
+          <t>144.7</t>
         </is>
       </c>
       <c r="CP10" t="inlineStr">
         <is>
-          <t>142.3</t>
+          <t>142.9</t>
         </is>
       </c>
       <c r="CQ10" t="inlineStr">
         <is>
-          <t>139.48</t>
+          <t>139.9</t>
         </is>
       </c>
       <c r="CR10" t="inlineStr">
         <is>
-          <t>138.2</t>
+          <t>138.44</t>
         </is>
       </c>
       <c r="CS10" t="inlineStr">
         <is>
-          <t>139.55</t>
+          <t>139.65</t>
         </is>
       </c>
       <c r="CT10" t="inlineStr">
         <is>
-          <t>135.6333333333333</t>
+          <t>0</t>
         </is>
       </c>
       <c r="CU10" t="inlineStr">
         <is>
-          <t>0.002777777777777768</t>
+          <t>0.00207756232686962</t>
         </is>
       </c>
       <c r="CV10" t="inlineStr">
         <is>
-          <t>0.004588775150017765</t>
+          <t>0.004216444132115305</t>
         </is>
       </c>
       <c r="CW10" t="inlineStr">
         <is>
-          <t>0.002876145964407772</t>
+          <t>0.003047141064707048</t>
         </is>
       </c>
       <c r="CX10" t="inlineStr">
         <is>
-          <t>0.001594433975938614</t>
+          <t>0.001736613603473325</t>
         </is>
       </c>
       <c r="CY10" t="inlineStr">
         <is>
-          <t>0.0007171029042669641</t>
+          <t>0.0007165890361877647</t>
         </is>
       </c>
       <c r="CZ10" t="inlineStr">
         <is>
-          <t>0.0003380350941888377</t>
+          <t>0</t>
         </is>
       </c>
       <c r="DA10" t="inlineStr">
         <is>
-          <t>63.63</t>
+          <t>49.52</t>
         </is>
       </c>
       <c r="DB10" t="n">
-        <v>1.98</v>
+        <v>2.06</v>
       </c>
       <c r="DC10" t="n">
-        <v>1.21</v>
+        <v>1.38</v>
       </c>
       <c r="DD10" t="inlineStr">
         <is>
@@ -9849,7 +9849,7 @@
       </c>
       <c r="DE10" t="inlineStr">
         <is>
-          <t>-36.26</t>
+          <t>-27.26</t>
         </is>
       </c>
       <c r="DF10" t="inlineStr">
@@ -9859,48 +9859,48 @@
       </c>
       <c r="DG10" t="inlineStr">
         <is>
-          <t>2218439785.568572</t>
+          <t>2517415638.848781</t>
         </is>
       </c>
       <c r="DH10" t="inlineStr">
         <is>
-          <t>1300476742.0</t>
+          <t>789765672.0</t>
         </is>
       </c>
       <c r="DI10" t="n">
-        <v>2424566350.6</v>
+        <v>2098161079.8</v>
       </c>
       <c r="DJ10" t="inlineStr">
         <is>
-          <t>2072134121.0</t>
+          <t>1996345528.8</t>
         </is>
       </c>
       <c r="DK10" t="inlineStr">
         <is>
-          <t>1501977696.5</t>
+          <t>1491758387.733333</t>
         </is>
       </c>
       <c r="DL10" t="n">
-        <v>1909506330.54</v>
+        <v>1849876216.36</v>
       </c>
       <c r="DM10" t="inlineStr">
         <is>
-          <t>2125272163.8375</t>
+          <t>2086692476.8625</t>
         </is>
       </c>
       <c r="DN10" t="inlineStr">
         <is>
-          <t>104730975.1213231</t>
+          <t>97918328.95973982</t>
         </is>
       </c>
       <c r="DO10" t="inlineStr">
         <is>
-          <t>186469424.1253116</t>
+          <t>60448775.09633851</t>
         </is>
       </c>
       <c r="DP10" t="inlineStr">
         <is>
-          <t>1300476742.0</t>
+          <t>789765672.0</t>
         </is>
       </c>
       <c r="DQ10" t="inlineStr">
@@ -9920,7 +9920,7 @@
       </c>
       <c r="DT10" t="inlineStr">
         <is>
-          <t>0.70</t>
+          <t>1.05</t>
         </is>
       </c>
       <c r="DU10" t="inlineStr">
@@ -9965,7 +9965,7 @@
       </c>
       <c r="EC10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="ED10" t="inlineStr">
@@ -9975,7 +9975,7 @@
       </c>
       <c r="EE10" t="inlineStr">
         <is>
-          <t>3.06</t>
+          <t>3.07</t>
         </is>
       </c>
       <c r="EF10" t="inlineStr">
@@ -10005,7 +10005,7 @@
       </c>
       <c r="EK10" t="inlineStr">
         <is>
-          <t>85.28</t>
+          <t>84.97</t>
         </is>
       </c>
       <c r="EL10" t="inlineStr">
@@ -10045,12 +10045,12 @@
       </c>
       <c r="ES10" t="inlineStr">
         <is>
-          <t>144.5</t>
+          <t>145.0</t>
         </is>
       </c>
       <c r="ET10" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>129.5</t>
         </is>
       </c>
       <c r="EU10" t="inlineStr">
@@ -10070,67 +10070,67 @@
       </c>
       <c r="EX10" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="EY10" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>5</t>
         </is>
       </c>
       <c r="EZ10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FA10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FB10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FC10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FD10" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="FE10" t="inlineStr">
         <is>
-          <t>15.0</t>
+          <t>15</t>
         </is>
       </c>
       <c r="FF10" t="inlineStr">
         <is>
-          <t>1.614249237022542</t>
+          <t>1.406501949010705</t>
         </is>
       </c>
       <c r="FG10" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="FH10" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="FI10" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="FJ10" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="FK10" t="inlineStr">

--- a/Result/checksun_type/電信.xlsx
+++ b/Result/checksun_type/電信.xlsx
@@ -1433,7 +1433,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>【b1】</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1448,7 +1448,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>7052.714</t>
+          <t>7080.591</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -1478,7 +1478,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>0.04819550174243172</t>
+          <t>-0.010140903336412965</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -1523,7 +1523,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>60.0</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -1538,47 +1538,47 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>143.325</t>
+          <t>143.7</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>148.4781799073856</t>
+          <t>148.2814270357867</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>138.1718200926144</t>
+          <t>139.1185729642133</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>0.07190901667379143</t>
+          <t>0.0637637722447697</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>0.002798670631450006</t>
+          <t>0.002616431187859813</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-0.0007149631119904853</t>
+          <t>-0.001325129872452147</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>-0.09199085545746999</t>
+          <t>-0.1132715312464632</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>0.05137843623728422</t>
+          <t>0.0479762948677207</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>0.9852782093293254</t>
+          <t>0.8505447270309883</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
@@ -1623,24 +1623,24 @@
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
+          <t>4.0</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
           <t>2.0</t>
         </is>
       </c>
-      <c r="AO2" t="inlineStr">
+      <c r="AP2" t="inlineStr">
         <is>
           <t>3.0</t>
         </is>
       </c>
-      <c r="AP2" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
-      </c>
       <c r="AQ2" t="inlineStr">
         <is>
           <t>False</t>
@@ -1678,7 +1678,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -1693,12 +1693,12 @@
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>18.0</t>
+          <t>19.0</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>18.0</t>
+          <t>19.0</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
@@ -1718,32 +1718,32 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>18108850.0</t>
+          <t>17850578.0</t>
         </is>
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>1199596.0</t>
+          <t>1360796.0</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>4011399.0</t>
+          <t>4418171.0</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
         <is>
-          <t>-2811803.0</t>
+          <t>-3057375.0</t>
         </is>
       </c>
       <c r="BJ2" t="inlineStr">
         <is>
-          <t>-248002.0</t>
+          <t>-284018.0</t>
         </is>
       </c>
       <c r="BK2" t="inlineStr">
         <is>
-          <t>15049045.0</t>
+          <t>14509185.0</t>
         </is>
       </c>
       <c r="BL2" t="inlineStr">
@@ -1758,7 +1758,7 @@
       </c>
       <c r="BN2" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="BO2" t="inlineStr">
@@ -1803,24 +1803,24 @@
       </c>
       <c r="BW2" t="inlineStr">
         <is>
+          <t>2026/10/07</t>
+        </is>
+      </c>
+      <c r="BX2" t="inlineStr">
+        <is>
+          <t>145.5</t>
+        </is>
+      </c>
+      <c r="BY2" t="inlineStr">
+        <is>
           <t>2026/08/05</t>
         </is>
       </c>
-      <c r="BX2" t="inlineStr">
+      <c r="BZ2" t="inlineStr">
         <is>
           <t>137.0</t>
         </is>
       </c>
-      <c r="BY2" t="inlineStr">
-        <is>
-          <t>2026/06/24</t>
-        </is>
-      </c>
-      <c r="BZ2" t="inlineStr">
-        <is>
-          <t>143.5</t>
-        </is>
-      </c>
       <c r="CA2" t="inlineStr">
         <is>
           <t>2026-09-18 00:00:00</t>
@@ -1828,12 +1828,12 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="CC2" t="inlineStr">
         <is>
-          <t>11.77</t>
+          <t>11.82</t>
         </is>
       </c>
       <c r="CD2" t="inlineStr">
@@ -1849,12 +1849,12 @@
       <c r="CF2" t="inlineStr"/>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>50</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
         <is>
-          <t>7053</t>
+          <t>7081</t>
         </is>
       </c>
       <c r="CI2" t="inlineStr">
@@ -1864,92 +1864,92 @@
       </c>
       <c r="CJ2" t="inlineStr">
         <is>
-          <t>86.67</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="CK2" t="n">
-        <v>0.21</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="CL2" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="CM2" t="inlineStr">
         <is>
-          <t>2.64</t>
+          <t>2.83</t>
         </is>
       </c>
       <c r="CN2" t="inlineStr">
         <is>
-          <t>-0.27</t>
+          <t>-0.21</t>
         </is>
       </c>
       <c r="CO2" t="inlineStr">
         <is>
-          <t>145.2</t>
+          <t>145.6</t>
         </is>
       </c>
       <c r="CP2" t="inlineStr">
         <is>
-          <t>145.0</t>
+          <t>145.1</t>
         </is>
       </c>
       <c r="CQ2" t="inlineStr">
         <is>
-          <t>143.32</t>
+          <t>143.7</t>
         </is>
       </c>
       <c r="CR2" t="inlineStr">
         <is>
-          <t>139.64</t>
+          <t>139.74</t>
         </is>
       </c>
       <c r="CS2" t="inlineStr">
         <is>
-          <t>140.02</t>
+          <t>140.03</t>
         </is>
       </c>
       <c r="CT2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>136.1125</t>
         </is>
       </c>
       <c r="CU2" t="inlineStr">
         <is>
-          <t>0.00207039337474102</t>
+          <t>0.002754820936639257</t>
         </is>
       </c>
       <c r="CV2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.0006896551724138167</t>
         </is>
       </c>
       <c r="CW2" t="inlineStr">
         <is>
-          <t>0.002798670631450006</t>
+          <t>0.002616431187859813</t>
         </is>
       </c>
       <c r="CX2" t="inlineStr">
         <is>
-          <t>0.0009318328435237166</t>
+          <t>0.000716127184188009</t>
         </is>
       </c>
       <c r="CY2" t="inlineStr">
         <is>
-          <t>0.0001339225927414756</t>
+          <t>4.463488662742598e-05</t>
         </is>
       </c>
       <c r="CZ2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0003827956330675342</t>
         </is>
       </c>
       <c r="DA2" t="inlineStr">
         <is>
-          <t>1.30</t>
+          <t>-1.50</t>
         </is>
       </c>
       <c r="DB2" t="n">
-        <v>1.88</v>
+        <v>1.82</v>
       </c>
       <c r="DC2" t="n">
         <v>1.85</v>
@@ -1961,7 +1961,7 @@
       </c>
       <c r="DE2" t="inlineStr">
         <is>
-          <t>-2.18</t>
+          <t>-2.54</t>
         </is>
       </c>
       <c r="DF2" t="inlineStr">
@@ -1971,48 +1971,48 @@
       </c>
       <c r="DG2" t="inlineStr">
         <is>
-          <t>2517415638.848781</t>
+          <t>2214561876.963068</t>
         </is>
       </c>
       <c r="DH2" t="inlineStr">
         <is>
-          <t>1019972816.0</t>
+          <t>1027931012.0</t>
         </is>
       </c>
       <c r="DI2" t="n">
-        <v>1298042299.8</v>
+        <v>1198822702.4</v>
       </c>
       <c r="DJ2" t="inlineStr">
         <is>
-          <t>1238358968.0</t>
+          <t>1211104395.0</t>
         </is>
       </c>
       <c r="DK2" t="inlineStr">
         <is>
-          <t>1512402699.433333</t>
+          <t>1514483902.3</t>
         </is>
       </c>
       <c r="DL2" t="n">
-        <v>1630284122.58</v>
+        <v>1587854042.56</v>
       </c>
       <c r="DM2" t="inlineStr">
         <is>
-          <t>1973713221.6375</t>
+          <t>1954971026.825</t>
         </is>
       </c>
       <c r="DN2" t="inlineStr">
         <is>
-          <t>-21930809.76943394</t>
+          <t>-35595349.43602777</t>
         </is>
       </c>
       <c r="DO2" t="inlineStr">
         <is>
-          <t>-97535680.67310739</t>
+          <t>-110750317.6099069</t>
         </is>
       </c>
       <c r="DP2" t="inlineStr">
         <is>
-          <t>1019972816.0</t>
+          <t>1027931012.0</t>
         </is>
       </c>
       <c r="DQ2" t="inlineStr">
@@ -2117,7 +2117,7 @@
       </c>
       <c r="EK2" t="inlineStr">
         <is>
-          <t>84.97</t>
+          <t>85.4</t>
         </is>
       </c>
       <c r="EL2" t="inlineStr">
@@ -2162,7 +2162,7 @@
       </c>
       <c r="ET2" t="inlineStr">
         <is>
-          <t>129.5</t>
+          <t>128.0</t>
         </is>
       </c>
       <c r="EU2" t="inlineStr">
@@ -2182,42 +2182,42 @@
       </c>
       <c r="EX2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="EY2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="EZ2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FA2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FB2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FC2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FD2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="FE2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FF2" t="inlineStr">
@@ -2227,22 +2227,22 @@
       </c>
       <c r="FG2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="FH2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FI2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FJ2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FK2" t="inlineStr">
@@ -2429,12 +2429,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>8515.486</t>
+          <t>7052.714</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-0.07440392378152937</t>
+          <t>0.04819550174243172</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -2509,7 +2509,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>60.0</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -2524,47 +2524,47 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>142.925</t>
+          <t>143.325</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>148.5844122811834</t>
+          <t>148.4781799073893</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>137.2655877188166</t>
+          <t>138.1718200926107</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>0.07919415471307878</t>
+          <t>0.07190901667384339</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>0.002630655910206947</t>
+          <t>0.002798670631450006</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>0.0007131716764898766</t>
+          <t>-0.0007149631119872657</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>-0.04789697107505919</t>
+          <t>-0.09199085545733376</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>0.05137843623728422</t>
+          <t>0.0479762948677207</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>1.123964812126167</t>
+          <t>0.98527820932962</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
@@ -2574,7 +2574,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
@@ -2609,24 +2609,24 @@
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
           <t>3.0</t>
         </is>
       </c>
-      <c r="AO3" t="inlineStr">
+      <c r="AP3" t="inlineStr">
         <is>
           <t>2.0</t>
         </is>
       </c>
-      <c r="AP3" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
-      </c>
       <c r="AQ3" t="inlineStr">
         <is>
           <t>False</t>
@@ -2649,7 +2649,7 @@
       </c>
       <c r="AU3" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AV3" t="inlineStr">
@@ -2664,7 +2664,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -2674,17 +2674,17 @@
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>16.0</t>
+          <t>17.0</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>17.0</t>
+          <t>18.0</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>17.0</t>
+          <t>18.0</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
@@ -2704,32 +2704,32 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>18108850.0</t>
+          <t>17850578.0</t>
         </is>
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>1199596.0</t>
+          <t>1360796.0</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>4011399.0</t>
+          <t>4418171.0</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
         <is>
-          <t>-2811803.0</t>
+          <t>-3057375.0</t>
         </is>
       </c>
       <c r="BJ3" t="inlineStr">
         <is>
-          <t>-248002.0</t>
+          <t>-284018.0</t>
         </is>
       </c>
       <c r="BK3" t="inlineStr">
         <is>
-          <t>15049045.0</t>
+          <t>14509185.0</t>
         </is>
       </c>
       <c r="BL3" t="inlineStr">
@@ -2744,7 +2744,7 @@
       </c>
       <c r="BN3" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="BO3" t="inlineStr">
@@ -2789,24 +2789,24 @@
       </c>
       <c r="BW3" t="inlineStr">
         <is>
+          <t>2026/10/07</t>
+        </is>
+      </c>
+      <c r="BX3" t="inlineStr">
+        <is>
+          <t>145.5</t>
+        </is>
+      </c>
+      <c r="BY3" t="inlineStr">
+        <is>
           <t>2026/08/05</t>
         </is>
       </c>
-      <c r="BX3" t="inlineStr">
+      <c r="BZ3" t="inlineStr">
         <is>
           <t>137.0</t>
         </is>
       </c>
-      <c r="BY3" t="inlineStr">
-        <is>
-          <t>2026/06/24</t>
-        </is>
-      </c>
-      <c r="BZ3" t="inlineStr">
-        <is>
-          <t>143.5</t>
-        </is>
-      </c>
       <c r="CA3" t="inlineStr">
         <is>
           <t>2026-09-18 00:00:00</t>
@@ -2814,17 +2814,17 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="CC3" t="inlineStr">
         <is>
-          <t>14.21</t>
+          <t>11.77</t>
         </is>
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>1.04</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
@@ -2835,12 +2835,12 @@
       <c r="CF3" t="inlineStr"/>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>50</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
         <is>
-          <t>7053</t>
+          <t>7081</t>
         </is>
       </c>
       <c r="CI3" t="inlineStr">
@@ -2850,28 +2850,28 @@
       </c>
       <c r="CJ3" t="inlineStr">
         <is>
-          <t>93.33</t>
+          <t>86.67</t>
         </is>
       </c>
       <c r="CK3" t="n">
-        <v>0.41</v>
+        <v>0.21</v>
       </c>
       <c r="CL3" t="n">
-        <v>1.38</v>
+        <v>1.31</v>
       </c>
       <c r="CM3" t="inlineStr">
         <is>
-          <t>2.45</t>
+          <t>2.64</t>
         </is>
       </c>
       <c r="CN3" t="inlineStr">
         <is>
-          <t>-0.35</t>
+          <t>-0.27</t>
         </is>
       </c>
       <c r="CO3" t="inlineStr">
         <is>
-          <t>144.9</t>
+          <t>145.2</t>
         </is>
       </c>
       <c r="CP3" t="inlineStr">
@@ -2881,61 +2881,61 @@
       </c>
       <c r="CQ3" t="inlineStr">
         <is>
-          <t>142.93</t>
+          <t>143.32</t>
         </is>
       </c>
       <c r="CR3" t="inlineStr">
         <is>
-          <t>139.51</t>
+          <t>139.64</t>
         </is>
       </c>
       <c r="CS3" t="inlineStr">
         <is>
-          <t>140.01</t>
+          <t>140.02</t>
         </is>
       </c>
       <c r="CT3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>136.0604166666667</t>
         </is>
       </c>
       <c r="CU3" t="inlineStr">
         <is>
-          <t>0.0006906077348065587</t>
+          <t>0.00207039337474102</t>
         </is>
       </c>
       <c r="CV3" t="inlineStr">
         <is>
-          <t>0.0003449465332874269</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="CW3" t="inlineStr">
         <is>
-          <t>0.002630655910206947</t>
+          <t>0.002798670631450006</t>
         </is>
       </c>
       <c r="CX3" t="inlineStr">
         <is>
-          <t>0.001076349024110135</t>
+          <t>0.0009318328435237166</t>
         </is>
       </c>
       <c r="CY3" t="inlineStr">
         <is>
-          <t>0.0003125837277841992</t>
+          <t>0.0001339225927414756</t>
         </is>
       </c>
       <c r="CZ3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0003676189017385312</t>
         </is>
       </c>
       <c r="DA3" t="inlineStr">
         <is>
-          <t>4.21</t>
+          <t>1.30</t>
         </is>
       </c>
       <c r="DB3" t="n">
-        <v>1.93</v>
+        <v>1.88</v>
       </c>
       <c r="DC3" t="n">
         <v>1.85</v>
@@ -2947,7 +2947,7 @@
       </c>
       <c r="DE3" t="inlineStr">
         <is>
-          <t>-2.50</t>
+          <t>-2.18</t>
         </is>
       </c>
       <c r="DF3" t="inlineStr">
@@ -2957,48 +2957,48 @@
       </c>
       <c r="DG3" t="inlineStr">
         <is>
-          <t>2517415638.848781</t>
+          <t>2214561876.963068</t>
         </is>
       </c>
       <c r="DH3" t="inlineStr">
         <is>
-          <t>1239700787.0</t>
+          <t>1019972816.0</t>
         </is>
       </c>
       <c r="DI3" t="n">
-        <v>1429392742.2</v>
+        <v>1298042299.8</v>
       </c>
       <c r="DJ3" t="inlineStr">
         <is>
-          <t>1544294297.4</t>
+          <t>1238358968.0</t>
         </is>
       </c>
       <c r="DK3" t="inlineStr">
         <is>
-          <t>1502594940.533333</t>
+          <t>1512402699.433333</t>
         </is>
       </c>
       <c r="DL3" t="n">
-        <v>1654145469.66</v>
+        <v>1630284122.58</v>
       </c>
       <c r="DM3" t="inlineStr">
         <is>
-          <t>1987286590.375</t>
+          <t>1973713221.6375</t>
         </is>
       </c>
       <c r="DN3" t="inlineStr">
         <is>
-          <t>-8184469.605129678</t>
+          <t>-21930809.76804974</t>
         </is>
       </c>
       <c r="DO3" t="inlineStr">
         <is>
-          <t>-74321546.88183999</t>
+          <t>-97535680.67281032</t>
         </is>
       </c>
       <c r="DP3" t="inlineStr">
         <is>
-          <t>1239700787.0</t>
+          <t>1019972816.0</t>
         </is>
       </c>
       <c r="DQ3" t="inlineStr">
@@ -3063,7 +3063,7 @@
       </c>
       <c r="EC3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="ED3" t="inlineStr">
@@ -3103,7 +3103,7 @@
       </c>
       <c r="EK3" t="inlineStr">
         <is>
-          <t>84.97</t>
+          <t>85.4</t>
         </is>
       </c>
       <c r="EL3" t="inlineStr">
@@ -3128,12 +3128,12 @@
       </c>
       <c r="EP3" t="inlineStr">
         <is>
-          <t>147.0</t>
+          <t>145.5</t>
         </is>
       </c>
       <c r="EQ3" t="inlineStr">
         <is>
-          <t>147.0</t>
+          <t>145.5</t>
         </is>
       </c>
       <c r="ER3" t="inlineStr">
@@ -3148,7 +3148,7 @@
       </c>
       <c r="ET3" t="inlineStr">
         <is>
-          <t>129.5</t>
+          <t>128.0</t>
         </is>
       </c>
       <c r="EU3" t="inlineStr">
@@ -3168,42 +3168,42 @@
       </c>
       <c r="EX3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="EY3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="EZ3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FA3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FB3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FC3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FD3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="FE3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FF3" t="inlineStr">
@@ -3213,22 +3213,22 @@
       </c>
       <c r="FG3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="FH3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FI3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FJ3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FK3" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.34</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>10009.961</t>
+          <t>8515.486</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -3430,7 +3430,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>146.0</t>
+          <t>145.5</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -3440,7 +3440,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -3450,7 +3450,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-0.16786321196452753</t>
+          <t>-0.07440392378152937</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -3495,7 +3495,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>60.0</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -3510,47 +3510,47 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>142.55</t>
+          <t>142.925</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>148.4785216050076</t>
+          <t>148.5844122811866</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>136.6214783949924</t>
+          <t>137.2655877188134</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>0.08317813546134833</t>
+          <t>0.07919415471312412</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>0.002990325417766115</t>
+          <t>0.002630655910206947</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>0.001688232507605081</t>
+          <t>0.000713171676491875</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>-0.03152921474358805</t>
+          <t>-0.0478969710749888</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>0.05137843623728422</t>
+          <t>0.0479762948677207</t>
         </is>
       </c>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>1.23096372806679</t>
+          <t>1.123964812126325</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
@@ -3565,7 +3565,7 @@
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>35.0</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
@@ -3595,62 +3595,62 @@
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
+          <t>3.0</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
           <t>2.0</t>
         </is>
       </c>
-      <c r="AO4" t="inlineStr">
+      <c r="AP4" t="inlineStr">
         <is>
           <t>2.0</t>
         </is>
       </c>
-      <c r="AP4" t="inlineStr">
+      <c r="AQ4" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AR4" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AS4" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AU4" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="AV4" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AW4" t="inlineStr">
         <is>
           <t>3.0</t>
         </is>
       </c>
-      <c r="AQ4" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AR4" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AS4" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AT4" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AU4" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="AV4" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AW4" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
-      </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -3665,12 +3665,12 @@
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>16.0</t>
+          <t>17.0</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>16.0</t>
+          <t>17.0</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
@@ -3690,32 +3690,32 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>18108850.0</t>
+          <t>17850578.0</t>
         </is>
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>1199596.0</t>
+          <t>1360796.0</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>4011399.0</t>
+          <t>4418171.0</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
         <is>
-          <t>-2811803.0</t>
+          <t>-3057375.0</t>
         </is>
       </c>
       <c r="BJ4" t="inlineStr">
         <is>
-          <t>-248002.0</t>
+          <t>-284018.0</t>
         </is>
       </c>
       <c r="BK4" t="inlineStr">
         <is>
-          <t>15049045.0</t>
+          <t>14509185.0</t>
         </is>
       </c>
       <c r="BL4" t="inlineStr">
@@ -3730,7 +3730,7 @@
       </c>
       <c r="BN4" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="BO4" t="inlineStr">
@@ -3750,7 +3750,7 @@
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-0.05</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
@@ -3775,24 +3775,24 @@
       </c>
       <c r="BW4" t="inlineStr">
         <is>
+          <t>2026/10/07</t>
+        </is>
+      </c>
+      <c r="BX4" t="inlineStr">
+        <is>
+          <t>145.5</t>
+        </is>
+      </c>
+      <c r="BY4" t="inlineStr">
+        <is>
           <t>2026/08/05</t>
         </is>
       </c>
-      <c r="BX4" t="inlineStr">
+      <c r="BZ4" t="inlineStr">
         <is>
           <t>137.0</t>
         </is>
       </c>
-      <c r="BY4" t="inlineStr">
-        <is>
-          <t>2026/06/24</t>
-        </is>
-      </c>
-      <c r="BZ4" t="inlineStr">
-        <is>
-          <t>143.5</t>
-        </is>
-      </c>
       <c r="CA4" t="inlineStr">
         <is>
           <t>2026-09-18 00:00:00</t>
@@ -3800,17 +3800,17 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="CC4" t="inlineStr">
         <is>
-          <t>16.71</t>
+          <t>14.21</t>
         </is>
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
@@ -3821,177 +3821,177 @@
       <c r="CF4" t="inlineStr"/>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>50</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
         <is>
-          <t>7053</t>
+          <t>7081</t>
         </is>
       </c>
       <c r="CI4" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="CJ4" t="inlineStr">
         <is>
-          <t>66.67</t>
+          <t>93.33</t>
         </is>
       </c>
       <c r="CK4" t="n">
-        <v>0.83</v>
+        <v>0.41</v>
       </c>
       <c r="CL4" t="n">
-        <v>1.58</v>
+        <v>1.38</v>
       </c>
       <c r="CM4" t="inlineStr">
         <is>
-          <t>2.29</t>
+          <t>2.45</t>
         </is>
       </c>
       <c r="CN4" t="inlineStr">
         <is>
-          <t>-0.43</t>
+          <t>-0.35</t>
         </is>
       </c>
       <c r="CO4" t="inlineStr">
         <is>
-          <t>144.8</t>
+          <t>144.9</t>
         </is>
       </c>
       <c r="CP4" t="inlineStr">
         <is>
-          <t>144.95</t>
+          <t>145.0</t>
         </is>
       </c>
       <c r="CQ4" t="inlineStr">
         <is>
-          <t>142.55</t>
+          <t>142.93</t>
         </is>
       </c>
       <c r="CR4" t="inlineStr">
         <is>
-          <t>139.36</t>
+          <t>139.51</t>
         </is>
       </c>
       <c r="CS4" t="inlineStr">
         <is>
-          <t>139.96</t>
+          <t>140.01</t>
         </is>
       </c>
       <c r="CT4" t="inlineStr">
         <is>
+          <t>136.0104166666667</t>
+        </is>
+      </c>
+      <c r="CU4" t="inlineStr">
+        <is>
+          <t>0.0006906077348065587</t>
+        </is>
+      </c>
+      <c r="CV4" t="inlineStr">
+        <is>
+          <t>0.0003449465332874269</t>
+        </is>
+      </c>
+      <c r="CW4" t="inlineStr">
+        <is>
+          <t>0.002630655910206947</t>
+        </is>
+      </c>
+      <c r="CX4" t="inlineStr">
+        <is>
+          <t>0.001076349024110135</t>
+        </is>
+      </c>
+      <c r="CY4" t="inlineStr">
+        <is>
+          <t>0.0003125837277841992</t>
+        </is>
+      </c>
+      <c r="CZ4" t="inlineStr">
+        <is>
+          <t>0.0003830830524056417</t>
+        </is>
+      </c>
+      <c r="DA4" t="inlineStr">
+        <is>
+          <t>4.21</t>
+        </is>
+      </c>
+      <c r="DB4" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="DC4" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="DD4" t="inlineStr">
+        <is>
+          <t>1.9</t>
+        </is>
+      </c>
+      <c r="DE4" t="inlineStr">
+        <is>
+          <t>-2.49</t>
+        </is>
+      </c>
+      <c r="DF4" t="inlineStr">
+        <is>
+          <t>2026/08/21</t>
+        </is>
+      </c>
+      <c r="DG4" t="inlineStr">
+        <is>
+          <t>2214561876.963068</t>
+        </is>
+      </c>
+      <c r="DH4" t="inlineStr">
+        <is>
+          <t>1239700787.0</t>
+        </is>
+      </c>
+      <c r="DI4" t="n">
+        <v>1429392742.2</v>
+      </c>
+      <c r="DJ4" t="inlineStr">
+        <is>
+          <t>1544294297.4</t>
+        </is>
+      </c>
+      <c r="DK4" t="inlineStr">
+        <is>
+          <t>1502594940.533333</t>
+        </is>
+      </c>
+      <c r="DL4" t="n">
+        <v>1654145469.66</v>
+      </c>
+      <c r="DM4" t="inlineStr">
+        <is>
+          <t>1987286590.375</t>
+        </is>
+      </c>
+      <c r="DN4" t="inlineStr">
+        <is>
+          <t>-8184469.60354781</t>
+        </is>
+      </c>
+      <c r="DO4" t="inlineStr">
+        <is>
+          <t>-74321546.88150048</t>
+        </is>
+      </c>
+      <c r="DP4" t="inlineStr">
+        <is>
+          <t>1239700787.0</t>
+        </is>
+      </c>
+      <c r="DQ4" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="CU4" t="inlineStr">
-        <is>
-          <t>0.0006910850034556049</t>
-        </is>
-      </c>
-      <c r="CV4" t="inlineStr">
-        <is>
-          <t>0.001727712508638568</t>
-        </is>
-      </c>
-      <c r="CW4" t="inlineStr">
-        <is>
-          <t>0.002990325417766115</t>
-        </is>
-      </c>
-      <c r="CX4" t="inlineStr">
-        <is>
-          <t>0.001077508799655291</t>
-        </is>
-      </c>
-      <c r="CY4" t="inlineStr">
-        <is>
-          <t>0.0006702712364270447</t>
-        </is>
-      </c>
-      <c r="CZ4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="DA4" t="inlineStr">
-        <is>
-          <t>7.12</t>
-        </is>
-      </c>
-      <c r="DB4" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="DC4" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="DD4" t="inlineStr">
-        <is>
-          <t>1.9</t>
-        </is>
-      </c>
-      <c r="DE4" t="inlineStr">
-        <is>
-          <t>-3.52</t>
-        </is>
-      </c>
-      <c r="DF4" t="inlineStr">
-        <is>
-          <t>2026/08/21</t>
-        </is>
-      </c>
-      <c r="DG4" t="inlineStr">
-        <is>
-          <t>2517415638.848781</t>
-        </is>
-      </c>
-      <c r="DH4" t="inlineStr">
-        <is>
-          <t>1458318100.0</t>
-        </is>
-      </c>
-      <c r="DI4" t="n">
-        <v>1365056504.4</v>
-      </c>
-      <c r="DJ4" t="inlineStr">
-        <is>
-          <t>1640423214.1</t>
-        </is>
-      </c>
-      <c r="DK4" t="inlineStr">
-        <is>
-          <t>1485353753.433333</t>
-        </is>
-      </c>
-      <c r="DL4" t="n">
-        <v>1659414895.68</v>
-      </c>
-      <c r="DM4" t="inlineStr">
-        <is>
-          <t>2004348026.1375</t>
-        </is>
-      </c>
-      <c r="DN4" t="inlineStr">
-        <is>
-          <t>3840453.53609038</t>
-        </is>
-      </c>
-      <c r="DO4" t="inlineStr">
-        <is>
-          <t>-62046440.25567794</t>
-        </is>
-      </c>
-      <c r="DP4" t="inlineStr">
-        <is>
-          <t>1458318100.0</t>
-        </is>
-      </c>
-      <c r="DQ4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="DR4" t="inlineStr">
         <is>
           <t>143.5</t>
@@ -4004,7 +4004,7 @@
       </c>
       <c r="DT4" t="inlineStr">
         <is>
-          <t>1.74</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="DU4" t="inlineStr">
@@ -4059,7 +4059,7 @@
       </c>
       <c r="EE4" t="inlineStr">
         <is>
-          <t>3.09</t>
+          <t>3.08</t>
         </is>
       </c>
       <c r="EF4" t="inlineStr">
@@ -4089,7 +4089,7 @@
       </c>
       <c r="EK4" t="inlineStr">
         <is>
-          <t>84.97</t>
+          <t>85.4</t>
         </is>
       </c>
       <c r="EL4" t="inlineStr">
@@ -4114,12 +4114,12 @@
       </c>
       <c r="EP4" t="inlineStr">
         <is>
-          <t>145.0</t>
+          <t>147.0</t>
         </is>
       </c>
       <c r="EQ4" t="inlineStr">
         <is>
-          <t>146.5</t>
+          <t>147.0</t>
         </is>
       </c>
       <c r="ER4" t="inlineStr">
@@ -4129,12 +4129,12 @@
       </c>
       <c r="ES4" t="inlineStr">
         <is>
-          <t>146.0</t>
+          <t>145.5</t>
         </is>
       </c>
       <c r="ET4" t="inlineStr">
         <is>
-          <t>129.5</t>
+          <t>128.0</t>
         </is>
       </c>
       <c r="EU4" t="inlineStr">
@@ -4154,42 +4154,42 @@
       </c>
       <c r="EX4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="EY4" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="EZ4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FA4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FB4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FC4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FD4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="FE4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FF4" t="inlineStr">
@@ -4199,22 +4199,22 @@
       </c>
       <c r="FG4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="FH4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FI4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FJ4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FK4" t="inlineStr">
@@ -4401,12 +4401,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>0.34</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8628.434</t>
+          <t>10009.961</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -4416,369 +4416,369 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
+          <t>146.0</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>-0.34</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>-0.16786321196452753</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>60.0</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>轉強</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>TrendType : 轉強&lt;br&gt;TrendScore : 60&lt;br&gt;HH : True&lt;br&gt;HL : False&lt;br&gt;MA : True&lt;br&gt;VOL : False</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>142.55</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>148.4785216050106</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>136.6214783949895</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>0.0831781354613898</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>0.002990325417766115</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>0.001688232507606857</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>-0.03152921474353376</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>0.0479762948677207</t>
+        </is>
+      </c>
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t>1.230963728066852</t>
+        </is>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>2026-09-02 00:00:00</t>
+        </is>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="AG5" t="inlineStr">
+        <is>
+          <t>40.0</t>
+        </is>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>2026-09-03 00:00:00</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AL5" t="inlineStr">
+        <is>
+          <t>2026-09-08 00:00:00</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
+      </c>
+      <c r="AN5" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="AP5" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
+      </c>
+      <c r="AQ5" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AR5" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AS5" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AU5" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="AV5" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>7.0</t>
+        </is>
+      </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>16.0</t>
+        </is>
+      </c>
+      <c r="BA5" t="inlineStr">
+        <is>
+          <t>16.0</t>
+        </is>
+      </c>
+      <c r="BB5" t="inlineStr">
+        <is>
+          <t>16.0</t>
+        </is>
+      </c>
+      <c r="BC5" t="inlineStr">
+        <is>
+          <t>盤整</t>
+        </is>
+      </c>
+      <c r="BD5" t="inlineStr">
+        <is>
+          <t>盤整</t>
+        </is>
+      </c>
+      <c r="BE5" t="inlineStr">
+        <is>
+          <t>58.3</t>
+        </is>
+      </c>
+      <c r="BF5" t="inlineStr">
+        <is>
+          <t>17850578.0</t>
+        </is>
+      </c>
+      <c r="BG5" t="inlineStr">
+        <is>
+          <t>1360796.0</t>
+        </is>
+      </c>
+      <c r="BH5" t="inlineStr">
+        <is>
+          <t>4418171.0</t>
+        </is>
+      </c>
+      <c r="BI5" t="inlineStr">
+        <is>
+          <t>-3057375.0</t>
+        </is>
+      </c>
+      <c r="BJ5" t="inlineStr">
+        <is>
+          <t>-284018.0</t>
+        </is>
+      </c>
+      <c r="BK5" t="inlineStr">
+        <is>
+          <t>14509185.0</t>
+        </is>
+      </c>
+      <c r="BL5" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="BM5" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="BN5" t="inlineStr">
+        <is>
+          <t>-1.0</t>
+        </is>
+      </c>
+      <c r="BO5" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="BP5" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="BQ5" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="BR5" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="BS5" t="inlineStr">
+        <is>
+          <t>2026/07/20</t>
+        </is>
+      </c>
+      <c r="BT5" t="inlineStr">
+        <is>
+          <t>139.0</t>
+        </is>
+      </c>
+      <c r="BU5" t="inlineStr">
+        <is>
+          <t>2026/04/16</t>
+        </is>
+      </c>
+      <c r="BV5" t="inlineStr">
+        <is>
+          <t>136.5</t>
+        </is>
+      </c>
+      <c r="BW5" t="inlineStr">
+        <is>
+          <t>2026/10/07</t>
+        </is>
+      </c>
+      <c r="BX5" t="inlineStr">
+        <is>
           <t>145.5</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>-0.22942768703039035</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>99.0</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="R5" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>轉強</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>TrendType : 轉強&lt;br&gt;TrendScore : 60&lt;br&gt;HH : True&lt;br&gt;HL : False&lt;br&gt;MA : True&lt;br&gt;VOL : False</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>142.125</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>148.228277807866</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>136.021722192134</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>0.08588605534376148</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>0.003353335686551384</t>
-        </is>
-      </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>0.0007628237184782449</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>-0.05914846279594743</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>0.05137843623728422</t>
-        </is>
-      </c>
-      <c r="AD5" t="inlineStr">
-        <is>
-          <t>1.334686942343627</t>
-        </is>
-      </c>
-      <c r="AE5" t="inlineStr">
-        <is>
-          <t>2026-09-02 00:00:00</t>
-        </is>
-      </c>
-      <c r="AF5" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="AG5" t="inlineStr">
-        <is>
-          <t>40.0</t>
-        </is>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>2026-09-03 00:00:00</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AL5" t="inlineStr">
-        <is>
-          <t>2026-09-08 00:00:00</t>
-        </is>
-      </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AN5" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
-      </c>
-      <c r="AP5" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
-      </c>
-      <c r="AQ5" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AR5" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AS5" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AT5" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AU5" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="AV5" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AW5" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr">
-        <is>
-          <t>7.0</t>
-        </is>
-      </c>
-      <c r="AZ5" t="inlineStr">
-        <is>
-          <t>15.0</t>
-        </is>
-      </c>
-      <c r="BA5" t="inlineStr">
-        <is>
-          <t>15.0</t>
-        </is>
-      </c>
-      <c r="BB5" t="inlineStr">
-        <is>
-          <t>15.0</t>
-        </is>
-      </c>
-      <c r="BC5" t="inlineStr">
-        <is>
-          <t>盤整</t>
-        </is>
-      </c>
-      <c r="BD5" t="inlineStr">
-        <is>
-          <t>盤整</t>
-        </is>
-      </c>
-      <c r="BE5" t="inlineStr">
-        <is>
-          <t>58.3</t>
-        </is>
-      </c>
-      <c r="BF5" t="inlineStr">
-        <is>
-          <t>18108850.0</t>
-        </is>
-      </c>
-      <c r="BG5" t="inlineStr">
-        <is>
-          <t>1199596.0</t>
-        </is>
-      </c>
-      <c r="BH5" t="inlineStr">
-        <is>
-          <t>4011399.0</t>
-        </is>
-      </c>
-      <c r="BI5" t="inlineStr">
-        <is>
-          <t>-2811803.0</t>
-        </is>
-      </c>
-      <c r="BJ5" t="inlineStr">
-        <is>
-          <t>-248002.0</t>
-        </is>
-      </c>
-      <c r="BK5" t="inlineStr">
-        <is>
-          <t>15049045.0</t>
-        </is>
-      </c>
-      <c r="BL5" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
-      </c>
-      <c r="BM5" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
-      </c>
-      <c r="BN5" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="BO5" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="BP5" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="BQ5" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="BR5" t="inlineStr">
-        <is>
-          <t>-0.01</t>
-        </is>
-      </c>
-      <c r="BS5" t="inlineStr">
-        <is>
-          <t>2026/07/20</t>
-        </is>
-      </c>
-      <c r="BT5" t="inlineStr">
-        <is>
-          <t>139.0</t>
-        </is>
-      </c>
-      <c r="BU5" t="inlineStr">
-        <is>
-          <t>2026/04/16</t>
-        </is>
-      </c>
-      <c r="BV5" t="inlineStr">
-        <is>
-          <t>136.5</t>
-        </is>
-      </c>
-      <c r="BW5" t="inlineStr">
+      <c r="BY5" t="inlineStr">
         <is>
           <t>2026/08/05</t>
         </is>
       </c>
-      <c r="BX5" t="inlineStr">
+      <c r="BZ5" t="inlineStr">
         <is>
           <t>137.0</t>
         </is>
       </c>
-      <c r="BY5" t="inlineStr">
-        <is>
-          <t>2026/06/24</t>
-        </is>
-      </c>
-      <c r="BZ5" t="inlineStr">
-        <is>
-          <t>143.5</t>
-        </is>
-      </c>
       <c r="CA5" t="inlineStr">
         <is>
           <t>2026-09-18 00:00:00</t>
@@ -4786,17 +4786,17 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="CC5" t="inlineStr">
         <is>
-          <t>14.40</t>
+          <t>16.71</t>
         </is>
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>1.40</t>
+          <t>1.05</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
@@ -4807,12 +4807,12 @@
       <c r="CF5" t="inlineStr"/>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>50</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
         <is>
-          <t>7053</t>
+          <t>7081</t>
         </is>
       </c>
       <c r="CI5" t="inlineStr">
@@ -4822,162 +4822,162 @@
       </c>
       <c r="CJ5" t="inlineStr">
         <is>
-          <t>41.67</t>
+          <t>66.67</t>
         </is>
       </c>
       <c r="CK5" t="n">
-        <v>0.55</v>
+        <v>0.83</v>
       </c>
       <c r="CL5" t="n">
-        <v>1.81</v>
+        <v>1.58</v>
       </c>
       <c r="CM5" t="inlineStr">
         <is>
-          <t>2.09</t>
+          <t>2.29</t>
         </is>
       </c>
       <c r="CN5" t="inlineStr">
         <is>
-          <t>-0.47</t>
+          <t>-0.43</t>
         </is>
       </c>
       <c r="CO5" t="inlineStr">
         <is>
-          <t>144.7</t>
+          <t>144.8</t>
         </is>
       </c>
       <c r="CP5" t="inlineStr">
         <is>
-          <t>144.7</t>
+          <t>144.95</t>
         </is>
       </c>
       <c r="CQ5" t="inlineStr">
         <is>
-          <t>142.12</t>
+          <t>142.55</t>
         </is>
       </c>
       <c r="CR5" t="inlineStr">
         <is>
-          <t>139.21</t>
+          <t>139.36</t>
         </is>
       </c>
       <c r="CS5" t="inlineStr">
         <is>
-          <t>139.87</t>
+          <t>139.96</t>
         </is>
       </c>
       <c r="CT5" t="inlineStr">
         <is>
+          <t>135.9583333333333</t>
+        </is>
+      </c>
+      <c r="CU5" t="inlineStr">
+        <is>
+          <t>0.0006910850034556049</t>
+        </is>
+      </c>
+      <c r="CV5" t="inlineStr">
+        <is>
+          <t>0.001727712508638568</t>
+        </is>
+      </c>
+      <c r="CW5" t="inlineStr">
+        <is>
+          <t>0.002990325417766115</t>
+        </is>
+      </c>
+      <c r="CX5" t="inlineStr">
+        <is>
+          <t>0.001077508799655291</t>
+        </is>
+      </c>
+      <c r="CY5" t="inlineStr">
+        <is>
+          <t>0.0006702712364270447</t>
+        </is>
+      </c>
+      <c r="CZ5" t="inlineStr">
+        <is>
+          <t>0.0003985651654045963</t>
+        </is>
+      </c>
+      <c r="DA5" t="inlineStr">
+        <is>
+          <t>7.12</t>
+        </is>
+      </c>
+      <c r="DB5" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="DC5" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="DD5" t="inlineStr">
+        <is>
+          <t>1.9</t>
+        </is>
+      </c>
+      <c r="DE5" t="inlineStr">
+        <is>
+          <t>-3.52</t>
+        </is>
+      </c>
+      <c r="DF5" t="inlineStr">
+        <is>
+          <t>2026/08/21</t>
+        </is>
+      </c>
+      <c r="DG5" t="inlineStr">
+        <is>
+          <t>2214561876.963068</t>
+        </is>
+      </c>
+      <c r="DH5" t="inlineStr">
+        <is>
+          <t>1458318100.0</t>
+        </is>
+      </c>
+      <c r="DI5" t="n">
+        <v>1365056504.4</v>
+      </c>
+      <c r="DJ5" t="inlineStr">
+        <is>
+          <t>1640423214.1</t>
+        </is>
+      </c>
+      <c r="DK5" t="inlineStr">
+        <is>
+          <t>1485353753.433333</t>
+        </is>
+      </c>
+      <c r="DL5" t="n">
+        <v>1659414895.68</v>
+      </c>
+      <c r="DM5" t="inlineStr">
+        <is>
+          <t>2004348026.1375</t>
+        </is>
+      </c>
+      <c r="DN5" t="inlineStr">
+        <is>
+          <t>3840453.537898131</t>
+        </is>
+      </c>
+      <c r="DO5" t="inlineStr">
+        <is>
+          <t>-62046440.25528979</t>
+        </is>
+      </c>
+      <c r="DP5" t="inlineStr">
+        <is>
+          <t>1458318100.0</t>
+        </is>
+      </c>
+      <c r="DQ5" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="CU5" t="inlineStr">
-        <is>
-          <t>0.0006915629322268302</t>
-        </is>
-      </c>
-      <c r="CV5" t="inlineStr">
-        <is>
-          <t>0.00138408304498272</t>
-        </is>
-      </c>
-      <c r="CW5" t="inlineStr">
-        <is>
-          <t>0.003353335686551384</t>
-        </is>
-      </c>
-      <c r="CX5" t="inlineStr">
-        <is>
-          <t>0.0009347138337647554</t>
-        </is>
-      </c>
-      <c r="CY5" t="inlineStr">
-        <is>
-          <t>0.0004023245417970056</t>
-        </is>
-      </c>
-      <c r="CZ5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="DA5" t="inlineStr">
-        <is>
-          <t>6.98</t>
-        </is>
-      </c>
-      <c r="DB5" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="DC5" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="DD5" t="inlineStr">
-        <is>
-          <t>1.9</t>
-        </is>
-      </c>
-      <c r="DE5" t="inlineStr">
-        <is>
-          <t>-5.24</t>
-        </is>
-      </c>
-      <c r="DF5" t="inlineStr">
-        <is>
-          <t>2026/08/21</t>
-        </is>
-      </c>
-      <c r="DG5" t="inlineStr">
-        <is>
-          <t>2517415638.848781</t>
-        </is>
-      </c>
-      <c r="DH5" t="inlineStr">
-        <is>
-          <t>1248190797.0</t>
-        </is>
-      </c>
-      <c r="DI5" t="n">
-        <v>1315071112.6</v>
-      </c>
-      <c r="DJ5" t="inlineStr">
-        <is>
-          <t>1706616096.2</t>
-        </is>
-      </c>
-      <c r="DK5" t="inlineStr">
-        <is>
-          <t>1469076947.433333</t>
-        </is>
-      </c>
-      <c r="DL5" t="n">
-        <v>1667394181.32</v>
-      </c>
-      <c r="DM5" t="inlineStr">
-        <is>
-          <t>2016079760.0875</t>
-        </is>
-      </c>
-      <c r="DN5" t="inlineStr">
-        <is>
-          <t>15819888.77095735</t>
-        </is>
-      </c>
-      <c r="DO5" t="inlineStr">
-        <is>
-          <t>-65717912.88774347</t>
-        </is>
-      </c>
-      <c r="DP5" t="inlineStr">
-        <is>
-          <t>1248190797.0</t>
-        </is>
-      </c>
-      <c r="DQ5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="DR5" t="inlineStr">
         <is>
           <t>143.5</t>
@@ -4990,7 +4990,7 @@
       </c>
       <c r="DT5" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>1.74</t>
         </is>
       </c>
       <c r="DU5" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="ED5" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="EE5" t="inlineStr">
         <is>
-          <t>3.08</t>
+          <t>3.09</t>
         </is>
       </c>
       <c r="EF5" t="inlineStr">
@@ -5075,7 +5075,7 @@
       </c>
       <c r="EK5" t="inlineStr">
         <is>
-          <t>84.97</t>
+          <t>85.4</t>
         </is>
       </c>
       <c r="EL5" t="inlineStr">
@@ -5100,27 +5100,27 @@
       </c>
       <c r="EP5" t="inlineStr">
         <is>
+          <t>145.0</t>
+        </is>
+      </c>
+      <c r="EQ5" t="inlineStr">
+        <is>
+          <t>146.5</t>
+        </is>
+      </c>
+      <c r="ER5" t="inlineStr">
+        <is>
           <t>144.0</t>
         </is>
       </c>
-      <c r="EQ5" t="inlineStr">
+      <c r="ES5" t="inlineStr">
         <is>
           <t>146.0</t>
         </is>
       </c>
-      <c r="ER5" t="inlineStr">
-        <is>
-          <t>143.0</t>
-        </is>
-      </c>
-      <c r="ES5" t="inlineStr">
-        <is>
-          <t>145.5</t>
-        </is>
-      </c>
       <c r="ET5" t="inlineStr">
         <is>
-          <t>129.5</t>
+          <t>128.0</t>
         </is>
       </c>
       <c r="EU5" t="inlineStr">
@@ -5140,42 +5140,42 @@
       </c>
       <c r="EX5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="EY5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="EZ5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FA5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FB5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FC5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FD5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="FE5" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FF5" t="inlineStr">
@@ -5185,22 +5185,22 @@
       </c>
       <c r="FG5" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="FH5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FI5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FJ5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FK5" t="inlineStr">
@@ -5387,12 +5387,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>10607.859</t>
+          <t>8628.434</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -5402,7 +5402,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>143.5</t>
+          <t>145.5</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -5412,7 +5412,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -5422,7 +5422,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-0.3292751984432931</t>
+          <t>-0.22942768703039035</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -5432,7 +5432,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>99.0</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -5457,7 +5457,7 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
@@ -5467,62 +5467,62 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>60.0</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>盤整偏多</t>
+          <t>轉強</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>TrendType : 盤整偏多&lt;br&gt;TrendScore : 40&lt;br&gt;HH : True&lt;br&gt;HL : False&lt;br&gt;MA : False&lt;br&gt;VOL : False</t>
+          <t>TrendType : 轉強&lt;br&gt;TrendScore : 60&lt;br&gt;HH : True&lt;br&gt;HL : False&lt;br&gt;MA : True&lt;br&gt;VOL : False</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>141.65</t>
+          <t>142.125</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>148.1152919500972</t>
+          <t>148.2282778078687</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>135.1847080499028</t>
+          <t>136.0217221921313</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>0.09128544934835393</t>
+          <t>0.08588605534379948</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>0.002654397451778534</t>
+          <t>0.003353335686551384</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-0.0002059336306642345</t>
+          <t>0.0007628237184804654</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>-0.06151019020493131</t>
+          <t>-0.0591484627958786</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>0.05137843623728422</t>
+          <t>0.0479762948677207</t>
         </is>
       </c>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>1.49820616914414</t>
+          <t>1.334686942343584</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
@@ -5567,142 +5567,142 @@
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
           <t>3.0</t>
         </is>
       </c>
-      <c r="AO6" t="inlineStr">
+      <c r="AP6" t="inlineStr">
         <is>
           <t>2.0</t>
         </is>
       </c>
-      <c r="AP6" t="inlineStr">
+      <c r="AQ6" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AR6" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AS6" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AU6" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="AV6" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>7.0</t>
+        </is>
+      </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>15.0</t>
+        </is>
+      </c>
+      <c r="BA6" t="inlineStr">
+        <is>
+          <t>15.0</t>
+        </is>
+      </c>
+      <c r="BB6" t="inlineStr">
+        <is>
+          <t>15.0</t>
+        </is>
+      </c>
+      <c r="BC6" t="inlineStr">
+        <is>
+          <t>盤整</t>
+        </is>
+      </c>
+      <c r="BD6" t="inlineStr">
+        <is>
+          <t>盤整</t>
+        </is>
+      </c>
+      <c r="BE6" t="inlineStr">
+        <is>
+          <t>58.3</t>
+        </is>
+      </c>
+      <c r="BF6" t="inlineStr">
+        <is>
+          <t>17850578.0</t>
+        </is>
+      </c>
+      <c r="BG6" t="inlineStr">
+        <is>
+          <t>1360796.0</t>
+        </is>
+      </c>
+      <c r="BH6" t="inlineStr">
+        <is>
+          <t>4418171.0</t>
+        </is>
+      </c>
+      <c r="BI6" t="inlineStr">
+        <is>
+          <t>-3057375.0</t>
+        </is>
+      </c>
+      <c r="BJ6" t="inlineStr">
+        <is>
+          <t>-284018.0</t>
+        </is>
+      </c>
+      <c r="BK6" t="inlineStr">
+        <is>
+          <t>14509185.0</t>
+        </is>
+      </c>
+      <c r="BL6" t="inlineStr">
         <is>
           <t>5.0</t>
         </is>
       </c>
-      <c r="AQ6" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AR6" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AS6" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AT6" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AU6" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="AV6" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AW6" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr">
-        <is>
-          <t>7.0</t>
-        </is>
-      </c>
-      <c r="AZ6" t="inlineStr">
-        <is>
-          <t>14.0</t>
-        </is>
-      </c>
-      <c r="BA6" t="inlineStr">
-        <is>
-          <t>14.0</t>
-        </is>
-      </c>
-      <c r="BB6" t="inlineStr">
-        <is>
-          <t>14.0</t>
-        </is>
-      </c>
-      <c r="BC6" t="inlineStr">
-        <is>
-          <t>盤整</t>
-        </is>
-      </c>
-      <c r="BD6" t="inlineStr">
-        <is>
-          <t>盤整</t>
-        </is>
-      </c>
-      <c r="BE6" t="inlineStr">
-        <is>
-          <t>58.3</t>
-        </is>
-      </c>
-      <c r="BF6" t="inlineStr">
-        <is>
-          <t>18108850.0</t>
-        </is>
-      </c>
-      <c r="BG6" t="inlineStr">
-        <is>
-          <t>1199596.0</t>
-        </is>
-      </c>
-      <c r="BH6" t="inlineStr">
-        <is>
-          <t>4011399.0</t>
-        </is>
-      </c>
-      <c r="BI6" t="inlineStr">
-        <is>
-          <t>-2811803.0</t>
-        </is>
-      </c>
-      <c r="BJ6" t="inlineStr">
-        <is>
-          <t>-248002.0</t>
-        </is>
-      </c>
-      <c r="BK6" t="inlineStr">
-        <is>
-          <t>15049045.0</t>
-        </is>
-      </c>
-      <c r="BL6" t="inlineStr">
+      <c r="BM6" t="inlineStr">
         <is>
           <t>5.0</t>
         </is>
       </c>
-      <c r="BM6" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
-      </c>
       <c r="BN6" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="BO6" t="inlineStr">
@@ -5722,7 +5722,7 @@
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>-0.18</t>
+          <t>-0.01</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
@@ -5747,24 +5747,24 @@
       </c>
       <c r="BW6" t="inlineStr">
         <is>
+          <t>2026/10/07</t>
+        </is>
+      </c>
+      <c r="BX6" t="inlineStr">
+        <is>
+          <t>145.5</t>
+        </is>
+      </c>
+      <c r="BY6" t="inlineStr">
+        <is>
           <t>2026/08/05</t>
         </is>
       </c>
-      <c r="BX6" t="inlineStr">
+      <c r="BZ6" t="inlineStr">
         <is>
           <t>137.0</t>
         </is>
       </c>
-      <c r="BY6" t="inlineStr">
-        <is>
-          <t>2026/06/24</t>
-        </is>
-      </c>
-      <c r="BZ6" t="inlineStr">
-        <is>
-          <t>143.5</t>
-        </is>
-      </c>
       <c r="CA6" t="inlineStr">
         <is>
           <t>2026-09-18 00:00:00</t>
@@ -5772,17 +5772,17 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="CC6" t="inlineStr">
         <is>
-          <t>17.70</t>
+          <t>14.40</t>
         </is>
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>-0.70</t>
+          <t>1.40</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
@@ -5793,177 +5793,177 @@
       <c r="CF6" t="inlineStr"/>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>50</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
         <is>
-          <t>7053</t>
+          <t>7081</t>
         </is>
       </c>
       <c r="CI6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="CJ6" t="inlineStr">
         <is>
-          <t>36.11</t>
+          <t>41.67</t>
         </is>
       </c>
       <c r="CK6" t="n">
-        <v>-0.76</v>
+        <v>0.55</v>
       </c>
       <c r="CL6" t="n">
-        <v>2.08</v>
+        <v>1.81</v>
       </c>
       <c r="CM6" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>2.09</t>
         </is>
       </c>
       <c r="CN6" t="inlineStr">
         <is>
-          <t>-0.52</t>
+          <t>-0.47</t>
         </is>
       </c>
       <c r="CO6" t="inlineStr">
         <is>
-          <t>144.6</t>
+          <t>144.7</t>
         </is>
       </c>
       <c r="CP6" t="inlineStr">
         <is>
-          <t>144.5</t>
+          <t>144.7</t>
         </is>
       </c>
       <c r="CQ6" t="inlineStr">
         <is>
-          <t>141.65</t>
+          <t>142.12</t>
         </is>
       </c>
       <c r="CR6" t="inlineStr">
         <is>
-          <t>139.08</t>
+          <t>139.21</t>
         </is>
       </c>
       <c r="CS6" t="inlineStr">
         <is>
-          <t>139.81</t>
+          <t>139.87</t>
         </is>
       </c>
       <c r="CT6" t="inlineStr">
         <is>
+          <t>135.9041666666667</t>
+        </is>
+      </c>
+      <c r="CU6" t="inlineStr">
+        <is>
+          <t>0.0006915629322268302</t>
+        </is>
+      </c>
+      <c r="CV6" t="inlineStr">
+        <is>
+          <t>0.00138408304498272</t>
+        </is>
+      </c>
+      <c r="CW6" t="inlineStr">
+        <is>
+          <t>0.003353335686551384</t>
+        </is>
+      </c>
+      <c r="CX6" t="inlineStr">
+        <is>
+          <t>0.0009347138337647554</t>
+        </is>
+      </c>
+      <c r="CY6" t="inlineStr">
+        <is>
+          <t>0.0004023245417970056</t>
+        </is>
+      </c>
+      <c r="CZ6" t="inlineStr">
+        <is>
+          <t>0.0003833826619026315</t>
+        </is>
+      </c>
+      <c r="DA6" t="inlineStr">
+        <is>
+          <t>6.98</t>
+        </is>
+      </c>
+      <c r="DB6" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="DC6" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="DD6" t="inlineStr">
+        <is>
+          <t>1.9</t>
+        </is>
+      </c>
+      <c r="DE6" t="inlineStr">
+        <is>
+          <t>-5.24</t>
+        </is>
+      </c>
+      <c r="DF6" t="inlineStr">
+        <is>
+          <t>2026/08/21</t>
+        </is>
+      </c>
+      <c r="DG6" t="inlineStr">
+        <is>
+          <t>2214561876.963068</t>
+        </is>
+      </c>
+      <c r="DH6" t="inlineStr">
+        <is>
+          <t>1248190797.0</t>
+        </is>
+      </c>
+      <c r="DI6" t="n">
+        <v>1315071112.6</v>
+      </c>
+      <c r="DJ6" t="inlineStr">
+        <is>
+          <t>1706616096.2</t>
+        </is>
+      </c>
+      <c r="DK6" t="inlineStr">
+        <is>
+          <t>1469076947.433333</t>
+        </is>
+      </c>
+      <c r="DL6" t="n">
+        <v>1667394181.32</v>
+      </c>
+      <c r="DM6" t="inlineStr">
+        <is>
+          <t>2016079760.0875</t>
+        </is>
+      </c>
+      <c r="DN6" t="inlineStr">
+        <is>
+          <t>15819888.77302321</t>
+        </is>
+      </c>
+      <c r="DO6" t="inlineStr">
+        <is>
+          <t>-65717912.88730001</t>
+        </is>
+      </c>
+      <c r="DP6" t="inlineStr">
+        <is>
+          <t>1248190797.0</t>
+        </is>
+      </c>
+      <c r="DQ6" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="CU6" t="inlineStr">
-        <is>
-          <t>-0.001381215469613339</t>
-        </is>
-      </c>
-      <c r="CV6" t="inlineStr">
-        <is>
-          <t>0.0006925207756232066</t>
-        </is>
-      </c>
-      <c r="CW6" t="inlineStr">
-        <is>
-          <t>0.002654397451778534</t>
-        </is>
-      </c>
-      <c r="CX6" t="inlineStr">
-        <is>
-          <t>0.0006475285991798252</t>
-        </is>
-      </c>
-      <c r="CY6" t="inlineStr">
-        <is>
-          <t>0.0001788428865241443</t>
-        </is>
-      </c>
-      <c r="CZ6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="DA6" t="inlineStr">
-        <is>
-          <t>7.47</t>
-        </is>
-      </c>
-      <c r="DB6" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="DC6" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="DD6" t="inlineStr">
-        <is>
-          <t>1.9</t>
-        </is>
-      </c>
-      <c r="DE6" t="inlineStr">
-        <is>
-          <t>-6.89</t>
-        </is>
-      </c>
-      <c r="DF6" t="inlineStr">
-        <is>
-          <t>2026/08/21</t>
-        </is>
-      </c>
-      <c r="DG6" t="inlineStr">
-        <is>
-          <t>2517415638.848781</t>
-        </is>
-      </c>
-      <c r="DH6" t="inlineStr">
-        <is>
-          <t>1524028999.0</t>
-        </is>
-      </c>
-      <c r="DI6" t="n">
-        <v>1223386087.6</v>
-      </c>
-      <c r="DJ6" t="inlineStr">
-        <is>
-          <t>1823976219.1</t>
-        </is>
-      </c>
-      <c r="DK6" t="inlineStr">
-        <is>
-          <t>1490856706.633333</t>
-        </is>
-      </c>
-      <c r="DL6" t="n">
-        <v>1693335182.06</v>
-      </c>
-      <c r="DM6" t="inlineStr">
-        <is>
-          <t>2020913533.8875</t>
-        </is>
-      </c>
-      <c r="DN6" t="inlineStr">
-        <is>
-          <t>30644943.61799386</t>
-        </is>
-      </c>
-      <c r="DO6" t="inlineStr">
-        <is>
-          <t>-46102165.86613226</t>
-        </is>
-      </c>
-      <c r="DP6" t="inlineStr">
-        <is>
-          <t>1524028999.0</t>
-        </is>
-      </c>
-      <c r="DQ6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="DR6" t="inlineStr">
         <is>
           <t>143.5</t>
@@ -5976,7 +5976,7 @@
       </c>
       <c r="DT6" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="DU6" t="inlineStr">
@@ -6021,7 +6021,7 @@
       </c>
       <c r="EC6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="ED6" t="inlineStr">
@@ -6031,7 +6031,7 @@
       </c>
       <c r="EE6" t="inlineStr">
         <is>
-          <t>3.04</t>
+          <t>3.08</t>
         </is>
       </c>
       <c r="EF6" t="inlineStr">
@@ -6061,7 +6061,7 @@
       </c>
       <c r="EK6" t="inlineStr">
         <is>
-          <t>84.97</t>
+          <t>85.4</t>
         </is>
       </c>
       <c r="EL6" t="inlineStr">
@@ -6086,12 +6086,12 @@
       </c>
       <c r="EP6" t="inlineStr">
         <is>
-          <t>145.0</t>
+          <t>144.0</t>
         </is>
       </c>
       <c r="EQ6" t="inlineStr">
         <is>
-          <t>145.0</t>
+          <t>146.0</t>
         </is>
       </c>
       <c r="ER6" t="inlineStr">
@@ -6101,12 +6101,12 @@
       </c>
       <c r="ES6" t="inlineStr">
         <is>
-          <t>143.5</t>
+          <t>145.5</t>
         </is>
       </c>
       <c r="ET6" t="inlineStr">
         <is>
-          <t>129.5</t>
+          <t>128.0</t>
         </is>
       </c>
       <c r="EU6" t="inlineStr">
@@ -6126,42 +6126,42 @@
       </c>
       <c r="EX6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="EY6" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="EZ6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FA6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FB6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FC6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FD6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="FE6" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="FF6" t="inlineStr">
@@ -6171,22 +6171,22 @@
       </c>
       <c r="FG6" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="FH6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="FI6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FJ6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FK6" t="inlineStr">
@@ -6373,12 +6373,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-0.68</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>11652.18</t>
+          <t>10607.859</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -6388,7 +6388,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>144.0</t>
+          <t>143.5</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -6398,7 +6398,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>1.03</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -6408,7 +6408,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-0.39166013609889294</t>
+          <t>-0.3292751984432931</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -6453,7 +6453,7 @@
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -6468,47 +6468,47 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>141.275</t>
+          <t>141.65</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>148.1458001525903</t>
+          <t>148.1152919500996</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>134.4041998474098</t>
+          <t>135.1847080499005</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>0.09726845022247742</t>
+          <t>0.09128544934838764</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>0.003017394391196415</t>
+          <t>0.002654397451778534</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>0.0006164580977021661</t>
+          <t>-0.0002059336306624582</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>-0.04919128589699406</t>
+          <t>-0.06151019020487603</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>0.05137843623728422</t>
+          <t>0.0479762948677207</t>
         </is>
       </c>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>1.699323642510904</t>
+          <t>1.498206169143926</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
@@ -6553,69 +6553,69 @@
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
+          <t>3.0</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
           <t>2.0</t>
         </is>
       </c>
-      <c r="AO7" t="inlineStr">
+      <c r="AP7" t="inlineStr">
         <is>
           <t>5.0</t>
         </is>
       </c>
-      <c r="AP7" t="inlineStr">
+      <c r="AQ7" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AR7" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AS7" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AU7" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="AV7" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
         <is>
           <t>7.0</t>
         </is>
       </c>
-      <c r="AQ7" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AR7" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AS7" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AT7" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AU7" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="AV7" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AW7" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="AX7" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr">
-        <is>
-          <t>8.0</t>
-        </is>
-      </c>
       <c r="AZ7" t="inlineStr">
         <is>
           <t>14.0</t>
@@ -6638,7 +6638,7 @@
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>強勢</t>
+          <t>盤整</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -6648,32 +6648,32 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>18108850.0</t>
+          <t>17850578.0</t>
         </is>
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>1199596.0</t>
+          <t>1360796.0</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>4011399.0</t>
+          <t>4418171.0</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
         <is>
-          <t>-2811803.0</t>
+          <t>-3057375.0</t>
         </is>
       </c>
       <c r="BJ7" t="inlineStr">
         <is>
-          <t>-248002.0</t>
+          <t>-284018.0</t>
         </is>
       </c>
       <c r="BK7" t="inlineStr">
         <is>
-          <t>15049045.0</t>
+          <t>14509185.0</t>
         </is>
       </c>
       <c r="BL7" t="inlineStr">
@@ -6688,7 +6688,7 @@
       </c>
       <c r="BN7" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="BO7" t="inlineStr">
@@ -6733,24 +6733,24 @@
       </c>
       <c r="BW7" t="inlineStr">
         <is>
+          <t>2026/10/07</t>
+        </is>
+      </c>
+      <c r="BX7" t="inlineStr">
+        <is>
+          <t>145.5</t>
+        </is>
+      </c>
+      <c r="BY7" t="inlineStr">
+        <is>
           <t>2026/08/05</t>
         </is>
       </c>
-      <c r="BX7" t="inlineStr">
+      <c r="BZ7" t="inlineStr">
         <is>
           <t>137.0</t>
         </is>
       </c>
-      <c r="BY7" t="inlineStr">
-        <is>
-          <t>2026/06/24</t>
-        </is>
-      </c>
-      <c r="BZ7" t="inlineStr">
-        <is>
-          <t>143.5</t>
-        </is>
-      </c>
       <c r="CA7" t="inlineStr">
         <is>
           <t>2026-09-18 00:00:00</t>
@@ -6758,17 +6758,17 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="CC7" t="inlineStr">
         <is>
-          <t>19.45</t>
+          <t>17.70</t>
         </is>
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>-0.69</t>
+          <t>-0.70</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
@@ -6779,177 +6779,177 @@
       <c r="CF7" t="inlineStr"/>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>50</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
         <is>
-          <t>7053</t>
+          <t>7081</t>
         </is>
       </c>
       <c r="CI7" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="CJ7" t="inlineStr">
         <is>
-          <t>69.44</t>
+          <t>36.11</t>
         </is>
       </c>
       <c r="CK7" t="n">
-        <v>-0.55</v>
+        <v>-0.76</v>
       </c>
       <c r="CL7" t="n">
-        <v>2.5</v>
+        <v>2.08</v>
       </c>
       <c r="CM7" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="CN7" t="inlineStr">
         <is>
-          <t>-0.57</t>
+          <t>-0.52</t>
         </is>
       </c>
       <c r="CO7" t="inlineStr">
         <is>
-          <t>144.8</t>
+          <t>144.6</t>
         </is>
       </c>
       <c r="CP7" t="inlineStr">
         <is>
-          <t>144.4</t>
+          <t>144.5</t>
         </is>
       </c>
       <c r="CQ7" t="inlineStr">
         <is>
-          <t>141.28</t>
+          <t>141.65</t>
         </is>
       </c>
       <c r="CR7" t="inlineStr">
         <is>
-          <t>138.99</t>
+          <t>139.08</t>
         </is>
       </c>
       <c r="CS7" t="inlineStr">
         <is>
-          <t>139.79</t>
+          <t>139.81</t>
         </is>
       </c>
       <c r="CT7" t="inlineStr">
         <is>
+          <t>135.8520833333333</t>
+        </is>
+      </c>
+      <c r="CU7" t="inlineStr">
+        <is>
+          <t>-0.001381215469613339</t>
+        </is>
+      </c>
+      <c r="CV7" t="inlineStr">
+        <is>
+          <t>0.0006925207756232066</t>
+        </is>
+      </c>
+      <c r="CW7" t="inlineStr">
+        <is>
+          <t>0.002654397451778534</t>
+        </is>
+      </c>
+      <c r="CX7" t="inlineStr">
+        <is>
+          <t>0.0006475285991798252</t>
+        </is>
+      </c>
+      <c r="CY7" t="inlineStr">
+        <is>
+          <t>0.0001788428865241443</t>
+        </is>
+      </c>
+      <c r="CZ7" t="inlineStr">
+        <is>
+          <t>0.0002761117332146235</t>
+        </is>
+      </c>
+      <c r="DA7" t="inlineStr">
+        <is>
+          <t>7.47</t>
+        </is>
+      </c>
+      <c r="DB7" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="DC7" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="DD7" t="inlineStr">
+        <is>
+          <t>1.9</t>
+        </is>
+      </c>
+      <c r="DE7" t="inlineStr">
+        <is>
+          <t>-6.89</t>
+        </is>
+      </c>
+      <c r="DF7" t="inlineStr">
+        <is>
+          <t>2026/08/21</t>
+        </is>
+      </c>
+      <c r="DG7" t="inlineStr">
+        <is>
+          <t>2214561876.963068</t>
+        </is>
+      </c>
+      <c r="DH7" t="inlineStr">
+        <is>
+          <t>1524028999.0</t>
+        </is>
+      </c>
+      <c r="DI7" t="n">
+        <v>1223386087.6</v>
+      </c>
+      <c r="DJ7" t="inlineStr">
+        <is>
+          <t>1823976219.1</t>
+        </is>
+      </c>
+      <c r="DK7" t="inlineStr">
+        <is>
+          <t>1490856706.633333</t>
+        </is>
+      </c>
+      <c r="DL7" t="n">
+        <v>1693335182.06</v>
+      </c>
+      <c r="DM7" t="inlineStr">
+        <is>
+          <t>2020913533.8875</t>
+        </is>
+      </c>
+      <c r="DN7" t="inlineStr">
+        <is>
+          <t>30644943.6203547</t>
+        </is>
+      </c>
+      <c r="DO7" t="inlineStr">
+        <is>
+          <t>-46102165.86562538</t>
+        </is>
+      </c>
+      <c r="DP7" t="inlineStr">
+        <is>
+          <t>1524028999.0</t>
+        </is>
+      </c>
+      <c r="DQ7" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="CU7" t="inlineStr">
-        <is>
-          <t>-0.002067539627842785</t>
-        </is>
-      </c>
-      <c r="CV7" t="inlineStr">
-        <is>
-          <t>0.002429711905588272</t>
-        </is>
-      </c>
-      <c r="CW7" t="inlineStr">
-        <is>
-          <t>0.003017394391196415</t>
-        </is>
-      </c>
-      <c r="CX7" t="inlineStr">
-        <is>
-          <t>0.0008641175199828321</t>
-        </is>
-      </c>
-      <c r="CY7" t="inlineStr">
-        <is>
-          <t>0.0002683363148479057</t>
-        </is>
-      </c>
-      <c r="CZ7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="DA7" t="inlineStr">
-        <is>
-          <t>17.86</t>
-        </is>
-      </c>
-      <c r="DB7" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="DC7" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="DD7" t="inlineStr">
-        <is>
-          <t>1.9</t>
-        </is>
-      </c>
-      <c r="DE7" t="inlineStr">
-        <is>
-          <t>-8.63</t>
-        </is>
-      </c>
-      <c r="DF7" t="inlineStr">
-        <is>
-          <t>2026/08/21</t>
-        </is>
-      </c>
-      <c r="DG7" t="inlineStr">
-        <is>
-          <t>2517415638.848781</t>
-        </is>
-      </c>
-      <c r="DH7" t="inlineStr">
-        <is>
-          <t>1676725028.0</t>
-        </is>
-      </c>
-      <c r="DI7" t="n">
-        <v>1178675636.2</v>
-      </c>
-      <c r="DJ7" t="inlineStr">
-        <is>
-          <t>1937528191.3</t>
-        </is>
-      </c>
-      <c r="DK7" t="inlineStr">
-        <is>
-          <t>1486546014.1</t>
-        </is>
-      </c>
-      <c r="DL7" t="n">
-        <v>1735471199.16</v>
-      </c>
-      <c r="DM7" t="inlineStr">
-        <is>
-          <t>2026673727.9875</t>
-        </is>
-      </c>
-      <c r="DN7" t="inlineStr">
-        <is>
-          <t>44598963.52419861</t>
-        </is>
-      </c>
-      <c r="DO7" t="inlineStr">
-        <is>
-          <t>-45987257.26861119</t>
-        </is>
-      </c>
-      <c r="DP7" t="inlineStr">
-        <is>
-          <t>1676725028.0</t>
-        </is>
-      </c>
-      <c r="DQ7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="DR7" t="inlineStr">
         <is>
           <t>143.5</t>
@@ -6962,7 +6962,7 @@
       </c>
       <c r="DT7" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="DU7" t="inlineStr">
@@ -7007,7 +7007,7 @@
       </c>
       <c r="EC7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="ED7" t="inlineStr">
@@ -7017,7 +7017,7 @@
       </c>
       <c r="EE7" t="inlineStr">
         <is>
-          <t>3.05</t>
+          <t>3.04</t>
         </is>
       </c>
       <c r="EF7" t="inlineStr">
@@ -7047,7 +7047,7 @@
       </c>
       <c r="EK7" t="inlineStr">
         <is>
-          <t>84.97</t>
+          <t>85.4</t>
         </is>
       </c>
       <c r="EL7" t="inlineStr">
@@ -7072,12 +7072,12 @@
       </c>
       <c r="EP7" t="inlineStr">
         <is>
-          <t>146.0</t>
+          <t>145.0</t>
         </is>
       </c>
       <c r="EQ7" t="inlineStr">
         <is>
-          <t>146.0</t>
+          <t>145.0</t>
         </is>
       </c>
       <c r="ER7" t="inlineStr">
@@ -7087,12 +7087,12 @@
       </c>
       <c r="ES7" t="inlineStr">
         <is>
-          <t>144.0</t>
+          <t>143.5</t>
         </is>
       </c>
       <c r="ET7" t="inlineStr">
         <is>
-          <t>129.5</t>
+          <t>128.0</t>
         </is>
       </c>
       <c r="EU7" t="inlineStr">
@@ -7112,42 +7112,42 @@
       </c>
       <c r="EX7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="EY7" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="EZ7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FA7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FB7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FC7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FD7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="FE7" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="FF7" t="inlineStr">
@@ -7157,22 +7157,22 @@
       </c>
       <c r="FG7" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="FH7" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="FI7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FJ7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FK7" t="inlineStr">
@@ -7359,12 +7359,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>-0.68</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>6311.915</t>
+          <t>11652.18</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -7374,7 +7374,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>145.0</t>
+          <t>144.0</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -7384,7 +7384,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>0.34</t>
+          <t>1.03</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -7394,7 +7394,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-0.15933593107033336</t>
+          <t>-0.39166013609889294</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -7439,7 +7439,7 @@
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
@@ -7454,47 +7454,47 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>140.85</t>
+          <t>141.275</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>148.0545307382152</t>
+          <t>148.1458001525924</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>133.6454692617848</t>
+          <t>134.4041998474076</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>0.1023007559561973</t>
+          <t>0.0972684502225076</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>0.00338379341050743</t>
+          <t>0.003017394391196415</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>0.002539703250194592</t>
+          <t>0.0006164580977034984</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>-0.01700799986583423</t>
+          <t>-0.0491912858969541</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>0.05137843623728422</t>
+          <t>0.0479762948677207</t>
         </is>
       </c>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>1.907951888344739</t>
+          <t>1.699323642510481</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
@@ -7539,24 +7539,24 @@
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
           <t>5.0</t>
         </is>
       </c>
-      <c r="AO8" t="inlineStr">
+      <c r="AP8" t="inlineStr">
         <is>
           <t>7.0</t>
         </is>
       </c>
-      <c r="AP8" t="inlineStr">
-        <is>
-          <t>7.0</t>
-        </is>
-      </c>
       <c r="AQ8" t="inlineStr">
         <is>
           <t>False</t>
@@ -7589,17 +7589,17 @@
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>9.0</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
@@ -7619,14 +7619,14 @@
       </c>
       <c r="BC8" t="inlineStr">
         <is>
+          <t>盤整</t>
+        </is>
+      </c>
+      <c r="BD8" t="inlineStr">
+        <is>
           <t>強勢</t>
         </is>
       </c>
-      <c r="BD8" t="inlineStr">
-        <is>
-          <t>強勢</t>
-        </is>
-      </c>
       <c r="BE8" t="inlineStr">
         <is>
           <t>58.3</t>
@@ -7634,32 +7634,32 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>18108850.0</t>
+          <t>17850578.0</t>
         </is>
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>1199596.0</t>
+          <t>1360796.0</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>4011399.0</t>
+          <t>4418171.0</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
         <is>
-          <t>-2811803.0</t>
+          <t>-3057375.0</t>
         </is>
       </c>
       <c r="BJ8" t="inlineStr">
         <is>
-          <t>-248002.0</t>
+          <t>-284018.0</t>
         </is>
       </c>
       <c r="BK8" t="inlineStr">
         <is>
-          <t>15049045.0</t>
+          <t>14509185.0</t>
         </is>
       </c>
       <c r="BL8" t="inlineStr">
@@ -7674,7 +7674,7 @@
       </c>
       <c r="BN8" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="BO8" t="inlineStr">
@@ -7694,7 +7694,7 @@
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>-0.18</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
@@ -7719,24 +7719,24 @@
       </c>
       <c r="BW8" t="inlineStr">
         <is>
+          <t>2026/10/07</t>
+        </is>
+      </c>
+      <c r="BX8" t="inlineStr">
+        <is>
+          <t>145.5</t>
+        </is>
+      </c>
+      <c r="BY8" t="inlineStr">
+        <is>
           <t>2026/08/05</t>
         </is>
       </c>
-      <c r="BX8" t="inlineStr">
+      <c r="BZ8" t="inlineStr">
         <is>
           <t>137.0</t>
         </is>
       </c>
-      <c r="BY8" t="inlineStr">
-        <is>
-          <t>2026/06/24</t>
-        </is>
-      </c>
-      <c r="BZ8" t="inlineStr">
-        <is>
-          <t>143.5</t>
-        </is>
-      </c>
       <c r="CA8" t="inlineStr">
         <is>
           <t>2026-09-18 00:00:00</t>
@@ -7744,12 +7744,12 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="CC8" t="inlineStr">
         <is>
-          <t>10.53</t>
+          <t>19.45</t>
         </is>
       </c>
       <c r="CD8" t="inlineStr">
@@ -7765,177 +7765,177 @@
       <c r="CF8" t="inlineStr"/>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>50</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
         <is>
-          <t>7053</t>
+          <t>7081</t>
         </is>
       </c>
       <c r="CI8" t="inlineStr">
         <is>
-          <t>83.33</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="CJ8" t="inlineStr">
         <is>
-          <t>91.67</t>
+          <t>69.44</t>
         </is>
       </c>
       <c r="CK8" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.55</v>
       </c>
       <c r="CL8" t="n">
-        <v>3.02</v>
+        <v>2.5</v>
       </c>
       <c r="CM8" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="CN8" t="inlineStr">
         <is>
-          <t>-0.63</t>
+          <t>-0.57</t>
         </is>
       </c>
       <c r="CO8" t="inlineStr">
         <is>
-          <t>145.1</t>
+          <t>144.8</t>
         </is>
       </c>
       <c r="CP8" t="inlineStr">
         <is>
-          <t>144.05</t>
+          <t>144.4</t>
         </is>
       </c>
       <c r="CQ8" t="inlineStr">
         <is>
-          <t>140.85</t>
+          <t>141.28</t>
         </is>
       </c>
       <c r="CR8" t="inlineStr">
         <is>
-          <t>138.87</t>
+          <t>138.99</t>
         </is>
       </c>
       <c r="CS8" t="inlineStr">
         <is>
-          <t>139.75</t>
+          <t>139.79</t>
         </is>
       </c>
       <c r="CT8" t="inlineStr">
         <is>
+          <t>135.8145833333333</t>
+        </is>
+      </c>
+      <c r="CU8" t="inlineStr">
+        <is>
+          <t>-0.002067539627842785</t>
+        </is>
+      </c>
+      <c r="CV8" t="inlineStr">
+        <is>
+          <t>0.002429711905588272</t>
+        </is>
+      </c>
+      <c r="CW8" t="inlineStr">
+        <is>
+          <t>0.003017394391196415</t>
+        </is>
+      </c>
+      <c r="CX8" t="inlineStr">
+        <is>
+          <t>0.0008641175199828321</t>
+        </is>
+      </c>
+      <c r="CY8" t="inlineStr">
+        <is>
+          <t>0.0002683363148479057</t>
+        </is>
+      </c>
+      <c r="CZ8" t="inlineStr">
+        <is>
+          <t>0.0003222341568205334</t>
+        </is>
+      </c>
+      <c r="DA8" t="inlineStr">
+        <is>
+          <t>17.86</t>
+        </is>
+      </c>
+      <c r="DB8" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="DC8" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="DD8" t="inlineStr">
+        <is>
+          <t>1.9</t>
+        </is>
+      </c>
+      <c r="DE8" t="inlineStr">
+        <is>
+          <t>-8.63</t>
+        </is>
+      </c>
+      <c r="DF8" t="inlineStr">
+        <is>
+          <t>2026/08/21</t>
+        </is>
+      </c>
+      <c r="DG8" t="inlineStr">
+        <is>
+          <t>2214561876.963068</t>
+        </is>
+      </c>
+      <c r="DH8" t="inlineStr">
+        <is>
+          <t>1676725028.0</t>
+        </is>
+      </c>
+      <c r="DI8" t="n">
+        <v>1178675636.2</v>
+      </c>
+      <c r="DJ8" t="inlineStr">
+        <is>
+          <t>1937528191.3</t>
+        </is>
+      </c>
+      <c r="DK8" t="inlineStr">
+        <is>
+          <t>1486546014.1</t>
+        </is>
+      </c>
+      <c r="DL8" t="n">
+        <v>1735471199.16</v>
+      </c>
+      <c r="DM8" t="inlineStr">
+        <is>
+          <t>2026673727.9875</t>
+        </is>
+      </c>
+      <c r="DN8" t="inlineStr">
+        <is>
+          <t>44598963.52689654</t>
+        </is>
+      </c>
+      <c r="DO8" t="inlineStr">
+        <is>
+          <t>-45987257.26803184</t>
+        </is>
+      </c>
+      <c r="DP8" t="inlineStr">
+        <is>
+          <t>1676725028.0</t>
+        </is>
+      </c>
+      <c r="DQ8" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="CU8" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="CV8" t="inlineStr">
-        <is>
-          <t>0.003832752613240453</t>
-        </is>
-      </c>
-      <c r="CW8" t="inlineStr">
-        <is>
-          <t>0.00338379341050743</t>
-        </is>
-      </c>
-      <c r="CX8" t="inlineStr">
-        <is>
-          <t>0.001297858533420015</t>
-        </is>
-      </c>
-      <c r="CY8" t="inlineStr">
-        <is>
-          <t>0.0002684083385522396</t>
-        </is>
-      </c>
-      <c r="CZ8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="DA8" t="inlineStr">
-        <is>
-          <t>29.64</t>
-        </is>
-      </c>
-      <c r="DB8" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="DC8" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="DD8" t="inlineStr">
-        <is>
-          <t>1.9</t>
-        </is>
-      </c>
-      <c r="DE8" t="inlineStr">
-        <is>
-          <t>-12.71</t>
-        </is>
-      </c>
-      <c r="DF8" t="inlineStr">
-        <is>
-          <t>2026/08/21</t>
-        </is>
-      </c>
-      <c r="DG8" t="inlineStr">
-        <is>
-          <t>2517415638.848781</t>
-        </is>
-      </c>
-      <c r="DH8" t="inlineStr">
-        <is>
-          <t>918019598.0</t>
-        </is>
-      </c>
-      <c r="DI8" t="n">
-        <v>1659195852.6</v>
-      </c>
-      <c r="DJ8" t="inlineStr">
-        <is>
-          <t>1973672854.5</t>
-        </is>
-      </c>
-      <c r="DK8" t="inlineStr">
-        <is>
-          <t>1482010386.8</t>
-        </is>
-      </c>
-      <c r="DL8" t="n">
-        <v>1806077677.02</v>
-      </c>
-      <c r="DM8" t="inlineStr">
-        <is>
-          <t>2030537576.35</t>
-        </is>
-      </c>
-      <c r="DN8" t="inlineStr">
-        <is>
-          <t>61069185.48652767</t>
-        </is>
-      </c>
-      <c r="DO8" t="inlineStr">
-        <is>
-          <t>-60540988.90541673</t>
-        </is>
-      </c>
-      <c r="DP8" t="inlineStr">
-        <is>
-          <t>918019598.0</t>
-        </is>
-      </c>
-      <c r="DQ8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="DR8" t="inlineStr">
         <is>
           <t>143.5</t>
@@ -7948,7 +7948,7 @@
       </c>
       <c r="DT8" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>0.35</t>
         </is>
       </c>
       <c r="DU8" t="inlineStr">
@@ -8003,7 +8003,7 @@
       </c>
       <c r="EE8" t="inlineStr">
         <is>
-          <t>3.07</t>
+          <t>3.05</t>
         </is>
       </c>
       <c r="EF8" t="inlineStr">
@@ -8033,7 +8033,7 @@
       </c>
       <c r="EK8" t="inlineStr">
         <is>
-          <t>84.97</t>
+          <t>85.4</t>
         </is>
       </c>
       <c r="EL8" t="inlineStr">
@@ -8058,7 +8058,7 @@
       </c>
       <c r="EP8" t="inlineStr">
         <is>
-          <t>145.5</t>
+          <t>146.0</t>
         </is>
       </c>
       <c r="EQ8" t="inlineStr">
@@ -8068,17 +8068,17 @@
       </c>
       <c r="ER8" t="inlineStr">
         <is>
-          <t>145.0</t>
+          <t>143.0</t>
         </is>
       </c>
       <c r="ES8" t="inlineStr">
         <is>
-          <t>145.0</t>
+          <t>144.0</t>
         </is>
       </c>
       <c r="ET8" t="inlineStr">
         <is>
-          <t>129.5</t>
+          <t>128.0</t>
         </is>
       </c>
       <c r="EU8" t="inlineStr">
@@ -8098,67 +8098,67 @@
       </c>
       <c r="EX8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="EY8" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="EZ8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FA8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FB8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FC8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FD8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="FE8" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>13.0</t>
         </is>
       </c>
       <c r="FF8" t="inlineStr">
         <is>
-          <t>1.119557506059444</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FG8" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="FH8" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="FI8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FJ8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FK8" t="inlineStr">
@@ -8345,384 +8345,384 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
+          <t>-0.34</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>6311.915</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>145.0</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
           <t>0.34</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>8326.189</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>-0.15933593107033336</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>99.0</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>40.0</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>盤整偏多</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>TrendType : 盤整偏多&lt;br&gt;TrendScore : 40&lt;br&gt;HH : True&lt;br&gt;HL : False&lt;br&gt;MA : False&lt;br&gt;VOL : False</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>140.85</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>148.0545307382171</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>133.6454692617829</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>0.1023007559562248</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>0.00338379341050743</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>0.002539703250195702</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>-0.01700799986580759</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>0.0479762948677207</t>
+        </is>
+      </c>
+      <c r="AD9" t="inlineStr">
+        <is>
+          <t>1.907951888344097</t>
+        </is>
+      </c>
+      <c r="AE9" t="inlineStr">
+        <is>
+          <t>2026-09-02 00:00:00</t>
+        </is>
+      </c>
+      <c r="AF9" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="AG9" t="inlineStr">
+        <is>
+          <t>40.0</t>
+        </is>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>2026-09-03 00:00:00</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AL9" t="inlineStr">
+        <is>
+          <t>2026-09-08 00:00:00</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="AN9" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>7.0</t>
+        </is>
+      </c>
+      <c r="AP9" t="inlineStr">
+        <is>
+          <t>7.0</t>
+        </is>
+      </c>
+      <c r="AQ9" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AR9" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AS9" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AU9" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="AV9" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>4.0</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>9.0</t>
+        </is>
+      </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>14.0</t>
+        </is>
+      </c>
+      <c r="BA9" t="inlineStr">
+        <is>
+          <t>14.0</t>
+        </is>
+      </c>
+      <c r="BB9" t="inlineStr">
+        <is>
+          <t>14.0</t>
+        </is>
+      </c>
+      <c r="BC9" t="inlineStr">
+        <is>
+          <t>強勢</t>
+        </is>
+      </c>
+      <c r="BD9" t="inlineStr">
+        <is>
+          <t>強勢</t>
+        </is>
+      </c>
+      <c r="BE9" t="inlineStr">
+        <is>
+          <t>58.3</t>
+        </is>
+      </c>
+      <c r="BF9" t="inlineStr">
+        <is>
+          <t>17850578.0</t>
+        </is>
+      </c>
+      <c r="BG9" t="inlineStr">
+        <is>
+          <t>1360796.0</t>
+        </is>
+      </c>
+      <c r="BH9" t="inlineStr">
+        <is>
+          <t>4418171.0</t>
+        </is>
+      </c>
+      <c r="BI9" t="inlineStr">
+        <is>
+          <t>-3057375.0</t>
+        </is>
+      </c>
+      <c r="BJ9" t="inlineStr">
+        <is>
+          <t>-284018.0</t>
+        </is>
+      </c>
+      <c r="BK9" t="inlineStr">
+        <is>
+          <t>14509185.0</t>
+        </is>
+      </c>
+      <c r="BL9" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="BM9" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="BN9" t="inlineStr">
+        <is>
+          <t>-1.0</t>
+        </is>
+      </c>
+      <c r="BO9" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="BP9" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="BQ9" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="BR9" t="inlineStr">
+        <is>
+          <t>-0.12</t>
+        </is>
+      </c>
+      <c r="BS9" t="inlineStr">
+        <is>
+          <t>2026/07/20</t>
+        </is>
+      </c>
+      <c r="BT9" t="inlineStr">
+        <is>
+          <t>139.0</t>
+        </is>
+      </c>
+      <c r="BU9" t="inlineStr">
+        <is>
+          <t>2026/04/16</t>
+        </is>
+      </c>
+      <c r="BV9" t="inlineStr">
+        <is>
+          <t>136.5</t>
+        </is>
+      </c>
+      <c r="BW9" t="inlineStr">
+        <is>
+          <t>2026/10/07</t>
+        </is>
+      </c>
+      <c r="BX9" t="inlineStr">
         <is>
           <t>145.5</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>-0.03295367443261963</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>99.0</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="R9" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>弱勢整理</t>
-        </is>
-      </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>TrendType : 弱勢整理&lt;br&gt;TrendScore : 30&lt;br&gt;HH : False&lt;br&gt;HL : False&lt;br&gt;MA : True&lt;br&gt;VOL : True</t>
-        </is>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>140.375</t>
-        </is>
-      </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>147.6794687115415</t>
-        </is>
-      </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>133.0705312884585</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>0.104070791972096</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>0.003395282344531791</t>
-        </is>
-      </c>
-      <c r="AA9" t="inlineStr">
-        <is>
-          <t>0.004384515128182942</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>0.02031726359982433</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>0.05137843623728422</t>
-        </is>
-      </c>
-      <c r="AD9" t="inlineStr">
-        <is>
-          <t>2.079004612848601</t>
-        </is>
-      </c>
-      <c r="AE9" t="inlineStr">
-        <is>
-          <t>2026-09-02 00:00:00</t>
-        </is>
-      </c>
-      <c r="AF9" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="AG9" t="inlineStr">
-        <is>
-          <t>40.0</t>
-        </is>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>20.0</t>
-        </is>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>2026-09-03 00:00:00</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AL9" t="inlineStr">
-        <is>
-          <t>2026-09-08 00:00:00</t>
-        </is>
-      </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AN9" t="inlineStr">
-        <is>
-          <t>7.0</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>7.0</t>
-        </is>
-      </c>
-      <c r="AP9" t="inlineStr">
-        <is>
-          <t>8.0</t>
-        </is>
-      </c>
-      <c r="AQ9" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AR9" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AS9" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AT9" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AU9" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="AV9" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="AW9" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
-      </c>
-      <c r="AX9" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
-      </c>
-      <c r="AY9" t="inlineStr">
-        <is>
-          <t>10.0</t>
-        </is>
-      </c>
-      <c r="AZ9" t="inlineStr">
-        <is>
-          <t>14.0</t>
-        </is>
-      </c>
-      <c r="BA9" t="inlineStr">
-        <is>
-          <t>14.0</t>
-        </is>
-      </c>
-      <c r="BB9" t="inlineStr">
-        <is>
-          <t>14.0</t>
-        </is>
-      </c>
-      <c r="BC9" t="inlineStr">
-        <is>
-          <t>強勢</t>
-        </is>
-      </c>
-      <c r="BD9" t="inlineStr">
-        <is>
-          <t>強勢</t>
-        </is>
-      </c>
-      <c r="BE9" t="inlineStr">
-        <is>
-          <t>58.3</t>
-        </is>
-      </c>
-      <c r="BF9" t="inlineStr">
-        <is>
-          <t>18108850.0</t>
-        </is>
-      </c>
-      <c r="BG9" t="inlineStr">
-        <is>
-          <t>1199596.0</t>
-        </is>
-      </c>
-      <c r="BH9" t="inlineStr">
-        <is>
-          <t>4011399.0</t>
-        </is>
-      </c>
-      <c r="BI9" t="inlineStr">
-        <is>
-          <t>-2811803.0</t>
-        </is>
-      </c>
-      <c r="BJ9" t="inlineStr">
-        <is>
-          <t>-248002.0</t>
-        </is>
-      </c>
-      <c r="BK9" t="inlineStr">
-        <is>
-          <t>15049045.0</t>
-        </is>
-      </c>
-      <c r="BL9" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
-      </c>
-      <c r="BM9" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
-      </c>
-      <c r="BN9" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="BO9" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="BP9" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="BQ9" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="BR9" t="inlineStr">
-        <is>
-          <t>-0.07</t>
-        </is>
-      </c>
-      <c r="BS9" t="inlineStr">
-        <is>
-          <t>2026/07/20</t>
-        </is>
-      </c>
-      <c r="BT9" t="inlineStr">
-        <is>
-          <t>139.0</t>
-        </is>
-      </c>
-      <c r="BU9" t="inlineStr">
-        <is>
-          <t>2026/04/16</t>
-        </is>
-      </c>
-      <c r="BV9" t="inlineStr">
-        <is>
-          <t>136.5</t>
-        </is>
-      </c>
-      <c r="BW9" t="inlineStr">
+      <c r="BY9" t="inlineStr">
         <is>
           <t>2026/08/05</t>
         </is>
       </c>
-      <c r="BX9" t="inlineStr">
+      <c r="BZ9" t="inlineStr">
         <is>
           <t>137.0</t>
         </is>
       </c>
-      <c r="BY9" t="inlineStr">
-        <is>
-          <t>2026/06/24</t>
-        </is>
-      </c>
-      <c r="BZ9" t="inlineStr">
-        <is>
-          <t>143.5</t>
-        </is>
-      </c>
       <c r="CA9" t="inlineStr">
         <is>
           <t>2026-09-18 00:00:00</t>
@@ -8730,17 +8730,17 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="CC9" t="inlineStr">
         <is>
-          <t>13.90</t>
+          <t>10.53</t>
         </is>
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>0.69</t>
+          <t>-0.69</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
@@ -8751,17 +8751,17 @@
       <c r="CF9" t="inlineStr"/>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>50</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
         <is>
-          <t>7053</t>
+          <t>7081</t>
         </is>
       </c>
       <c r="CI9" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>83.33</t>
         </is>
       </c>
       <c r="CJ9" t="inlineStr">
@@ -8770,19 +8770,19 @@
         </is>
       </c>
       <c r="CK9" t="n">
-        <v>0.28</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="CL9" t="n">
-        <v>3.37</v>
+        <v>3.02</v>
       </c>
       <c r="CM9" t="inlineStr">
         <is>
-          <t>1.21</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="CN9" t="inlineStr">
         <is>
-          <t>-0.73</t>
+          <t>-0.63</t>
         </is>
       </c>
       <c r="CO9" t="inlineStr">
@@ -8792,69 +8792,69 @@
       </c>
       <c r="CP9" t="inlineStr">
         <is>
-          <t>143.5</t>
+          <t>144.05</t>
         </is>
       </c>
       <c r="CQ9" t="inlineStr">
         <is>
-          <t>140.38</t>
+          <t>140.85</t>
         </is>
       </c>
       <c r="CR9" t="inlineStr">
         <is>
-          <t>138.69</t>
+          <t>138.87</t>
         </is>
       </c>
       <c r="CS9" t="inlineStr">
         <is>
-          <t>139.71</t>
+          <t>139.75</t>
         </is>
       </c>
       <c r="CT9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>135.7708333333333</t>
         </is>
       </c>
       <c r="CU9" t="inlineStr">
         <is>
-          <t>0.002764340013821753</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="CV9" t="inlineStr">
         <is>
-          <t>0.004198740377886701</t>
+          <t>0.003832752613240453</t>
         </is>
       </c>
       <c r="CW9" t="inlineStr">
         <is>
-          <t>0.003395282344531791</t>
+          <t>0.00338379341050743</t>
         </is>
       </c>
       <c r="CX9" t="inlineStr">
         <is>
-          <t>0.001805836463449895</t>
+          <t>0.001297858533420015</t>
         </is>
       </c>
       <c r="CY9" t="inlineStr">
         <is>
-          <t>0.0004475474400287283</t>
+          <t>0.0002684083385522396</t>
         </is>
       </c>
       <c r="CZ9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0003223380251424768</t>
         </is>
       </c>
       <c r="DA9" t="inlineStr">
         <is>
-          <t>39.98</t>
+          <t>29.64</t>
         </is>
       </c>
       <c r="DB9" t="n">
         <v>2.14</v>
       </c>
       <c r="DC9" t="n">
-        <v>1.53</v>
+        <v>1.65</v>
       </c>
       <c r="DD9" t="inlineStr">
         <is>
@@ -8863,7 +8863,7 @@
       </c>
       <c r="DE9" t="inlineStr">
         <is>
-          <t>-19.18</t>
+          <t>-12.71</t>
         </is>
       </c>
       <c r="DF9" t="inlineStr">
@@ -8873,48 +8873,48 @@
       </c>
       <c r="DG9" t="inlineStr">
         <is>
-          <t>2517415638.848781</t>
+          <t>2214561876.963068</t>
         </is>
       </c>
       <c r="DH9" t="inlineStr">
         <is>
-          <t>1208391141.0</t>
+          <t>918019598.0</t>
         </is>
       </c>
       <c r="DI9" t="n">
-        <v>1915789923.8</v>
+        <v>1659195852.6</v>
       </c>
       <c r="DJ9" t="inlineStr">
         <is>
-          <t>1981073577.5</t>
+          <t>1973672854.5</t>
         </is>
       </c>
       <c r="DK9" t="inlineStr">
         <is>
-          <t>1491726965.1</t>
+          <t>1482010386.8</t>
         </is>
       </c>
       <c r="DL9" t="n">
-        <v>1845563731.54</v>
+        <v>1806077677.02</v>
       </c>
       <c r="DM9" t="inlineStr">
         <is>
-          <t>2053704109.375</t>
+          <t>2030537576.35</t>
         </is>
       </c>
       <c r="DN9" t="inlineStr">
         <is>
-          <t>83180126.28506301</t>
+          <t>61069185.48961079</t>
         </is>
       </c>
       <c r="DO9" t="inlineStr">
         <is>
-          <t>2120011.574340582</t>
+          <t>-60540988.90475464</t>
         </is>
       </c>
       <c r="DP9" t="inlineStr">
         <is>
-          <t>1208391141.0</t>
+          <t>918019598.0</t>
         </is>
       </c>
       <c r="DQ9" t="inlineStr">
@@ -8934,7 +8934,7 @@
       </c>
       <c r="DT9" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>1.05</t>
         </is>
       </c>
       <c r="DU9" t="inlineStr">
@@ -8979,7 +8979,7 @@
       </c>
       <c r="EC9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="ED9" t="inlineStr">
@@ -8989,7 +8989,7 @@
       </c>
       <c r="EE9" t="inlineStr">
         <is>
-          <t>3.08</t>
+          <t>3.07</t>
         </is>
       </c>
       <c r="EF9" t="inlineStr">
@@ -9019,7 +9019,7 @@
       </c>
       <c r="EK9" t="inlineStr">
         <is>
-          <t>84.97</t>
+          <t>85.4</t>
         </is>
       </c>
       <c r="EL9" t="inlineStr">
@@ -9044,27 +9044,27 @@
       </c>
       <c r="EP9" t="inlineStr">
         <is>
+          <t>145.5</t>
+        </is>
+      </c>
+      <c r="EQ9" t="inlineStr">
+        <is>
+          <t>146.0</t>
+        </is>
+      </c>
+      <c r="ER9" t="inlineStr">
+        <is>
           <t>145.0</t>
         </is>
       </c>
-      <c r="EQ9" t="inlineStr">
-        <is>
-          <t>145.5</t>
-        </is>
-      </c>
-      <c r="ER9" t="inlineStr">
-        <is>
-          <t>144.5</t>
-        </is>
-      </c>
       <c r="ES9" t="inlineStr">
         <is>
-          <t>145.5</t>
+          <t>145.0</t>
         </is>
       </c>
       <c r="ET9" t="inlineStr">
         <is>
-          <t>129.5</t>
+          <t>128.0</t>
         </is>
       </c>
       <c r="EU9" t="inlineStr">
@@ -9084,67 +9084,67 @@
       </c>
       <c r="EX9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="EY9" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="EZ9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FA9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FB9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FC9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FD9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="FE9" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14.0</t>
         </is>
       </c>
       <c r="FF9" t="inlineStr">
         <is>
-          <t>1.284276525544721</t>
+          <t>1.119557506059444</t>
         </is>
       </c>
       <c r="FG9" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="FH9" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="FI9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="FJ9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FK9" t="inlineStr">
@@ -9336,7 +9336,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>5469.034</t>
+          <t>8326.189</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -9346,7 +9346,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>145.0</t>
+          <t>145.5</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -9356,7 +9356,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>0.34</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -9366,7 +9366,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>0.05100096628122345</t>
+          <t>-0.03295367443261963</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -9411,7 +9411,7 @@
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>30.0</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
@@ -9426,47 +9426,47 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>139.9</t>
+          <t>140.375</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>147.0347924397203</t>
+          <t>147.6794687115433</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>132.7652075602797</t>
+          <t>133.0705312884567</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>0.1019984623262371</t>
+          <t>0.1040707919721211</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>0.003047141064707048</t>
+          <t>0.003395282344531791</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>0.004760596003286599</t>
+          <t>0.004384515128183608</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>0.03642388578015932</t>
+          <t>0.02031726359983477</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>0.05137843623728422</t>
+          <t>0.0479762948677207</t>
         </is>
       </c>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>2.179114382213557</t>
+          <t>2.079004612847744</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
@@ -9486,7 +9486,7 @@
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
@@ -9511,7 +9511,7 @@
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
@@ -9521,14 +9521,14 @@
       </c>
       <c r="AO10" t="inlineStr">
         <is>
+          <t>7.0</t>
+        </is>
+      </c>
+      <c r="AP10" t="inlineStr">
+        <is>
           <t>8.0</t>
         </is>
       </c>
-      <c r="AP10" t="inlineStr">
-        <is>
-          <t>7.0</t>
-        </is>
-      </c>
       <c r="AQ10" t="inlineStr">
         <is>
           <t>False</t>
@@ -9576,17 +9576,17 @@
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>13.0</t>
+          <t>14.0</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>13.0</t>
+          <t>14.0</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>13.0</t>
+          <t>14.0</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
@@ -9606,32 +9606,32 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>18108850.0</t>
+          <t>17850578.0</t>
         </is>
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>1199596.0</t>
+          <t>1360796.0</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>4011399.0</t>
+          <t>4418171.0</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
         <is>
-          <t>-2811803.0</t>
+          <t>-3057375.0</t>
         </is>
       </c>
       <c r="BJ10" t="inlineStr">
         <is>
-          <t>-248002.0</t>
+          <t>-284018.0</t>
         </is>
       </c>
       <c r="BK10" t="inlineStr">
         <is>
-          <t>15049045.0</t>
+          <t>14509185.0</t>
         </is>
       </c>
       <c r="BL10" t="inlineStr">
@@ -9646,7 +9646,7 @@
       </c>
       <c r="BN10" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="BO10" t="inlineStr">
@@ -9666,7 +9666,7 @@
       </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>-0.09</t>
+          <t>-0.07</t>
         </is>
       </c>
       <c r="BS10" t="inlineStr">
@@ -9691,24 +9691,24 @@
       </c>
       <c r="BW10" t="inlineStr">
         <is>
+          <t>2026/10/07</t>
+        </is>
+      </c>
+      <c r="BX10" t="inlineStr">
+        <is>
+          <t>145.5</t>
+        </is>
+      </c>
+      <c r="BY10" t="inlineStr">
+        <is>
           <t>2026/08/05</t>
         </is>
       </c>
-      <c r="BX10" t="inlineStr">
+      <c r="BZ10" t="inlineStr">
         <is>
           <t>137.0</t>
         </is>
       </c>
-      <c r="BY10" t="inlineStr">
-        <is>
-          <t>2026/06/24</t>
-        </is>
-      </c>
-      <c r="BZ10" t="inlineStr">
-        <is>
-          <t>143.5</t>
-        </is>
-      </c>
       <c r="CA10" t="inlineStr">
         <is>
           <t>2026-09-18 00:00:00</t>
@@ -9716,17 +9716,17 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="CC10" t="inlineStr">
         <is>
-          <t>9.13</t>
+          <t>13.90</t>
         </is>
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>1.40</t>
+          <t>0.69</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
@@ -9737,177 +9737,177 @@
       <c r="CF10" t="inlineStr"/>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>50</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
         <is>
-          <t>7053</t>
+          <t>7081</t>
         </is>
       </c>
       <c r="CI10" t="inlineStr">
         <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="CJ10" t="inlineStr">
+        <is>
           <t>91.67</t>
         </is>
       </c>
-      <c r="CJ10" t="inlineStr">
-        <is>
-          <t>91.67</t>
-        </is>
-      </c>
       <c r="CK10" t="n">
-        <v>0.21</v>
+        <v>0.28</v>
       </c>
       <c r="CL10" t="n">
-        <v>3.43</v>
+        <v>3.37</v>
       </c>
       <c r="CM10" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>1.21</t>
         </is>
       </c>
       <c r="CN10" t="inlineStr">
         <is>
-          <t>-0.87</t>
+          <t>-0.73</t>
         </is>
       </c>
       <c r="CO10" t="inlineStr">
         <is>
-          <t>144.7</t>
+          <t>145.1</t>
         </is>
       </c>
       <c r="CP10" t="inlineStr">
         <is>
-          <t>142.9</t>
+          <t>143.5</t>
         </is>
       </c>
       <c r="CQ10" t="inlineStr">
         <is>
-          <t>139.9</t>
+          <t>140.38</t>
         </is>
       </c>
       <c r="CR10" t="inlineStr">
         <is>
-          <t>138.44</t>
+          <t>138.69</t>
         </is>
       </c>
       <c r="CS10" t="inlineStr">
         <is>
-          <t>139.65</t>
+          <t>139.71</t>
         </is>
       </c>
       <c r="CT10" t="inlineStr">
         <is>
+          <t>135.7270833333333</t>
+        </is>
+      </c>
+      <c r="CU10" t="inlineStr">
+        <is>
+          <t>0.002764340013821753</t>
+        </is>
+      </c>
+      <c r="CV10" t="inlineStr">
+        <is>
+          <t>0.004198740377886701</t>
+        </is>
+      </c>
+      <c r="CW10" t="inlineStr">
+        <is>
+          <t>0.003395282344531791</t>
+        </is>
+      </c>
+      <c r="CX10" t="inlineStr">
+        <is>
+          <t>0.001805836463449895</t>
+        </is>
+      </c>
+      <c r="CY10" t="inlineStr">
+        <is>
+          <t>0.0004475474400287283</t>
+        </is>
+      </c>
+      <c r="CZ10" t="inlineStr">
+        <is>
+          <t>0.0003685220729365835</t>
+        </is>
+      </c>
+      <c r="DA10" t="inlineStr">
+        <is>
+          <t>39.98</t>
+        </is>
+      </c>
+      <c r="DB10" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="DC10" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="DD10" t="inlineStr">
+        <is>
+          <t>1.9</t>
+        </is>
+      </c>
+      <c r="DE10" t="inlineStr">
+        <is>
+          <t>-19.18</t>
+        </is>
+      </c>
+      <c r="DF10" t="inlineStr">
+        <is>
+          <t>2026/08/21</t>
+        </is>
+      </c>
+      <c r="DG10" t="inlineStr">
+        <is>
+          <t>2214561876.963068</t>
+        </is>
+      </c>
+      <c r="DH10" t="inlineStr">
+        <is>
+          <t>1208391141.0</t>
+        </is>
+      </c>
+      <c r="DI10" t="n">
+        <v>1915789923.8</v>
+      </c>
+      <c r="DJ10" t="inlineStr">
+        <is>
+          <t>1981073577.5</t>
+        </is>
+      </c>
+      <c r="DK10" t="inlineStr">
+        <is>
+          <t>1491726965.1</t>
+        </is>
+      </c>
+      <c r="DL10" t="n">
+        <v>1845563731.54</v>
+      </c>
+      <c r="DM10" t="inlineStr">
+        <is>
+          <t>2053704109.375</t>
+        </is>
+      </c>
+      <c r="DN10" t="inlineStr">
+        <is>
+          <t>83180126.28858632</t>
+        </is>
+      </c>
+      <c r="DO10" t="inlineStr">
+        <is>
+          <t>2120011.575097084</t>
+        </is>
+      </c>
+      <c r="DP10" t="inlineStr">
+        <is>
+          <t>1208391141.0</t>
+        </is>
+      </c>
+      <c r="DQ10" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="CU10" t="inlineStr">
-        <is>
-          <t>0.00207756232686962</t>
-        </is>
-      </c>
-      <c r="CV10" t="inlineStr">
-        <is>
-          <t>0.004216444132115305</t>
-        </is>
-      </c>
-      <c r="CW10" t="inlineStr">
-        <is>
-          <t>0.003047141064707048</t>
-        </is>
-      </c>
-      <c r="CX10" t="inlineStr">
-        <is>
-          <t>0.001736613603473325</t>
-        </is>
-      </c>
-      <c r="CY10" t="inlineStr">
-        <is>
-          <t>0.0007165890361877647</t>
-        </is>
-      </c>
-      <c r="CZ10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="DA10" t="inlineStr">
-        <is>
-          <t>49.52</t>
-        </is>
-      </c>
-      <c r="DB10" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="DC10" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="DD10" t="inlineStr">
-        <is>
-          <t>1.9</t>
-        </is>
-      </c>
-      <c r="DE10" t="inlineStr">
-        <is>
-          <t>-27.26</t>
-        </is>
-      </c>
-      <c r="DF10" t="inlineStr">
-        <is>
-          <t>2026/08/21</t>
-        </is>
-      </c>
-      <c r="DG10" t="inlineStr">
-        <is>
-          <t>2517415638.848781</t>
-        </is>
-      </c>
-      <c r="DH10" t="inlineStr">
-        <is>
-          <t>789765672.0</t>
-        </is>
-      </c>
-      <c r="DI10" t="n">
-        <v>2098161079.8</v>
-      </c>
-      <c r="DJ10" t="inlineStr">
-        <is>
-          <t>1996345528.8</t>
-        </is>
-      </c>
-      <c r="DK10" t="inlineStr">
-        <is>
-          <t>1491758387.733333</t>
-        </is>
-      </c>
-      <c r="DL10" t="n">
-        <v>1849876216.36</v>
-      </c>
-      <c r="DM10" t="inlineStr">
-        <is>
-          <t>2086692476.8625</t>
-        </is>
-      </c>
-      <c r="DN10" t="inlineStr">
-        <is>
-          <t>97918328.95973982</t>
-        </is>
-      </c>
-      <c r="DO10" t="inlineStr">
-        <is>
-          <t>60448775.09633851</t>
-        </is>
-      </c>
-      <c r="DP10" t="inlineStr">
-        <is>
-          <t>789765672.0</t>
-        </is>
-      </c>
-      <c r="DQ10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="DR10" t="inlineStr">
         <is>
           <t>143.5</t>
@@ -9920,7 +9920,7 @@
       </c>
       <c r="DT10" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="DU10" t="inlineStr">
@@ -9965,7 +9965,7 @@
       </c>
       <c r="EC10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
         </is>
       </c>
       <c r="ED10" t="inlineStr">
@@ -9975,7 +9975,7 @@
       </c>
       <c r="EE10" t="inlineStr">
         <is>
-          <t>3.07</t>
+          <t>3.08</t>
         </is>
       </c>
       <c r="EF10" t="inlineStr">
@@ -10005,7 +10005,7 @@
       </c>
       <c r="EK10" t="inlineStr">
         <is>
-          <t>84.97</t>
+          <t>85.4</t>
         </is>
       </c>
       <c r="EL10" t="inlineStr">
@@ -10035,22 +10035,22 @@
       </c>
       <c r="EQ10" t="inlineStr">
         <is>
-          <t>145.0</t>
+          <t>145.5</t>
         </is>
       </c>
       <c r="ER10" t="inlineStr">
         <is>
-          <t>143.0</t>
+          <t>144.5</t>
         </is>
       </c>
       <c r="ES10" t="inlineStr">
         <is>
-          <t>145.0</t>
+          <t>145.5</t>
         </is>
       </c>
       <c r="ET10" t="inlineStr">
         <is>
-          <t>129.5</t>
+          <t>128.0</t>
         </is>
       </c>
       <c r="EU10" t="inlineStr">
@@ -10070,67 +10070,67 @@
       </c>
       <c r="EX10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="EY10" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="EZ10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FA10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FB10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FC10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FD10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="FE10" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>15.0</t>
         </is>
       </c>
       <c r="FF10" t="inlineStr">
         <is>
-          <t>1.406501949010705</t>
+          <t>1.284276525544721</t>
         </is>
       </c>
       <c r="FG10" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="FH10" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="FI10" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="FJ10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="FK10" t="inlineStr">

--- a/Result/checksun_type/電信.xlsx
+++ b/Result/checksun_type/電信.xlsx
@@ -1443,12 +1443,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.69</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>7080.591</t>
+          <t>9157.281</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -1458,359 +1458,359 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
+          <t>146.5</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>-0.03876808142516339</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>99.0</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>轉強</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>TrendType : 轉強&lt;br&gt;TrendScore : 60&lt;br&gt;HH : True&lt;br&gt;HL : False&lt;br&gt;MA : True&lt;br&gt;VOL : False</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>144.075</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>148.246015274611</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>139.9039847253889</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>0.05790061113463198</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>0.002609603340292255</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>-0.0002388145425843424</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>-0.0919512899515399</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>0.05147900810379896</t>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>0.7578569091489935</t>
+        </is>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>2026-09-02 00:00:00</t>
+        </is>
+      </c>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AG2" t="inlineStr">
+        <is>
+          <t>30.0</t>
+        </is>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>2026-09-03 00:00:00</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AL2" t="inlineStr">
+        <is>
+          <t>2026-09-08 00:00:00</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AN2" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>4.0</t>
+        </is>
+      </c>
+      <c r="AP2" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="AQ2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AR2" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AS2" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AT2" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AU2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AV2" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>7.0</t>
+        </is>
+      </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>17.0</t>
+        </is>
+      </c>
+      <c r="BA2" t="inlineStr">
+        <is>
+          <t>20.0</t>
+        </is>
+      </c>
+      <c r="BB2" t="inlineStr">
+        <is>
+          <t>20.0</t>
+        </is>
+      </c>
+      <c r="BC2" t="inlineStr">
+        <is>
+          <t>盤整</t>
+        </is>
+      </c>
+      <c r="BD2" t="inlineStr">
+        <is>
+          <t>盤整</t>
+        </is>
+      </c>
+      <c r="BE2" t="inlineStr">
+        <is>
+          <t>58.3</t>
+        </is>
+      </c>
+      <c r="BF2" t="inlineStr">
+        <is>
+          <t>17134672.0</t>
+        </is>
+      </c>
+      <c r="BG2" t="inlineStr">
+        <is>
+          <t>1355796.0</t>
+        </is>
+      </c>
+      <c r="BH2" t="inlineStr">
+        <is>
+          <t>4433570.0</t>
+        </is>
+      </c>
+      <c r="BI2" t="inlineStr">
+        <is>
+          <t>-3077774.0</t>
+        </is>
+      </c>
+      <c r="BJ2" t="inlineStr">
+        <is>
+          <t>-302018.0</t>
+        </is>
+      </c>
+      <c r="BK2" t="inlineStr">
+        <is>
+          <t>13754880.0</t>
+        </is>
+      </c>
+      <c r="BL2" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="BM2" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="BN2" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="BO2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="BP2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="BQ2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="BR2" t="inlineStr">
+        <is>
+          <t>0.02</t>
+        </is>
+      </c>
+      <c r="BS2" t="inlineStr">
+        <is>
+          <t>2026/07/20</t>
+        </is>
+      </c>
+      <c r="BT2" t="inlineStr">
+        <is>
+          <t>139.0</t>
+        </is>
+      </c>
+      <c r="BU2" t="inlineStr">
+        <is>
+          <t>2026/04/16</t>
+        </is>
+      </c>
+      <c r="BV2" t="inlineStr">
+        <is>
+          <t>136.5</t>
+        </is>
+      </c>
+      <c r="BW2" t="inlineStr">
+        <is>
+          <t>2026/10/07</t>
+        </is>
+      </c>
+      <c r="BX2" t="inlineStr">
+        <is>
           <t>145.5</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>-0.010140903336412965</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>99.0</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>60.0</t>
-        </is>
-      </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>轉強</t>
-        </is>
-      </c>
-      <c r="U2" t="inlineStr">
-        <is>
-          <t>TrendType : 轉強&lt;br&gt;TrendScore : 60&lt;br&gt;HH : True&lt;br&gt;HL : False&lt;br&gt;MA : True&lt;br&gt;VOL : False</t>
-        </is>
-      </c>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t>143.7</t>
-        </is>
-      </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>148.2814270357867</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>139.1185729642133</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>0.0637637722447697</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>0.002616431187859813</t>
-        </is>
-      </c>
-      <c r="AA2" t="inlineStr">
-        <is>
-          <t>-0.001325129872452147</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>-0.1132715312464632</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>0.0479762948677207</t>
-        </is>
-      </c>
-      <c r="AD2" t="inlineStr">
-        <is>
-          <t>0.8505447270309883</t>
-        </is>
-      </c>
-      <c r="AE2" t="inlineStr">
-        <is>
-          <t>2026-09-02 00:00:00</t>
-        </is>
-      </c>
-      <c r="AF2" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AG2" t="inlineStr">
-        <is>
-          <t>35.0</t>
-        </is>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>2026-09-03 00:00:00</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AL2" t="inlineStr">
-        <is>
-          <t>2026-09-08 00:00:00</t>
-        </is>
-      </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AN2" t="inlineStr">
-        <is>
-          <t>4.0</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
-      </c>
-      <c r="AP2" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
-      </c>
-      <c r="AQ2" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AR2" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AS2" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AT2" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AU2" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AV2" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AW2" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
-      </c>
-      <c r="AX2" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>7.0</t>
-        </is>
-      </c>
-      <c r="AZ2" t="inlineStr">
-        <is>
-          <t>17.0</t>
-        </is>
-      </c>
-      <c r="BA2" t="inlineStr">
-        <is>
-          <t>19.0</t>
-        </is>
-      </c>
-      <c r="BB2" t="inlineStr">
-        <is>
-          <t>19.0</t>
-        </is>
-      </c>
-      <c r="BC2" t="inlineStr">
-        <is>
-          <t>盤整</t>
-        </is>
-      </c>
-      <c r="BD2" t="inlineStr">
-        <is>
-          <t>盤整</t>
-        </is>
-      </c>
-      <c r="BE2" t="inlineStr">
-        <is>
-          <t>58.3</t>
-        </is>
-      </c>
-      <c r="BF2" t="inlineStr">
-        <is>
-          <t>17850578.0</t>
-        </is>
-      </c>
-      <c r="BG2" t="inlineStr">
-        <is>
-          <t>1360796.0</t>
-        </is>
-      </c>
-      <c r="BH2" t="inlineStr">
-        <is>
-          <t>4418171.0</t>
-        </is>
-      </c>
-      <c r="BI2" t="inlineStr">
-        <is>
-          <t>-3057375.0</t>
-        </is>
-      </c>
-      <c r="BJ2" t="inlineStr">
-        <is>
-          <t>-284018.0</t>
-        </is>
-      </c>
-      <c r="BK2" t="inlineStr">
-        <is>
-          <t>14509185.0</t>
-        </is>
-      </c>
-      <c r="BL2" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
-      </c>
-      <c r="BM2" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
-      </c>
-      <c r="BN2" t="inlineStr">
-        <is>
-          <t>-1.0</t>
-        </is>
-      </c>
-      <c r="BO2" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="BP2" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="BQ2" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="BR2" t="inlineStr">
-        <is>
-          <t>-0.05</t>
-        </is>
-      </c>
-      <c r="BS2" t="inlineStr">
-        <is>
-          <t>2026/07/20</t>
-        </is>
-      </c>
-      <c r="BT2" t="inlineStr">
-        <is>
-          <t>139.0</t>
-        </is>
-      </c>
-      <c r="BU2" t="inlineStr">
-        <is>
-          <t>2026/04/16</t>
-        </is>
-      </c>
-      <c r="BV2" t="inlineStr">
-        <is>
-          <t>136.5</t>
-        </is>
-      </c>
-      <c r="BW2" t="inlineStr">
-        <is>
-          <t>2026/10/07</t>
-        </is>
-      </c>
-      <c r="BX2" t="inlineStr">
-        <is>
-          <t>145.5</t>
-        </is>
-      </c>
       <c r="BY2" t="inlineStr">
         <is>
           <t>2026/08/05</t>
@@ -1828,17 +1828,17 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="CC2" t="inlineStr">
         <is>
-          <t>11.82</t>
+          <t>15.28</t>
         </is>
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>1.04</t>
+          <t>1.03</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
@@ -1849,110 +1849,110 @@
       <c r="CF2" t="inlineStr"/>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>67</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
         <is>
-          <t>7081</t>
+          <t>9157</t>
         </is>
       </c>
       <c r="CI2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="CJ2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>86.67</t>
         </is>
       </c>
       <c r="CK2" t="n">
-        <v>-0.07000000000000001</v>
+        <v>0.48</v>
       </c>
       <c r="CL2" t="n">
-        <v>1.32</v>
+        <v>1.2</v>
       </c>
       <c r="CM2" t="inlineStr">
         <is>
-          <t>2.83</t>
+          <t>3.02</t>
         </is>
       </c>
       <c r="CN2" t="inlineStr">
         <is>
-          <t>-0.21</t>
+          <t>-0.14</t>
         </is>
       </c>
       <c r="CO2" t="inlineStr">
         <is>
-          <t>145.6</t>
+          <t>145.8</t>
         </is>
       </c>
       <c r="CP2" t="inlineStr">
         <is>
-          <t>145.1</t>
+          <t>145.25</t>
         </is>
       </c>
       <c r="CQ2" t="inlineStr">
         <is>
-          <t>143.7</t>
+          <t>144.07</t>
         </is>
       </c>
       <c r="CR2" t="inlineStr">
         <is>
-          <t>139.74</t>
+          <t>139.85</t>
         </is>
       </c>
       <c r="CS2" t="inlineStr">
         <is>
-          <t>140.03</t>
+          <t>140.05</t>
         </is>
       </c>
       <c r="CT2" t="inlineStr">
         <is>
-          <t>136.1125</t>
+          <t>0</t>
         </is>
       </c>
       <c r="CU2" t="inlineStr">
         <is>
-          <t>0.002754820936639257</t>
+          <t>0.001373626373626591</t>
         </is>
       </c>
       <c r="CV2" t="inlineStr">
         <is>
-          <t>0.0006896551724138167</t>
+          <t>0.001033769813921559</t>
         </is>
       </c>
       <c r="CW2" t="inlineStr">
         <is>
-          <t>0.002616431187859813</t>
+          <t>0.002609603340292255</t>
         </is>
       </c>
       <c r="CX2" t="inlineStr">
         <is>
-          <t>0.000716127184188009</t>
+          <t>0.0007871761843423197</t>
         </is>
       </c>
       <c r="CY2" t="inlineStr">
         <is>
-          <t>4.463488662742598e-05</t>
+          <t>0.0001338986833296918</t>
         </is>
       </c>
       <c r="CZ2" t="inlineStr">
         <is>
-          <t>0.0003827956330675342</t>
+          <t>0</t>
         </is>
       </c>
       <c r="DA2" t="inlineStr">
         <is>
-          <t>-1.50</t>
+          <t>-0.64</t>
         </is>
       </c>
       <c r="DB2" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="DC2" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="DD2" t="inlineStr">
         <is>
@@ -1961,7 +1961,7 @@
       </c>
       <c r="DE2" t="inlineStr">
         <is>
-          <t>-2.54</t>
+          <t>-2.70</t>
         </is>
       </c>
       <c r="DF2" t="inlineStr">
@@ -1971,48 +1971,48 @@
       </c>
       <c r="DG2" t="inlineStr">
         <is>
-          <t>2214561876.963068</t>
+          <t>2510241792.666667</t>
         </is>
       </c>
       <c r="DH2" t="inlineStr">
         <is>
-          <t>1027931012.0</t>
+          <t>1338632400.0</t>
         </is>
       </c>
       <c r="DI2" t="n">
-        <v>1198822702.4</v>
+        <v>1216911023</v>
       </c>
       <c r="DJ2" t="inlineStr">
         <is>
-          <t>1211104395.0</t>
+          <t>1265991067.8</t>
         </is>
       </c>
       <c r="DK2" t="inlineStr">
         <is>
-          <t>1514483902.3</t>
+          <t>1538893271.133333</t>
         </is>
       </c>
       <c r="DL2" t="n">
-        <v>1587854042.56</v>
+        <v>1564334397.6</v>
       </c>
       <c r="DM2" t="inlineStr">
         <is>
-          <t>1954971026.825</t>
+          <t>1955293045.375</t>
         </is>
       </c>
       <c r="DN2" t="inlineStr">
         <is>
-          <t>-35595349.43602777</t>
+          <t>-44569788.20471825</t>
         </is>
       </c>
       <c r="DO2" t="inlineStr">
         <is>
-          <t>-110750317.6099069</t>
+          <t>-93929201.4258542</t>
         </is>
       </c>
       <c r="DP2" t="inlineStr">
         <is>
-          <t>1027931012.0</t>
+          <t>1338632400.0</t>
         </is>
       </c>
       <c r="DQ2" t="inlineStr">
@@ -2032,7 +2032,7 @@
       </c>
       <c r="DT2" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>2.09</t>
         </is>
       </c>
       <c r="DU2" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="EC2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="ED2" t="inlineStr">
@@ -2087,12 +2087,12 @@
       </c>
       <c r="EE2" t="inlineStr">
         <is>
-          <t>3.08</t>
+          <t>3.10</t>
         </is>
       </c>
       <c r="EF2" t="inlineStr">
         <is>
-          <t>3.57</t>
+          <t>3.55</t>
         </is>
       </c>
       <c r="EG2" t="inlineStr">
@@ -2102,7 +2102,7 @@
       </c>
       <c r="EH2" t="inlineStr">
         <is>
-          <t>28.59</t>
+          <t>28.78</t>
         </is>
       </c>
       <c r="EI2" t="inlineStr">
@@ -2117,12 +2117,12 @@
       </c>
       <c r="EK2" t="inlineStr">
         <is>
-          <t>85.4</t>
+          <t>84.4</t>
         </is>
       </c>
       <c r="EL2" t="inlineStr">
         <is>
-          <t>1128708</t>
+          <t>1136466</t>
         </is>
       </c>
       <c r="EM2" t="inlineStr">
@@ -2142,27 +2142,27 @@
       </c>
       <c r="EP2" t="inlineStr">
         <is>
-          <t>145.5</t>
+          <t>145.0</t>
         </is>
       </c>
       <c r="EQ2" t="inlineStr">
         <is>
-          <t>145.5</t>
+          <t>146.5</t>
         </is>
       </c>
       <c r="ER2" t="inlineStr">
         <is>
-          <t>144.0</t>
+          <t>145.0</t>
         </is>
       </c>
       <c r="ES2" t="inlineStr">
         <is>
-          <t>145.5</t>
+          <t>146.5</t>
         </is>
       </c>
       <c r="ET2" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>129.5</t>
         </is>
       </c>
       <c r="EU2" t="inlineStr">
@@ -2182,42 +2182,42 @@
       </c>
       <c r="EX2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="EY2" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>5</t>
         </is>
       </c>
       <c r="EZ2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FA2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FB2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FC2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FD2" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="FE2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FF2" t="inlineStr">
@@ -2227,22 +2227,22 @@
       </c>
       <c r="FG2" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="FH2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FI2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FJ2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FK2" t="inlineStr">
@@ -2419,7 +2419,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>【b1】</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -2434,7 +2434,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>7052.714</t>
+          <t>7080.591</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -2454,7 +2454,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.68</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>0.04819550174243172</t>
+          <t>-0.010140903336412965</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -2509,7 +2509,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>60.0</t>
+          <t>60</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -2524,47 +2524,47 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>143.325</t>
+          <t>143.7</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>148.4781799073893</t>
+          <t>148.2814270357823</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>138.1718200926107</t>
+          <t>139.1185729642176</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>0.07190901667384339</t>
+          <t>0.06376377224470918</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>0.002798670631450006</t>
+          <t>0.002616431187859813</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-0.0007149631119872657</t>
+          <t>-0.001325129872456365</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>-0.09199085545733376</t>
+          <t>-0.113271531246664</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>0.0479762948677207</t>
+          <t>0.05147900810379896</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>0.98527820932962</t>
+          <t>0.850544727030544</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
@@ -2609,24 +2609,24 @@
       </c>
       <c r="AM3" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AN3" t="inlineStr">
+        <is>
           <t>4.0</t>
         </is>
       </c>
-      <c r="AN3" t="inlineStr">
+      <c r="AO3" t="inlineStr">
         <is>
           <t>2.0</t>
         </is>
       </c>
-      <c r="AO3" t="inlineStr">
+      <c r="AP3" t="inlineStr">
         <is>
           <t>3.0</t>
         </is>
       </c>
-      <c r="AP3" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
-      </c>
       <c r="AQ3" t="inlineStr">
         <is>
           <t>False</t>
@@ -2664,7 +2664,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -2679,12 +2679,12 @@
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>18.0</t>
+          <t>19.0</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>18.0</t>
+          <t>19.0</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
@@ -2704,32 +2704,32 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>17850578.0</t>
+          <t>17134672.0</t>
         </is>
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>1360796.0</t>
+          <t>1355796.0</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>4418171.0</t>
+          <t>4433570.0</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
         <is>
-          <t>-3057375.0</t>
+          <t>-3077774.0</t>
         </is>
       </c>
       <c r="BJ3" t="inlineStr">
         <is>
-          <t>-284018.0</t>
+          <t>-302018.0</t>
         </is>
       </c>
       <c r="BK3" t="inlineStr">
         <is>
-          <t>14509185.0</t>
+          <t>13754880.0</t>
         </is>
       </c>
       <c r="BL3" t="inlineStr">
@@ -2744,7 +2744,7 @@
       </c>
       <c r="BN3" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="BO3" t="inlineStr">
@@ -2814,12 +2814,12 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="CC3" t="inlineStr">
         <is>
-          <t>11.77</t>
+          <t>11.82</t>
         </is>
       </c>
       <c r="CD3" t="inlineStr">
@@ -2835,12 +2835,12 @@
       <c r="CF3" t="inlineStr"/>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>67</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
         <is>
-          <t>7081</t>
+          <t>9157</t>
         </is>
       </c>
       <c r="CI3" t="inlineStr">
@@ -2850,92 +2850,92 @@
       </c>
       <c r="CJ3" t="inlineStr">
         <is>
-          <t>86.67</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="CK3" t="n">
-        <v>0.21</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="CL3" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="CM3" t="inlineStr">
         <is>
-          <t>2.64</t>
+          <t>2.83</t>
         </is>
       </c>
       <c r="CN3" t="inlineStr">
         <is>
-          <t>-0.27</t>
+          <t>-0.21</t>
         </is>
       </c>
       <c r="CO3" t="inlineStr">
         <is>
-          <t>145.2</t>
+          <t>145.6</t>
         </is>
       </c>
       <c r="CP3" t="inlineStr">
         <is>
-          <t>145.0</t>
+          <t>145.1</t>
         </is>
       </c>
       <c r="CQ3" t="inlineStr">
         <is>
-          <t>143.32</t>
+          <t>143.7</t>
         </is>
       </c>
       <c r="CR3" t="inlineStr">
         <is>
-          <t>139.64</t>
+          <t>139.74</t>
         </is>
       </c>
       <c r="CS3" t="inlineStr">
         <is>
-          <t>140.02</t>
+          <t>140.03</t>
         </is>
       </c>
       <c r="CT3" t="inlineStr">
         <is>
-          <t>136.0604166666667</t>
+          <t>0</t>
         </is>
       </c>
       <c r="CU3" t="inlineStr">
         <is>
-          <t>0.00207039337474102</t>
+          <t>0.002754820936639257</t>
         </is>
       </c>
       <c r="CV3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.0006896551724138167</t>
         </is>
       </c>
       <c r="CW3" t="inlineStr">
         <is>
-          <t>0.002798670631450006</t>
+          <t>0.002616431187859813</t>
         </is>
       </c>
       <c r="CX3" t="inlineStr">
         <is>
-          <t>0.0009318328435237166</t>
+          <t>0.000716127184188009</t>
         </is>
       </c>
       <c r="CY3" t="inlineStr">
         <is>
-          <t>0.0001339225927414756</t>
+          <t>4.463488662742598e-05</t>
         </is>
       </c>
       <c r="CZ3" t="inlineStr">
         <is>
-          <t>0.0003676189017385312</t>
+          <t>0</t>
         </is>
       </c>
       <c r="DA3" t="inlineStr">
         <is>
-          <t>1.30</t>
+          <t>-1.50</t>
         </is>
       </c>
       <c r="DB3" t="n">
-        <v>1.88</v>
+        <v>1.82</v>
       </c>
       <c r="DC3" t="n">
         <v>1.85</v>
@@ -2947,7 +2947,7 @@
       </c>
       <c r="DE3" t="inlineStr">
         <is>
-          <t>-2.18</t>
+          <t>-2.55</t>
         </is>
       </c>
       <c r="DF3" t="inlineStr">
@@ -2957,48 +2957,48 @@
       </c>
       <c r="DG3" t="inlineStr">
         <is>
-          <t>2214561876.963068</t>
+          <t>2510241792.666667</t>
         </is>
       </c>
       <c r="DH3" t="inlineStr">
         <is>
-          <t>1019972816.0</t>
+          <t>1027931012.0</t>
         </is>
       </c>
       <c r="DI3" t="n">
-        <v>1298042299.8</v>
+        <v>1198822702.4</v>
       </c>
       <c r="DJ3" t="inlineStr">
         <is>
-          <t>1238358968.0</t>
+          <t>1211104395.0</t>
         </is>
       </c>
       <c r="DK3" t="inlineStr">
         <is>
-          <t>1512402699.433333</t>
+          <t>1514483902.3</t>
         </is>
       </c>
       <c r="DL3" t="n">
-        <v>1630284122.58</v>
+        <v>1587854042.56</v>
       </c>
       <c r="DM3" t="inlineStr">
         <is>
-          <t>1973713221.6375</t>
+          <t>1954971026.825</t>
         </is>
       </c>
       <c r="DN3" t="inlineStr">
         <is>
-          <t>-21930809.76804974</t>
+          <t>-35595349.43723899</t>
         </is>
       </c>
       <c r="DO3" t="inlineStr">
         <is>
-          <t>-97535680.67281032</t>
+          <t>-110750317.6101668</t>
         </is>
       </c>
       <c r="DP3" t="inlineStr">
         <is>
-          <t>1019972816.0</t>
+          <t>1027931012.0</t>
         </is>
       </c>
       <c r="DQ3" t="inlineStr">
@@ -3078,7 +3078,7 @@
       </c>
       <c r="EF3" t="inlineStr">
         <is>
-          <t>3.57</t>
+          <t>3.55</t>
         </is>
       </c>
       <c r="EG3" t="inlineStr">
@@ -3088,7 +3088,7 @@
       </c>
       <c r="EH3" t="inlineStr">
         <is>
-          <t>28.59</t>
+          <t>28.78</t>
         </is>
       </c>
       <c r="EI3" t="inlineStr">
@@ -3103,12 +3103,12 @@
       </c>
       <c r="EK3" t="inlineStr">
         <is>
-          <t>85.4</t>
+          <t>84.4</t>
         </is>
       </c>
       <c r="EL3" t="inlineStr">
         <is>
-          <t>1128708</t>
+          <t>1136466</t>
         </is>
       </c>
       <c r="EM3" t="inlineStr">
@@ -3148,7 +3148,7 @@
       </c>
       <c r="ET3" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>129.5</t>
         </is>
       </c>
       <c r="EU3" t="inlineStr">
@@ -3168,42 +3168,42 @@
       </c>
       <c r="EX3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="EY3" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>5</t>
         </is>
       </c>
       <c r="EZ3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FA3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FB3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FC3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FD3" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="FE3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FF3" t="inlineStr">
@@ -3213,22 +3213,22 @@
       </c>
       <c r="FG3" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="FH3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FI3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FJ3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FK3" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>8515.486</t>
+          <t>7052.714</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -3440,7 +3440,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.68</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -3450,7 +3450,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-0.07440392378152937</t>
+          <t>0.04819550174243172</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -3495,7 +3495,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>60.0</t>
+          <t>60</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -3510,47 +3510,47 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>142.925</t>
+          <t>143.325</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>148.5844122811866</t>
+          <t>148.4781799073856</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>137.2655877188134</t>
+          <t>138.1718200926144</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>0.07919415471312412</t>
+          <t>0.07190901667379143</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>0.002630655910206947</t>
+          <t>0.002798670631450006</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>0.000713171676491875</t>
+          <t>-0.0007149631119904853</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>-0.0478969710749888</t>
+          <t>-0.09199085545746999</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>0.0479762948677207</t>
+          <t>0.05147900810379896</t>
         </is>
       </c>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>1.123964812126325</t>
+          <t>0.9852782093293254</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
@@ -3560,7 +3560,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
@@ -3595,24 +3595,24 @@
       </c>
       <c r="AM4" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AN4" t="inlineStr">
+        <is>
           <t>2.0</t>
         </is>
       </c>
-      <c r="AN4" t="inlineStr">
+      <c r="AO4" t="inlineStr">
         <is>
           <t>3.0</t>
         </is>
       </c>
-      <c r="AO4" t="inlineStr">
+      <c r="AP4" t="inlineStr">
         <is>
           <t>2.0</t>
         </is>
       </c>
-      <c r="AP4" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
-      </c>
       <c r="AQ4" t="inlineStr">
         <is>
           <t>False</t>
@@ -3635,7 +3635,7 @@
       </c>
       <c r="AU4" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AV4" t="inlineStr">
@@ -3650,7 +3650,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -3660,17 +3660,17 @@
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>16.0</t>
+          <t>17.0</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>17.0</t>
+          <t>18.0</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>17.0</t>
+          <t>18.0</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
@@ -3690,32 +3690,32 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>17850578.0</t>
+          <t>17134672.0</t>
         </is>
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>1360796.0</t>
+          <t>1355796.0</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>4418171.0</t>
+          <t>4433570.0</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
         <is>
-          <t>-3057375.0</t>
+          <t>-3077774.0</t>
         </is>
       </c>
       <c r="BJ4" t="inlineStr">
         <is>
-          <t>-284018.0</t>
+          <t>-302018.0</t>
         </is>
       </c>
       <c r="BK4" t="inlineStr">
         <is>
-          <t>14509185.0</t>
+          <t>13754880.0</t>
         </is>
       </c>
       <c r="BL4" t="inlineStr">
@@ -3730,7 +3730,7 @@
       </c>
       <c r="BN4" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="BO4" t="inlineStr">
@@ -3800,17 +3800,17 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="CC4" t="inlineStr">
         <is>
-          <t>14.21</t>
+          <t>11.77</t>
         </is>
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>1.04</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
@@ -3821,12 +3821,12 @@
       <c r="CF4" t="inlineStr"/>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>67</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
         <is>
-          <t>7081</t>
+          <t>9157</t>
         </is>
       </c>
       <c r="CI4" t="inlineStr">
@@ -3836,28 +3836,28 @@
       </c>
       <c r="CJ4" t="inlineStr">
         <is>
-          <t>93.33</t>
+          <t>86.67</t>
         </is>
       </c>
       <c r="CK4" t="n">
-        <v>0.41</v>
+        <v>0.21</v>
       </c>
       <c r="CL4" t="n">
-        <v>1.38</v>
+        <v>1.31</v>
       </c>
       <c r="CM4" t="inlineStr">
         <is>
-          <t>2.45</t>
+          <t>2.64</t>
         </is>
       </c>
       <c r="CN4" t="inlineStr">
         <is>
-          <t>-0.35</t>
+          <t>-0.27</t>
         </is>
       </c>
       <c r="CO4" t="inlineStr">
         <is>
-          <t>144.9</t>
+          <t>145.2</t>
         </is>
       </c>
       <c r="CP4" t="inlineStr">
@@ -3867,61 +3867,61 @@
       </c>
       <c r="CQ4" t="inlineStr">
         <is>
-          <t>142.93</t>
+          <t>143.32</t>
         </is>
       </c>
       <c r="CR4" t="inlineStr">
         <is>
-          <t>139.51</t>
+          <t>139.64</t>
         </is>
       </c>
       <c r="CS4" t="inlineStr">
         <is>
-          <t>140.01</t>
+          <t>140.02</t>
         </is>
       </c>
       <c r="CT4" t="inlineStr">
         <is>
-          <t>136.0104166666667</t>
+          <t>0</t>
         </is>
       </c>
       <c r="CU4" t="inlineStr">
         <is>
-          <t>0.0006906077348065587</t>
+          <t>0.00207039337474102</t>
         </is>
       </c>
       <c r="CV4" t="inlineStr">
         <is>
-          <t>0.0003449465332874269</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="CW4" t="inlineStr">
         <is>
-          <t>0.002630655910206947</t>
+          <t>0.002798670631450006</t>
         </is>
       </c>
       <c r="CX4" t="inlineStr">
         <is>
-          <t>0.001076349024110135</t>
+          <t>0.0009318328435237166</t>
         </is>
       </c>
       <c r="CY4" t="inlineStr">
         <is>
-          <t>0.0003125837277841992</t>
+          <t>0.0001339225927414756</t>
         </is>
       </c>
       <c r="CZ4" t="inlineStr">
         <is>
-          <t>0.0003830830524056417</t>
+          <t>0</t>
         </is>
       </c>
       <c r="DA4" t="inlineStr">
         <is>
-          <t>4.21</t>
+          <t>1.30</t>
         </is>
       </c>
       <c r="DB4" t="n">
-        <v>1.93</v>
+        <v>1.88</v>
       </c>
       <c r="DC4" t="n">
         <v>1.85</v>
@@ -3933,7 +3933,7 @@
       </c>
       <c r="DE4" t="inlineStr">
         <is>
-          <t>-2.49</t>
+          <t>-2.18</t>
         </is>
       </c>
       <c r="DF4" t="inlineStr">
@@ -3943,48 +3943,48 @@
       </c>
       <c r="DG4" t="inlineStr">
         <is>
-          <t>2214561876.963068</t>
+          <t>2510241792.666667</t>
         </is>
       </c>
       <c r="DH4" t="inlineStr">
         <is>
-          <t>1239700787.0</t>
+          <t>1019972816.0</t>
         </is>
       </c>
       <c r="DI4" t="n">
-        <v>1429392742.2</v>
+        <v>1298042299.8</v>
       </c>
       <c r="DJ4" t="inlineStr">
         <is>
-          <t>1544294297.4</t>
+          <t>1238358968.0</t>
         </is>
       </c>
       <c r="DK4" t="inlineStr">
         <is>
-          <t>1502594940.533333</t>
+          <t>1512402699.433333</t>
         </is>
       </c>
       <c r="DL4" t="n">
-        <v>1654145469.66</v>
+        <v>1630284122.58</v>
       </c>
       <c r="DM4" t="inlineStr">
         <is>
-          <t>1987286590.375</t>
+          <t>1973713221.6375</t>
         </is>
       </c>
       <c r="DN4" t="inlineStr">
         <is>
-          <t>-8184469.60354781</t>
+          <t>-21930809.76943394</t>
         </is>
       </c>
       <c r="DO4" t="inlineStr">
         <is>
-          <t>-74321546.88150048</t>
+          <t>-97535680.67310739</t>
         </is>
       </c>
       <c r="DP4" t="inlineStr">
         <is>
-          <t>1239700787.0</t>
+          <t>1019972816.0</t>
         </is>
       </c>
       <c r="DQ4" t="inlineStr">
@@ -4049,7 +4049,7 @@
       </c>
       <c r="EC4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="ED4" t="inlineStr">
@@ -4064,7 +4064,7 @@
       </c>
       <c r="EF4" t="inlineStr">
         <is>
-          <t>3.57</t>
+          <t>3.55</t>
         </is>
       </c>
       <c r="EG4" t="inlineStr">
@@ -4074,7 +4074,7 @@
       </c>
       <c r="EH4" t="inlineStr">
         <is>
-          <t>28.59</t>
+          <t>28.78</t>
         </is>
       </c>
       <c r="EI4" t="inlineStr">
@@ -4089,12 +4089,12 @@
       </c>
       <c r="EK4" t="inlineStr">
         <is>
-          <t>85.4</t>
+          <t>84.4</t>
         </is>
       </c>
       <c r="EL4" t="inlineStr">
         <is>
-          <t>1128708</t>
+          <t>1136466</t>
         </is>
       </c>
       <c r="EM4" t="inlineStr">
@@ -4114,12 +4114,12 @@
       </c>
       <c r="EP4" t="inlineStr">
         <is>
-          <t>147.0</t>
+          <t>145.5</t>
         </is>
       </c>
       <c r="EQ4" t="inlineStr">
         <is>
-          <t>147.0</t>
+          <t>145.5</t>
         </is>
       </c>
       <c r="ER4" t="inlineStr">
@@ -4134,7 +4134,7 @@
       </c>
       <c r="ET4" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>129.5</t>
         </is>
       </c>
       <c r="EU4" t="inlineStr">
@@ -4154,42 +4154,42 @@
       </c>
       <c r="EX4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="EY4" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>5</t>
         </is>
       </c>
       <c r="EZ4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FA4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FB4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FC4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FD4" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="FE4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FF4" t="inlineStr">
@@ -4199,22 +4199,22 @@
       </c>
       <c r="FG4" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="FH4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FI4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FJ4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FK4" t="inlineStr">
@@ -4401,12 +4401,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0.34</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>10009.961</t>
+          <t>8515.486</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -4416,7 +4416,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>146.0</t>
+          <t>145.5</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -4426,7 +4426,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>0.68</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -4436,7 +4436,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-0.16786321196452753</t>
+          <t>-0.07440392378152937</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -4446,7 +4446,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>99.0</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -4481,7 +4481,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>60.0</t>
+          <t>60</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -4496,47 +4496,47 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>142.55</t>
+          <t>142.925</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>148.4785216050106</t>
+          <t>148.5844122811834</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>136.6214783949895</t>
+          <t>137.2655877188166</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>0.0831781354613898</t>
+          <t>0.07919415471307878</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>0.002990325417766115</t>
+          <t>0.002630655910206947</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>0.001688232507606857</t>
+          <t>0.0007131716764898766</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>-0.03152921474353376</t>
+          <t>-0.04789697107505919</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>0.0479762948677207</t>
+          <t>0.05147900810379896</t>
         </is>
       </c>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>1.230963728066852</t>
+          <t>1.123964812126167</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
@@ -4551,7 +4551,7 @@
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>35.0</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
@@ -4581,62 +4581,62 @@
       </c>
       <c r="AM5" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AN5" t="inlineStr">
+        <is>
           <t>3.0</t>
         </is>
       </c>
-      <c r="AN5" t="inlineStr">
+      <c r="AO5" t="inlineStr">
         <is>
           <t>2.0</t>
         </is>
       </c>
-      <c r="AO5" t="inlineStr">
+      <c r="AP5" t="inlineStr">
         <is>
           <t>2.0</t>
         </is>
       </c>
-      <c r="AP5" t="inlineStr">
+      <c r="AQ5" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AR5" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AS5" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AU5" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="AV5" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AW5" t="inlineStr">
         <is>
           <t>3.0</t>
         </is>
       </c>
-      <c r="AQ5" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AR5" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AS5" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AT5" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AU5" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="AV5" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AW5" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
-      </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
@@ -4651,12 +4651,12 @@
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>16.0</t>
+          <t>17.0</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>16.0</t>
+          <t>17.0</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
@@ -4676,32 +4676,32 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>17850578.0</t>
+          <t>17134672.0</t>
         </is>
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>1360796.0</t>
+          <t>1355796.0</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>4418171.0</t>
+          <t>4433570.0</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
         <is>
-          <t>-3057375.0</t>
+          <t>-3077774.0</t>
         </is>
       </c>
       <c r="BJ5" t="inlineStr">
         <is>
-          <t>-284018.0</t>
+          <t>-302018.0</t>
         </is>
       </c>
       <c r="BK5" t="inlineStr">
         <is>
-          <t>14509185.0</t>
+          <t>13754880.0</t>
         </is>
       </c>
       <c r="BL5" t="inlineStr">
@@ -4716,7 +4716,7 @@
       </c>
       <c r="BN5" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="BO5" t="inlineStr">
@@ -4736,7 +4736,7 @@
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-0.05</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
@@ -4786,17 +4786,17 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="CC5" t="inlineStr">
         <is>
-          <t>16.71</t>
+          <t>14.21</t>
         </is>
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
@@ -4807,110 +4807,110 @@
       <c r="CF5" t="inlineStr"/>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>67</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
         <is>
-          <t>7081</t>
+          <t>9157</t>
         </is>
       </c>
       <c r="CI5" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="CJ5" t="inlineStr">
         <is>
-          <t>66.67</t>
+          <t>93.33</t>
         </is>
       </c>
       <c r="CK5" t="n">
-        <v>0.83</v>
+        <v>0.41</v>
       </c>
       <c r="CL5" t="n">
-        <v>1.58</v>
+        <v>1.38</v>
       </c>
       <c r="CM5" t="inlineStr">
         <is>
-          <t>2.29</t>
+          <t>2.45</t>
         </is>
       </c>
       <c r="CN5" t="inlineStr">
         <is>
-          <t>-0.43</t>
+          <t>-0.35</t>
         </is>
       </c>
       <c r="CO5" t="inlineStr">
         <is>
-          <t>144.8</t>
+          <t>144.9</t>
         </is>
       </c>
       <c r="CP5" t="inlineStr">
         <is>
-          <t>144.95</t>
+          <t>145.0</t>
         </is>
       </c>
       <c r="CQ5" t="inlineStr">
         <is>
-          <t>142.55</t>
+          <t>142.93</t>
         </is>
       </c>
       <c r="CR5" t="inlineStr">
         <is>
-          <t>139.36</t>
+          <t>139.51</t>
         </is>
       </c>
       <c r="CS5" t="inlineStr">
         <is>
-          <t>139.96</t>
+          <t>140.01</t>
         </is>
       </c>
       <c r="CT5" t="inlineStr">
         <is>
-          <t>135.9583333333333</t>
+          <t>0</t>
         </is>
       </c>
       <c r="CU5" t="inlineStr">
         <is>
-          <t>0.0006910850034556049</t>
+          <t>0.0006906077348065587</t>
         </is>
       </c>
       <c r="CV5" t="inlineStr">
         <is>
-          <t>0.001727712508638568</t>
+          <t>0.0003449465332874269</t>
         </is>
       </c>
       <c r="CW5" t="inlineStr">
         <is>
-          <t>0.002990325417766115</t>
+          <t>0.002630655910206947</t>
         </is>
       </c>
       <c r="CX5" t="inlineStr">
         <is>
-          <t>0.001077508799655291</t>
+          <t>0.001076349024110135</t>
         </is>
       </c>
       <c r="CY5" t="inlineStr">
         <is>
-          <t>0.0006702712364270447</t>
+          <t>0.0003125837277841992</t>
         </is>
       </c>
       <c r="CZ5" t="inlineStr">
         <is>
-          <t>0.0003985651654045963</t>
+          <t>0</t>
         </is>
       </c>
       <c r="DA5" t="inlineStr">
         <is>
-          <t>7.12</t>
+          <t>4.21</t>
         </is>
       </c>
       <c r="DB5" t="n">
-        <v>1.96</v>
+        <v>1.93</v>
       </c>
       <c r="DC5" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="DD5" t="inlineStr">
         <is>
@@ -4919,7 +4919,7 @@
       </c>
       <c r="DE5" t="inlineStr">
         <is>
-          <t>-3.52</t>
+          <t>-2.50</t>
         </is>
       </c>
       <c r="DF5" t="inlineStr">
@@ -4929,48 +4929,48 @@
       </c>
       <c r="DG5" t="inlineStr">
         <is>
-          <t>2214561876.963068</t>
+          <t>2510241792.666667</t>
         </is>
       </c>
       <c r="DH5" t="inlineStr">
         <is>
-          <t>1458318100.0</t>
+          <t>1239700787.0</t>
         </is>
       </c>
       <c r="DI5" t="n">
-        <v>1365056504.4</v>
+        <v>1429392742.2</v>
       </c>
       <c r="DJ5" t="inlineStr">
         <is>
-          <t>1640423214.1</t>
+          <t>1544294297.4</t>
         </is>
       </c>
       <c r="DK5" t="inlineStr">
         <is>
-          <t>1485353753.433333</t>
+          <t>1502594940.533333</t>
         </is>
       </c>
       <c r="DL5" t="n">
-        <v>1659414895.68</v>
+        <v>1654145469.66</v>
       </c>
       <c r="DM5" t="inlineStr">
         <is>
-          <t>2004348026.1375</t>
+          <t>1987286590.375</t>
         </is>
       </c>
       <c r="DN5" t="inlineStr">
         <is>
-          <t>3840453.537898131</t>
+          <t>-8184469.605129678</t>
         </is>
       </c>
       <c r="DO5" t="inlineStr">
         <is>
-          <t>-62046440.25528979</t>
+          <t>-74321546.88183999</t>
         </is>
       </c>
       <c r="DP5" t="inlineStr">
         <is>
-          <t>1458318100.0</t>
+          <t>1239700787.0</t>
         </is>
       </c>
       <c r="DQ5" t="inlineStr">
@@ -4990,7 +4990,7 @@
       </c>
       <c r="DT5" t="inlineStr">
         <is>
-          <t>1.74</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="DU5" t="inlineStr">
@@ -5045,12 +5045,12 @@
       </c>
       <c r="EE5" t="inlineStr">
         <is>
-          <t>3.09</t>
+          <t>3.08</t>
         </is>
       </c>
       <c r="EF5" t="inlineStr">
         <is>
-          <t>3.57</t>
+          <t>3.55</t>
         </is>
       </c>
       <c r="EG5" t="inlineStr">
@@ -5060,7 +5060,7 @@
       </c>
       <c r="EH5" t="inlineStr">
         <is>
-          <t>28.59</t>
+          <t>28.78</t>
         </is>
       </c>
       <c r="EI5" t="inlineStr">
@@ -5075,12 +5075,12 @@
       </c>
       <c r="EK5" t="inlineStr">
         <is>
-          <t>85.4</t>
+          <t>84.4</t>
         </is>
       </c>
       <c r="EL5" t="inlineStr">
         <is>
-          <t>1128708</t>
+          <t>1136466</t>
         </is>
       </c>
       <c r="EM5" t="inlineStr">
@@ -5100,12 +5100,12 @@
       </c>
       <c r="EP5" t="inlineStr">
         <is>
-          <t>145.0</t>
+          <t>147.0</t>
         </is>
       </c>
       <c r="EQ5" t="inlineStr">
         <is>
-          <t>146.5</t>
+          <t>147.0</t>
         </is>
       </c>
       <c r="ER5" t="inlineStr">
@@ -5115,12 +5115,12 @@
       </c>
       <c r="ES5" t="inlineStr">
         <is>
-          <t>146.0</t>
+          <t>145.5</t>
         </is>
       </c>
       <c r="ET5" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>129.5</t>
         </is>
       </c>
       <c r="EU5" t="inlineStr">
@@ -5140,42 +5140,42 @@
       </c>
       <c r="EX5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="EY5" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>5</t>
         </is>
       </c>
       <c r="EZ5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FA5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FB5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FC5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FD5" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="FE5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FF5" t="inlineStr">
@@ -5185,22 +5185,22 @@
       </c>
       <c r="FG5" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>4</t>
         </is>
       </c>
       <c r="FH5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FI5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FJ5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FK5" t="inlineStr">
@@ -5387,12 +5387,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>0.34</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>8628.434</t>
+          <t>10009.961</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -5402,359 +5402,359 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
+          <t>146.0</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>0.34</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>-0.16786321196452753</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>99.0</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>轉強</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>TrendType : 轉強&lt;br&gt;TrendScore : 60&lt;br&gt;HH : True&lt;br&gt;HL : False&lt;br&gt;MA : True&lt;br&gt;VOL : False</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>142.55</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>148.4785216050076</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>136.6214783949924</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>0.08317813546134833</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>0.002990325417766115</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>0.001688232507605081</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>-0.03152921474358805</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>0.05147900810379896</t>
+        </is>
+      </c>
+      <c r="AD6" t="inlineStr">
+        <is>
+          <t>1.23096372806679</t>
+        </is>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t>2026-09-02 00:00:00</t>
+        </is>
+      </c>
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="AG6" t="inlineStr">
+        <is>
+          <t>40.0</t>
+        </is>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>2026-09-03 00:00:00</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AL6" t="inlineStr">
+        <is>
+          <t>2026-09-08 00:00:00</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AN6" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="AP6" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
+      </c>
+      <c r="AQ6" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AR6" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AS6" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AU6" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="AV6" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>7.0</t>
+        </is>
+      </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>16.0</t>
+        </is>
+      </c>
+      <c r="BA6" t="inlineStr">
+        <is>
+          <t>16.0</t>
+        </is>
+      </c>
+      <c r="BB6" t="inlineStr">
+        <is>
+          <t>16.0</t>
+        </is>
+      </c>
+      <c r="BC6" t="inlineStr">
+        <is>
+          <t>盤整</t>
+        </is>
+      </c>
+      <c r="BD6" t="inlineStr">
+        <is>
+          <t>盤整</t>
+        </is>
+      </c>
+      <c r="BE6" t="inlineStr">
+        <is>
+          <t>58.3</t>
+        </is>
+      </c>
+      <c r="BF6" t="inlineStr">
+        <is>
+          <t>17134672.0</t>
+        </is>
+      </c>
+      <c r="BG6" t="inlineStr">
+        <is>
+          <t>1355796.0</t>
+        </is>
+      </c>
+      <c r="BH6" t="inlineStr">
+        <is>
+          <t>4433570.0</t>
+        </is>
+      </c>
+      <c r="BI6" t="inlineStr">
+        <is>
+          <t>-3077774.0</t>
+        </is>
+      </c>
+      <c r="BJ6" t="inlineStr">
+        <is>
+          <t>-302018.0</t>
+        </is>
+      </c>
+      <c r="BK6" t="inlineStr">
+        <is>
+          <t>13754880.0</t>
+        </is>
+      </c>
+      <c r="BL6" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="BM6" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="BN6" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="BO6" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="BP6" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="BQ6" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="BR6" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="BS6" t="inlineStr">
+        <is>
+          <t>2026/07/20</t>
+        </is>
+      </c>
+      <c r="BT6" t="inlineStr">
+        <is>
+          <t>139.0</t>
+        </is>
+      </c>
+      <c r="BU6" t="inlineStr">
+        <is>
+          <t>2026/04/16</t>
+        </is>
+      </c>
+      <c r="BV6" t="inlineStr">
+        <is>
+          <t>136.5</t>
+        </is>
+      </c>
+      <c r="BW6" t="inlineStr">
+        <is>
+          <t>2026/10/07</t>
+        </is>
+      </c>
+      <c r="BX6" t="inlineStr">
+        <is>
           <t>145.5</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>-0.22942768703039035</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>99.0</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="R6" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>60.0</t>
-        </is>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>轉強</t>
-        </is>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>TrendType : 轉強&lt;br&gt;TrendScore : 60&lt;br&gt;HH : True&lt;br&gt;HL : False&lt;br&gt;MA : True&lt;br&gt;VOL : False</t>
-        </is>
-      </c>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>142.125</t>
-        </is>
-      </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>148.2282778078687</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>136.0217221921313</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>0.08588605534379948</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>0.003353335686551384</t>
-        </is>
-      </c>
-      <c r="AA6" t="inlineStr">
-        <is>
-          <t>0.0007628237184804654</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>-0.0591484627958786</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>0.0479762948677207</t>
-        </is>
-      </c>
-      <c r="AD6" t="inlineStr">
-        <is>
-          <t>1.334686942343584</t>
-        </is>
-      </c>
-      <c r="AE6" t="inlineStr">
-        <is>
-          <t>2026-09-02 00:00:00</t>
-        </is>
-      </c>
-      <c r="AF6" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="AG6" t="inlineStr">
-        <is>
-          <t>40.0</t>
-        </is>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>2026-09-03 00:00:00</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AL6" t="inlineStr">
-        <is>
-          <t>2026-09-08 00:00:00</t>
-        </is>
-      </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
-      </c>
-      <c r="AN6" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
-      </c>
-      <c r="AP6" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
-      </c>
-      <c r="AQ6" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AR6" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AS6" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AT6" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AU6" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="AV6" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AW6" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr">
-        <is>
-          <t>7.0</t>
-        </is>
-      </c>
-      <c r="AZ6" t="inlineStr">
-        <is>
-          <t>15.0</t>
-        </is>
-      </c>
-      <c r="BA6" t="inlineStr">
-        <is>
-          <t>15.0</t>
-        </is>
-      </c>
-      <c r="BB6" t="inlineStr">
-        <is>
-          <t>15.0</t>
-        </is>
-      </c>
-      <c r="BC6" t="inlineStr">
-        <is>
-          <t>盤整</t>
-        </is>
-      </c>
-      <c r="BD6" t="inlineStr">
-        <is>
-          <t>盤整</t>
-        </is>
-      </c>
-      <c r="BE6" t="inlineStr">
-        <is>
-          <t>58.3</t>
-        </is>
-      </c>
-      <c r="BF6" t="inlineStr">
-        <is>
-          <t>17850578.0</t>
-        </is>
-      </c>
-      <c r="BG6" t="inlineStr">
-        <is>
-          <t>1360796.0</t>
-        </is>
-      </c>
-      <c r="BH6" t="inlineStr">
-        <is>
-          <t>4418171.0</t>
-        </is>
-      </c>
-      <c r="BI6" t="inlineStr">
-        <is>
-          <t>-3057375.0</t>
-        </is>
-      </c>
-      <c r="BJ6" t="inlineStr">
-        <is>
-          <t>-284018.0</t>
-        </is>
-      </c>
-      <c r="BK6" t="inlineStr">
-        <is>
-          <t>14509185.0</t>
-        </is>
-      </c>
-      <c r="BL6" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
-      </c>
-      <c r="BM6" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
-      </c>
-      <c r="BN6" t="inlineStr">
-        <is>
-          <t>-1.0</t>
-        </is>
-      </c>
-      <c r="BO6" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="BP6" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="BQ6" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="BR6" t="inlineStr">
-        <is>
-          <t>-0.01</t>
-        </is>
-      </c>
-      <c r="BS6" t="inlineStr">
-        <is>
-          <t>2026/07/20</t>
-        </is>
-      </c>
-      <c r="BT6" t="inlineStr">
-        <is>
-          <t>139.0</t>
-        </is>
-      </c>
-      <c r="BU6" t="inlineStr">
-        <is>
-          <t>2026/04/16</t>
-        </is>
-      </c>
-      <c r="BV6" t="inlineStr">
-        <is>
-          <t>136.5</t>
-        </is>
-      </c>
-      <c r="BW6" t="inlineStr">
-        <is>
-          <t>2026/10/07</t>
-        </is>
-      </c>
-      <c r="BX6" t="inlineStr">
-        <is>
-          <t>145.5</t>
-        </is>
-      </c>
       <c r="BY6" t="inlineStr">
         <is>
           <t>2026/08/05</t>
@@ -5772,17 +5772,17 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="CC6" t="inlineStr">
         <is>
-          <t>14.40</t>
+          <t>16.71</t>
         </is>
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>1.40</t>
+          <t>1.05</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
@@ -5793,12 +5793,12 @@
       <c r="CF6" t="inlineStr"/>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>67</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
         <is>
-          <t>7081</t>
+          <t>9157</t>
         </is>
       </c>
       <c r="CI6" t="inlineStr">
@@ -5808,95 +5808,95 @@
       </c>
       <c r="CJ6" t="inlineStr">
         <is>
-          <t>41.67</t>
+          <t>66.67</t>
         </is>
       </c>
       <c r="CK6" t="n">
-        <v>0.55</v>
+        <v>0.83</v>
       </c>
       <c r="CL6" t="n">
-        <v>1.81</v>
+        <v>1.58</v>
       </c>
       <c r="CM6" t="inlineStr">
         <is>
-          <t>2.09</t>
+          <t>2.29</t>
         </is>
       </c>
       <c r="CN6" t="inlineStr">
         <is>
-          <t>-0.47</t>
+          <t>-0.43</t>
         </is>
       </c>
       <c r="CO6" t="inlineStr">
         <is>
-          <t>144.7</t>
+          <t>144.8</t>
         </is>
       </c>
       <c r="CP6" t="inlineStr">
         <is>
-          <t>144.7</t>
+          <t>144.95</t>
         </is>
       </c>
       <c r="CQ6" t="inlineStr">
         <is>
-          <t>142.12</t>
+          <t>142.55</t>
         </is>
       </c>
       <c r="CR6" t="inlineStr">
         <is>
-          <t>139.21</t>
+          <t>139.36</t>
         </is>
       </c>
       <c r="CS6" t="inlineStr">
         <is>
-          <t>139.87</t>
+          <t>139.96</t>
         </is>
       </c>
       <c r="CT6" t="inlineStr">
         <is>
-          <t>135.9041666666667</t>
+          <t>0</t>
         </is>
       </c>
       <c r="CU6" t="inlineStr">
         <is>
-          <t>0.0006915629322268302</t>
+          <t>0.0006910850034556049</t>
         </is>
       </c>
       <c r="CV6" t="inlineStr">
         <is>
-          <t>0.00138408304498272</t>
+          <t>0.001727712508638568</t>
         </is>
       </c>
       <c r="CW6" t="inlineStr">
         <is>
-          <t>0.003353335686551384</t>
+          <t>0.002990325417766115</t>
         </is>
       </c>
       <c r="CX6" t="inlineStr">
         <is>
-          <t>0.0009347138337647554</t>
+          <t>0.001077508799655291</t>
         </is>
       </c>
       <c r="CY6" t="inlineStr">
         <is>
-          <t>0.0004023245417970056</t>
+          <t>0.0006702712364270447</t>
         </is>
       </c>
       <c r="CZ6" t="inlineStr">
         <is>
-          <t>0.0003833826619026315</t>
+          <t>0</t>
         </is>
       </c>
       <c r="DA6" t="inlineStr">
         <is>
-          <t>6.98</t>
+          <t>7.12</t>
         </is>
       </c>
       <c r="DB6" t="n">
-        <v>1.92</v>
+        <v>1.96</v>
       </c>
       <c r="DC6" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="DD6" t="inlineStr">
         <is>
@@ -5905,7 +5905,7 @@
       </c>
       <c r="DE6" t="inlineStr">
         <is>
-          <t>-5.24</t>
+          <t>-3.52</t>
         </is>
       </c>
       <c r="DF6" t="inlineStr">
@@ -5915,48 +5915,48 @@
       </c>
       <c r="DG6" t="inlineStr">
         <is>
-          <t>2214561876.963068</t>
+          <t>2510241792.666667</t>
         </is>
       </c>
       <c r="DH6" t="inlineStr">
         <is>
-          <t>1248190797.0</t>
+          <t>1458318100.0</t>
         </is>
       </c>
       <c r="DI6" t="n">
-        <v>1315071112.6</v>
+        <v>1365056504.4</v>
       </c>
       <c r="DJ6" t="inlineStr">
         <is>
-          <t>1706616096.2</t>
+          <t>1640423214.1</t>
         </is>
       </c>
       <c r="DK6" t="inlineStr">
         <is>
-          <t>1469076947.433333</t>
+          <t>1485353753.433333</t>
         </is>
       </c>
       <c r="DL6" t="n">
-        <v>1667394181.32</v>
+        <v>1659414895.68</v>
       </c>
       <c r="DM6" t="inlineStr">
         <is>
-          <t>2016079760.0875</t>
+          <t>2004348026.1375</t>
         </is>
       </c>
       <c r="DN6" t="inlineStr">
         <is>
-          <t>15819888.77302321</t>
+          <t>3840453.53609038</t>
         </is>
       </c>
       <c r="DO6" t="inlineStr">
         <is>
-          <t>-65717912.88730001</t>
+          <t>-62046440.25567794</t>
         </is>
       </c>
       <c r="DP6" t="inlineStr">
         <is>
-          <t>1248190797.0</t>
+          <t>1458318100.0</t>
         </is>
       </c>
       <c r="DQ6" t="inlineStr">
@@ -5976,7 +5976,7 @@
       </c>
       <c r="DT6" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>1.74</t>
         </is>
       </c>
       <c r="DU6" t="inlineStr">
@@ -6026,17 +6026,17 @@
       </c>
       <c r="ED6" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="EE6" t="inlineStr">
         <is>
-          <t>3.08</t>
+          <t>3.09</t>
         </is>
       </c>
       <c r="EF6" t="inlineStr">
         <is>
-          <t>3.57</t>
+          <t>3.55</t>
         </is>
       </c>
       <c r="EG6" t="inlineStr">
@@ -6046,7 +6046,7 @@
       </c>
       <c r="EH6" t="inlineStr">
         <is>
-          <t>28.59</t>
+          <t>28.78</t>
         </is>
       </c>
       <c r="EI6" t="inlineStr">
@@ -6061,12 +6061,12 @@
       </c>
       <c r="EK6" t="inlineStr">
         <is>
-          <t>85.4</t>
+          <t>84.4</t>
         </is>
       </c>
       <c r="EL6" t="inlineStr">
         <is>
-          <t>1128708</t>
+          <t>1136466</t>
         </is>
       </c>
       <c r="EM6" t="inlineStr">
@@ -6086,27 +6086,27 @@
       </c>
       <c r="EP6" t="inlineStr">
         <is>
+          <t>145.0</t>
+        </is>
+      </c>
+      <c r="EQ6" t="inlineStr">
+        <is>
+          <t>146.5</t>
+        </is>
+      </c>
+      <c r="ER6" t="inlineStr">
+        <is>
           <t>144.0</t>
         </is>
       </c>
-      <c r="EQ6" t="inlineStr">
+      <c r="ES6" t="inlineStr">
         <is>
           <t>146.0</t>
         </is>
       </c>
-      <c r="ER6" t="inlineStr">
-        <is>
-          <t>143.0</t>
-        </is>
-      </c>
-      <c r="ES6" t="inlineStr">
-        <is>
-          <t>145.5</t>
-        </is>
-      </c>
       <c r="ET6" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>129.5</t>
         </is>
       </c>
       <c r="EU6" t="inlineStr">
@@ -6126,42 +6126,42 @@
       </c>
       <c r="EX6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="EY6" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>5</t>
         </is>
       </c>
       <c r="EZ6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FA6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FB6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FC6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FD6" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="FE6" t="inlineStr">
         <is>
-          <t>12.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FF6" t="inlineStr">
@@ -6171,22 +6171,22 @@
       </c>
       <c r="FG6" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>4</t>
         </is>
       </c>
       <c r="FH6" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FI6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FJ6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FK6" t="inlineStr">
@@ -6373,12 +6373,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>10607.859</t>
+          <t>8628.434</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -6388,7 +6388,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>143.5</t>
+          <t>145.5</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -6398,7 +6398,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>0.68</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -6408,7 +6408,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-0.3292751984432931</t>
+          <t>-0.22942768703039035</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -6443,7 +6443,7 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
@@ -6453,242 +6453,242 @@
       </c>
       <c r="S7" t="inlineStr">
         <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>轉強</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>TrendType : 轉強&lt;br&gt;TrendScore : 60&lt;br&gt;HH : True&lt;br&gt;HL : False&lt;br&gt;MA : True&lt;br&gt;VOL : False</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>142.125</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>148.228277807866</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>136.021722192134</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>0.08588605534376148</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>0.003353335686551384</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>0.0007628237184782449</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>-0.05914846279594743</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>0.05147900810379896</t>
+        </is>
+      </c>
+      <c r="AD7" t="inlineStr">
+        <is>
+          <t>1.334686942343627</t>
+        </is>
+      </c>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t>2026-09-02 00:00:00</t>
+        </is>
+      </c>
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="AG7" t="inlineStr">
+        <is>
           <t>40.0</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>盤整偏多</t>
-        </is>
-      </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>TrendType : 盤整偏多&lt;br&gt;TrendScore : 40&lt;br&gt;HH : True&lt;br&gt;HL : False&lt;br&gt;MA : False&lt;br&gt;VOL : False</t>
-        </is>
-      </c>
-      <c r="V7" t="inlineStr">
-        <is>
-          <t>141.65</t>
-        </is>
-      </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>148.1152919500996</t>
-        </is>
-      </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>135.1847080499005</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>0.09128544934838764</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>0.002654397451778534</t>
-        </is>
-      </c>
-      <c r="AA7" t="inlineStr">
-        <is>
-          <t>-0.0002059336306624582</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>-0.06151019020487603</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>0.0479762948677207</t>
-        </is>
-      </c>
-      <c r="AD7" t="inlineStr">
-        <is>
-          <t>1.498206169143926</t>
-        </is>
-      </c>
-      <c r="AE7" t="inlineStr">
-        <is>
-          <t>2026-09-02 00:00:00</t>
-        </is>
-      </c>
-      <c r="AF7" t="inlineStr">
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>2026-09-03 00:00:00</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AL7" t="inlineStr">
+        <is>
+          <t>2026-09-08 00:00:00</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AN7" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
+      </c>
+      <c r="AP7" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="AQ7" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AR7" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AS7" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AU7" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="AG7" t="inlineStr">
-        <is>
-          <t>40.0</t>
-        </is>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>2026-09-03 00:00:00</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AL7" t="inlineStr">
-        <is>
-          <t>2026-09-08 00:00:00</t>
-        </is>
-      </c>
-      <c r="AM7" t="inlineStr">
+      <c r="AV7" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
         <is>
           <t>2.0</t>
         </is>
       </c>
-      <c r="AN7" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
-      </c>
-      <c r="AP7" t="inlineStr">
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>7.0</t>
+        </is>
+      </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>15.0</t>
+        </is>
+      </c>
+      <c r="BA7" t="inlineStr">
+        <is>
+          <t>15.0</t>
+        </is>
+      </c>
+      <c r="BB7" t="inlineStr">
+        <is>
+          <t>15.0</t>
+        </is>
+      </c>
+      <c r="BC7" t="inlineStr">
+        <is>
+          <t>盤整</t>
+        </is>
+      </c>
+      <c r="BD7" t="inlineStr">
+        <is>
+          <t>盤整</t>
+        </is>
+      </c>
+      <c r="BE7" t="inlineStr">
+        <is>
+          <t>58.3</t>
+        </is>
+      </c>
+      <c r="BF7" t="inlineStr">
+        <is>
+          <t>17134672.0</t>
+        </is>
+      </c>
+      <c r="BG7" t="inlineStr">
+        <is>
+          <t>1355796.0</t>
+        </is>
+      </c>
+      <c r="BH7" t="inlineStr">
+        <is>
+          <t>4433570.0</t>
+        </is>
+      </c>
+      <c r="BI7" t="inlineStr">
+        <is>
+          <t>-3077774.0</t>
+        </is>
+      </c>
+      <c r="BJ7" t="inlineStr">
+        <is>
+          <t>-302018.0</t>
+        </is>
+      </c>
+      <c r="BK7" t="inlineStr">
+        <is>
+          <t>13754880.0</t>
+        </is>
+      </c>
+      <c r="BL7" t="inlineStr">
         <is>
           <t>5.0</t>
         </is>
       </c>
-      <c r="AQ7" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AR7" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AS7" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AT7" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AU7" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="AV7" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AW7" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AX7" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr">
-        <is>
-          <t>7.0</t>
-        </is>
-      </c>
-      <c r="AZ7" t="inlineStr">
-        <is>
-          <t>14.0</t>
-        </is>
-      </c>
-      <c r="BA7" t="inlineStr">
-        <is>
-          <t>14.0</t>
-        </is>
-      </c>
-      <c r="BB7" t="inlineStr">
-        <is>
-          <t>14.0</t>
-        </is>
-      </c>
-      <c r="BC7" t="inlineStr">
-        <is>
-          <t>盤整</t>
-        </is>
-      </c>
-      <c r="BD7" t="inlineStr">
-        <is>
-          <t>盤整</t>
-        </is>
-      </c>
-      <c r="BE7" t="inlineStr">
-        <is>
-          <t>58.3</t>
-        </is>
-      </c>
-      <c r="BF7" t="inlineStr">
-        <is>
-          <t>17850578.0</t>
-        </is>
-      </c>
-      <c r="BG7" t="inlineStr">
-        <is>
-          <t>1360796.0</t>
-        </is>
-      </c>
-      <c r="BH7" t="inlineStr">
-        <is>
-          <t>4418171.0</t>
-        </is>
-      </c>
-      <c r="BI7" t="inlineStr">
-        <is>
-          <t>-3057375.0</t>
-        </is>
-      </c>
-      <c r="BJ7" t="inlineStr">
-        <is>
-          <t>-284018.0</t>
-        </is>
-      </c>
-      <c r="BK7" t="inlineStr">
-        <is>
-          <t>14509185.0</t>
-        </is>
-      </c>
-      <c r="BL7" t="inlineStr">
+      <c r="BM7" t="inlineStr">
         <is>
           <t>5.0</t>
         </is>
       </c>
-      <c r="BM7" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
-      </c>
       <c r="BN7" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="BO7" t="inlineStr">
@@ -6708,7 +6708,7 @@
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>-0.18</t>
+          <t>-0.01</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
@@ -6758,17 +6758,17 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="CC7" t="inlineStr">
         <is>
-          <t>17.70</t>
+          <t>14.40</t>
         </is>
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>-0.70</t>
+          <t>1.40</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
@@ -6779,110 +6779,110 @@
       <c r="CF7" t="inlineStr"/>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>67</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
         <is>
-          <t>7081</t>
+          <t>9157</t>
         </is>
       </c>
       <c r="CI7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="CJ7" t="inlineStr">
         <is>
-          <t>36.11</t>
+          <t>41.67</t>
         </is>
       </c>
       <c r="CK7" t="n">
-        <v>-0.76</v>
+        <v>0.55</v>
       </c>
       <c r="CL7" t="n">
-        <v>2.08</v>
+        <v>1.81</v>
       </c>
       <c r="CM7" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>2.09</t>
         </is>
       </c>
       <c r="CN7" t="inlineStr">
         <is>
-          <t>-0.52</t>
+          <t>-0.47</t>
         </is>
       </c>
       <c r="CO7" t="inlineStr">
         <is>
-          <t>144.6</t>
+          <t>144.7</t>
         </is>
       </c>
       <c r="CP7" t="inlineStr">
         <is>
-          <t>144.5</t>
+          <t>144.7</t>
         </is>
       </c>
       <c r="CQ7" t="inlineStr">
         <is>
-          <t>141.65</t>
+          <t>142.12</t>
         </is>
       </c>
       <c r="CR7" t="inlineStr">
         <is>
-          <t>139.08</t>
+          <t>139.21</t>
         </is>
       </c>
       <c r="CS7" t="inlineStr">
         <is>
-          <t>139.81</t>
+          <t>139.87</t>
         </is>
       </c>
       <c r="CT7" t="inlineStr">
         <is>
-          <t>135.8520833333333</t>
+          <t>0</t>
         </is>
       </c>
       <c r="CU7" t="inlineStr">
         <is>
-          <t>-0.001381215469613339</t>
+          <t>0.0006915629322268302</t>
         </is>
       </c>
       <c r="CV7" t="inlineStr">
         <is>
-          <t>0.0006925207756232066</t>
+          <t>0.00138408304498272</t>
         </is>
       </c>
       <c r="CW7" t="inlineStr">
         <is>
-          <t>0.002654397451778534</t>
+          <t>0.003353335686551384</t>
         </is>
       </c>
       <c r="CX7" t="inlineStr">
         <is>
-          <t>0.0006475285991798252</t>
+          <t>0.0009347138337647554</t>
         </is>
       </c>
       <c r="CY7" t="inlineStr">
         <is>
-          <t>0.0001788428865241443</t>
+          <t>0.0004023245417970056</t>
         </is>
       </c>
       <c r="CZ7" t="inlineStr">
         <is>
-          <t>0.0002761117332146235</t>
+          <t>0</t>
         </is>
       </c>
       <c r="DA7" t="inlineStr">
         <is>
-          <t>7.47</t>
+          <t>6.98</t>
         </is>
       </c>
       <c r="DB7" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="DC7" t="n">
-        <v>1.76</v>
+        <v>1.8</v>
       </c>
       <c r="DD7" t="inlineStr">
         <is>
@@ -6891,7 +6891,7 @@
       </c>
       <c r="DE7" t="inlineStr">
         <is>
-          <t>-6.89</t>
+          <t>-5.24</t>
         </is>
       </c>
       <c r="DF7" t="inlineStr">
@@ -6901,48 +6901,48 @@
       </c>
       <c r="DG7" t="inlineStr">
         <is>
-          <t>2214561876.963068</t>
+          <t>2510241792.666667</t>
         </is>
       </c>
       <c r="DH7" t="inlineStr">
         <is>
-          <t>1524028999.0</t>
+          <t>1248190797.0</t>
         </is>
       </c>
       <c r="DI7" t="n">
-        <v>1223386087.6</v>
+        <v>1315071112.6</v>
       </c>
       <c r="DJ7" t="inlineStr">
         <is>
-          <t>1823976219.1</t>
+          <t>1706616096.2</t>
         </is>
       </c>
       <c r="DK7" t="inlineStr">
         <is>
-          <t>1490856706.633333</t>
+          <t>1469076947.433333</t>
         </is>
       </c>
       <c r="DL7" t="n">
-        <v>1693335182.06</v>
+        <v>1667394181.32</v>
       </c>
       <c r="DM7" t="inlineStr">
         <is>
-          <t>2020913533.8875</t>
+          <t>2016079760.0875</t>
         </is>
       </c>
       <c r="DN7" t="inlineStr">
         <is>
-          <t>30644943.6203547</t>
+          <t>15819888.77095735</t>
         </is>
       </c>
       <c r="DO7" t="inlineStr">
         <is>
-          <t>-46102165.86562538</t>
+          <t>-65717912.88774347</t>
         </is>
       </c>
       <c r="DP7" t="inlineStr">
         <is>
-          <t>1524028999.0</t>
+          <t>1248190797.0</t>
         </is>
       </c>
       <c r="DQ7" t="inlineStr">
@@ -6962,7 +6962,7 @@
       </c>
       <c r="DT7" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="DU7" t="inlineStr">
@@ -7007,7 +7007,7 @@
       </c>
       <c r="EC7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="ED7" t="inlineStr">
@@ -7017,12 +7017,12 @@
       </c>
       <c r="EE7" t="inlineStr">
         <is>
-          <t>3.04</t>
+          <t>3.08</t>
         </is>
       </c>
       <c r="EF7" t="inlineStr">
         <is>
-          <t>3.57</t>
+          <t>3.55</t>
         </is>
       </c>
       <c r="EG7" t="inlineStr">
@@ -7032,7 +7032,7 @@
       </c>
       <c r="EH7" t="inlineStr">
         <is>
-          <t>28.59</t>
+          <t>28.78</t>
         </is>
       </c>
       <c r="EI7" t="inlineStr">
@@ -7047,12 +7047,12 @@
       </c>
       <c r="EK7" t="inlineStr">
         <is>
-          <t>85.4</t>
+          <t>84.4</t>
         </is>
       </c>
       <c r="EL7" t="inlineStr">
         <is>
-          <t>1128708</t>
+          <t>1136466</t>
         </is>
       </c>
       <c r="EM7" t="inlineStr">
@@ -7072,12 +7072,12 @@
       </c>
       <c r="EP7" t="inlineStr">
         <is>
-          <t>145.0</t>
+          <t>144.0</t>
         </is>
       </c>
       <c r="EQ7" t="inlineStr">
         <is>
-          <t>145.0</t>
+          <t>146.0</t>
         </is>
       </c>
       <c r="ER7" t="inlineStr">
@@ -7087,12 +7087,12 @@
       </c>
       <c r="ES7" t="inlineStr">
         <is>
-          <t>143.5</t>
+          <t>145.5</t>
         </is>
       </c>
       <c r="ET7" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>129.5</t>
         </is>
       </c>
       <c r="EU7" t="inlineStr">
@@ -7112,42 +7112,42 @@
       </c>
       <c r="EX7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="EY7" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>5</t>
         </is>
       </c>
       <c r="EZ7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FA7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FB7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FC7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FD7" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="FE7" t="inlineStr">
         <is>
-          <t>12.0</t>
+          <t>12</t>
         </is>
       </c>
       <c r="FF7" t="inlineStr">
@@ -7157,22 +7157,22 @@
       </c>
       <c r="FG7" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>4</t>
         </is>
       </c>
       <c r="FH7" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="FI7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FJ7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FK7" t="inlineStr">
@@ -7359,12 +7359,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-0.68</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>11652.18</t>
+          <t>10607.859</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -7374,7 +7374,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>144.0</t>
+          <t>143.5</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -7384,7 +7384,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>1.03</t>
+          <t>2.05</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -7394,7 +7394,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-0.39166013609889294</t>
+          <t>-0.3292751984432931</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -7404,7 +7404,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>99.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -7439,244 +7439,244 @@
       </c>
       <c r="S8" t="inlineStr">
         <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>盤整偏多</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>TrendType : 盤整偏多&lt;br&gt;TrendScore : 40&lt;br&gt;HH : True&lt;br&gt;HL : False&lt;br&gt;MA : False&lt;br&gt;VOL : False</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>141.65</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>148.1152919500972</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>135.1847080499028</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>0.09128544934835393</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>0.002654397451778534</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>-0.0002059336306642345</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>-0.06151019020493131</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>0.05147900810379896</t>
+        </is>
+      </c>
+      <c r="AD8" t="inlineStr">
+        <is>
+          <t>1.49820616914414</t>
+        </is>
+      </c>
+      <c r="AE8" t="inlineStr">
+        <is>
+          <t>2026-09-02 00:00:00</t>
+        </is>
+      </c>
+      <c r="AF8" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="AG8" t="inlineStr">
+        <is>
           <t>40.0</t>
         </is>
       </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>盤整偏多</t>
-        </is>
-      </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>TrendType : 盤整偏多&lt;br&gt;TrendScore : 40&lt;br&gt;HH : True&lt;br&gt;HL : False&lt;br&gt;MA : False&lt;br&gt;VOL : False</t>
-        </is>
-      </c>
-      <c r="V8" t="inlineStr">
-        <is>
-          <t>141.275</t>
-        </is>
-      </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>148.1458001525924</t>
-        </is>
-      </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>134.4041998474076</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>0.0972684502225076</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>0.003017394391196415</t>
-        </is>
-      </c>
-      <c r="AA8" t="inlineStr">
-        <is>
-          <t>0.0006164580977034984</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>-0.0491912858969541</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>0.0479762948677207</t>
-        </is>
-      </c>
-      <c r="AD8" t="inlineStr">
-        <is>
-          <t>1.699323642510481</t>
-        </is>
-      </c>
-      <c r="AE8" t="inlineStr">
-        <is>
-          <t>2026-09-02 00:00:00</t>
-        </is>
-      </c>
-      <c r="AF8" t="inlineStr">
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>2026-09-03 00:00:00</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AL8" t="inlineStr">
+        <is>
+          <t>2026-09-08 00:00:00</t>
+        </is>
+      </c>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AN8" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="AP8" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="AQ8" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AR8" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AS8" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AU8" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="AG8" t="inlineStr">
-        <is>
-          <t>40.0</t>
-        </is>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>2026-09-03 00:00:00</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AL8" t="inlineStr">
-        <is>
-          <t>2026-09-08 00:00:00</t>
-        </is>
-      </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
-      </c>
-      <c r="AN8" t="inlineStr">
+      <c r="AV8" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
         <is>
           <t>2.0</t>
         </is>
       </c>
-      <c r="AO8" t="inlineStr">
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>7.0</t>
+        </is>
+      </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>14.0</t>
+        </is>
+      </c>
+      <c r="BA8" t="inlineStr">
+        <is>
+          <t>14.0</t>
+        </is>
+      </c>
+      <c r="BB8" t="inlineStr">
+        <is>
+          <t>14.0</t>
+        </is>
+      </c>
+      <c r="BC8" t="inlineStr">
+        <is>
+          <t>盤整</t>
+        </is>
+      </c>
+      <c r="BD8" t="inlineStr">
+        <is>
+          <t>盤整</t>
+        </is>
+      </c>
+      <c r="BE8" t="inlineStr">
+        <is>
+          <t>58.3</t>
+        </is>
+      </c>
+      <c r="BF8" t="inlineStr">
+        <is>
+          <t>17134672.0</t>
+        </is>
+      </c>
+      <c r="BG8" t="inlineStr">
+        <is>
+          <t>1355796.0</t>
+        </is>
+      </c>
+      <c r="BH8" t="inlineStr">
+        <is>
+          <t>4433570.0</t>
+        </is>
+      </c>
+      <c r="BI8" t="inlineStr">
+        <is>
+          <t>-3077774.0</t>
+        </is>
+      </c>
+      <c r="BJ8" t="inlineStr">
+        <is>
+          <t>-302018.0</t>
+        </is>
+      </c>
+      <c r="BK8" t="inlineStr">
+        <is>
+          <t>13754880.0</t>
+        </is>
+      </c>
+      <c r="BL8" t="inlineStr">
         <is>
           <t>5.0</t>
         </is>
       </c>
-      <c r="AP8" t="inlineStr">
-        <is>
-          <t>7.0</t>
-        </is>
-      </c>
-      <c r="AQ8" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AR8" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AS8" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AT8" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AU8" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="AV8" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AW8" t="inlineStr">
+      <c r="BM8" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="BN8" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="AX8" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr">
-        <is>
-          <t>8.0</t>
-        </is>
-      </c>
-      <c r="AZ8" t="inlineStr">
-        <is>
-          <t>14.0</t>
-        </is>
-      </c>
-      <c r="BA8" t="inlineStr">
-        <is>
-          <t>14.0</t>
-        </is>
-      </c>
-      <c r="BB8" t="inlineStr">
-        <is>
-          <t>14.0</t>
-        </is>
-      </c>
-      <c r="BC8" t="inlineStr">
-        <is>
-          <t>盤整</t>
-        </is>
-      </c>
-      <c r="BD8" t="inlineStr">
-        <is>
-          <t>強勢</t>
-        </is>
-      </c>
-      <c r="BE8" t="inlineStr">
-        <is>
-          <t>58.3</t>
-        </is>
-      </c>
-      <c r="BF8" t="inlineStr">
-        <is>
-          <t>17850578.0</t>
-        </is>
-      </c>
-      <c r="BG8" t="inlineStr">
-        <is>
-          <t>1360796.0</t>
-        </is>
-      </c>
-      <c r="BH8" t="inlineStr">
-        <is>
-          <t>4418171.0</t>
-        </is>
-      </c>
-      <c r="BI8" t="inlineStr">
-        <is>
-          <t>-3057375.0</t>
-        </is>
-      </c>
-      <c r="BJ8" t="inlineStr">
-        <is>
-          <t>-284018.0</t>
-        </is>
-      </c>
-      <c r="BK8" t="inlineStr">
-        <is>
-          <t>14509185.0</t>
-        </is>
-      </c>
-      <c r="BL8" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
-      </c>
-      <c r="BM8" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
-      </c>
-      <c r="BN8" t="inlineStr">
-        <is>
-          <t>-1.0</t>
-        </is>
-      </c>
       <c r="BO8" t="inlineStr">
         <is>
           <t>False</t>
@@ -7744,17 +7744,17 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="CC8" t="inlineStr">
         <is>
-          <t>19.45</t>
+          <t>17.70</t>
         </is>
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>-0.69</t>
+          <t>-0.70</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
@@ -7765,110 +7765,110 @@
       <c r="CF8" t="inlineStr"/>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>67</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
         <is>
-          <t>7081</t>
+          <t>9157</t>
         </is>
       </c>
       <c r="CI8" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="CJ8" t="inlineStr">
         <is>
-          <t>69.44</t>
+          <t>36.11</t>
         </is>
       </c>
       <c r="CK8" t="n">
-        <v>-0.55</v>
+        <v>-0.76</v>
       </c>
       <c r="CL8" t="n">
-        <v>2.5</v>
+        <v>2.08</v>
       </c>
       <c r="CM8" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="CN8" t="inlineStr">
         <is>
-          <t>-0.57</t>
+          <t>-0.52</t>
         </is>
       </c>
       <c r="CO8" t="inlineStr">
         <is>
-          <t>144.8</t>
+          <t>144.6</t>
         </is>
       </c>
       <c r="CP8" t="inlineStr">
         <is>
-          <t>144.4</t>
+          <t>144.5</t>
         </is>
       </c>
       <c r="CQ8" t="inlineStr">
         <is>
-          <t>141.28</t>
+          <t>141.65</t>
         </is>
       </c>
       <c r="CR8" t="inlineStr">
         <is>
-          <t>138.99</t>
+          <t>139.08</t>
         </is>
       </c>
       <c r="CS8" t="inlineStr">
         <is>
-          <t>139.79</t>
+          <t>139.81</t>
         </is>
       </c>
       <c r="CT8" t="inlineStr">
         <is>
-          <t>135.8145833333333</t>
+          <t>0</t>
         </is>
       </c>
       <c r="CU8" t="inlineStr">
         <is>
-          <t>-0.002067539627842785</t>
+          <t>-0.001381215469613339</t>
         </is>
       </c>
       <c r="CV8" t="inlineStr">
         <is>
-          <t>0.002429711905588272</t>
+          <t>0.0006925207756232066</t>
         </is>
       </c>
       <c r="CW8" t="inlineStr">
         <is>
-          <t>0.003017394391196415</t>
+          <t>0.002654397451778534</t>
         </is>
       </c>
       <c r="CX8" t="inlineStr">
         <is>
-          <t>0.0008641175199828321</t>
+          <t>0.0006475285991798252</t>
         </is>
       </c>
       <c r="CY8" t="inlineStr">
         <is>
-          <t>0.0002683363148479057</t>
+          <t>0.0001788428865241443</t>
         </is>
       </c>
       <c r="CZ8" t="inlineStr">
         <is>
-          <t>0.0003222341568205334</t>
+          <t>0</t>
         </is>
       </c>
       <c r="DA8" t="inlineStr">
         <is>
-          <t>17.86</t>
+          <t>7.47</t>
         </is>
       </c>
       <c r="DB8" t="n">
-        <v>2.04</v>
+        <v>1.9</v>
       </c>
       <c r="DC8" t="n">
-        <v>1.73</v>
+        <v>1.76</v>
       </c>
       <c r="DD8" t="inlineStr">
         <is>
@@ -7877,7 +7877,7 @@
       </c>
       <c r="DE8" t="inlineStr">
         <is>
-          <t>-8.63</t>
+          <t>-6.89</t>
         </is>
       </c>
       <c r="DF8" t="inlineStr">
@@ -7887,48 +7887,48 @@
       </c>
       <c r="DG8" t="inlineStr">
         <is>
-          <t>2214561876.963068</t>
+          <t>2510241792.666667</t>
         </is>
       </c>
       <c r="DH8" t="inlineStr">
         <is>
-          <t>1676725028.0</t>
+          <t>1524028999.0</t>
         </is>
       </c>
       <c r="DI8" t="n">
-        <v>1178675636.2</v>
+        <v>1223386087.6</v>
       </c>
       <c r="DJ8" t="inlineStr">
         <is>
-          <t>1937528191.3</t>
+          <t>1823976219.1</t>
         </is>
       </c>
       <c r="DK8" t="inlineStr">
         <is>
-          <t>1486546014.1</t>
+          <t>1490856706.633333</t>
         </is>
       </c>
       <c r="DL8" t="n">
-        <v>1735471199.16</v>
+        <v>1693335182.06</v>
       </c>
       <c r="DM8" t="inlineStr">
         <is>
-          <t>2026673727.9875</t>
+          <t>2020913533.8875</t>
         </is>
       </c>
       <c r="DN8" t="inlineStr">
         <is>
-          <t>44598963.52689654</t>
+          <t>30644943.61799386</t>
         </is>
       </c>
       <c r="DO8" t="inlineStr">
         <is>
-          <t>-45987257.26803184</t>
+          <t>-46102165.86613226</t>
         </is>
       </c>
       <c r="DP8" t="inlineStr">
         <is>
-          <t>1676725028.0</t>
+          <t>1524028999.0</t>
         </is>
       </c>
       <c r="DQ8" t="inlineStr">
@@ -7948,7 +7948,7 @@
       </c>
       <c r="DT8" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="DU8" t="inlineStr">
@@ -7993,7 +7993,7 @@
       </c>
       <c r="EC8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="ED8" t="inlineStr">
@@ -8003,12 +8003,12 @@
       </c>
       <c r="EE8" t="inlineStr">
         <is>
-          <t>3.05</t>
+          <t>3.04</t>
         </is>
       </c>
       <c r="EF8" t="inlineStr">
         <is>
-          <t>3.57</t>
+          <t>3.55</t>
         </is>
       </c>
       <c r="EG8" t="inlineStr">
@@ -8018,7 +8018,7 @@
       </c>
       <c r="EH8" t="inlineStr">
         <is>
-          <t>28.59</t>
+          <t>28.78</t>
         </is>
       </c>
       <c r="EI8" t="inlineStr">
@@ -8033,12 +8033,12 @@
       </c>
       <c r="EK8" t="inlineStr">
         <is>
-          <t>85.4</t>
+          <t>84.4</t>
         </is>
       </c>
       <c r="EL8" t="inlineStr">
         <is>
-          <t>1128708</t>
+          <t>1136466</t>
         </is>
       </c>
       <c r="EM8" t="inlineStr">
@@ -8058,12 +8058,12 @@
       </c>
       <c r="EP8" t="inlineStr">
         <is>
-          <t>146.0</t>
+          <t>145.0</t>
         </is>
       </c>
       <c r="EQ8" t="inlineStr">
         <is>
-          <t>146.0</t>
+          <t>145.0</t>
         </is>
       </c>
       <c r="ER8" t="inlineStr">
@@ -8073,12 +8073,12 @@
       </c>
       <c r="ES8" t="inlineStr">
         <is>
-          <t>144.0</t>
+          <t>143.5</t>
         </is>
       </c>
       <c r="ET8" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>129.5</t>
         </is>
       </c>
       <c r="EU8" t="inlineStr">
@@ -8098,42 +8098,42 @@
       </c>
       <c r="EX8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="EY8" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>5</t>
         </is>
       </c>
       <c r="EZ8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FA8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FB8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FC8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FD8" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="FE8" t="inlineStr">
         <is>
-          <t>13.0</t>
+          <t>12</t>
         </is>
       </c>
       <c r="FF8" t="inlineStr">
@@ -8143,22 +8143,22 @@
       </c>
       <c r="FG8" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>4</t>
         </is>
       </c>
       <c r="FH8" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="FI8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FJ8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FK8" t="inlineStr">
@@ -8345,12 +8345,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>-0.68</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>6311.915</t>
+          <t>11652.18</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -8360,7 +8360,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>145.0</t>
+          <t>144.0</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -8370,7 +8370,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0.34</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -8380,7 +8380,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-0.15933593107033336</t>
+          <t>-0.39166013609889294</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -8425,242 +8425,242 @@
       </c>
       <c r="S9" t="inlineStr">
         <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>盤整偏多</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>TrendType : 盤整偏多&lt;br&gt;TrendScore : 40&lt;br&gt;HH : True&lt;br&gt;HL : False&lt;br&gt;MA : False&lt;br&gt;VOL : False</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>141.275</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>148.1458001525903</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>134.4041998474098</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>0.09726845022247742</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>0.003017394391196415</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>0.0006164580977021661</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>-0.04919128589699406</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>0.05147900810379896</t>
+        </is>
+      </c>
+      <c r="AD9" t="inlineStr">
+        <is>
+          <t>1.699323642510904</t>
+        </is>
+      </c>
+      <c r="AE9" t="inlineStr">
+        <is>
+          <t>2026-09-02 00:00:00</t>
+        </is>
+      </c>
+      <c r="AF9" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="AG9" t="inlineStr">
+        <is>
           <t>40.0</t>
         </is>
       </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>盤整偏多</t>
-        </is>
-      </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>TrendType : 盤整偏多&lt;br&gt;TrendScore : 40&lt;br&gt;HH : True&lt;br&gt;HL : False&lt;br&gt;MA : False&lt;br&gt;VOL : False</t>
-        </is>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>140.85</t>
-        </is>
-      </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>148.0545307382171</t>
-        </is>
-      </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>133.6454692617829</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>0.1023007559562248</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>0.00338379341050743</t>
-        </is>
-      </c>
-      <c r="AA9" t="inlineStr">
-        <is>
-          <t>0.002539703250195702</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>-0.01700799986580759</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>0.0479762948677207</t>
-        </is>
-      </c>
-      <c r="AD9" t="inlineStr">
-        <is>
-          <t>1.907951888344097</t>
-        </is>
-      </c>
-      <c r="AE9" t="inlineStr">
-        <is>
-          <t>2026-09-02 00:00:00</t>
-        </is>
-      </c>
-      <c r="AF9" t="inlineStr">
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>2026-09-03 00:00:00</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AL9" t="inlineStr">
+        <is>
+          <t>2026-09-08 00:00:00</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AN9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="AP9" t="inlineStr">
+        <is>
+          <t>7.0</t>
+        </is>
+      </c>
+      <c r="AQ9" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AR9" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AS9" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AU9" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="AG9" t="inlineStr">
-        <is>
-          <t>40.0</t>
-        </is>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>2026-09-03 00:00:00</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AL9" t="inlineStr">
-        <is>
-          <t>2026-09-08 00:00:00</t>
-        </is>
-      </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
-      </c>
-      <c r="AN9" t="inlineStr">
+      <c r="AV9" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>8.0</t>
+        </is>
+      </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>14.0</t>
+        </is>
+      </c>
+      <c r="BA9" t="inlineStr">
+        <is>
+          <t>14.0</t>
+        </is>
+      </c>
+      <c r="BB9" t="inlineStr">
+        <is>
+          <t>14.0</t>
+        </is>
+      </c>
+      <c r="BC9" t="inlineStr">
+        <is>
+          <t>盤整</t>
+        </is>
+      </c>
+      <c r="BD9" t="inlineStr">
+        <is>
+          <t>強勢</t>
+        </is>
+      </c>
+      <c r="BE9" t="inlineStr">
+        <is>
+          <t>58.3</t>
+        </is>
+      </c>
+      <c r="BF9" t="inlineStr">
+        <is>
+          <t>17134672.0</t>
+        </is>
+      </c>
+      <c r="BG9" t="inlineStr">
+        <is>
+          <t>1355796.0</t>
+        </is>
+      </c>
+      <c r="BH9" t="inlineStr">
+        <is>
+          <t>4433570.0</t>
+        </is>
+      </c>
+      <c r="BI9" t="inlineStr">
+        <is>
+          <t>-3077774.0</t>
+        </is>
+      </c>
+      <c r="BJ9" t="inlineStr">
+        <is>
+          <t>-302018.0</t>
+        </is>
+      </c>
+      <c r="BK9" t="inlineStr">
+        <is>
+          <t>13754880.0</t>
+        </is>
+      </c>
+      <c r="BL9" t="inlineStr">
         <is>
           <t>5.0</t>
         </is>
       </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>7.0</t>
-        </is>
-      </c>
-      <c r="AP9" t="inlineStr">
-        <is>
-          <t>7.0</t>
-        </is>
-      </c>
-      <c r="AQ9" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AR9" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AS9" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AT9" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AU9" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="AV9" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AW9" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
-      </c>
-      <c r="AX9" t="inlineStr">
-        <is>
-          <t>4.0</t>
-        </is>
-      </c>
-      <c r="AY9" t="inlineStr">
-        <is>
-          <t>9.0</t>
-        </is>
-      </c>
-      <c r="AZ9" t="inlineStr">
-        <is>
-          <t>14.0</t>
-        </is>
-      </c>
-      <c r="BA9" t="inlineStr">
-        <is>
-          <t>14.0</t>
-        </is>
-      </c>
-      <c r="BB9" t="inlineStr">
-        <is>
-          <t>14.0</t>
-        </is>
-      </c>
-      <c r="BC9" t="inlineStr">
-        <is>
-          <t>強勢</t>
-        </is>
-      </c>
-      <c r="BD9" t="inlineStr">
-        <is>
-          <t>強勢</t>
-        </is>
-      </c>
-      <c r="BE9" t="inlineStr">
-        <is>
-          <t>58.3</t>
-        </is>
-      </c>
-      <c r="BF9" t="inlineStr">
-        <is>
-          <t>17850578.0</t>
-        </is>
-      </c>
-      <c r="BG9" t="inlineStr">
-        <is>
-          <t>1360796.0</t>
-        </is>
-      </c>
-      <c r="BH9" t="inlineStr">
-        <is>
-          <t>4418171.0</t>
-        </is>
-      </c>
-      <c r="BI9" t="inlineStr">
-        <is>
-          <t>-3057375.0</t>
-        </is>
-      </c>
-      <c r="BJ9" t="inlineStr">
-        <is>
-          <t>-284018.0</t>
-        </is>
-      </c>
-      <c r="BK9" t="inlineStr">
-        <is>
-          <t>14509185.0</t>
-        </is>
-      </c>
-      <c r="BL9" t="inlineStr">
+      <c r="BM9" t="inlineStr">
         <is>
           <t>5.0</t>
         </is>
       </c>
-      <c r="BM9" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
-      </c>
       <c r="BN9" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="BO9" t="inlineStr">
@@ -8680,7 +8680,7 @@
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>-0.18</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
@@ -8730,12 +8730,12 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="CC9" t="inlineStr">
         <is>
-          <t>10.53</t>
+          <t>19.45</t>
         </is>
       </c>
       <c r="CD9" t="inlineStr">
@@ -8751,110 +8751,110 @@
       <c r="CF9" t="inlineStr"/>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>67</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
         <is>
-          <t>7081</t>
+          <t>9157</t>
         </is>
       </c>
       <c r="CI9" t="inlineStr">
         <is>
-          <t>83.33</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="CJ9" t="inlineStr">
         <is>
-          <t>91.67</t>
+          <t>69.44</t>
         </is>
       </c>
       <c r="CK9" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.55</v>
       </c>
       <c r="CL9" t="n">
-        <v>3.02</v>
+        <v>2.5</v>
       </c>
       <c r="CM9" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="CN9" t="inlineStr">
         <is>
-          <t>-0.63</t>
+          <t>-0.57</t>
         </is>
       </c>
       <c r="CO9" t="inlineStr">
         <is>
-          <t>145.1</t>
+          <t>144.8</t>
         </is>
       </c>
       <c r="CP9" t="inlineStr">
         <is>
-          <t>144.05</t>
+          <t>144.4</t>
         </is>
       </c>
       <c r="CQ9" t="inlineStr">
         <is>
-          <t>140.85</t>
+          <t>141.28</t>
         </is>
       </c>
       <c r="CR9" t="inlineStr">
         <is>
-          <t>138.87</t>
+          <t>138.99</t>
         </is>
       </c>
       <c r="CS9" t="inlineStr">
         <is>
-          <t>139.75</t>
+          <t>139.79</t>
         </is>
       </c>
       <c r="CT9" t="inlineStr">
         <is>
-          <t>135.7708333333333</t>
+          <t>0</t>
         </is>
       </c>
       <c r="CU9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-0.002067539627842785</t>
         </is>
       </c>
       <c r="CV9" t="inlineStr">
         <is>
-          <t>0.003832752613240453</t>
+          <t>0.002429711905588272</t>
         </is>
       </c>
       <c r="CW9" t="inlineStr">
         <is>
-          <t>0.00338379341050743</t>
+          <t>0.003017394391196415</t>
         </is>
       </c>
       <c r="CX9" t="inlineStr">
         <is>
-          <t>0.001297858533420015</t>
+          <t>0.0008641175199828321</t>
         </is>
       </c>
       <c r="CY9" t="inlineStr">
         <is>
-          <t>0.0002684083385522396</t>
+          <t>0.0002683363148479057</t>
         </is>
       </c>
       <c r="CZ9" t="inlineStr">
         <is>
-          <t>0.0003223380251424768</t>
+          <t>0</t>
         </is>
       </c>
       <c r="DA9" t="inlineStr">
         <is>
-          <t>29.64</t>
+          <t>17.86</t>
         </is>
       </c>
       <c r="DB9" t="n">
-        <v>2.14</v>
+        <v>2.04</v>
       </c>
       <c r="DC9" t="n">
-        <v>1.65</v>
+        <v>1.73</v>
       </c>
       <c r="DD9" t="inlineStr">
         <is>
@@ -8863,7 +8863,7 @@
       </c>
       <c r="DE9" t="inlineStr">
         <is>
-          <t>-12.71</t>
+          <t>-8.63</t>
         </is>
       </c>
       <c r="DF9" t="inlineStr">
@@ -8873,48 +8873,48 @@
       </c>
       <c r="DG9" t="inlineStr">
         <is>
-          <t>2214561876.963068</t>
+          <t>2510241792.666667</t>
         </is>
       </c>
       <c r="DH9" t="inlineStr">
         <is>
-          <t>918019598.0</t>
+          <t>1676725028.0</t>
         </is>
       </c>
       <c r="DI9" t="n">
-        <v>1659195852.6</v>
+        <v>1178675636.2</v>
       </c>
       <c r="DJ9" t="inlineStr">
         <is>
-          <t>1973672854.5</t>
+          <t>1937528191.3</t>
         </is>
       </c>
       <c r="DK9" t="inlineStr">
         <is>
-          <t>1482010386.8</t>
+          <t>1486546014.1</t>
         </is>
       </c>
       <c r="DL9" t="n">
-        <v>1806077677.02</v>
+        <v>1735471199.16</v>
       </c>
       <c r="DM9" t="inlineStr">
         <is>
-          <t>2030537576.35</t>
+          <t>2026673727.9875</t>
         </is>
       </c>
       <c r="DN9" t="inlineStr">
         <is>
-          <t>61069185.48961079</t>
+          <t>44598963.52419861</t>
         </is>
       </c>
       <c r="DO9" t="inlineStr">
         <is>
-          <t>-60540988.90475464</t>
+          <t>-45987257.26861119</t>
         </is>
       </c>
       <c r="DP9" t="inlineStr">
         <is>
-          <t>918019598.0</t>
+          <t>1676725028.0</t>
         </is>
       </c>
       <c r="DQ9" t="inlineStr">
@@ -8934,7 +8934,7 @@
       </c>
       <c r="DT9" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>0.35</t>
         </is>
       </c>
       <c r="DU9" t="inlineStr">
@@ -8989,12 +8989,12 @@
       </c>
       <c r="EE9" t="inlineStr">
         <is>
-          <t>3.07</t>
+          <t>3.05</t>
         </is>
       </c>
       <c r="EF9" t="inlineStr">
         <is>
-          <t>3.57</t>
+          <t>3.55</t>
         </is>
       </c>
       <c r="EG9" t="inlineStr">
@@ -9004,7 +9004,7 @@
       </c>
       <c r="EH9" t="inlineStr">
         <is>
-          <t>28.59</t>
+          <t>28.78</t>
         </is>
       </c>
       <c r="EI9" t="inlineStr">
@@ -9019,12 +9019,12 @@
       </c>
       <c r="EK9" t="inlineStr">
         <is>
-          <t>85.4</t>
+          <t>84.4</t>
         </is>
       </c>
       <c r="EL9" t="inlineStr">
         <is>
-          <t>1128708</t>
+          <t>1136466</t>
         </is>
       </c>
       <c r="EM9" t="inlineStr">
@@ -9044,7 +9044,7 @@
       </c>
       <c r="EP9" t="inlineStr">
         <is>
-          <t>145.5</t>
+          <t>146.0</t>
         </is>
       </c>
       <c r="EQ9" t="inlineStr">
@@ -9054,17 +9054,17 @@
       </c>
       <c r="ER9" t="inlineStr">
         <is>
-          <t>145.0</t>
+          <t>143.0</t>
         </is>
       </c>
       <c r="ES9" t="inlineStr">
         <is>
-          <t>145.0</t>
+          <t>144.0</t>
         </is>
       </c>
       <c r="ET9" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>129.5</t>
         </is>
       </c>
       <c r="EU9" t="inlineStr">
@@ -9084,67 +9084,67 @@
       </c>
       <c r="EX9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="EY9" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>5</t>
         </is>
       </c>
       <c r="EZ9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FA9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FB9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FC9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FD9" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="FE9" t="inlineStr">
         <is>
-          <t>14.0</t>
+          <t>13</t>
         </is>
       </c>
       <c r="FF9" t="inlineStr">
         <is>
-          <t>1.119557506059444</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FG9" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>4</t>
         </is>
       </c>
       <c r="FH9" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="FI9" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FJ9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FK9" t="inlineStr">
@@ -9331,12 +9331,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>0.34</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>8326.189</t>
+          <t>6311.915</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -9346,359 +9346,359 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
+          <t>145.0</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>1.02</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>-0.15933593107033336</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>99.0</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>盤整偏多</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>TrendType : 盤整偏多&lt;br&gt;TrendScore : 40&lt;br&gt;HH : True&lt;br&gt;HL : False&lt;br&gt;MA : False&lt;br&gt;VOL : False</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>140.85</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>148.0545307382152</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>133.6454692617848</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>0.1023007559561973</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>0.00338379341050743</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>0.002539703250194592</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>-0.01700799986583423</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>0.05147900810379896</t>
+        </is>
+      </c>
+      <c r="AD10" t="inlineStr">
+        <is>
+          <t>1.907951888344739</t>
+        </is>
+      </c>
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t>2026-09-02 00:00:00</t>
+        </is>
+      </c>
+      <c r="AF10" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="AG10" t="inlineStr">
+        <is>
+          <t>40.0</t>
+        </is>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>2026-09-03 00:00:00</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AL10" t="inlineStr">
+        <is>
+          <t>2026-09-08 00:00:00</t>
+        </is>
+      </c>
+      <c r="AM10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AN10" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>7.0</t>
+        </is>
+      </c>
+      <c r="AP10" t="inlineStr">
+        <is>
+          <t>7.0</t>
+        </is>
+      </c>
+      <c r="AQ10" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AR10" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AS10" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AU10" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="AV10" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>4.0</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>9.0</t>
+        </is>
+      </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>14.0</t>
+        </is>
+      </c>
+      <c r="BA10" t="inlineStr">
+        <is>
+          <t>14.0</t>
+        </is>
+      </c>
+      <c r="BB10" t="inlineStr">
+        <is>
+          <t>14.0</t>
+        </is>
+      </c>
+      <c r="BC10" t="inlineStr">
+        <is>
+          <t>強勢</t>
+        </is>
+      </c>
+      <c r="BD10" t="inlineStr">
+        <is>
+          <t>強勢</t>
+        </is>
+      </c>
+      <c r="BE10" t="inlineStr">
+        <is>
+          <t>58.3</t>
+        </is>
+      </c>
+      <c r="BF10" t="inlineStr">
+        <is>
+          <t>17134672.0</t>
+        </is>
+      </c>
+      <c r="BG10" t="inlineStr">
+        <is>
+          <t>1355796.0</t>
+        </is>
+      </c>
+      <c r="BH10" t="inlineStr">
+        <is>
+          <t>4433570.0</t>
+        </is>
+      </c>
+      <c r="BI10" t="inlineStr">
+        <is>
+          <t>-3077774.0</t>
+        </is>
+      </c>
+      <c r="BJ10" t="inlineStr">
+        <is>
+          <t>-302018.0</t>
+        </is>
+      </c>
+      <c r="BK10" t="inlineStr">
+        <is>
+          <t>13754880.0</t>
+        </is>
+      </c>
+      <c r="BL10" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="BM10" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="BN10" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="BO10" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="BP10" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="BQ10" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="BR10" t="inlineStr">
+        <is>
+          <t>-0.12</t>
+        </is>
+      </c>
+      <c r="BS10" t="inlineStr">
+        <is>
+          <t>2026/07/20</t>
+        </is>
+      </c>
+      <c r="BT10" t="inlineStr">
+        <is>
+          <t>139.0</t>
+        </is>
+      </c>
+      <c r="BU10" t="inlineStr">
+        <is>
+          <t>2026/04/16</t>
+        </is>
+      </c>
+      <c r="BV10" t="inlineStr">
+        <is>
+          <t>136.5</t>
+        </is>
+      </c>
+      <c r="BW10" t="inlineStr">
+        <is>
+          <t>2026/10/07</t>
+        </is>
+      </c>
+      <c r="BX10" t="inlineStr">
+        <is>
           <t>145.5</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>-0.03295367443261963</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>99.0</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="R10" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>30.0</t>
-        </is>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>弱勢整理</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>TrendType : 弱勢整理&lt;br&gt;TrendScore : 30&lt;br&gt;HH : False&lt;br&gt;HL : False&lt;br&gt;MA : True&lt;br&gt;VOL : True</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>140.375</t>
-        </is>
-      </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>147.6794687115433</t>
-        </is>
-      </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>133.0705312884567</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>0.1040707919721211</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>0.003395282344531791</t>
-        </is>
-      </c>
-      <c r="AA10" t="inlineStr">
-        <is>
-          <t>0.004384515128183608</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>0.02031726359983477</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>0.0479762948677207</t>
-        </is>
-      </c>
-      <c r="AD10" t="inlineStr">
-        <is>
-          <t>2.079004612847744</t>
-        </is>
-      </c>
-      <c r="AE10" t="inlineStr">
-        <is>
-          <t>2026-09-02 00:00:00</t>
-        </is>
-      </c>
-      <c r="AF10" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="AG10" t="inlineStr">
-        <is>
-          <t>40.0</t>
-        </is>
-      </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>20.0</t>
-        </is>
-      </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AJ10" t="inlineStr">
-        <is>
-          <t>2026-09-03 00:00:00</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AL10" t="inlineStr">
-        <is>
-          <t>2026-09-08 00:00:00</t>
-        </is>
-      </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
-      </c>
-      <c r="AN10" t="inlineStr">
-        <is>
-          <t>7.0</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>7.0</t>
-        </is>
-      </c>
-      <c r="AP10" t="inlineStr">
-        <is>
-          <t>8.0</t>
-        </is>
-      </c>
-      <c r="AQ10" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AR10" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AS10" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AT10" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AU10" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="AV10" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="AW10" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
-      </c>
-      <c r="AX10" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
-      </c>
-      <c r="AY10" t="inlineStr">
-        <is>
-          <t>10.0</t>
-        </is>
-      </c>
-      <c r="AZ10" t="inlineStr">
-        <is>
-          <t>14.0</t>
-        </is>
-      </c>
-      <c r="BA10" t="inlineStr">
-        <is>
-          <t>14.0</t>
-        </is>
-      </c>
-      <c r="BB10" t="inlineStr">
-        <is>
-          <t>14.0</t>
-        </is>
-      </c>
-      <c r="BC10" t="inlineStr">
-        <is>
-          <t>強勢</t>
-        </is>
-      </c>
-      <c r="BD10" t="inlineStr">
-        <is>
-          <t>強勢</t>
-        </is>
-      </c>
-      <c r="BE10" t="inlineStr">
-        <is>
-          <t>58.3</t>
-        </is>
-      </c>
-      <c r="BF10" t="inlineStr">
-        <is>
-          <t>17850578.0</t>
-        </is>
-      </c>
-      <c r="BG10" t="inlineStr">
-        <is>
-          <t>1360796.0</t>
-        </is>
-      </c>
-      <c r="BH10" t="inlineStr">
-        <is>
-          <t>4418171.0</t>
-        </is>
-      </c>
-      <c r="BI10" t="inlineStr">
-        <is>
-          <t>-3057375.0</t>
-        </is>
-      </c>
-      <c r="BJ10" t="inlineStr">
-        <is>
-          <t>-284018.0</t>
-        </is>
-      </c>
-      <c r="BK10" t="inlineStr">
-        <is>
-          <t>14509185.0</t>
-        </is>
-      </c>
-      <c r="BL10" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
-      </c>
-      <c r="BM10" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
-      </c>
-      <c r="BN10" t="inlineStr">
-        <is>
-          <t>-1.0</t>
-        </is>
-      </c>
-      <c r="BO10" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="BP10" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="BQ10" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="BR10" t="inlineStr">
-        <is>
-          <t>-0.07</t>
-        </is>
-      </c>
-      <c r="BS10" t="inlineStr">
-        <is>
-          <t>2026/07/20</t>
-        </is>
-      </c>
-      <c r="BT10" t="inlineStr">
-        <is>
-          <t>139.0</t>
-        </is>
-      </c>
-      <c r="BU10" t="inlineStr">
-        <is>
-          <t>2026/04/16</t>
-        </is>
-      </c>
-      <c r="BV10" t="inlineStr">
-        <is>
-          <t>136.5</t>
-        </is>
-      </c>
-      <c r="BW10" t="inlineStr">
-        <is>
-          <t>2026/10/07</t>
-        </is>
-      </c>
-      <c r="BX10" t="inlineStr">
-        <is>
-          <t>145.5</t>
-        </is>
-      </c>
       <c r="BY10" t="inlineStr">
         <is>
           <t>2026/08/05</t>
@@ -9716,17 +9716,17 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="CC10" t="inlineStr">
         <is>
-          <t>13.90</t>
+          <t>10.53</t>
         </is>
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>0.69</t>
+          <t>-0.69</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
@@ -9737,17 +9737,17 @@
       <c r="CF10" t="inlineStr"/>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>67</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
         <is>
-          <t>7081</t>
+          <t>9157</t>
         </is>
       </c>
       <c r="CI10" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>83.33</t>
         </is>
       </c>
       <c r="CJ10" t="inlineStr">
@@ -9756,19 +9756,19 @@
         </is>
       </c>
       <c r="CK10" t="n">
-        <v>0.28</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="CL10" t="n">
-        <v>3.37</v>
+        <v>3.02</v>
       </c>
       <c r="CM10" t="inlineStr">
         <is>
-          <t>1.21</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="CN10" t="inlineStr">
         <is>
-          <t>-0.73</t>
+          <t>-0.63</t>
         </is>
       </c>
       <c r="CO10" t="inlineStr">
@@ -9778,69 +9778,69 @@
       </c>
       <c r="CP10" t="inlineStr">
         <is>
-          <t>143.5</t>
+          <t>144.05</t>
         </is>
       </c>
       <c r="CQ10" t="inlineStr">
         <is>
-          <t>140.38</t>
+          <t>140.85</t>
         </is>
       </c>
       <c r="CR10" t="inlineStr">
         <is>
-          <t>138.69</t>
+          <t>138.87</t>
         </is>
       </c>
       <c r="CS10" t="inlineStr">
         <is>
-          <t>139.71</t>
+          <t>139.75</t>
         </is>
       </c>
       <c r="CT10" t="inlineStr">
         <is>
-          <t>135.7270833333333</t>
+          <t>0</t>
         </is>
       </c>
       <c r="CU10" t="inlineStr">
         <is>
-          <t>0.002764340013821753</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="CV10" t="inlineStr">
         <is>
-          <t>0.004198740377886701</t>
+          <t>0.003832752613240453</t>
         </is>
       </c>
       <c r="CW10" t="inlineStr">
         <is>
-          <t>0.003395282344531791</t>
+          <t>0.00338379341050743</t>
         </is>
       </c>
       <c r="CX10" t="inlineStr">
         <is>
-          <t>0.001805836463449895</t>
+          <t>0.001297858533420015</t>
         </is>
       </c>
       <c r="CY10" t="inlineStr">
         <is>
-          <t>0.0004475474400287283</t>
+          <t>0.0002684083385522396</t>
         </is>
       </c>
       <c r="CZ10" t="inlineStr">
         <is>
-          <t>0.0003685220729365835</t>
+          <t>0</t>
         </is>
       </c>
       <c r="DA10" t="inlineStr">
         <is>
-          <t>39.98</t>
+          <t>29.64</t>
         </is>
       </c>
       <c r="DB10" t="n">
         <v>2.14</v>
       </c>
       <c r="DC10" t="n">
-        <v>1.53</v>
+        <v>1.65</v>
       </c>
       <c r="DD10" t="inlineStr">
         <is>
@@ -9849,7 +9849,7 @@
       </c>
       <c r="DE10" t="inlineStr">
         <is>
-          <t>-19.18</t>
+          <t>-12.71</t>
         </is>
       </c>
       <c r="DF10" t="inlineStr">
@@ -9859,48 +9859,48 @@
       </c>
       <c r="DG10" t="inlineStr">
         <is>
-          <t>2214561876.963068</t>
+          <t>2510241792.666667</t>
         </is>
       </c>
       <c r="DH10" t="inlineStr">
         <is>
-          <t>1208391141.0</t>
+          <t>918019598.0</t>
         </is>
       </c>
       <c r="DI10" t="n">
-        <v>1915789923.8</v>
+        <v>1659195852.6</v>
       </c>
       <c r="DJ10" t="inlineStr">
         <is>
-          <t>1981073577.5</t>
+          <t>1973672854.5</t>
         </is>
       </c>
       <c r="DK10" t="inlineStr">
         <is>
-          <t>1491726965.1</t>
+          <t>1482010386.8</t>
         </is>
       </c>
       <c r="DL10" t="n">
-        <v>1845563731.54</v>
+        <v>1806077677.02</v>
       </c>
       <c r="DM10" t="inlineStr">
         <is>
-          <t>2053704109.375</t>
+          <t>2030537576.35</t>
         </is>
       </c>
       <c r="DN10" t="inlineStr">
         <is>
-          <t>83180126.28858632</t>
+          <t>61069185.48652767</t>
         </is>
       </c>
       <c r="DO10" t="inlineStr">
         <is>
-          <t>2120011.575097084</t>
+          <t>-60540988.90541673</t>
         </is>
       </c>
       <c r="DP10" t="inlineStr">
         <is>
-          <t>1208391141.0</t>
+          <t>918019598.0</t>
         </is>
       </c>
       <c r="DQ10" t="inlineStr">
@@ -9920,7 +9920,7 @@
       </c>
       <c r="DT10" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>1.05</t>
         </is>
       </c>
       <c r="DU10" t="inlineStr">
@@ -9965,7 +9965,7 @@
       </c>
       <c r="EC10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="ED10" t="inlineStr">
@@ -9975,12 +9975,12 @@
       </c>
       <c r="EE10" t="inlineStr">
         <is>
-          <t>3.08</t>
+          <t>3.07</t>
         </is>
       </c>
       <c r="EF10" t="inlineStr">
         <is>
-          <t>3.57</t>
+          <t>3.55</t>
         </is>
       </c>
       <c r="EG10" t="inlineStr">
@@ -9990,7 +9990,7 @@
       </c>
       <c r="EH10" t="inlineStr">
         <is>
-          <t>28.59</t>
+          <t>28.78</t>
         </is>
       </c>
       <c r="EI10" t="inlineStr">
@@ -10005,12 +10005,12 @@
       </c>
       <c r="EK10" t="inlineStr">
         <is>
-          <t>85.4</t>
+          <t>84.4</t>
         </is>
       </c>
       <c r="EL10" t="inlineStr">
         <is>
-          <t>1128708</t>
+          <t>1136466</t>
         </is>
       </c>
       <c r="EM10" t="inlineStr">
@@ -10030,27 +10030,27 @@
       </c>
       <c r="EP10" t="inlineStr">
         <is>
+          <t>145.5</t>
+        </is>
+      </c>
+      <c r="EQ10" t="inlineStr">
+        <is>
+          <t>146.0</t>
+        </is>
+      </c>
+      <c r="ER10" t="inlineStr">
+        <is>
           <t>145.0</t>
         </is>
       </c>
-      <c r="EQ10" t="inlineStr">
-        <is>
-          <t>145.5</t>
-        </is>
-      </c>
-      <c r="ER10" t="inlineStr">
-        <is>
-          <t>144.5</t>
-        </is>
-      </c>
       <c r="ES10" t="inlineStr">
         <is>
-          <t>145.5</t>
+          <t>145.0</t>
         </is>
       </c>
       <c r="ET10" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>129.5</t>
         </is>
       </c>
       <c r="EU10" t="inlineStr">
@@ -10070,67 +10070,67 @@
       </c>
       <c r="EX10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="EY10" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>5</t>
         </is>
       </c>
       <c r="EZ10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FA10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FB10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FC10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FD10" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="FE10" t="inlineStr">
         <is>
-          <t>15.0</t>
+          <t>14</t>
         </is>
       </c>
       <c r="FF10" t="inlineStr">
         <is>
-          <t>1.284276525544721</t>
+          <t>1.119557506059444</t>
         </is>
       </c>
       <c r="FG10" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>4</t>
         </is>
       </c>
       <c r="FH10" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>4</t>
         </is>
       </c>
       <c r="FI10" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="FJ10" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FK10" t="inlineStr">

--- a/Result/checksun_type/電信.xlsx
+++ b/Result/checksun_type/電信.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:GR10"/>
+  <dimension ref="A1:GS10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -821,610 +821,615 @@
       </c>
       <c r="CA1" s="1" t="inlineStr">
         <is>
+          <t>voc_cross</t>
+        </is>
+      </c>
+      <c r="CB1" s="1" t="inlineStr">
+        <is>
           <t>voc_cross_d</t>
         </is>
       </c>
-      <c r="CB1" s="1" t="inlineStr">
+      <c r="CC1" s="1" t="inlineStr">
         <is>
           <t>日期</t>
         </is>
       </c>
-      <c r="CC1" s="1" t="inlineStr">
+      <c r="CD1" s="1" t="inlineStr">
         <is>
           <t>量能</t>
         </is>
       </c>
-      <c r="CD1" s="1" t="inlineStr">
+      <c r="CE1" s="1" t="inlineStr">
         <is>
           <t>價能</t>
         </is>
       </c>
-      <c r="CE1" s="1" t="inlineStr">
+      <c r="CF1" s="1" t="inlineStr">
         <is>
           <t>cond_entry</t>
         </is>
       </c>
-      <c r="CF1" s="1" t="inlineStr">
+      <c r="CG1" s="1" t="inlineStr">
         <is>
           <t>text_desc</t>
         </is>
       </c>
-      <c r="CG1" s="1" t="inlineStr">
+      <c r="CH1" s="1" t="inlineStr">
         <is>
           <t>盤後量</t>
         </is>
       </c>
-      <c r="CH1" s="1" t="inlineStr">
+      <c r="CI1" s="1" t="inlineStr">
         <is>
           <t>成交量</t>
         </is>
       </c>
-      <c r="CI1" s="1" t="inlineStr">
+      <c r="CJ1" s="1" t="inlineStr">
         <is>
           <t>%K</t>
         </is>
       </c>
-      <c r="CJ1" s="1" t="inlineStr">
+      <c r="CK1" s="1" t="inlineStr">
         <is>
           <t>%D</t>
         </is>
       </c>
-      <c r="CK1" s="1" t="inlineStr">
+      <c r="CL1" s="1" t="inlineStr">
         <is>
           <t>MA5_%</t>
         </is>
       </c>
-      <c r="CL1" s="1" t="inlineStr">
+      <c r="CM1" s="1" t="inlineStr">
         <is>
           <t>均價_%</t>
         </is>
       </c>
-      <c r="CM1" s="1" t="inlineStr">
+      <c r="CN1" s="1" t="inlineStr">
         <is>
           <t>均價long_%</t>
         </is>
       </c>
-      <c r="CN1" s="1" t="inlineStr">
+      <c r="CO1" s="1" t="inlineStr">
         <is>
           <t>均價longlong_%</t>
         </is>
       </c>
-      <c r="CO1" s="1" t="inlineStr">
+      <c r="CP1" s="1" t="inlineStr">
         <is>
           <t>MA_5</t>
         </is>
       </c>
-      <c r="CP1" s="1" t="inlineStr">
+      <c r="CQ1" s="1" t="inlineStr">
         <is>
           <t>MA_10</t>
         </is>
       </c>
-      <c r="CQ1" s="1" t="inlineStr">
+      <c r="CR1" s="1" t="inlineStr">
         <is>
           <t>MA_20</t>
         </is>
       </c>
-      <c r="CR1" s="1" t="inlineStr">
+      <c r="CS1" s="1" t="inlineStr">
         <is>
           <t>MA_50</t>
         </is>
       </c>
-      <c r="CS1" s="1" t="inlineStr">
+      <c r="CT1" s="1" t="inlineStr">
         <is>
           <t>MA_80</t>
         </is>
       </c>
-      <c r="CT1" s="1" t="inlineStr">
+      <c r="CU1" s="1" t="inlineStr">
         <is>
           <t>MA_240</t>
         </is>
       </c>
-      <c r="CU1" s="1" t="inlineStr">
+      <c r="CV1" s="1" t="inlineStr">
         <is>
           <t>MA_5_斜率</t>
         </is>
       </c>
-      <c r="CV1" s="1" t="inlineStr">
+      <c r="CW1" s="1" t="inlineStr">
         <is>
           <t>MA_10_斜率</t>
         </is>
       </c>
-      <c r="CW1" s="1" t="inlineStr">
+      <c r="CX1" s="1" t="inlineStr">
         <is>
           <t>MA_20_斜率</t>
         </is>
       </c>
-      <c r="CX1" s="1" t="inlineStr">
+      <c r="CY1" s="1" t="inlineStr">
         <is>
           <t>MA_50_斜率</t>
         </is>
       </c>
-      <c r="CY1" s="1" t="inlineStr">
+      <c r="CZ1" s="1" t="inlineStr">
         <is>
           <t>MA_80_斜率</t>
         </is>
       </c>
-      <c r="CZ1" s="1" t="inlineStr">
+      <c r="DA1" s="1" t="inlineStr">
         <is>
           <t>MA_240_斜率</t>
         </is>
       </c>
-      <c r="DA1" s="1" t="inlineStr">
+      <c r="DB1" s="1" t="inlineStr">
         <is>
           <t>MACD_%</t>
         </is>
       </c>
-      <c r="DB1" s="1" t="inlineStr">
+      <c r="DC1" s="1" t="inlineStr">
         <is>
           <t>MACD</t>
         </is>
       </c>
-      <c r="DC1" s="1" t="inlineStr">
+      <c r="DD1" s="1" t="inlineStr">
         <is>
           <t>MACD-SL</t>
         </is>
       </c>
-      <c r="DD1" s="1" t="inlineStr">
+      <c r="DE1" s="1" t="inlineStr">
         <is>
           <t>MACD-SL_max</t>
         </is>
       </c>
-      <c r="DE1" s="1" t="inlineStr">
+      <c r="DF1" s="1" t="inlineStr">
         <is>
           <t>MACDSL_%</t>
         </is>
       </c>
-      <c r="DF1" s="1" t="inlineStr">
+      <c r="DG1" s="1" t="inlineStr">
         <is>
           <t>MACD_last_cross_date</t>
         </is>
       </c>
-      <c r="DG1" s="1" t="inlineStr">
+      <c r="DH1" s="1" t="inlineStr">
         <is>
           <t>成交金額平均</t>
         </is>
       </c>
-      <c r="DH1" s="1" t="inlineStr">
+      <c r="DI1" s="1" t="inlineStr">
         <is>
           <t>成交金額</t>
         </is>
       </c>
-      <c r="DI1" s="1" t="inlineStr">
+      <c r="DJ1" s="1" t="inlineStr">
         <is>
           <t>Volume_MA_5</t>
         </is>
       </c>
-      <c r="DJ1" s="1" t="inlineStr">
+      <c r="DK1" s="1" t="inlineStr">
         <is>
           <t>Volume_MA_10</t>
         </is>
       </c>
-      <c r="DK1" s="1" t="inlineStr">
+      <c r="DL1" s="1" t="inlineStr">
         <is>
           <t>Volume_MA_30</t>
         </is>
       </c>
-      <c r="DL1" s="1" t="inlineStr">
+      <c r="DM1" s="1" t="inlineStr">
         <is>
           <t>Volume_MA_50</t>
         </is>
       </c>
-      <c r="DM1" s="1" t="inlineStr">
+      <c r="DN1" s="1" t="inlineStr">
         <is>
           <t>Volume_MA_80</t>
         </is>
       </c>
-      <c r="DN1" s="1" t="inlineStr">
+      <c r="DO1" s="1" t="inlineStr">
         <is>
           <t>volume_threshold</t>
         </is>
       </c>
-      <c r="DO1" s="1" t="inlineStr">
+      <c r="DP1" s="1" t="inlineStr">
         <is>
           <t>VPC_MACD</t>
         </is>
       </c>
-      <c r="DP1" s="1" t="inlineStr">
+      <c r="DQ1" s="1" t="inlineStr">
         <is>
           <t>成交金額_補值</t>
         </is>
       </c>
-      <c r="DQ1" s="1" t="inlineStr">
+      <c r="DR1" s="1" t="inlineStr">
         <is>
           <t>highlight_enddate</t>
         </is>
       </c>
-      <c r="DR1" s="1" t="inlineStr">
+      <c r="DS1" s="1" t="inlineStr">
         <is>
           <t>MA_last_cross_date收盤價</t>
         </is>
       </c>
-      <c r="DS1" s="1" t="inlineStr">
+      <c r="DT1" s="1" t="inlineStr">
         <is>
           <t>MA_last_cross_date</t>
         </is>
       </c>
-      <c r="DT1" s="1" t="inlineStr">
+      <c r="DU1" s="1" t="inlineStr">
         <is>
           <t>MA_last_cross_%</t>
         </is>
       </c>
-      <c r="DU1" s="1" t="inlineStr">
+      <c r="DV1" s="1" t="inlineStr">
         <is>
           <t>stock_name</t>
         </is>
       </c>
-      <c r="DV1" s="1" t="inlineStr">
+      <c r="DW1" s="1" t="inlineStr">
         <is>
           <t>Type0</t>
         </is>
       </c>
-      <c r="DW1" s="1" t="inlineStr">
+      <c r="DX1" s="1" t="inlineStr">
         <is>
           <t>Type1</t>
         </is>
       </c>
-      <c r="DX1" s="1" t="inlineStr">
+      <c r="DY1" s="1" t="inlineStr">
         <is>
           <t>Type2</t>
         </is>
       </c>
-      <c r="DY1" s="1" t="inlineStr">
+      <c r="DZ1" s="1" t="inlineStr">
         <is>
           <t>貝他值</t>
         </is>
       </c>
-      <c r="DZ1" s="1" t="inlineStr">
+      <c r="EA1" s="1" t="inlineStr">
         <is>
           <t>營業收入-上月比較增減(%)</t>
         </is>
       </c>
-      <c r="EA1" s="1" t="inlineStr">
+      <c r="EB1" s="1" t="inlineStr">
         <is>
           <t>營業收入-去年同月增減(%)</t>
         </is>
       </c>
-      <c r="EB1" s="1" t="inlineStr">
+      <c r="EC1" s="1" t="inlineStr">
         <is>
           <t>累計營業收入-前期比較增減(%)</t>
         </is>
       </c>
-      <c r="EC1" s="1" t="inlineStr">
+      <c r="ED1" s="1" t="inlineStr">
         <is>
           <t>Full_Summary</t>
         </is>
       </c>
-      <c r="ED1" s="1" t="inlineStr">
+      <c r="EE1" s="1" t="inlineStr">
         <is>
           <t>textdesc</t>
         </is>
       </c>
-      <c r="EE1" s="1" t="inlineStr">
+      <c r="EF1" s="1" t="inlineStr">
         <is>
           <t>淨值倍率</t>
         </is>
       </c>
-      <c r="EF1" s="1" t="inlineStr">
+      <c r="EG1" s="1" t="inlineStr">
         <is>
           <t>殖利率</t>
         </is>
       </c>
-      <c r="EG1" s="1" t="inlineStr">
+      <c r="EH1" s="1" t="inlineStr">
         <is>
           <t>每股營收(元)</t>
         </is>
       </c>
-      <c r="EH1" s="1" t="inlineStr">
+      <c r="EI1" s="1" t="inlineStr">
         <is>
           <t>本益比</t>
         </is>
       </c>
-      <c r="EI1" s="1" t="inlineStr">
+      <c r="EJ1" s="1" t="inlineStr">
         <is>
           <t>營業毛利率</t>
         </is>
       </c>
-      <c r="EJ1" s="1" t="inlineStr">
+      <c r="EK1" s="1" t="inlineStr">
         <is>
           <t>營業利益率</t>
         </is>
       </c>
-      <c r="EK1" s="1" t="inlineStr">
+      <c r="EL1" s="1" t="inlineStr">
         <is>
           <t>同業平均本益比</t>
         </is>
       </c>
-      <c r="EL1" s="1" t="inlineStr">
+      <c r="EM1" s="1" t="inlineStr">
         <is>
           <t>總市值</t>
         </is>
       </c>
-      <c r="EM1" s="1" t="inlineStr">
+      <c r="EN1" s="1" t="inlineStr">
         <is>
           <t>營收比重</t>
         </is>
       </c>
-      <c r="EN1" s="1" t="inlineStr">
+      <c r="EO1" s="1" t="inlineStr">
         <is>
           <t>Type</t>
         </is>
       </c>
-      <c r="EO1" s="1" t="inlineStr">
+      <c r="EP1" s="1" t="inlineStr">
         <is>
           <t>Typelevel</t>
         </is>
       </c>
-      <c r="EP1" s="1" t="inlineStr">
+      <c r="EQ1" s="1" t="inlineStr">
         <is>
           <t>開盤價</t>
         </is>
       </c>
-      <c r="EQ1" s="1" t="inlineStr">
+      <c r="ER1" s="1" t="inlineStr">
         <is>
           <t>最高價</t>
         </is>
       </c>
-      <c r="ER1" s="1" t="inlineStr">
+      <c r="ES1" s="1" t="inlineStr">
         <is>
           <t>最低價</t>
         </is>
       </c>
-      <c r="ES1" s="1" t="inlineStr">
+      <c r="ET1" s="1" t="inlineStr">
         <is>
           <t>收盤價</t>
         </is>
       </c>
-      <c r="ET1" s="1" t="inlineStr">
+      <c r="EU1" s="1" t="inlineStr">
         <is>
           <t>最小收盤價</t>
         </is>
       </c>
-      <c r="EU1" s="1" t="inlineStr">
+      <c r="EV1" s="1" t="inlineStr">
         <is>
           <t>每股淨值(元)</t>
         </is>
       </c>
-      <c r="EV1" s="1" t="inlineStr">
+      <c r="EW1" s="1" t="inlineStr">
         <is>
           <t>desc</t>
         </is>
       </c>
-      <c r="EW1" s="1" t="inlineStr">
+      <c r="EX1" s="1" t="inlineStr">
         <is>
           <t>flag_stat</t>
         </is>
       </c>
-      <c r="EX1" s="1" t="inlineStr">
+      <c r="EY1" s="1" t="inlineStr">
         <is>
           <t>盤整震盪_前15日次數</t>
         </is>
       </c>
-      <c r="EY1" s="1" t="inlineStr">
+      <c r="EZ1" s="1" t="inlineStr">
         <is>
           <t>多頭排列_前5日次數</t>
         </is>
       </c>
-      <c r="EZ1" s="1" t="inlineStr">
+      <c r="FA1" s="1" t="inlineStr">
         <is>
           <t>下跌帶量_前15日次數</t>
         </is>
       </c>
-      <c r="FA1" s="1" t="inlineStr">
+      <c r="FB1" s="1" t="inlineStr">
         <is>
           <t>MA_break_前15日次數</t>
         </is>
       </c>
-      <c r="FB1" s="1" t="inlineStr">
+      <c r="FC1" s="1" t="inlineStr">
         <is>
           <t>抄底訊號_前15日次數</t>
         </is>
       </c>
-      <c r="FC1" s="1" t="inlineStr">
+      <c r="FD1" s="1" t="inlineStr">
         <is>
           <t>黃金交叉_前15日次數</t>
         </is>
       </c>
-      <c r="FD1" s="1" t="inlineStr">
+      <c r="FE1" s="1" t="inlineStr">
         <is>
           <t>量起點_前15日次數</t>
         </is>
       </c>
-      <c r="FE1" s="1" t="inlineStr">
+      <c r="FF1" s="1" t="inlineStr">
         <is>
           <t>價過5日_前15日次數</t>
         </is>
       </c>
-      <c r="FF1" s="1" t="inlineStr">
+      <c r="FG1" s="1" t="inlineStr">
         <is>
           <t>量短5長30比</t>
         </is>
       </c>
-      <c r="FG1" s="1" t="inlineStr">
+      <c r="FH1" s="1" t="inlineStr">
         <is>
           <t>checkpoint_前10日次數</t>
         </is>
       </c>
-      <c r="FH1" s="1" t="inlineStr">
+      <c r="FI1" s="1" t="inlineStr">
         <is>
           <t>checkpoint_前5日次數</t>
         </is>
       </c>
-      <c r="FI1" s="1" t="inlineStr">
+      <c r="FJ1" s="1" t="inlineStr">
         <is>
           <t>checkpoint_前2日次數</t>
         </is>
       </c>
-      <c r="FJ1" s="1" t="inlineStr">
+      <c r="FK1" s="1" t="inlineStr">
         <is>
           <t>checkpoint_前1日次數</t>
         </is>
       </c>
-      <c r="FK1" s="1" t="inlineStr">
+      <c r="FL1" s="1" t="inlineStr">
         <is>
           <t>季別</t>
         </is>
       </c>
-      <c r="FL1" s="1" t="inlineStr">
+      <c r="FM1" s="1" t="inlineStr">
         <is>
           <t>營業收入</t>
         </is>
       </c>
-      <c r="FM1" s="1" t="inlineStr">
+      <c r="FN1" s="1" t="inlineStr">
         <is>
           <t>營業成本</t>
         </is>
       </c>
-      <c r="FN1" s="1" t="inlineStr">
+      <c r="FO1" s="1" t="inlineStr">
         <is>
           <t>營業毛利</t>
         </is>
       </c>
-      <c r="FO1" s="1" t="inlineStr">
+      <c r="FP1" s="1" t="inlineStr">
         <is>
           <t>毛利率</t>
         </is>
       </c>
-      <c r="FP1" s="1" t="inlineStr">
+      <c r="FQ1" s="1" t="inlineStr">
         <is>
           <t>營業利益</t>
         </is>
       </c>
-      <c r="FQ1" s="1" t="inlineStr">
+      <c r="FR1" s="1" t="inlineStr">
         <is>
           <t>營益率</t>
         </is>
       </c>
-      <c r="FR1" s="1" t="inlineStr">
+      <c r="FS1" s="1" t="inlineStr">
         <is>
           <t>業外收支</t>
         </is>
       </c>
-      <c r="FS1" s="1" t="inlineStr">
+      <c r="FT1" s="1" t="inlineStr">
         <is>
           <t>稅前淨利</t>
         </is>
       </c>
-      <c r="FT1" s="1" t="inlineStr">
+      <c r="FU1" s="1" t="inlineStr">
         <is>
           <t>稅後淨利</t>
         </is>
       </c>
-      <c r="FU1" s="1" t="inlineStr">
+      <c r="FV1" s="1" t="inlineStr">
         <is>
           <t>EPS(元)</t>
         </is>
       </c>
-      <c r="FV1" s="1" t="inlineStr">
+      <c r="FW1" s="1" t="inlineStr">
         <is>
           <t>EPS_前8季全為正</t>
         </is>
       </c>
-      <c r="FW1" s="1" t="inlineStr">
+      <c r="FX1" s="1" t="inlineStr">
         <is>
           <t>去年同季比較</t>
         </is>
       </c>
-      <c r="FX1" s="1" t="inlineStr">
+      <c r="FY1" s="1" t="inlineStr">
         <is>
           <t>EPS_MA_8</t>
         </is>
       </c>
-      <c r="FY1" s="1" t="inlineStr">
+      <c r="FZ1" s="1" t="inlineStr">
         <is>
           <t>GM_MA_8</t>
         </is>
       </c>
-      <c r="FZ1" s="1" t="inlineStr">
+      <c r="GA1" s="1" t="inlineStr">
         <is>
           <t>EPS_維持</t>
         </is>
       </c>
-      <c r="GA1" s="1" t="inlineStr">
+      <c r="GB1" s="1" t="inlineStr">
         <is>
           <t>毛利率_維持</t>
         </is>
       </c>
-      <c r="GB1" s="1" t="inlineStr">
+      <c r="GC1" s="1" t="inlineStr">
         <is>
           <t>EPS_創新高</t>
         </is>
       </c>
-      <c r="GC1" s="1" t="inlineStr">
+      <c r="GD1" s="1" t="inlineStr">
         <is>
           <t>毛利率_創新高</t>
         </is>
       </c>
-      <c r="GD1" s="1" t="inlineStr">
+      <c r="GE1" s="1" t="inlineStr">
         <is>
           <t>財報健康</t>
         </is>
       </c>
-      <c r="GE1" s="1" t="inlineStr">
+      <c r="GF1" s="1" t="inlineStr">
         <is>
           <t>財報強勢</t>
         </is>
       </c>
-      <c r="GF1" s="1" t="inlineStr">
+      <c r="GG1" s="1" t="inlineStr">
         <is>
           <t>EPS_QoQ</t>
         </is>
       </c>
-      <c r="GG1" s="1" t="inlineStr">
+      <c r="GH1" s="1" t="inlineStr">
         <is>
           <t>EPS_QoQ_%</t>
         </is>
       </c>
-      <c r="GH1" s="1" t="inlineStr">
+      <c r="GI1" s="1" t="inlineStr">
         <is>
           <t>GM_QoQ</t>
         </is>
       </c>
-      <c r="GI1" s="1" t="inlineStr">
+      <c r="GJ1" s="1" t="inlineStr">
         <is>
           <t>GM_QoQ_%</t>
         </is>
       </c>
-      <c r="GJ1" s="1" t="inlineStr">
+      <c r="GK1" s="1" t="inlineStr">
         <is>
           <t>EPS_YoY</t>
         </is>
       </c>
-      <c r="GK1" s="1" t="inlineStr">
+      <c r="GL1" s="1" t="inlineStr">
         <is>
           <t>EPS_YoY_%</t>
         </is>
       </c>
-      <c r="GL1" s="1" t="inlineStr">
+      <c r="GM1" s="1" t="inlineStr">
         <is>
           <t>GM_YoY</t>
         </is>
       </c>
-      <c r="GM1" s="1" t="inlineStr">
+      <c r="GN1" s="1" t="inlineStr">
         <is>
           <t>GM_YoY_%</t>
         </is>
       </c>
-      <c r="GN1" s="1" t="inlineStr">
+      <c r="GO1" s="1" t="inlineStr">
         <is>
           <t>EPS_成長</t>
         </is>
       </c>
-      <c r="GO1" s="1" t="inlineStr">
+      <c r="GP1" s="1" t="inlineStr">
         <is>
           <t>EPS_YoY成長</t>
         </is>
       </c>
-      <c r="GP1" s="1" t="inlineStr">
+      <c r="GQ1" s="1" t="inlineStr">
         <is>
           <t>毛利率成長</t>
         </is>
       </c>
-      <c r="GQ1" s="1" t="inlineStr">
+      <c r="GR1" s="1" t="inlineStr">
         <is>
           <t>毛利率YoY成長</t>
         </is>
       </c>
-      <c r="GR1" s="1" t="inlineStr">
+      <c r="GS1" s="1" t="inlineStr">
         <is>
           <t>財報動能強</t>
         </is>
@@ -1823,378 +1828,378 @@
       </c>
       <c r="CA2" t="inlineStr">
         <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="CB2" t="inlineStr">
+        <is>
           <t>2026-09-18 00:00:00</t>
         </is>
       </c>
-      <c r="CB2" t="inlineStr">
+      <c r="CC2" t="inlineStr">
         <is>
           <t>2026-10-08</t>
         </is>
       </c>
-      <c r="CC2" t="inlineStr">
+      <c r="CD2" t="inlineStr">
         <is>
           <t>15.28</t>
         </is>
       </c>
-      <c r="CD2" t="inlineStr">
+      <c r="CE2" t="inlineStr">
         <is>
           <t>1.03</t>
         </is>
       </c>
-      <c r="CE2" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="CF2" t="inlineStr"/>
-      <c r="CG2" t="inlineStr">
+      <c r="CF2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="CG2" t="inlineStr"/>
+      <c r="CH2" t="inlineStr">
         <is>
           <t>67</t>
         </is>
       </c>
-      <c r="CH2" t="inlineStr">
+      <c r="CI2" t="inlineStr">
         <is>
           <t>9157</t>
         </is>
       </c>
-      <c r="CI2" t="inlineStr">
+      <c r="CJ2" t="inlineStr">
         <is>
           <t>100.0</t>
         </is>
       </c>
-      <c r="CJ2" t="inlineStr">
+      <c r="CK2" t="inlineStr">
         <is>
           <t>86.67</t>
         </is>
       </c>
-      <c r="CK2" t="n">
+      <c r="CL2" t="n">
         <v>0.48</v>
       </c>
-      <c r="CL2" t="n">
+      <c r="CM2" t="n">
         <v>1.2</v>
       </c>
-      <c r="CM2" t="inlineStr">
+      <c r="CN2" t="inlineStr">
         <is>
           <t>3.02</t>
         </is>
       </c>
-      <c r="CN2" t="inlineStr">
+      <c r="CO2" t="inlineStr">
         <is>
           <t>-0.14</t>
         </is>
       </c>
-      <c r="CO2" t="inlineStr">
+      <c r="CP2" t="inlineStr">
         <is>
           <t>145.8</t>
         </is>
       </c>
-      <c r="CP2" t="inlineStr">
+      <c r="CQ2" t="inlineStr">
         <is>
           <t>145.25</t>
         </is>
       </c>
-      <c r="CQ2" t="inlineStr">
+      <c r="CR2" t="inlineStr">
         <is>
           <t>144.07</t>
         </is>
       </c>
-      <c r="CR2" t="inlineStr">
+      <c r="CS2" t="inlineStr">
         <is>
           <t>139.85</t>
         </is>
       </c>
-      <c r="CS2" t="inlineStr">
+      <c r="CT2" t="inlineStr">
         <is>
           <t>140.05</t>
         </is>
       </c>
-      <c r="CT2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="CU2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CV2" t="inlineStr">
+        <is>
           <t>0.001373626373626591</t>
         </is>
       </c>
-      <c r="CV2" t="inlineStr">
+      <c r="CW2" t="inlineStr">
         <is>
           <t>0.001033769813921559</t>
         </is>
       </c>
-      <c r="CW2" t="inlineStr">
+      <c r="CX2" t="inlineStr">
         <is>
           <t>0.002609603340292255</t>
         </is>
       </c>
-      <c r="CX2" t="inlineStr">
+      <c r="CY2" t="inlineStr">
         <is>
           <t>0.0007871761843423197</t>
         </is>
       </c>
-      <c r="CY2" t="inlineStr">
+      <c r="CZ2" t="inlineStr">
         <is>
           <t>0.0001338986833296918</t>
         </is>
       </c>
-      <c r="CZ2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="DA2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="DB2" t="inlineStr">
+        <is>
           <t>-0.64</t>
         </is>
       </c>
-      <c r="DB2" t="n">
+      <c r="DC2" t="n">
         <v>1.83</v>
       </c>
-      <c r="DC2" t="n">
+      <c r="DD2" t="n">
         <v>1.84</v>
       </c>
-      <c r="DD2" t="inlineStr">
+      <c r="DE2" t="inlineStr">
         <is>
           <t>1.9</t>
         </is>
       </c>
-      <c r="DE2" t="inlineStr">
+      <c r="DF2" t="inlineStr">
         <is>
           <t>-2.70</t>
         </is>
       </c>
-      <c r="DF2" t="inlineStr">
+      <c r="DG2" t="inlineStr">
         <is>
           <t>2026/08/21</t>
         </is>
       </c>
-      <c r="DG2" t="inlineStr">
+      <c r="DH2" t="inlineStr">
         <is>
           <t>2510241792.666667</t>
         </is>
       </c>
-      <c r="DH2" t="inlineStr">
+      <c r="DI2" t="inlineStr">
         <is>
           <t>1338632400.0</t>
         </is>
       </c>
-      <c r="DI2" t="n">
+      <c r="DJ2" t="n">
         <v>1216911023</v>
       </c>
-      <c r="DJ2" t="inlineStr">
+      <c r="DK2" t="inlineStr">
         <is>
           <t>1265991067.8</t>
         </is>
       </c>
-      <c r="DK2" t="inlineStr">
+      <c r="DL2" t="inlineStr">
         <is>
           <t>1538893271.133333</t>
         </is>
       </c>
-      <c r="DL2" t="n">
+      <c r="DM2" t="n">
         <v>1564334397.6</v>
       </c>
-      <c r="DM2" t="inlineStr">
+      <c r="DN2" t="inlineStr">
         <is>
           <t>1955293045.375</t>
         </is>
       </c>
-      <c r="DN2" t="inlineStr">
+      <c r="DO2" t="inlineStr">
         <is>
           <t>-44569788.20471825</t>
         </is>
       </c>
-      <c r="DO2" t="inlineStr">
+      <c r="DP2" t="inlineStr">
         <is>
           <t>-93929201.4258542</t>
         </is>
       </c>
-      <c r="DP2" t="inlineStr">
+      <c r="DQ2" t="inlineStr">
         <is>
           <t>1338632400.0</t>
         </is>
       </c>
-      <c r="DQ2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="DR2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="DS2" t="inlineStr">
+        <is>
           <t>143.5</t>
         </is>
       </c>
-      <c r="DS2" t="inlineStr">
+      <c r="DT2" t="inlineStr">
         <is>
           <t>2026/09/15</t>
         </is>
       </c>
-      <c r="DT2" t="inlineStr">
+      <c r="DU2" t="inlineStr">
         <is>
           <t>2.09</t>
         </is>
       </c>
-      <c r="DU2" t="inlineStr">
+      <c r="DV2" t="inlineStr">
         <is>
           <t>中華電</t>
         </is>
       </c>
-      <c r="DV2" t="inlineStr">
+      <c r="DW2" t="inlineStr">
         <is>
           <t>中華電</t>
         </is>
       </c>
-      <c r="DW2" t="inlineStr">
+      <c r="DX2" t="inlineStr">
         <is>
           <t>通信網路業</t>
         </is>
       </c>
-      <c r="DX2" t="inlineStr">
+      <c r="DY2" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="DY2" t="inlineStr">
+      <c r="DZ2" t="inlineStr">
         <is>
           <t>0.01</t>
         </is>
       </c>
-      <c r="DZ2" t="inlineStr">
+      <c r="EA2" t="inlineStr">
         <is>
           <t>-1.398042523039787</t>
         </is>
       </c>
-      <c r="EA2" t="inlineStr">
+      <c r="EB2" t="inlineStr">
         <is>
           <t>7.608984617555596</t>
         </is>
       </c>
-      <c r="EB2" t="inlineStr">
+      <c r="EC2" t="inlineStr">
         <is>
           <t>7.52024426560034</t>
         </is>
       </c>
-      <c r="EC2" t="inlineStr">
+      <c r="ED2" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
-      <c r="ED2" t="inlineStr">
+      <c r="EE2" t="inlineStr">
         <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="EE2" t="inlineStr">
+      <c r="EF2" t="inlineStr">
         <is>
           <t>3.10</t>
         </is>
       </c>
-      <c r="EF2" t="inlineStr">
+      <c r="EG2" t="inlineStr">
         <is>
           <t>3.55</t>
         </is>
       </c>
-      <c r="EG2" t="inlineStr">
+      <c r="EH2" t="inlineStr">
         <is>
           <t>7.91</t>
         </is>
       </c>
-      <c r="EH2" t="inlineStr">
+      <c r="EI2" t="inlineStr">
         <is>
           <t>28.78</t>
         </is>
       </c>
-      <c r="EI2" t="inlineStr">
+      <c r="EJ2" t="inlineStr">
         <is>
           <t>37.54%</t>
         </is>
       </c>
-      <c r="EJ2" t="inlineStr">
+      <c r="EK2" t="inlineStr">
         <is>
           <t>21.61%</t>
         </is>
       </c>
-      <c r="EK2" t="inlineStr">
+      <c r="EL2" t="inlineStr">
         <is>
           <t>84.4</t>
         </is>
       </c>
-      <c r="EL2" t="inlineStr">
+      <c r="EM2" t="inlineStr">
         <is>
           <t>1136466</t>
         </is>
       </c>
-      <c r="EM2" t="inlineStr">
+      <c r="EN2" t="inlineStr">
         <is>
           <t>個人家庭60.70%、企業客戶32.70%、國際客戶4.00%、其他2.60% (2025年)</t>
         </is>
       </c>
-      <c r="EN2" t="inlineStr">
+      <c r="EO2" t="inlineStr">
         <is>
           <t>中華電-通信網路業-上市</t>
         </is>
       </c>
-      <c r="EO2" t="inlineStr">
+      <c r="EP2" t="inlineStr">
         <is>
           <t>通信網路業右上上市</t>
         </is>
       </c>
-      <c r="EP2" t="inlineStr">
+      <c r="EQ2" t="inlineStr">
         <is>
           <t>145.0</t>
         </is>
       </c>
-      <c r="EQ2" t="inlineStr">
+      <c r="ER2" t="inlineStr">
         <is>
           <t>146.5</t>
         </is>
       </c>
-      <c r="ER2" t="inlineStr">
+      <c r="ES2" t="inlineStr">
         <is>
           <t>145.0</t>
         </is>
       </c>
-      <c r="ES2" t="inlineStr">
+      <c r="ET2" t="inlineStr">
         <is>
           <t>146.5</t>
         </is>
       </c>
-      <c r="ET2" t="inlineStr">
+      <c r="EU2" t="inlineStr">
         <is>
           <t>129.5</t>
         </is>
       </c>
-      <c r="EU2" t="inlineStr">
+      <c r="EV2" t="inlineStr">
         <is>
           <t>47.26</t>
         </is>
       </c>
-      <c r="EV2" t="inlineStr">
+      <c r="EW2" t="inlineStr">
         <is>
           <t>** 通信網路 - 電信服務業** 智慧電網 - 能源管理服務、系統整合服務</t>
         </is>
       </c>
-      <c r="EW2" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
       <c r="EX2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="EY2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="EZ2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="EZ2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="FA2" t="inlineStr">
         <is>
           <t>0</t>
@@ -2212,29 +2217,29 @@
       </c>
       <c r="FD2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="FE2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="FE2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="FF2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FG2" t="inlineStr">
         <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="FH2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="FH2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="FI2" t="inlineStr">
         <is>
           <t>0</t>
@@ -2247,170 +2252,175 @@
       </c>
       <c r="FK2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="FL2" t="inlineStr">
+        <is>
           <t>115.2Q</t>
         </is>
       </c>
-      <c r="FL2" t="inlineStr">
+      <c r="FM2" t="inlineStr">
         <is>
           <t>61363.0</t>
         </is>
       </c>
-      <c r="FM2" t="inlineStr">
+      <c r="FN2" t="inlineStr">
         <is>
           <t>38328.0</t>
         </is>
       </c>
-      <c r="FN2" t="inlineStr">
+      <c r="FO2" t="inlineStr">
         <is>
           <t>23035.0</t>
         </is>
       </c>
-      <c r="FO2" t="inlineStr">
+      <c r="FP2" t="inlineStr">
         <is>
           <t>37.54</t>
         </is>
       </c>
-      <c r="FP2" t="inlineStr">
+      <c r="FQ2" t="inlineStr">
         <is>
           <t>13261.0</t>
         </is>
       </c>
-      <c r="FQ2" t="inlineStr">
+      <c r="FR2" t="inlineStr">
         <is>
           <t>21.61%</t>
         </is>
       </c>
-      <c r="FR2" t="inlineStr">
+      <c r="FS2" t="inlineStr">
         <is>
           <t>691.0</t>
         </is>
       </c>
-      <c r="FS2" t="inlineStr">
+      <c r="FT2" t="inlineStr">
         <is>
           <t>13953.0</t>
         </is>
       </c>
-      <c r="FT2" t="inlineStr">
+      <c r="FU2" t="inlineStr">
         <is>
           <t>10641.0</t>
         </is>
       </c>
-      <c r="FU2" t="inlineStr">
+      <c r="FV2" t="inlineStr">
         <is>
           <t>1.37</t>
         </is>
       </c>
-      <c r="FV2" t="inlineStr">
+      <c r="FW2" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="FW2" t="inlineStr">
+      <c r="FX2" t="inlineStr">
         <is>
           <t>EPS成長 / 毛利率衰退</t>
         </is>
       </c>
-      <c r="FX2" t="inlineStr">
+      <c r="FY2" t="inlineStr">
         <is>
           <t>1.2475</t>
         </is>
       </c>
-      <c r="FY2" t="inlineStr">
+      <c r="FZ2" t="inlineStr">
         <is>
           <t>36.6475</t>
         </is>
       </c>
-      <c r="FZ2" t="inlineStr">
+      <c r="GA2" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="GA2" t="inlineStr">
+      <c r="GB2" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="GB2" t="inlineStr">
+      <c r="GC2" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="GC2" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="GD2" t="inlineStr">
         <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="GE2" t="inlineStr">
+        <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="GE2" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="GF2" t="inlineStr">
         <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="GG2" t="inlineStr">
+        <is>
           <t>0.07000000000000006</t>
         </is>
       </c>
-      <c r="GG2" t="inlineStr">
+      <c r="GH2" t="inlineStr">
         <is>
           <t>0.05384615384615388</t>
         </is>
       </c>
-      <c r="GH2" t="inlineStr">
+      <c r="GI2" t="inlineStr">
         <is>
           <t>-0.3800000000000026</t>
         </is>
       </c>
-      <c r="GI2" t="inlineStr">
+      <c r="GJ2" t="inlineStr">
         <is>
           <t>-0.01002109704641352</t>
         </is>
       </c>
-      <c r="GJ2" t="inlineStr">
+      <c r="GK2" t="inlineStr">
         <is>
           <t>0.06000000000000005</t>
         </is>
       </c>
-      <c r="GK2" t="inlineStr">
+      <c r="GL2" t="inlineStr">
         <is>
           <t>0.04580152671755733</t>
         </is>
       </c>
-      <c r="GL2" t="inlineStr">
+      <c r="GM2" t="inlineStr">
         <is>
           <t>-0.8400000000000034</t>
         </is>
       </c>
-      <c r="GM2" t="inlineStr">
+      <c r="GN2" t="inlineStr">
         <is>
           <t>-0.02188639916623247</t>
         </is>
       </c>
-      <c r="GN2" t="inlineStr">
+      <c r="GO2" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="GO2" t="inlineStr">
+      <c r="GP2" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="GP2" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="GQ2" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
       <c r="GR2" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="GS2" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
@@ -2809,378 +2819,378 @@
       </c>
       <c r="CA3" t="inlineStr">
         <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="CB3" t="inlineStr">
+        <is>
           <t>2026-09-18 00:00:00</t>
         </is>
       </c>
-      <c r="CB3" t="inlineStr">
+      <c r="CC3" t="inlineStr">
         <is>
           <t>2026-10-07</t>
         </is>
       </c>
-      <c r="CC3" t="inlineStr">
+      <c r="CD3" t="inlineStr">
         <is>
           <t>11.82</t>
         </is>
       </c>
-      <c r="CD3" t="inlineStr">
+      <c r="CE3" t="inlineStr">
         <is>
           <t>1.04</t>
         </is>
       </c>
-      <c r="CE3" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="CF3" t="inlineStr"/>
-      <c r="CG3" t="inlineStr">
+      <c r="CF3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="CG3" t="inlineStr"/>
+      <c r="CH3" t="inlineStr">
         <is>
           <t>67</t>
         </is>
       </c>
-      <c r="CH3" t="inlineStr">
+      <c r="CI3" t="inlineStr">
         <is>
           <t>9157</t>
         </is>
       </c>
-      <c r="CI3" t="inlineStr">
+      <c r="CJ3" t="inlineStr">
         <is>
           <t>80.0</t>
         </is>
       </c>
-      <c r="CJ3" t="inlineStr">
+      <c r="CK3" t="inlineStr">
         <is>
           <t>80.0</t>
         </is>
       </c>
-      <c r="CK3" t="n">
+      <c r="CL3" t="n">
         <v>-0.07000000000000001</v>
       </c>
-      <c r="CL3" t="n">
+      <c r="CM3" t="n">
         <v>1.32</v>
       </c>
-      <c r="CM3" t="inlineStr">
+      <c r="CN3" t="inlineStr">
         <is>
           <t>2.83</t>
         </is>
       </c>
-      <c r="CN3" t="inlineStr">
+      <c r="CO3" t="inlineStr">
         <is>
           <t>-0.21</t>
         </is>
       </c>
-      <c r="CO3" t="inlineStr">
+      <c r="CP3" t="inlineStr">
         <is>
           <t>145.6</t>
         </is>
       </c>
-      <c r="CP3" t="inlineStr">
+      <c r="CQ3" t="inlineStr">
         <is>
           <t>145.1</t>
         </is>
       </c>
-      <c r="CQ3" t="inlineStr">
+      <c r="CR3" t="inlineStr">
         <is>
           <t>143.7</t>
         </is>
       </c>
-      <c r="CR3" t="inlineStr">
+      <c r="CS3" t="inlineStr">
         <is>
           <t>139.74</t>
         </is>
       </c>
-      <c r="CS3" t="inlineStr">
+      <c r="CT3" t="inlineStr">
         <is>
           <t>140.03</t>
         </is>
       </c>
-      <c r="CT3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="CU3" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CV3" t="inlineStr">
+        <is>
           <t>0.002754820936639257</t>
         </is>
       </c>
-      <c r="CV3" t="inlineStr">
+      <c r="CW3" t="inlineStr">
         <is>
           <t>0.0006896551724138167</t>
         </is>
       </c>
-      <c r="CW3" t="inlineStr">
+      <c r="CX3" t="inlineStr">
         <is>
           <t>0.002616431187859813</t>
         </is>
       </c>
-      <c r="CX3" t="inlineStr">
+      <c r="CY3" t="inlineStr">
         <is>
           <t>0.000716127184188009</t>
         </is>
       </c>
-      <c r="CY3" t="inlineStr">
+      <c r="CZ3" t="inlineStr">
         <is>
           <t>4.463488662742598e-05</t>
         </is>
       </c>
-      <c r="CZ3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="DA3" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="DB3" t="inlineStr">
+        <is>
           <t>-1.50</t>
         </is>
       </c>
-      <c r="DB3" t="n">
+      <c r="DC3" t="n">
         <v>1.82</v>
       </c>
-      <c r="DC3" t="n">
+      <c r="DD3" t="n">
         <v>1.85</v>
       </c>
-      <c r="DD3" t="inlineStr">
+      <c r="DE3" t="inlineStr">
         <is>
           <t>1.9</t>
         </is>
       </c>
-      <c r="DE3" t="inlineStr">
+      <c r="DF3" t="inlineStr">
         <is>
           <t>-2.55</t>
         </is>
       </c>
-      <c r="DF3" t="inlineStr">
+      <c r="DG3" t="inlineStr">
         <is>
           <t>2026/08/21</t>
         </is>
       </c>
-      <c r="DG3" t="inlineStr">
+      <c r="DH3" t="inlineStr">
         <is>
           <t>2510241792.666667</t>
         </is>
       </c>
-      <c r="DH3" t="inlineStr">
+      <c r="DI3" t="inlineStr">
         <is>
           <t>1027931012.0</t>
         </is>
       </c>
-      <c r="DI3" t="n">
+      <c r="DJ3" t="n">
         <v>1198822702.4</v>
       </c>
-      <c r="DJ3" t="inlineStr">
+      <c r="DK3" t="inlineStr">
         <is>
           <t>1211104395.0</t>
         </is>
       </c>
-      <c r="DK3" t="inlineStr">
+      <c r="DL3" t="inlineStr">
         <is>
           <t>1514483902.3</t>
         </is>
       </c>
-      <c r="DL3" t="n">
+      <c r="DM3" t="n">
         <v>1587854042.56</v>
       </c>
-      <c r="DM3" t="inlineStr">
+      <c r="DN3" t="inlineStr">
         <is>
           <t>1954971026.825</t>
         </is>
       </c>
-      <c r="DN3" t="inlineStr">
+      <c r="DO3" t="inlineStr">
         <is>
           <t>-35595349.43723899</t>
         </is>
       </c>
-      <c r="DO3" t="inlineStr">
+      <c r="DP3" t="inlineStr">
         <is>
           <t>-110750317.6101668</t>
         </is>
       </c>
-      <c r="DP3" t="inlineStr">
+      <c r="DQ3" t="inlineStr">
         <is>
           <t>1027931012.0</t>
         </is>
       </c>
-      <c r="DQ3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="DR3" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="DS3" t="inlineStr">
+        <is>
           <t>143.5</t>
         </is>
       </c>
-      <c r="DS3" t="inlineStr">
+      <c r="DT3" t="inlineStr">
         <is>
           <t>2026/09/15</t>
         </is>
       </c>
-      <c r="DT3" t="inlineStr">
+      <c r="DU3" t="inlineStr">
         <is>
           <t>1.39</t>
         </is>
       </c>
-      <c r="DU3" t="inlineStr">
+      <c r="DV3" t="inlineStr">
         <is>
           <t>中華電</t>
         </is>
       </c>
-      <c r="DV3" t="inlineStr">
+      <c r="DW3" t="inlineStr">
         <is>
           <t>中華電</t>
         </is>
       </c>
-      <c r="DW3" t="inlineStr">
+      <c r="DX3" t="inlineStr">
         <is>
           <t>通信網路業</t>
         </is>
       </c>
-      <c r="DX3" t="inlineStr">
+      <c r="DY3" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="DY3" t="inlineStr">
+      <c r="DZ3" t="inlineStr">
         <is>
           <t>0.01</t>
         </is>
       </c>
-      <c r="DZ3" t="inlineStr">
+      <c r="EA3" t="inlineStr">
         <is>
           <t>-1.398042523039787</t>
         </is>
       </c>
-      <c r="EA3" t="inlineStr">
+      <c r="EB3" t="inlineStr">
         <is>
           <t>7.608984617555596</t>
         </is>
       </c>
-      <c r="EB3" t="inlineStr">
+      <c r="EC3" t="inlineStr">
         <is>
           <t>7.52024426560034</t>
         </is>
       </c>
-      <c r="EC3" t="inlineStr">
+      <c r="ED3" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
-      <c r="ED3" t="inlineStr">
+      <c r="EE3" t="inlineStr">
         <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="EE3" t="inlineStr">
+      <c r="EF3" t="inlineStr">
         <is>
           <t>3.08</t>
         </is>
       </c>
-      <c r="EF3" t="inlineStr">
+      <c r="EG3" t="inlineStr">
         <is>
           <t>3.55</t>
         </is>
       </c>
-      <c r="EG3" t="inlineStr">
+      <c r="EH3" t="inlineStr">
         <is>
           <t>7.91</t>
         </is>
       </c>
-      <c r="EH3" t="inlineStr">
+      <c r="EI3" t="inlineStr">
         <is>
           <t>28.78</t>
         </is>
       </c>
-      <c r="EI3" t="inlineStr">
+      <c r="EJ3" t="inlineStr">
         <is>
           <t>37.54%</t>
         </is>
       </c>
-      <c r="EJ3" t="inlineStr">
+      <c r="EK3" t="inlineStr">
         <is>
           <t>21.61%</t>
         </is>
       </c>
-      <c r="EK3" t="inlineStr">
+      <c r="EL3" t="inlineStr">
         <is>
           <t>84.4</t>
         </is>
       </c>
-      <c r="EL3" t="inlineStr">
+      <c r="EM3" t="inlineStr">
         <is>
           <t>1136466</t>
         </is>
       </c>
-      <c r="EM3" t="inlineStr">
+      <c r="EN3" t="inlineStr">
         <is>
           <t>個人家庭60.70%、企業客戶32.70%、國際客戶4.00%、其他2.60% (2025年)</t>
         </is>
       </c>
-      <c r="EN3" t="inlineStr">
+      <c r="EO3" t="inlineStr">
         <is>
           <t>中華電-通信網路業-上市</t>
         </is>
       </c>
-      <c r="EO3" t="inlineStr">
+      <c r="EP3" t="inlineStr">
         <is>
           <t>通信網路業右上上市</t>
         </is>
       </c>
-      <c r="EP3" t="inlineStr">
+      <c r="EQ3" t="inlineStr">
         <is>
           <t>145.5</t>
         </is>
       </c>
-      <c r="EQ3" t="inlineStr">
+      <c r="ER3" t="inlineStr">
         <is>
           <t>145.5</t>
         </is>
       </c>
-      <c r="ER3" t="inlineStr">
+      <c r="ES3" t="inlineStr">
         <is>
           <t>144.0</t>
         </is>
       </c>
-      <c r="ES3" t="inlineStr">
+      <c r="ET3" t="inlineStr">
         <is>
           <t>145.5</t>
         </is>
       </c>
-      <c r="ET3" t="inlineStr">
+      <c r="EU3" t="inlineStr">
         <is>
           <t>129.5</t>
         </is>
       </c>
-      <c r="EU3" t="inlineStr">
+      <c r="EV3" t="inlineStr">
         <is>
           <t>47.26</t>
         </is>
       </c>
-      <c r="EV3" t="inlineStr">
+      <c r="EW3" t="inlineStr">
         <is>
           <t>** 通信網路 - 電信服務業** 智慧電網 - 能源管理服務、系統整合服務</t>
         </is>
       </c>
-      <c r="EW3" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
       <c r="EX3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="EY3" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="EZ3" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="EZ3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="FA3" t="inlineStr">
         <is>
           <t>0</t>
@@ -3198,29 +3208,29 @@
       </c>
       <c r="FD3" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="FE3" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="FE3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="FF3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FG3" t="inlineStr">
         <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="FH3" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="FH3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="FI3" t="inlineStr">
         <is>
           <t>0</t>
@@ -3233,170 +3243,175 @@
       </c>
       <c r="FK3" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="FL3" t="inlineStr">
+        <is>
           <t>115.2Q</t>
         </is>
       </c>
-      <c r="FL3" t="inlineStr">
+      <c r="FM3" t="inlineStr">
         <is>
           <t>61363.0</t>
         </is>
       </c>
-      <c r="FM3" t="inlineStr">
+      <c r="FN3" t="inlineStr">
         <is>
           <t>38328.0</t>
         </is>
       </c>
-      <c r="FN3" t="inlineStr">
+      <c r="FO3" t="inlineStr">
         <is>
           <t>23035.0</t>
         </is>
       </c>
-      <c r="FO3" t="inlineStr">
+      <c r="FP3" t="inlineStr">
         <is>
           <t>37.54</t>
         </is>
       </c>
-      <c r="FP3" t="inlineStr">
+      <c r="FQ3" t="inlineStr">
         <is>
           <t>13261.0</t>
         </is>
       </c>
-      <c r="FQ3" t="inlineStr">
+      <c r="FR3" t="inlineStr">
         <is>
           <t>21.61%</t>
         </is>
       </c>
-      <c r="FR3" t="inlineStr">
+      <c r="FS3" t="inlineStr">
         <is>
           <t>691.0</t>
         </is>
       </c>
-      <c r="FS3" t="inlineStr">
+      <c r="FT3" t="inlineStr">
         <is>
           <t>13953.0</t>
         </is>
       </c>
-      <c r="FT3" t="inlineStr">
+      <c r="FU3" t="inlineStr">
         <is>
           <t>10641.0</t>
         </is>
       </c>
-      <c r="FU3" t="inlineStr">
+      <c r="FV3" t="inlineStr">
         <is>
           <t>1.37</t>
         </is>
       </c>
-      <c r="FV3" t="inlineStr">
+      <c r="FW3" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="FW3" t="inlineStr">
+      <c r="FX3" t="inlineStr">
         <is>
           <t>EPS成長 / 毛利率衰退</t>
         </is>
       </c>
-      <c r="FX3" t="inlineStr">
+      <c r="FY3" t="inlineStr">
         <is>
           <t>1.2475</t>
         </is>
       </c>
-      <c r="FY3" t="inlineStr">
+      <c r="FZ3" t="inlineStr">
         <is>
           <t>36.6475</t>
         </is>
       </c>
-      <c r="FZ3" t="inlineStr">
+      <c r="GA3" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="GA3" t="inlineStr">
+      <c r="GB3" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="GB3" t="inlineStr">
+      <c r="GC3" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="GC3" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="GD3" t="inlineStr">
         <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="GE3" t="inlineStr">
+        <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="GE3" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="GF3" t="inlineStr">
         <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="GG3" t="inlineStr">
+        <is>
           <t>0.07000000000000006</t>
         </is>
       </c>
-      <c r="GG3" t="inlineStr">
+      <c r="GH3" t="inlineStr">
         <is>
           <t>0.05384615384615388</t>
         </is>
       </c>
-      <c r="GH3" t="inlineStr">
+      <c r="GI3" t="inlineStr">
         <is>
           <t>-0.3800000000000026</t>
         </is>
       </c>
-      <c r="GI3" t="inlineStr">
+      <c r="GJ3" t="inlineStr">
         <is>
           <t>-0.01002109704641352</t>
         </is>
       </c>
-      <c r="GJ3" t="inlineStr">
+      <c r="GK3" t="inlineStr">
         <is>
           <t>0.06000000000000005</t>
         </is>
       </c>
-      <c r="GK3" t="inlineStr">
+      <c r="GL3" t="inlineStr">
         <is>
           <t>0.04580152671755733</t>
         </is>
       </c>
-      <c r="GL3" t="inlineStr">
+      <c r="GM3" t="inlineStr">
         <is>
           <t>-0.8400000000000034</t>
         </is>
       </c>
-      <c r="GM3" t="inlineStr">
+      <c r="GN3" t="inlineStr">
         <is>
           <t>-0.02188639916623247</t>
         </is>
       </c>
-      <c r="GN3" t="inlineStr">
+      <c r="GO3" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="GO3" t="inlineStr">
+      <c r="GP3" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="GP3" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="GQ3" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
       <c r="GR3" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="GS3" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
@@ -3795,378 +3810,378 @@
       </c>
       <c r="CA4" t="inlineStr">
         <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="CB4" t="inlineStr">
+        <is>
           <t>2026-09-18 00:00:00</t>
         </is>
       </c>
-      <c r="CB4" t="inlineStr">
+      <c r="CC4" t="inlineStr">
         <is>
           <t>2026-10-06</t>
         </is>
       </c>
-      <c r="CC4" t="inlineStr">
+      <c r="CD4" t="inlineStr">
         <is>
           <t>11.77</t>
         </is>
       </c>
-      <c r="CD4" t="inlineStr">
+      <c r="CE4" t="inlineStr">
         <is>
           <t>1.04</t>
         </is>
       </c>
-      <c r="CE4" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="CF4" t="inlineStr"/>
-      <c r="CG4" t="inlineStr">
+      <c r="CF4" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="CG4" t="inlineStr"/>
+      <c r="CH4" t="inlineStr">
         <is>
           <t>67</t>
         </is>
       </c>
-      <c r="CH4" t="inlineStr">
+      <c r="CI4" t="inlineStr">
         <is>
           <t>9157</t>
         </is>
       </c>
-      <c r="CI4" t="inlineStr">
+      <c r="CJ4" t="inlineStr">
         <is>
           <t>80.0</t>
         </is>
       </c>
-      <c r="CJ4" t="inlineStr">
+      <c r="CK4" t="inlineStr">
         <is>
           <t>86.67</t>
         </is>
       </c>
-      <c r="CK4" t="n">
+      <c r="CL4" t="n">
         <v>0.21</v>
       </c>
-      <c r="CL4" t="n">
+      <c r="CM4" t="n">
         <v>1.31</v>
       </c>
-      <c r="CM4" t="inlineStr">
+      <c r="CN4" t="inlineStr">
         <is>
           <t>2.64</t>
         </is>
       </c>
-      <c r="CN4" t="inlineStr">
+      <c r="CO4" t="inlineStr">
         <is>
           <t>-0.27</t>
         </is>
       </c>
-      <c r="CO4" t="inlineStr">
+      <c r="CP4" t="inlineStr">
         <is>
           <t>145.2</t>
         </is>
       </c>
-      <c r="CP4" t="inlineStr">
+      <c r="CQ4" t="inlineStr">
         <is>
           <t>145.0</t>
         </is>
       </c>
-      <c r="CQ4" t="inlineStr">
+      <c r="CR4" t="inlineStr">
         <is>
           <t>143.32</t>
         </is>
       </c>
-      <c r="CR4" t="inlineStr">
+      <c r="CS4" t="inlineStr">
         <is>
           <t>139.64</t>
         </is>
       </c>
-      <c r="CS4" t="inlineStr">
+      <c r="CT4" t="inlineStr">
         <is>
           <t>140.02</t>
         </is>
       </c>
-      <c r="CT4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="CU4" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CV4" t="inlineStr">
+        <is>
           <t>0.00207039337474102</t>
         </is>
       </c>
-      <c r="CV4" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="CW4" t="inlineStr">
         <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="CX4" t="inlineStr">
+        <is>
           <t>0.002798670631450006</t>
         </is>
       </c>
-      <c r="CX4" t="inlineStr">
+      <c r="CY4" t="inlineStr">
         <is>
           <t>0.0009318328435237166</t>
         </is>
       </c>
-      <c r="CY4" t="inlineStr">
+      <c r="CZ4" t="inlineStr">
         <is>
           <t>0.0001339225927414756</t>
         </is>
       </c>
-      <c r="CZ4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="DA4" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="DB4" t="inlineStr">
+        <is>
           <t>1.30</t>
         </is>
       </c>
-      <c r="DB4" t="n">
+      <c r="DC4" t="n">
         <v>1.88</v>
       </c>
-      <c r="DC4" t="n">
+      <c r="DD4" t="n">
         <v>1.85</v>
       </c>
-      <c r="DD4" t="inlineStr">
+      <c r="DE4" t="inlineStr">
         <is>
           <t>1.9</t>
         </is>
       </c>
-      <c r="DE4" t="inlineStr">
+      <c r="DF4" t="inlineStr">
         <is>
           <t>-2.18</t>
         </is>
       </c>
-      <c r="DF4" t="inlineStr">
+      <c r="DG4" t="inlineStr">
         <is>
           <t>2026/08/21</t>
         </is>
       </c>
-      <c r="DG4" t="inlineStr">
+      <c r="DH4" t="inlineStr">
         <is>
           <t>2510241792.666667</t>
         </is>
       </c>
-      <c r="DH4" t="inlineStr">
+      <c r="DI4" t="inlineStr">
         <is>
           <t>1019972816.0</t>
         </is>
       </c>
-      <c r="DI4" t="n">
+      <c r="DJ4" t="n">
         <v>1298042299.8</v>
       </c>
-      <c r="DJ4" t="inlineStr">
+      <c r="DK4" t="inlineStr">
         <is>
           <t>1238358968.0</t>
         </is>
       </c>
-      <c r="DK4" t="inlineStr">
+      <c r="DL4" t="inlineStr">
         <is>
           <t>1512402699.433333</t>
         </is>
       </c>
-      <c r="DL4" t="n">
+      <c r="DM4" t="n">
         <v>1630284122.58</v>
       </c>
-      <c r="DM4" t="inlineStr">
+      <c r="DN4" t="inlineStr">
         <is>
           <t>1973713221.6375</t>
         </is>
       </c>
-      <c r="DN4" t="inlineStr">
+      <c r="DO4" t="inlineStr">
         <is>
           <t>-21930809.76943394</t>
         </is>
       </c>
-      <c r="DO4" t="inlineStr">
+      <c r="DP4" t="inlineStr">
         <is>
           <t>-97535680.67310739</t>
         </is>
       </c>
-      <c r="DP4" t="inlineStr">
+      <c r="DQ4" t="inlineStr">
         <is>
           <t>1019972816.0</t>
         </is>
       </c>
-      <c r="DQ4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="DR4" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="DS4" t="inlineStr">
+        <is>
           <t>143.5</t>
         </is>
       </c>
-      <c r="DS4" t="inlineStr">
+      <c r="DT4" t="inlineStr">
         <is>
           <t>2026/09/15</t>
         </is>
       </c>
-      <c r="DT4" t="inlineStr">
+      <c r="DU4" t="inlineStr">
         <is>
           <t>1.39</t>
         </is>
       </c>
-      <c r="DU4" t="inlineStr">
+      <c r="DV4" t="inlineStr">
         <is>
           <t>中華電</t>
         </is>
       </c>
-      <c r="DV4" t="inlineStr">
+      <c r="DW4" t="inlineStr">
         <is>
           <t>中華電</t>
         </is>
       </c>
-      <c r="DW4" t="inlineStr">
+      <c r="DX4" t="inlineStr">
         <is>
           <t>通信網路業</t>
         </is>
       </c>
-      <c r="DX4" t="inlineStr">
+      <c r="DY4" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="DY4" t="inlineStr">
+      <c r="DZ4" t="inlineStr">
         <is>
           <t>0.01</t>
         </is>
       </c>
-      <c r="DZ4" t="inlineStr">
+      <c r="EA4" t="inlineStr">
         <is>
           <t>-1.398042523039787</t>
         </is>
       </c>
-      <c r="EA4" t="inlineStr">
+      <c r="EB4" t="inlineStr">
         <is>
           <t>7.608984617555596</t>
         </is>
       </c>
-      <c r="EB4" t="inlineStr">
+      <c r="EC4" t="inlineStr">
         <is>
           <t>7.52024426560034</t>
         </is>
       </c>
-      <c r="EC4" t="inlineStr">
+      <c r="ED4" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
-      <c r="ED4" t="inlineStr">
+      <c r="EE4" t="inlineStr">
         <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="EE4" t="inlineStr">
+      <c r="EF4" t="inlineStr">
         <is>
           <t>3.08</t>
         </is>
       </c>
-      <c r="EF4" t="inlineStr">
+      <c r="EG4" t="inlineStr">
         <is>
           <t>3.55</t>
         </is>
       </c>
-      <c r="EG4" t="inlineStr">
+      <c r="EH4" t="inlineStr">
         <is>
           <t>7.91</t>
         </is>
       </c>
-      <c r="EH4" t="inlineStr">
+      <c r="EI4" t="inlineStr">
         <is>
           <t>28.78</t>
         </is>
       </c>
-      <c r="EI4" t="inlineStr">
+      <c r="EJ4" t="inlineStr">
         <is>
           <t>37.54%</t>
         </is>
       </c>
-      <c r="EJ4" t="inlineStr">
+      <c r="EK4" t="inlineStr">
         <is>
           <t>21.61%</t>
         </is>
       </c>
-      <c r="EK4" t="inlineStr">
+      <c r="EL4" t="inlineStr">
         <is>
           <t>84.4</t>
         </is>
       </c>
-      <c r="EL4" t="inlineStr">
+      <c r="EM4" t="inlineStr">
         <is>
           <t>1136466</t>
         </is>
       </c>
-      <c r="EM4" t="inlineStr">
+      <c r="EN4" t="inlineStr">
         <is>
           <t>個人家庭60.70%、企業客戶32.70%、國際客戶4.00%、其他2.60% (2025年)</t>
         </is>
       </c>
-      <c r="EN4" t="inlineStr">
+      <c r="EO4" t="inlineStr">
         <is>
           <t>中華電-通信網路業-上市</t>
         </is>
       </c>
-      <c r="EO4" t="inlineStr">
+      <c r="EP4" t="inlineStr">
         <is>
           <t>通信網路業右上上市</t>
         </is>
       </c>
-      <c r="EP4" t="inlineStr">
+      <c r="EQ4" t="inlineStr">
         <is>
           <t>145.5</t>
         </is>
       </c>
-      <c r="EQ4" t="inlineStr">
+      <c r="ER4" t="inlineStr">
         <is>
           <t>145.5</t>
         </is>
       </c>
-      <c r="ER4" t="inlineStr">
+      <c r="ES4" t="inlineStr">
         <is>
           <t>144.0</t>
         </is>
       </c>
-      <c r="ES4" t="inlineStr">
+      <c r="ET4" t="inlineStr">
         <is>
           <t>145.5</t>
         </is>
       </c>
-      <c r="ET4" t="inlineStr">
+      <c r="EU4" t="inlineStr">
         <is>
           <t>129.5</t>
         </is>
       </c>
-      <c r="EU4" t="inlineStr">
+      <c r="EV4" t="inlineStr">
         <is>
           <t>47.26</t>
         </is>
       </c>
-      <c r="EV4" t="inlineStr">
+      <c r="EW4" t="inlineStr">
         <is>
           <t>** 通信網路 - 電信服務業** 智慧電網 - 能源管理服務、系統整合服務</t>
         </is>
       </c>
-      <c r="EW4" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
       <c r="EX4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="EY4" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="EZ4" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="EZ4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="FA4" t="inlineStr">
         <is>
           <t>0</t>
@@ -4184,29 +4199,29 @@
       </c>
       <c r="FD4" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="FE4" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="FE4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="FF4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FG4" t="inlineStr">
         <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="FH4" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="FH4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="FI4" t="inlineStr">
         <is>
           <t>0</t>
@@ -4219,170 +4234,175 @@
       </c>
       <c r="FK4" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="FL4" t="inlineStr">
+        <is>
           <t>115.2Q</t>
         </is>
       </c>
-      <c r="FL4" t="inlineStr">
+      <c r="FM4" t="inlineStr">
         <is>
           <t>61363.0</t>
         </is>
       </c>
-      <c r="FM4" t="inlineStr">
+      <c r="FN4" t="inlineStr">
         <is>
           <t>38328.0</t>
         </is>
       </c>
-      <c r="FN4" t="inlineStr">
+      <c r="FO4" t="inlineStr">
         <is>
           <t>23035.0</t>
         </is>
       </c>
-      <c r="FO4" t="inlineStr">
+      <c r="FP4" t="inlineStr">
         <is>
           <t>37.54</t>
         </is>
       </c>
-      <c r="FP4" t="inlineStr">
+      <c r="FQ4" t="inlineStr">
         <is>
           <t>13261.0</t>
         </is>
       </c>
-      <c r="FQ4" t="inlineStr">
+      <c r="FR4" t="inlineStr">
         <is>
           <t>21.61%</t>
         </is>
       </c>
-      <c r="FR4" t="inlineStr">
+      <c r="FS4" t="inlineStr">
         <is>
           <t>691.0</t>
         </is>
       </c>
-      <c r="FS4" t="inlineStr">
+      <c r="FT4" t="inlineStr">
         <is>
           <t>13953.0</t>
         </is>
       </c>
-      <c r="FT4" t="inlineStr">
+      <c r="FU4" t="inlineStr">
         <is>
           <t>10641.0</t>
         </is>
       </c>
-      <c r="FU4" t="inlineStr">
+      <c r="FV4" t="inlineStr">
         <is>
           <t>1.37</t>
         </is>
       </c>
-      <c r="FV4" t="inlineStr">
+      <c r="FW4" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="FW4" t="inlineStr">
+      <c r="FX4" t="inlineStr">
         <is>
           <t>EPS成長 / 毛利率衰退</t>
         </is>
       </c>
-      <c r="FX4" t="inlineStr">
+      <c r="FY4" t="inlineStr">
         <is>
           <t>1.2475</t>
         </is>
       </c>
-      <c r="FY4" t="inlineStr">
+      <c r="FZ4" t="inlineStr">
         <is>
           <t>36.6475</t>
         </is>
       </c>
-      <c r="FZ4" t="inlineStr">
+      <c r="GA4" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="GA4" t="inlineStr">
+      <c r="GB4" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="GB4" t="inlineStr">
+      <c r="GC4" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="GC4" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="GD4" t="inlineStr">
         <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="GE4" t="inlineStr">
+        <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="GE4" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="GF4" t="inlineStr">
         <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="GG4" t="inlineStr">
+        <is>
           <t>0.07000000000000006</t>
         </is>
       </c>
-      <c r="GG4" t="inlineStr">
+      <c r="GH4" t="inlineStr">
         <is>
           <t>0.05384615384615388</t>
         </is>
       </c>
-      <c r="GH4" t="inlineStr">
+      <c r="GI4" t="inlineStr">
         <is>
           <t>-0.3800000000000026</t>
         </is>
       </c>
-      <c r="GI4" t="inlineStr">
+      <c r="GJ4" t="inlineStr">
         <is>
           <t>-0.01002109704641352</t>
         </is>
       </c>
-      <c r="GJ4" t="inlineStr">
+      <c r="GK4" t="inlineStr">
         <is>
           <t>0.06000000000000005</t>
         </is>
       </c>
-      <c r="GK4" t="inlineStr">
+      <c r="GL4" t="inlineStr">
         <is>
           <t>0.04580152671755733</t>
         </is>
       </c>
-      <c r="GL4" t="inlineStr">
+      <c r="GM4" t="inlineStr">
         <is>
           <t>-0.8400000000000034</t>
         </is>
       </c>
-      <c r="GM4" t="inlineStr">
+      <c r="GN4" t="inlineStr">
         <is>
           <t>-0.02188639916623247</t>
         </is>
       </c>
-      <c r="GN4" t="inlineStr">
+      <c r="GO4" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="GO4" t="inlineStr">
+      <c r="GP4" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="GP4" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="GQ4" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
       <c r="GR4" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="GS4" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
@@ -4781,378 +4801,378 @@
       </c>
       <c r="CA5" t="inlineStr">
         <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="CB5" t="inlineStr">
+        <is>
           <t>2026-09-18 00:00:00</t>
         </is>
       </c>
-      <c r="CB5" t="inlineStr">
+      <c r="CC5" t="inlineStr">
         <is>
           <t>2026-10-05</t>
         </is>
       </c>
-      <c r="CC5" t="inlineStr">
+      <c r="CD5" t="inlineStr">
         <is>
           <t>14.21</t>
         </is>
       </c>
-      <c r="CD5" t="inlineStr">
+      <c r="CE5" t="inlineStr">
         <is>
           <t>0.01</t>
         </is>
       </c>
-      <c r="CE5" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="CF5" t="inlineStr"/>
-      <c r="CG5" t="inlineStr">
+      <c r="CF5" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="CG5" t="inlineStr"/>
+      <c r="CH5" t="inlineStr">
         <is>
           <t>67</t>
         </is>
       </c>
-      <c r="CH5" t="inlineStr">
+      <c r="CI5" t="inlineStr">
         <is>
           <t>9157</t>
         </is>
       </c>
-      <c r="CI5" t="inlineStr">
+      <c r="CJ5" t="inlineStr">
         <is>
           <t>80.0</t>
         </is>
       </c>
-      <c r="CJ5" t="inlineStr">
+      <c r="CK5" t="inlineStr">
         <is>
           <t>93.33</t>
         </is>
       </c>
-      <c r="CK5" t="n">
+      <c r="CL5" t="n">
         <v>0.41</v>
       </c>
-      <c r="CL5" t="n">
+      <c r="CM5" t="n">
         <v>1.38</v>
       </c>
-      <c r="CM5" t="inlineStr">
+      <c r="CN5" t="inlineStr">
         <is>
           <t>2.45</t>
         </is>
       </c>
-      <c r="CN5" t="inlineStr">
+      <c r="CO5" t="inlineStr">
         <is>
           <t>-0.35</t>
         </is>
       </c>
-      <c r="CO5" t="inlineStr">
+      <c r="CP5" t="inlineStr">
         <is>
           <t>144.9</t>
         </is>
       </c>
-      <c r="CP5" t="inlineStr">
+      <c r="CQ5" t="inlineStr">
         <is>
           <t>145.0</t>
         </is>
       </c>
-      <c r="CQ5" t="inlineStr">
+      <c r="CR5" t="inlineStr">
         <is>
           <t>142.93</t>
         </is>
       </c>
-      <c r="CR5" t="inlineStr">
+      <c r="CS5" t="inlineStr">
         <is>
           <t>139.51</t>
         </is>
       </c>
-      <c r="CS5" t="inlineStr">
+      <c r="CT5" t="inlineStr">
         <is>
           <t>140.01</t>
         </is>
       </c>
-      <c r="CT5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="CU5" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CV5" t="inlineStr">
+        <is>
           <t>0.0006906077348065587</t>
         </is>
       </c>
-      <c r="CV5" t="inlineStr">
+      <c r="CW5" t="inlineStr">
         <is>
           <t>0.0003449465332874269</t>
         </is>
       </c>
-      <c r="CW5" t="inlineStr">
+      <c r="CX5" t="inlineStr">
         <is>
           <t>0.002630655910206947</t>
         </is>
       </c>
-      <c r="CX5" t="inlineStr">
+      <c r="CY5" t="inlineStr">
         <is>
           <t>0.001076349024110135</t>
         </is>
       </c>
-      <c r="CY5" t="inlineStr">
+      <c r="CZ5" t="inlineStr">
         <is>
           <t>0.0003125837277841992</t>
         </is>
       </c>
-      <c r="CZ5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="DA5" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="DB5" t="inlineStr">
+        <is>
           <t>4.21</t>
         </is>
       </c>
-      <c r="DB5" t="n">
+      <c r="DC5" t="n">
         <v>1.93</v>
       </c>
-      <c r="DC5" t="n">
+      <c r="DD5" t="n">
         <v>1.85</v>
       </c>
-      <c r="DD5" t="inlineStr">
+      <c r="DE5" t="inlineStr">
         <is>
           <t>1.9</t>
         </is>
       </c>
-      <c r="DE5" t="inlineStr">
+      <c r="DF5" t="inlineStr">
         <is>
           <t>-2.50</t>
         </is>
       </c>
-      <c r="DF5" t="inlineStr">
+      <c r="DG5" t="inlineStr">
         <is>
           <t>2026/08/21</t>
         </is>
       </c>
-      <c r="DG5" t="inlineStr">
+      <c r="DH5" t="inlineStr">
         <is>
           <t>2510241792.666667</t>
         </is>
       </c>
-      <c r="DH5" t="inlineStr">
+      <c r="DI5" t="inlineStr">
         <is>
           <t>1239700787.0</t>
         </is>
       </c>
-      <c r="DI5" t="n">
+      <c r="DJ5" t="n">
         <v>1429392742.2</v>
       </c>
-      <c r="DJ5" t="inlineStr">
+      <c r="DK5" t="inlineStr">
         <is>
           <t>1544294297.4</t>
         </is>
       </c>
-      <c r="DK5" t="inlineStr">
+      <c r="DL5" t="inlineStr">
         <is>
           <t>1502594940.533333</t>
         </is>
       </c>
-      <c r="DL5" t="n">
+      <c r="DM5" t="n">
         <v>1654145469.66</v>
       </c>
-      <c r="DM5" t="inlineStr">
+      <c r="DN5" t="inlineStr">
         <is>
           <t>1987286590.375</t>
         </is>
       </c>
-      <c r="DN5" t="inlineStr">
+      <c r="DO5" t="inlineStr">
         <is>
           <t>-8184469.605129678</t>
         </is>
       </c>
-      <c r="DO5" t="inlineStr">
+      <c r="DP5" t="inlineStr">
         <is>
           <t>-74321546.88183999</t>
         </is>
       </c>
-      <c r="DP5" t="inlineStr">
+      <c r="DQ5" t="inlineStr">
         <is>
           <t>1239700787.0</t>
         </is>
       </c>
-      <c r="DQ5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="DR5" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="DS5" t="inlineStr">
+        <is>
           <t>143.5</t>
         </is>
       </c>
-      <c r="DS5" t="inlineStr">
+      <c r="DT5" t="inlineStr">
         <is>
           <t>2026/09/15</t>
         </is>
       </c>
-      <c r="DT5" t="inlineStr">
+      <c r="DU5" t="inlineStr">
         <is>
           <t>1.39</t>
         </is>
       </c>
-      <c r="DU5" t="inlineStr">
+      <c r="DV5" t="inlineStr">
         <is>
           <t>中華電</t>
         </is>
       </c>
-      <c r="DV5" t="inlineStr">
+      <c r="DW5" t="inlineStr">
         <is>
           <t>中華電</t>
         </is>
       </c>
-      <c r="DW5" t="inlineStr">
+      <c r="DX5" t="inlineStr">
         <is>
           <t>通信網路業</t>
         </is>
       </c>
-      <c r="DX5" t="inlineStr">
+      <c r="DY5" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="DY5" t="inlineStr">
+      <c r="DZ5" t="inlineStr">
         <is>
           <t>0.01</t>
         </is>
       </c>
-      <c r="DZ5" t="inlineStr">
+      <c r="EA5" t="inlineStr">
         <is>
           <t>-1.398042523039787</t>
         </is>
       </c>
-      <c r="EA5" t="inlineStr">
+      <c r="EB5" t="inlineStr">
         <is>
           <t>7.608984617555596</t>
         </is>
       </c>
-      <c r="EB5" t="inlineStr">
+      <c r="EC5" t="inlineStr">
         <is>
           <t>7.52024426560034</t>
         </is>
       </c>
-      <c r="EC5" t="inlineStr">
+      <c r="ED5" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
-      <c r="ED5" t="inlineStr">
+      <c r="EE5" t="inlineStr">
         <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="EE5" t="inlineStr">
+      <c r="EF5" t="inlineStr">
         <is>
           <t>3.08</t>
         </is>
       </c>
-      <c r="EF5" t="inlineStr">
+      <c r="EG5" t="inlineStr">
         <is>
           <t>3.55</t>
         </is>
       </c>
-      <c r="EG5" t="inlineStr">
+      <c r="EH5" t="inlineStr">
         <is>
           <t>7.91</t>
         </is>
       </c>
-      <c r="EH5" t="inlineStr">
+      <c r="EI5" t="inlineStr">
         <is>
           <t>28.78</t>
         </is>
       </c>
-      <c r="EI5" t="inlineStr">
+      <c r="EJ5" t="inlineStr">
         <is>
           <t>37.54%</t>
         </is>
       </c>
-      <c r="EJ5" t="inlineStr">
+      <c r="EK5" t="inlineStr">
         <is>
           <t>21.61%</t>
         </is>
       </c>
-      <c r="EK5" t="inlineStr">
+      <c r="EL5" t="inlineStr">
         <is>
           <t>84.4</t>
         </is>
       </c>
-      <c r="EL5" t="inlineStr">
+      <c r="EM5" t="inlineStr">
         <is>
           <t>1136466</t>
         </is>
       </c>
-      <c r="EM5" t="inlineStr">
+      <c r="EN5" t="inlineStr">
         <is>
           <t>個人家庭60.70%、企業客戶32.70%、國際客戶4.00%、其他2.60% (2025年)</t>
         </is>
       </c>
-      <c r="EN5" t="inlineStr">
+      <c r="EO5" t="inlineStr">
         <is>
           <t>中華電-通信網路業-上市</t>
         </is>
       </c>
-      <c r="EO5" t="inlineStr">
+      <c r="EP5" t="inlineStr">
         <is>
           <t>通信網路業右上上市</t>
         </is>
       </c>
-      <c r="EP5" t="inlineStr">
+      <c r="EQ5" t="inlineStr">
         <is>
           <t>147.0</t>
         </is>
       </c>
-      <c r="EQ5" t="inlineStr">
+      <c r="ER5" t="inlineStr">
         <is>
           <t>147.0</t>
         </is>
       </c>
-      <c r="ER5" t="inlineStr">
+      <c r="ES5" t="inlineStr">
         <is>
           <t>144.0</t>
         </is>
       </c>
-      <c r="ES5" t="inlineStr">
+      <c r="ET5" t="inlineStr">
         <is>
           <t>145.5</t>
         </is>
       </c>
-      <c r="ET5" t="inlineStr">
+      <c r="EU5" t="inlineStr">
         <is>
           <t>129.5</t>
         </is>
       </c>
-      <c r="EU5" t="inlineStr">
+      <c r="EV5" t="inlineStr">
         <is>
           <t>47.26</t>
         </is>
       </c>
-      <c r="EV5" t="inlineStr">
+      <c r="EW5" t="inlineStr">
         <is>
           <t>** 通信網路 - 電信服務業** 智慧電網 - 能源管理服務、系統整合服務</t>
         </is>
       </c>
-      <c r="EW5" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
       <c r="EX5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="EY5" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="EZ5" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="EZ5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="FA5" t="inlineStr">
         <is>
           <t>0</t>
@@ -5170,29 +5190,29 @@
       </c>
       <c r="FD5" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="FE5" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="FE5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="FF5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FG5" t="inlineStr">
         <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="FH5" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="FH5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="FI5" t="inlineStr">
         <is>
           <t>0</t>
@@ -5205,170 +5225,175 @@
       </c>
       <c r="FK5" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="FL5" t="inlineStr">
+        <is>
           <t>115.2Q</t>
         </is>
       </c>
-      <c r="FL5" t="inlineStr">
+      <c r="FM5" t="inlineStr">
         <is>
           <t>61363.0</t>
         </is>
       </c>
-      <c r="FM5" t="inlineStr">
+      <c r="FN5" t="inlineStr">
         <is>
           <t>38328.0</t>
         </is>
       </c>
-      <c r="FN5" t="inlineStr">
+      <c r="FO5" t="inlineStr">
         <is>
           <t>23035.0</t>
         </is>
       </c>
-      <c r="FO5" t="inlineStr">
+      <c r="FP5" t="inlineStr">
         <is>
           <t>37.54</t>
         </is>
       </c>
-      <c r="FP5" t="inlineStr">
+      <c r="FQ5" t="inlineStr">
         <is>
           <t>13261.0</t>
         </is>
       </c>
-      <c r="FQ5" t="inlineStr">
+      <c r="FR5" t="inlineStr">
         <is>
           <t>21.61%</t>
         </is>
       </c>
-      <c r="FR5" t="inlineStr">
+      <c r="FS5" t="inlineStr">
         <is>
           <t>691.0</t>
         </is>
       </c>
-      <c r="FS5" t="inlineStr">
+      <c r="FT5" t="inlineStr">
         <is>
           <t>13953.0</t>
         </is>
       </c>
-      <c r="FT5" t="inlineStr">
+      <c r="FU5" t="inlineStr">
         <is>
           <t>10641.0</t>
         </is>
       </c>
-      <c r="FU5" t="inlineStr">
+      <c r="FV5" t="inlineStr">
         <is>
           <t>1.37</t>
         </is>
       </c>
-      <c r="FV5" t="inlineStr">
+      <c r="FW5" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="FW5" t="inlineStr">
+      <c r="FX5" t="inlineStr">
         <is>
           <t>EPS成長 / 毛利率衰退</t>
         </is>
       </c>
-      <c r="FX5" t="inlineStr">
+      <c r="FY5" t="inlineStr">
         <is>
           <t>1.2475</t>
         </is>
       </c>
-      <c r="FY5" t="inlineStr">
+      <c r="FZ5" t="inlineStr">
         <is>
           <t>36.6475</t>
         </is>
       </c>
-      <c r="FZ5" t="inlineStr">
+      <c r="GA5" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="GA5" t="inlineStr">
+      <c r="GB5" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="GB5" t="inlineStr">
+      <c r="GC5" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="GC5" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="GD5" t="inlineStr">
         <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="GE5" t="inlineStr">
+        <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="GE5" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="GF5" t="inlineStr">
         <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="GG5" t="inlineStr">
+        <is>
           <t>0.07000000000000006</t>
         </is>
       </c>
-      <c r="GG5" t="inlineStr">
+      <c r="GH5" t="inlineStr">
         <is>
           <t>0.05384615384615388</t>
         </is>
       </c>
-      <c r="GH5" t="inlineStr">
+      <c r="GI5" t="inlineStr">
         <is>
           <t>-0.3800000000000026</t>
         </is>
       </c>
-      <c r="GI5" t="inlineStr">
+      <c r="GJ5" t="inlineStr">
         <is>
           <t>-0.01002109704641352</t>
         </is>
       </c>
-      <c r="GJ5" t="inlineStr">
+      <c r="GK5" t="inlineStr">
         <is>
           <t>0.06000000000000005</t>
         </is>
       </c>
-      <c r="GK5" t="inlineStr">
+      <c r="GL5" t="inlineStr">
         <is>
           <t>0.04580152671755733</t>
         </is>
       </c>
-      <c r="GL5" t="inlineStr">
+      <c r="GM5" t="inlineStr">
         <is>
           <t>-0.8400000000000034</t>
         </is>
       </c>
-      <c r="GM5" t="inlineStr">
+      <c r="GN5" t="inlineStr">
         <is>
           <t>-0.02188639916623247</t>
         </is>
       </c>
-      <c r="GN5" t="inlineStr">
+      <c r="GO5" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="GO5" t="inlineStr">
+      <c r="GP5" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="GP5" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="GQ5" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
       <c r="GR5" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="GS5" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
@@ -5767,378 +5792,378 @@
       </c>
       <c r="CA6" t="inlineStr">
         <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="CB6" t="inlineStr">
+        <is>
           <t>2026-09-18 00:00:00</t>
         </is>
       </c>
-      <c r="CB6" t="inlineStr">
+      <c r="CC6" t="inlineStr">
         <is>
           <t>2026-10-02</t>
         </is>
       </c>
-      <c r="CC6" t="inlineStr">
+      <c r="CD6" t="inlineStr">
         <is>
           <t>16.71</t>
         </is>
       </c>
-      <c r="CD6" t="inlineStr">
+      <c r="CE6" t="inlineStr">
         <is>
           <t>1.05</t>
         </is>
       </c>
-      <c r="CE6" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="CF6" t="inlineStr"/>
-      <c r="CG6" t="inlineStr">
+      <c r="CF6" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="CG6" t="inlineStr"/>
+      <c r="CH6" t="inlineStr">
         <is>
           <t>67</t>
         </is>
       </c>
-      <c r="CH6" t="inlineStr">
+      <c r="CI6" t="inlineStr">
         <is>
           <t>9157</t>
         </is>
       </c>
-      <c r="CI6" t="inlineStr">
+      <c r="CJ6" t="inlineStr">
         <is>
           <t>100.0</t>
         </is>
       </c>
-      <c r="CJ6" t="inlineStr">
+      <c r="CK6" t="inlineStr">
         <is>
           <t>66.67</t>
         </is>
       </c>
-      <c r="CK6" t="n">
+      <c r="CL6" t="n">
         <v>0.83</v>
       </c>
-      <c r="CL6" t="n">
+      <c r="CM6" t="n">
         <v>1.58</v>
       </c>
-      <c r="CM6" t="inlineStr">
+      <c r="CN6" t="inlineStr">
         <is>
           <t>2.29</t>
         </is>
       </c>
-      <c r="CN6" t="inlineStr">
+      <c r="CO6" t="inlineStr">
         <is>
           <t>-0.43</t>
         </is>
       </c>
-      <c r="CO6" t="inlineStr">
+      <c r="CP6" t="inlineStr">
         <is>
           <t>144.8</t>
         </is>
       </c>
-      <c r="CP6" t="inlineStr">
+      <c r="CQ6" t="inlineStr">
         <is>
           <t>144.95</t>
         </is>
       </c>
-      <c r="CQ6" t="inlineStr">
+      <c r="CR6" t="inlineStr">
         <is>
           <t>142.55</t>
         </is>
       </c>
-      <c r="CR6" t="inlineStr">
+      <c r="CS6" t="inlineStr">
         <is>
           <t>139.36</t>
         </is>
       </c>
-      <c r="CS6" t="inlineStr">
+      <c r="CT6" t="inlineStr">
         <is>
           <t>139.96</t>
         </is>
       </c>
-      <c r="CT6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="CU6" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CV6" t="inlineStr">
+        <is>
           <t>0.0006910850034556049</t>
         </is>
       </c>
-      <c r="CV6" t="inlineStr">
+      <c r="CW6" t="inlineStr">
         <is>
           <t>0.001727712508638568</t>
         </is>
       </c>
-      <c r="CW6" t="inlineStr">
+      <c r="CX6" t="inlineStr">
         <is>
           <t>0.002990325417766115</t>
         </is>
       </c>
-      <c r="CX6" t="inlineStr">
+      <c r="CY6" t="inlineStr">
         <is>
           <t>0.001077508799655291</t>
         </is>
       </c>
-      <c r="CY6" t="inlineStr">
+      <c r="CZ6" t="inlineStr">
         <is>
           <t>0.0006702712364270447</t>
         </is>
       </c>
-      <c r="CZ6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="DA6" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="DB6" t="inlineStr">
+        <is>
           <t>7.12</t>
         </is>
       </c>
-      <c r="DB6" t="n">
+      <c r="DC6" t="n">
         <v>1.96</v>
       </c>
-      <c r="DC6" t="n">
+      <c r="DD6" t="n">
         <v>1.83</v>
       </c>
-      <c r="DD6" t="inlineStr">
+      <c r="DE6" t="inlineStr">
         <is>
           <t>1.9</t>
         </is>
       </c>
-      <c r="DE6" t="inlineStr">
+      <c r="DF6" t="inlineStr">
         <is>
           <t>-3.52</t>
         </is>
       </c>
-      <c r="DF6" t="inlineStr">
+      <c r="DG6" t="inlineStr">
         <is>
           <t>2026/08/21</t>
         </is>
       </c>
-      <c r="DG6" t="inlineStr">
+      <c r="DH6" t="inlineStr">
         <is>
           <t>2510241792.666667</t>
         </is>
       </c>
-      <c r="DH6" t="inlineStr">
+      <c r="DI6" t="inlineStr">
         <is>
           <t>1458318100.0</t>
         </is>
       </c>
-      <c r="DI6" t="n">
+      <c r="DJ6" t="n">
         <v>1365056504.4</v>
       </c>
-      <c r="DJ6" t="inlineStr">
+      <c r="DK6" t="inlineStr">
         <is>
           <t>1640423214.1</t>
         </is>
       </c>
-      <c r="DK6" t="inlineStr">
+      <c r="DL6" t="inlineStr">
         <is>
           <t>1485353753.433333</t>
         </is>
       </c>
-      <c r="DL6" t="n">
+      <c r="DM6" t="n">
         <v>1659414895.68</v>
       </c>
-      <c r="DM6" t="inlineStr">
+      <c r="DN6" t="inlineStr">
         <is>
           <t>2004348026.1375</t>
         </is>
       </c>
-      <c r="DN6" t="inlineStr">
+      <c r="DO6" t="inlineStr">
         <is>
           <t>3840453.53609038</t>
         </is>
       </c>
-      <c r="DO6" t="inlineStr">
+      <c r="DP6" t="inlineStr">
         <is>
           <t>-62046440.25567794</t>
         </is>
       </c>
-      <c r="DP6" t="inlineStr">
+      <c r="DQ6" t="inlineStr">
         <is>
           <t>1458318100.0</t>
         </is>
       </c>
-      <c r="DQ6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="DR6" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="DS6" t="inlineStr">
+        <is>
           <t>143.5</t>
         </is>
       </c>
-      <c r="DS6" t="inlineStr">
+      <c r="DT6" t="inlineStr">
         <is>
           <t>2026/09/15</t>
         </is>
       </c>
-      <c r="DT6" t="inlineStr">
+      <c r="DU6" t="inlineStr">
         <is>
           <t>1.74</t>
         </is>
       </c>
-      <c r="DU6" t="inlineStr">
+      <c r="DV6" t="inlineStr">
         <is>
           <t>中華電</t>
         </is>
       </c>
-      <c r="DV6" t="inlineStr">
+      <c r="DW6" t="inlineStr">
         <is>
           <t>中華電</t>
         </is>
       </c>
-      <c r="DW6" t="inlineStr">
+      <c r="DX6" t="inlineStr">
         <is>
           <t>通信網路業</t>
         </is>
       </c>
-      <c r="DX6" t="inlineStr">
+      <c r="DY6" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="DY6" t="inlineStr">
+      <c r="DZ6" t="inlineStr">
         <is>
           <t>0.01</t>
         </is>
       </c>
-      <c r="DZ6" t="inlineStr">
+      <c r="EA6" t="inlineStr">
         <is>
           <t>-1.398042523039787</t>
         </is>
       </c>
-      <c r="EA6" t="inlineStr">
+      <c r="EB6" t="inlineStr">
         <is>
           <t>7.608984617555596</t>
         </is>
       </c>
-      <c r="EB6" t="inlineStr">
+      <c r="EC6" t="inlineStr">
         <is>
           <t>7.52024426560034</t>
         </is>
       </c>
-      <c r="EC6" t="inlineStr">
+      <c r="ED6" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
-      <c r="ED6" t="inlineStr">
+      <c r="EE6" t="inlineStr">
         <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="EE6" t="inlineStr">
+      <c r="EF6" t="inlineStr">
         <is>
           <t>3.09</t>
         </is>
       </c>
-      <c r="EF6" t="inlineStr">
+      <c r="EG6" t="inlineStr">
         <is>
           <t>3.55</t>
         </is>
       </c>
-      <c r="EG6" t="inlineStr">
+      <c r="EH6" t="inlineStr">
         <is>
           <t>7.91</t>
         </is>
       </c>
-      <c r="EH6" t="inlineStr">
+      <c r="EI6" t="inlineStr">
         <is>
           <t>28.78</t>
         </is>
       </c>
-      <c r="EI6" t="inlineStr">
+      <c r="EJ6" t="inlineStr">
         <is>
           <t>37.54%</t>
         </is>
       </c>
-      <c r="EJ6" t="inlineStr">
+      <c r="EK6" t="inlineStr">
         <is>
           <t>21.61%</t>
         </is>
       </c>
-      <c r="EK6" t="inlineStr">
+      <c r="EL6" t="inlineStr">
         <is>
           <t>84.4</t>
         </is>
       </c>
-      <c r="EL6" t="inlineStr">
+      <c r="EM6" t="inlineStr">
         <is>
           <t>1136466</t>
         </is>
       </c>
-      <c r="EM6" t="inlineStr">
+      <c r="EN6" t="inlineStr">
         <is>
           <t>個人家庭60.70%、企業客戶32.70%、國際客戶4.00%、其他2.60% (2025年)</t>
         </is>
       </c>
-      <c r="EN6" t="inlineStr">
+      <c r="EO6" t="inlineStr">
         <is>
           <t>中華電-通信網路業-上市</t>
         </is>
       </c>
-      <c r="EO6" t="inlineStr">
+      <c r="EP6" t="inlineStr">
         <is>
           <t>通信網路業右上上市</t>
         </is>
       </c>
-      <c r="EP6" t="inlineStr">
+      <c r="EQ6" t="inlineStr">
         <is>
           <t>145.0</t>
         </is>
       </c>
-      <c r="EQ6" t="inlineStr">
+      <c r="ER6" t="inlineStr">
         <is>
           <t>146.5</t>
         </is>
       </c>
-      <c r="ER6" t="inlineStr">
+      <c r="ES6" t="inlineStr">
         <is>
           <t>144.0</t>
         </is>
       </c>
-      <c r="ES6" t="inlineStr">
+      <c r="ET6" t="inlineStr">
         <is>
           <t>146.0</t>
         </is>
       </c>
-      <c r="ET6" t="inlineStr">
+      <c r="EU6" t="inlineStr">
         <is>
           <t>129.5</t>
         </is>
       </c>
-      <c r="EU6" t="inlineStr">
+      <c r="EV6" t="inlineStr">
         <is>
           <t>47.26</t>
         </is>
       </c>
-      <c r="EV6" t="inlineStr">
+      <c r="EW6" t="inlineStr">
         <is>
           <t>** 通信網路 - 電信服務業** 智慧電網 - 能源管理服務、系統整合服務</t>
         </is>
       </c>
-      <c r="EW6" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
       <c r="EX6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="EY6" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="EZ6" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="EZ6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="FA6" t="inlineStr">
         <is>
           <t>0</t>
@@ -6156,29 +6181,29 @@
       </c>
       <c r="FD6" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="FE6" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="FE6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="FF6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FG6" t="inlineStr">
         <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="FH6" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="FH6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="FI6" t="inlineStr">
         <is>
           <t>0</t>
@@ -6191,170 +6216,175 @@
       </c>
       <c r="FK6" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="FL6" t="inlineStr">
+        <is>
           <t>115.2Q</t>
         </is>
       </c>
-      <c r="FL6" t="inlineStr">
+      <c r="FM6" t="inlineStr">
         <is>
           <t>61363.0</t>
         </is>
       </c>
-      <c r="FM6" t="inlineStr">
+      <c r="FN6" t="inlineStr">
         <is>
           <t>38328.0</t>
         </is>
       </c>
-      <c r="FN6" t="inlineStr">
+      <c r="FO6" t="inlineStr">
         <is>
           <t>23035.0</t>
         </is>
       </c>
-      <c r="FO6" t="inlineStr">
+      <c r="FP6" t="inlineStr">
         <is>
           <t>37.54</t>
         </is>
       </c>
-      <c r="FP6" t="inlineStr">
+      <c r="FQ6" t="inlineStr">
         <is>
           <t>13261.0</t>
         </is>
       </c>
-      <c r="FQ6" t="inlineStr">
+      <c r="FR6" t="inlineStr">
         <is>
           <t>21.61%</t>
         </is>
       </c>
-      <c r="FR6" t="inlineStr">
+      <c r="FS6" t="inlineStr">
         <is>
           <t>691.0</t>
         </is>
       </c>
-      <c r="FS6" t="inlineStr">
+      <c r="FT6" t="inlineStr">
         <is>
           <t>13953.0</t>
         </is>
       </c>
-      <c r="FT6" t="inlineStr">
+      <c r="FU6" t="inlineStr">
         <is>
           <t>10641.0</t>
         </is>
       </c>
-      <c r="FU6" t="inlineStr">
+      <c r="FV6" t="inlineStr">
         <is>
           <t>1.37</t>
         </is>
       </c>
-      <c r="FV6" t="inlineStr">
+      <c r="FW6" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="FW6" t="inlineStr">
+      <c r="FX6" t="inlineStr">
         <is>
           <t>EPS成長 / 毛利率衰退</t>
         </is>
       </c>
-      <c r="FX6" t="inlineStr">
+      <c r="FY6" t="inlineStr">
         <is>
           <t>1.2475</t>
         </is>
       </c>
-      <c r="FY6" t="inlineStr">
+      <c r="FZ6" t="inlineStr">
         <is>
           <t>36.6475</t>
         </is>
       </c>
-      <c r="FZ6" t="inlineStr">
+      <c r="GA6" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="GA6" t="inlineStr">
+      <c r="GB6" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="GB6" t="inlineStr">
+      <c r="GC6" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="GC6" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="GD6" t="inlineStr">
         <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="GE6" t="inlineStr">
+        <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="GE6" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="GF6" t="inlineStr">
         <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="GG6" t="inlineStr">
+        <is>
           <t>0.07000000000000006</t>
         </is>
       </c>
-      <c r="GG6" t="inlineStr">
+      <c r="GH6" t="inlineStr">
         <is>
           <t>0.05384615384615388</t>
         </is>
       </c>
-      <c r="GH6" t="inlineStr">
+      <c r="GI6" t="inlineStr">
         <is>
           <t>-0.3800000000000026</t>
         </is>
       </c>
-      <c r="GI6" t="inlineStr">
+      <c r="GJ6" t="inlineStr">
         <is>
           <t>-0.01002109704641352</t>
         </is>
       </c>
-      <c r="GJ6" t="inlineStr">
+      <c r="GK6" t="inlineStr">
         <is>
           <t>0.06000000000000005</t>
         </is>
       </c>
-      <c r="GK6" t="inlineStr">
+      <c r="GL6" t="inlineStr">
         <is>
           <t>0.04580152671755733</t>
         </is>
       </c>
-      <c r="GL6" t="inlineStr">
+      <c r="GM6" t="inlineStr">
         <is>
           <t>-0.8400000000000034</t>
         </is>
       </c>
-      <c r="GM6" t="inlineStr">
+      <c r="GN6" t="inlineStr">
         <is>
           <t>-0.02188639916623247</t>
         </is>
       </c>
-      <c r="GN6" t="inlineStr">
+      <c r="GO6" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="GO6" t="inlineStr">
+      <c r="GP6" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="GP6" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="GQ6" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
       <c r="GR6" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="GS6" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
@@ -6753,378 +6783,378 @@
       </c>
       <c r="CA7" t="inlineStr">
         <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="CB7" t="inlineStr">
+        <is>
           <t>2026-09-18 00:00:00</t>
         </is>
       </c>
-      <c r="CB7" t="inlineStr">
+      <c r="CC7" t="inlineStr">
         <is>
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="CC7" t="inlineStr">
+      <c r="CD7" t="inlineStr">
         <is>
           <t>14.40</t>
         </is>
       </c>
-      <c r="CD7" t="inlineStr">
+      <c r="CE7" t="inlineStr">
         <is>
           <t>1.40</t>
         </is>
       </c>
-      <c r="CE7" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="CF7" t="inlineStr"/>
-      <c r="CG7" t="inlineStr">
+      <c r="CF7" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="CG7" t="inlineStr"/>
+      <c r="CH7" t="inlineStr">
         <is>
           <t>67</t>
         </is>
       </c>
-      <c r="CH7" t="inlineStr">
+      <c r="CI7" t="inlineStr">
         <is>
           <t>9157</t>
         </is>
       </c>
-      <c r="CI7" t="inlineStr">
+      <c r="CJ7" t="inlineStr">
         <is>
           <t>100.0</t>
         </is>
       </c>
-      <c r="CJ7" t="inlineStr">
+      <c r="CK7" t="inlineStr">
         <is>
           <t>41.67</t>
         </is>
       </c>
-      <c r="CK7" t="n">
+      <c r="CL7" t="n">
         <v>0.55</v>
       </c>
-      <c r="CL7" t="n">
+      <c r="CM7" t="n">
         <v>1.81</v>
       </c>
-      <c r="CM7" t="inlineStr">
+      <c r="CN7" t="inlineStr">
         <is>
           <t>2.09</t>
         </is>
       </c>
-      <c r="CN7" t="inlineStr">
+      <c r="CO7" t="inlineStr">
         <is>
           <t>-0.47</t>
         </is>
       </c>
-      <c r="CO7" t="inlineStr">
+      <c r="CP7" t="inlineStr">
         <is>
           <t>144.7</t>
         </is>
       </c>
-      <c r="CP7" t="inlineStr">
+      <c r="CQ7" t="inlineStr">
         <is>
           <t>144.7</t>
         </is>
       </c>
-      <c r="CQ7" t="inlineStr">
+      <c r="CR7" t="inlineStr">
         <is>
           <t>142.12</t>
         </is>
       </c>
-      <c r="CR7" t="inlineStr">
+      <c r="CS7" t="inlineStr">
         <is>
           <t>139.21</t>
         </is>
       </c>
-      <c r="CS7" t="inlineStr">
+      <c r="CT7" t="inlineStr">
         <is>
           <t>139.87</t>
         </is>
       </c>
-      <c r="CT7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="CU7" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CV7" t="inlineStr">
+        <is>
           <t>0.0006915629322268302</t>
         </is>
       </c>
-      <c r="CV7" t="inlineStr">
+      <c r="CW7" t="inlineStr">
         <is>
           <t>0.00138408304498272</t>
         </is>
       </c>
-      <c r="CW7" t="inlineStr">
+      <c r="CX7" t="inlineStr">
         <is>
           <t>0.003353335686551384</t>
         </is>
       </c>
-      <c r="CX7" t="inlineStr">
+      <c r="CY7" t="inlineStr">
         <is>
           <t>0.0009347138337647554</t>
         </is>
       </c>
-      <c r="CY7" t="inlineStr">
+      <c r="CZ7" t="inlineStr">
         <is>
           <t>0.0004023245417970056</t>
         </is>
       </c>
-      <c r="CZ7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="DA7" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="DB7" t="inlineStr">
+        <is>
           <t>6.98</t>
         </is>
       </c>
-      <c r="DB7" t="n">
+      <c r="DC7" t="n">
         <v>1.92</v>
       </c>
-      <c r="DC7" t="n">
+      <c r="DD7" t="n">
         <v>1.8</v>
       </c>
-      <c r="DD7" t="inlineStr">
+      <c r="DE7" t="inlineStr">
         <is>
           <t>1.9</t>
         </is>
       </c>
-      <c r="DE7" t="inlineStr">
+      <c r="DF7" t="inlineStr">
         <is>
           <t>-5.24</t>
         </is>
       </c>
-      <c r="DF7" t="inlineStr">
+      <c r="DG7" t="inlineStr">
         <is>
           <t>2026/08/21</t>
         </is>
       </c>
-      <c r="DG7" t="inlineStr">
+      <c r="DH7" t="inlineStr">
         <is>
           <t>2510241792.666667</t>
         </is>
       </c>
-      <c r="DH7" t="inlineStr">
+      <c r="DI7" t="inlineStr">
         <is>
           <t>1248190797.0</t>
         </is>
       </c>
-      <c r="DI7" t="n">
+      <c r="DJ7" t="n">
         <v>1315071112.6</v>
       </c>
-      <c r="DJ7" t="inlineStr">
+      <c r="DK7" t="inlineStr">
         <is>
           <t>1706616096.2</t>
         </is>
       </c>
-      <c r="DK7" t="inlineStr">
+      <c r="DL7" t="inlineStr">
         <is>
           <t>1469076947.433333</t>
         </is>
       </c>
-      <c r="DL7" t="n">
+      <c r="DM7" t="n">
         <v>1667394181.32</v>
       </c>
-      <c r="DM7" t="inlineStr">
+      <c r="DN7" t="inlineStr">
         <is>
           <t>2016079760.0875</t>
         </is>
       </c>
-      <c r="DN7" t="inlineStr">
+      <c r="DO7" t="inlineStr">
         <is>
           <t>15819888.77095735</t>
         </is>
       </c>
-      <c r="DO7" t="inlineStr">
+      <c r="DP7" t="inlineStr">
         <is>
           <t>-65717912.88774347</t>
         </is>
       </c>
-      <c r="DP7" t="inlineStr">
+      <c r="DQ7" t="inlineStr">
         <is>
           <t>1248190797.0</t>
         </is>
       </c>
-      <c r="DQ7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="DR7" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="DS7" t="inlineStr">
+        <is>
           <t>143.5</t>
         </is>
       </c>
-      <c r="DS7" t="inlineStr">
+      <c r="DT7" t="inlineStr">
         <is>
           <t>2026/09/15</t>
         </is>
       </c>
-      <c r="DT7" t="inlineStr">
+      <c r="DU7" t="inlineStr">
         <is>
           <t>1.39</t>
         </is>
       </c>
-      <c r="DU7" t="inlineStr">
+      <c r="DV7" t="inlineStr">
         <is>
           <t>中華電</t>
         </is>
       </c>
-      <c r="DV7" t="inlineStr">
+      <c r="DW7" t="inlineStr">
         <is>
           <t>中華電</t>
         </is>
       </c>
-      <c r="DW7" t="inlineStr">
+      <c r="DX7" t="inlineStr">
         <is>
           <t>通信網路業</t>
         </is>
       </c>
-      <c r="DX7" t="inlineStr">
+      <c r="DY7" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="DY7" t="inlineStr">
+      <c r="DZ7" t="inlineStr">
         <is>
           <t>0.01</t>
         </is>
       </c>
-      <c r="DZ7" t="inlineStr">
+      <c r="EA7" t="inlineStr">
         <is>
           <t>-1.398042523039787</t>
         </is>
       </c>
-      <c r="EA7" t="inlineStr">
+      <c r="EB7" t="inlineStr">
         <is>
           <t>7.608984617555596</t>
         </is>
       </c>
-      <c r="EB7" t="inlineStr">
+      <c r="EC7" t="inlineStr">
         <is>
           <t>7.52024426560034</t>
         </is>
       </c>
-      <c r="EC7" t="inlineStr">
+      <c r="ED7" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
-      <c r="ED7" t="inlineStr">
+      <c r="EE7" t="inlineStr">
         <is>
           <t>價-量增</t>
         </is>
       </c>
-      <c r="EE7" t="inlineStr">
+      <c r="EF7" t="inlineStr">
         <is>
           <t>3.08</t>
         </is>
       </c>
-      <c r="EF7" t="inlineStr">
+      <c r="EG7" t="inlineStr">
         <is>
           <t>3.55</t>
         </is>
       </c>
-      <c r="EG7" t="inlineStr">
+      <c r="EH7" t="inlineStr">
         <is>
           <t>7.91</t>
         </is>
       </c>
-      <c r="EH7" t="inlineStr">
+      <c r="EI7" t="inlineStr">
         <is>
           <t>28.78</t>
         </is>
       </c>
-      <c r="EI7" t="inlineStr">
+      <c r="EJ7" t="inlineStr">
         <is>
           <t>37.54%</t>
         </is>
       </c>
-      <c r="EJ7" t="inlineStr">
+      <c r="EK7" t="inlineStr">
         <is>
           <t>21.61%</t>
         </is>
       </c>
-      <c r="EK7" t="inlineStr">
+      <c r="EL7" t="inlineStr">
         <is>
           <t>84.4</t>
         </is>
       </c>
-      <c r="EL7" t="inlineStr">
+      <c r="EM7" t="inlineStr">
         <is>
           <t>1136466</t>
         </is>
       </c>
-      <c r="EM7" t="inlineStr">
+      <c r="EN7" t="inlineStr">
         <is>
           <t>個人家庭60.70%、企業客戶32.70%、國際客戶4.00%、其他2.60% (2025年)</t>
         </is>
       </c>
-      <c r="EN7" t="inlineStr">
+      <c r="EO7" t="inlineStr">
         <is>
           <t>中華電-通信網路業-上市</t>
         </is>
       </c>
-      <c r="EO7" t="inlineStr">
+      <c r="EP7" t="inlineStr">
         <is>
           <t>通信網路業右上上市</t>
         </is>
       </c>
-      <c r="EP7" t="inlineStr">
+      <c r="EQ7" t="inlineStr">
         <is>
           <t>144.0</t>
         </is>
       </c>
-      <c r="EQ7" t="inlineStr">
+      <c r="ER7" t="inlineStr">
         <is>
           <t>146.0</t>
         </is>
       </c>
-      <c r="ER7" t="inlineStr">
+      <c r="ES7" t="inlineStr">
         <is>
           <t>143.0</t>
         </is>
       </c>
-      <c r="ES7" t="inlineStr">
+      <c r="ET7" t="inlineStr">
         <is>
           <t>145.5</t>
         </is>
       </c>
-      <c r="ET7" t="inlineStr">
+      <c r="EU7" t="inlineStr">
         <is>
           <t>129.5</t>
         </is>
       </c>
-      <c r="EU7" t="inlineStr">
+      <c r="EV7" t="inlineStr">
         <is>
           <t>47.26</t>
         </is>
       </c>
-      <c r="EV7" t="inlineStr">
+      <c r="EW7" t="inlineStr">
         <is>
           <t>** 通信網路 - 電信服務業** 智慧電網 - 能源管理服務、系統整合服務</t>
         </is>
       </c>
-      <c r="EW7" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
       <c r="EX7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="EY7" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="EZ7" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="EZ7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="FA7" t="inlineStr">
         <is>
           <t>0</t>
@@ -7142,34 +7172,34 @@
       </c>
       <c r="FD7" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="FE7" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="FE7" t="inlineStr">
+      <c r="FF7" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="FF7" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="FG7" t="inlineStr">
         <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="FH7" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="FH7" t="inlineStr">
+      <c r="FI7" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="FI7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="FJ7" t="inlineStr">
         <is>
           <t>0</t>
@@ -7177,170 +7207,175 @@
       </c>
       <c r="FK7" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="FL7" t="inlineStr">
+        <is>
           <t>115.2Q</t>
         </is>
       </c>
-      <c r="FL7" t="inlineStr">
+      <c r="FM7" t="inlineStr">
         <is>
           <t>61363.0</t>
         </is>
       </c>
-      <c r="FM7" t="inlineStr">
+      <c r="FN7" t="inlineStr">
         <is>
           <t>38328.0</t>
         </is>
       </c>
-      <c r="FN7" t="inlineStr">
+      <c r="FO7" t="inlineStr">
         <is>
           <t>23035.0</t>
         </is>
       </c>
-      <c r="FO7" t="inlineStr">
+      <c r="FP7" t="inlineStr">
         <is>
           <t>37.54</t>
         </is>
       </c>
-      <c r="FP7" t="inlineStr">
+      <c r="FQ7" t="inlineStr">
         <is>
           <t>13261.0</t>
         </is>
       </c>
-      <c r="FQ7" t="inlineStr">
+      <c r="FR7" t="inlineStr">
         <is>
           <t>21.61%</t>
         </is>
       </c>
-      <c r="FR7" t="inlineStr">
+      <c r="FS7" t="inlineStr">
         <is>
           <t>691.0</t>
         </is>
       </c>
-      <c r="FS7" t="inlineStr">
+      <c r="FT7" t="inlineStr">
         <is>
           <t>13953.0</t>
         </is>
       </c>
-      <c r="FT7" t="inlineStr">
+      <c r="FU7" t="inlineStr">
         <is>
           <t>10641.0</t>
         </is>
       </c>
-      <c r="FU7" t="inlineStr">
+      <c r="FV7" t="inlineStr">
         <is>
           <t>1.37</t>
         </is>
       </c>
-      <c r="FV7" t="inlineStr">
+      <c r="FW7" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="FW7" t="inlineStr">
+      <c r="FX7" t="inlineStr">
         <is>
           <t>EPS成長 / 毛利率衰退</t>
         </is>
       </c>
-      <c r="FX7" t="inlineStr">
+      <c r="FY7" t="inlineStr">
         <is>
           <t>1.2475</t>
         </is>
       </c>
-      <c r="FY7" t="inlineStr">
+      <c r="FZ7" t="inlineStr">
         <is>
           <t>36.6475</t>
         </is>
       </c>
-      <c r="FZ7" t="inlineStr">
+      <c r="GA7" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="GA7" t="inlineStr">
+      <c r="GB7" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="GB7" t="inlineStr">
+      <c r="GC7" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="GC7" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="GD7" t="inlineStr">
         <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="GE7" t="inlineStr">
+        <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="GE7" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="GF7" t="inlineStr">
         <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="GG7" t="inlineStr">
+        <is>
           <t>0.07000000000000006</t>
         </is>
       </c>
-      <c r="GG7" t="inlineStr">
+      <c r="GH7" t="inlineStr">
         <is>
           <t>0.05384615384615388</t>
         </is>
       </c>
-      <c r="GH7" t="inlineStr">
+      <c r="GI7" t="inlineStr">
         <is>
           <t>-0.3800000000000026</t>
         </is>
       </c>
-      <c r="GI7" t="inlineStr">
+      <c r="GJ7" t="inlineStr">
         <is>
           <t>-0.01002109704641352</t>
         </is>
       </c>
-      <c r="GJ7" t="inlineStr">
+      <c r="GK7" t="inlineStr">
         <is>
           <t>0.06000000000000005</t>
         </is>
       </c>
-      <c r="GK7" t="inlineStr">
+      <c r="GL7" t="inlineStr">
         <is>
           <t>0.04580152671755733</t>
         </is>
       </c>
-      <c r="GL7" t="inlineStr">
+      <c r="GM7" t="inlineStr">
         <is>
           <t>-0.8400000000000034</t>
         </is>
       </c>
-      <c r="GM7" t="inlineStr">
+      <c r="GN7" t="inlineStr">
         <is>
           <t>-0.02188639916623247</t>
         </is>
       </c>
-      <c r="GN7" t="inlineStr">
+      <c r="GO7" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="GO7" t="inlineStr">
+      <c r="GP7" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="GP7" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="GQ7" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
       <c r="GR7" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="GS7" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
@@ -7739,378 +7774,378 @@
       </c>
       <c r="CA8" t="inlineStr">
         <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="CB8" t="inlineStr">
+        <is>
           <t>2026-09-18 00:00:00</t>
         </is>
       </c>
-      <c r="CB8" t="inlineStr">
+      <c r="CC8" t="inlineStr">
         <is>
           <t>2026-09-30</t>
         </is>
       </c>
-      <c r="CC8" t="inlineStr">
+      <c r="CD8" t="inlineStr">
         <is>
           <t>17.70</t>
         </is>
       </c>
-      <c r="CD8" t="inlineStr">
+      <c r="CE8" t="inlineStr">
         <is>
           <t>-0.70</t>
         </is>
       </c>
-      <c r="CE8" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="CF8" t="inlineStr"/>
-      <c r="CG8" t="inlineStr">
+      <c r="CF8" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="CG8" t="inlineStr"/>
+      <c r="CH8" t="inlineStr">
         <is>
           <t>67</t>
         </is>
       </c>
-      <c r="CH8" t="inlineStr">
+      <c r="CI8" t="inlineStr">
         <is>
           <t>9157</t>
         </is>
       </c>
-      <c r="CI8" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="CJ8" t="inlineStr">
         <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="CK8" t="inlineStr">
+        <is>
           <t>36.11</t>
         </is>
       </c>
-      <c r="CK8" t="n">
+      <c r="CL8" t="n">
         <v>-0.76</v>
       </c>
-      <c r="CL8" t="n">
+      <c r="CM8" t="n">
         <v>2.08</v>
       </c>
-      <c r="CM8" t="inlineStr">
+      <c r="CN8" t="inlineStr">
         <is>
           <t>1.85</t>
         </is>
       </c>
-      <c r="CN8" t="inlineStr">
+      <c r="CO8" t="inlineStr">
         <is>
           <t>-0.52</t>
         </is>
       </c>
-      <c r="CO8" t="inlineStr">
+      <c r="CP8" t="inlineStr">
         <is>
           <t>144.6</t>
         </is>
       </c>
-      <c r="CP8" t="inlineStr">
+      <c r="CQ8" t="inlineStr">
         <is>
           <t>144.5</t>
         </is>
       </c>
-      <c r="CQ8" t="inlineStr">
+      <c r="CR8" t="inlineStr">
         <is>
           <t>141.65</t>
         </is>
       </c>
-      <c r="CR8" t="inlineStr">
+      <c r="CS8" t="inlineStr">
         <is>
           <t>139.08</t>
         </is>
       </c>
-      <c r="CS8" t="inlineStr">
+      <c r="CT8" t="inlineStr">
         <is>
           <t>139.81</t>
         </is>
       </c>
-      <c r="CT8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="CU8" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CV8" t="inlineStr">
+        <is>
           <t>-0.001381215469613339</t>
         </is>
       </c>
-      <c r="CV8" t="inlineStr">
+      <c r="CW8" t="inlineStr">
         <is>
           <t>0.0006925207756232066</t>
         </is>
       </c>
-      <c r="CW8" t="inlineStr">
+      <c r="CX8" t="inlineStr">
         <is>
           <t>0.002654397451778534</t>
         </is>
       </c>
-      <c r="CX8" t="inlineStr">
+      <c r="CY8" t="inlineStr">
         <is>
           <t>0.0006475285991798252</t>
         </is>
       </c>
-      <c r="CY8" t="inlineStr">
+      <c r="CZ8" t="inlineStr">
         <is>
           <t>0.0001788428865241443</t>
         </is>
       </c>
-      <c r="CZ8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="DA8" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="DB8" t="inlineStr">
+        <is>
           <t>7.47</t>
         </is>
       </c>
-      <c r="DB8" t="n">
+      <c r="DC8" t="n">
         <v>1.9</v>
       </c>
-      <c r="DC8" t="n">
+      <c r="DD8" t="n">
         <v>1.76</v>
       </c>
-      <c r="DD8" t="inlineStr">
+      <c r="DE8" t="inlineStr">
         <is>
           <t>1.9</t>
         </is>
       </c>
-      <c r="DE8" t="inlineStr">
+      <c r="DF8" t="inlineStr">
         <is>
           <t>-6.89</t>
         </is>
       </c>
-      <c r="DF8" t="inlineStr">
+      <c r="DG8" t="inlineStr">
         <is>
           <t>2026/08/21</t>
         </is>
       </c>
-      <c r="DG8" t="inlineStr">
+      <c r="DH8" t="inlineStr">
         <is>
           <t>2510241792.666667</t>
         </is>
       </c>
-      <c r="DH8" t="inlineStr">
+      <c r="DI8" t="inlineStr">
         <is>
           <t>1524028999.0</t>
         </is>
       </c>
-      <c r="DI8" t="n">
+      <c r="DJ8" t="n">
         <v>1223386087.6</v>
       </c>
-      <c r="DJ8" t="inlineStr">
+      <c r="DK8" t="inlineStr">
         <is>
           <t>1823976219.1</t>
         </is>
       </c>
-      <c r="DK8" t="inlineStr">
+      <c r="DL8" t="inlineStr">
         <is>
           <t>1490856706.633333</t>
         </is>
       </c>
-      <c r="DL8" t="n">
+      <c r="DM8" t="n">
         <v>1693335182.06</v>
       </c>
-      <c r="DM8" t="inlineStr">
+      <c r="DN8" t="inlineStr">
         <is>
           <t>2020913533.8875</t>
         </is>
       </c>
-      <c r="DN8" t="inlineStr">
+      <c r="DO8" t="inlineStr">
         <is>
           <t>30644943.61799386</t>
         </is>
       </c>
-      <c r="DO8" t="inlineStr">
+      <c r="DP8" t="inlineStr">
         <is>
           <t>-46102165.86613226</t>
         </is>
       </c>
-      <c r="DP8" t="inlineStr">
+      <c r="DQ8" t="inlineStr">
         <is>
           <t>1524028999.0</t>
         </is>
       </c>
-      <c r="DQ8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="DR8" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="DS8" t="inlineStr">
+        <is>
           <t>143.5</t>
         </is>
       </c>
-      <c r="DS8" t="inlineStr">
+      <c r="DT8" t="inlineStr">
         <is>
           <t>2026/09/15</t>
         </is>
       </c>
-      <c r="DT8" t="inlineStr">
+      <c r="DU8" t="inlineStr">
         <is>
           <t>0.00</t>
         </is>
       </c>
-      <c r="DU8" t="inlineStr">
+      <c r="DV8" t="inlineStr">
         <is>
           <t>中華電</t>
         </is>
       </c>
-      <c r="DV8" t="inlineStr">
+      <c r="DW8" t="inlineStr">
         <is>
           <t>中華電</t>
         </is>
       </c>
-      <c r="DW8" t="inlineStr">
+      <c r="DX8" t="inlineStr">
         <is>
           <t>通信網路業</t>
         </is>
       </c>
-      <c r="DX8" t="inlineStr">
+      <c r="DY8" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="DY8" t="inlineStr">
+      <c r="DZ8" t="inlineStr">
         <is>
           <t>0.01</t>
         </is>
       </c>
-      <c r="DZ8" t="inlineStr">
+      <c r="EA8" t="inlineStr">
         <is>
           <t>-1.398042523039787</t>
         </is>
       </c>
-      <c r="EA8" t="inlineStr">
+      <c r="EB8" t="inlineStr">
         <is>
           <t>7.608984617555596</t>
         </is>
       </c>
-      <c r="EB8" t="inlineStr">
+      <c r="EC8" t="inlineStr">
         <is>
           <t>7.52024426560034</t>
         </is>
       </c>
-      <c r="EC8" t="inlineStr">
+      <c r="ED8" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
-      <c r="ED8" t="inlineStr">
+      <c r="EE8" t="inlineStr">
         <is>
           <t>價-量增</t>
         </is>
       </c>
-      <c r="EE8" t="inlineStr">
+      <c r="EF8" t="inlineStr">
         <is>
           <t>3.04</t>
         </is>
       </c>
-      <c r="EF8" t="inlineStr">
+      <c r="EG8" t="inlineStr">
         <is>
           <t>3.55</t>
         </is>
       </c>
-      <c r="EG8" t="inlineStr">
+      <c r="EH8" t="inlineStr">
         <is>
           <t>7.91</t>
         </is>
       </c>
-      <c r="EH8" t="inlineStr">
+      <c r="EI8" t="inlineStr">
         <is>
           <t>28.78</t>
         </is>
       </c>
-      <c r="EI8" t="inlineStr">
+      <c r="EJ8" t="inlineStr">
         <is>
           <t>37.54%</t>
         </is>
       </c>
-      <c r="EJ8" t="inlineStr">
+      <c r="EK8" t="inlineStr">
         <is>
           <t>21.61%</t>
         </is>
       </c>
-      <c r="EK8" t="inlineStr">
+      <c r="EL8" t="inlineStr">
         <is>
           <t>84.4</t>
         </is>
       </c>
-      <c r="EL8" t="inlineStr">
+      <c r="EM8" t="inlineStr">
         <is>
           <t>1136466</t>
         </is>
       </c>
-      <c r="EM8" t="inlineStr">
+      <c r="EN8" t="inlineStr">
         <is>
           <t>個人家庭60.70%、企業客戶32.70%、國際客戶4.00%、其他2.60% (2025年)</t>
         </is>
       </c>
-      <c r="EN8" t="inlineStr">
+      <c r="EO8" t="inlineStr">
         <is>
           <t>中華電-通信網路業-上市</t>
         </is>
       </c>
-      <c r="EO8" t="inlineStr">
+      <c r="EP8" t="inlineStr">
         <is>
           <t>通信網路業右上上市</t>
         </is>
       </c>
-      <c r="EP8" t="inlineStr">
+      <c r="EQ8" t="inlineStr">
         <is>
           <t>145.0</t>
         </is>
       </c>
-      <c r="EQ8" t="inlineStr">
+      <c r="ER8" t="inlineStr">
         <is>
           <t>145.0</t>
         </is>
       </c>
-      <c r="ER8" t="inlineStr">
+      <c r="ES8" t="inlineStr">
         <is>
           <t>143.0</t>
         </is>
       </c>
-      <c r="ES8" t="inlineStr">
+      <c r="ET8" t="inlineStr">
         <is>
           <t>143.5</t>
         </is>
       </c>
-      <c r="ET8" t="inlineStr">
+      <c r="EU8" t="inlineStr">
         <is>
           <t>129.5</t>
         </is>
       </c>
-      <c r="EU8" t="inlineStr">
+      <c r="EV8" t="inlineStr">
         <is>
           <t>47.26</t>
         </is>
       </c>
-      <c r="EV8" t="inlineStr">
+      <c r="EW8" t="inlineStr">
         <is>
           <t>** 通信網路 - 電信服務業** 智慧電網 - 能源管理服務、系統整合服務</t>
         </is>
       </c>
-      <c r="EW8" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
       <c r="EX8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="EY8" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="EZ8" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="EZ8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="FA8" t="inlineStr">
         <is>
           <t>0</t>
@@ -8128,34 +8163,34 @@
       </c>
       <c r="FD8" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="FE8" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="FE8" t="inlineStr">
+      <c r="FF8" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="FF8" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="FG8" t="inlineStr">
         <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="FH8" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="FH8" t="inlineStr">
+      <c r="FI8" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="FI8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="FJ8" t="inlineStr">
         <is>
           <t>0</t>
@@ -8163,170 +8198,175 @@
       </c>
       <c r="FK8" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="FL8" t="inlineStr">
+        <is>
           <t>115.2Q</t>
         </is>
       </c>
-      <c r="FL8" t="inlineStr">
+      <c r="FM8" t="inlineStr">
         <is>
           <t>61363.0</t>
         </is>
       </c>
-      <c r="FM8" t="inlineStr">
+      <c r="FN8" t="inlineStr">
         <is>
           <t>38328.0</t>
         </is>
       </c>
-      <c r="FN8" t="inlineStr">
+      <c r="FO8" t="inlineStr">
         <is>
           <t>23035.0</t>
         </is>
       </c>
-      <c r="FO8" t="inlineStr">
+      <c r="FP8" t="inlineStr">
         <is>
           <t>37.54</t>
         </is>
       </c>
-      <c r="FP8" t="inlineStr">
+      <c r="FQ8" t="inlineStr">
         <is>
           <t>13261.0</t>
         </is>
       </c>
-      <c r="FQ8" t="inlineStr">
+      <c r="FR8" t="inlineStr">
         <is>
           <t>21.61%</t>
         </is>
       </c>
-      <c r="FR8" t="inlineStr">
+      <c r="FS8" t="inlineStr">
         <is>
           <t>691.0</t>
         </is>
       </c>
-      <c r="FS8" t="inlineStr">
+      <c r="FT8" t="inlineStr">
         <is>
           <t>13953.0</t>
         </is>
       </c>
-      <c r="FT8" t="inlineStr">
+      <c r="FU8" t="inlineStr">
         <is>
           <t>10641.0</t>
         </is>
       </c>
-      <c r="FU8" t="inlineStr">
+      <c r="FV8" t="inlineStr">
         <is>
           <t>1.37</t>
         </is>
       </c>
-      <c r="FV8" t="inlineStr">
+      <c r="FW8" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="FW8" t="inlineStr">
+      <c r="FX8" t="inlineStr">
         <is>
           <t>EPS成長 / 毛利率衰退</t>
         </is>
       </c>
-      <c r="FX8" t="inlineStr">
+      <c r="FY8" t="inlineStr">
         <is>
           <t>1.2475</t>
         </is>
       </c>
-      <c r="FY8" t="inlineStr">
+      <c r="FZ8" t="inlineStr">
         <is>
           <t>36.6475</t>
         </is>
       </c>
-      <c r="FZ8" t="inlineStr">
+      <c r="GA8" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="GA8" t="inlineStr">
+      <c r="GB8" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="GB8" t="inlineStr">
+      <c r="GC8" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="GC8" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="GD8" t="inlineStr">
         <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="GE8" t="inlineStr">
+        <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="GE8" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="GF8" t="inlineStr">
         <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="GG8" t="inlineStr">
+        <is>
           <t>0.07000000000000006</t>
         </is>
       </c>
-      <c r="GG8" t="inlineStr">
+      <c r="GH8" t="inlineStr">
         <is>
           <t>0.05384615384615388</t>
         </is>
       </c>
-      <c r="GH8" t="inlineStr">
+      <c r="GI8" t="inlineStr">
         <is>
           <t>-0.3800000000000026</t>
         </is>
       </c>
-      <c r="GI8" t="inlineStr">
+      <c r="GJ8" t="inlineStr">
         <is>
           <t>-0.01002109704641352</t>
         </is>
       </c>
-      <c r="GJ8" t="inlineStr">
+      <c r="GK8" t="inlineStr">
         <is>
           <t>0.06000000000000005</t>
         </is>
       </c>
-      <c r="GK8" t="inlineStr">
+      <c r="GL8" t="inlineStr">
         <is>
           <t>0.04580152671755733</t>
         </is>
       </c>
-      <c r="GL8" t="inlineStr">
+      <c r="GM8" t="inlineStr">
         <is>
           <t>-0.8400000000000034</t>
         </is>
       </c>
-      <c r="GM8" t="inlineStr">
+      <c r="GN8" t="inlineStr">
         <is>
           <t>-0.02188639916623247</t>
         </is>
       </c>
-      <c r="GN8" t="inlineStr">
+      <c r="GO8" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="GO8" t="inlineStr">
+      <c r="GP8" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="GP8" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="GQ8" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
       <c r="GR8" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="GS8" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
@@ -8725,378 +8765,378 @@
       </c>
       <c r="CA9" t="inlineStr">
         <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="CB9" t="inlineStr">
+        <is>
           <t>2026-09-18 00:00:00</t>
         </is>
       </c>
-      <c r="CB9" t="inlineStr">
+      <c r="CC9" t="inlineStr">
         <is>
           <t>2026-09-29</t>
         </is>
       </c>
-      <c r="CC9" t="inlineStr">
+      <c r="CD9" t="inlineStr">
         <is>
           <t>19.45</t>
         </is>
       </c>
-      <c r="CD9" t="inlineStr">
+      <c r="CE9" t="inlineStr">
         <is>
           <t>-0.69</t>
         </is>
       </c>
-      <c r="CE9" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="CF9" t="inlineStr"/>
-      <c r="CG9" t="inlineStr">
+      <c r="CF9" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="CG9" t="inlineStr"/>
+      <c r="CH9" t="inlineStr">
         <is>
           <t>67</t>
         </is>
       </c>
-      <c r="CH9" t="inlineStr">
+      <c r="CI9" t="inlineStr">
         <is>
           <t>9157</t>
         </is>
       </c>
-      <c r="CI9" t="inlineStr">
+      <c r="CJ9" t="inlineStr">
         <is>
           <t>25.0</t>
         </is>
       </c>
-      <c r="CJ9" t="inlineStr">
+      <c r="CK9" t="inlineStr">
         <is>
           <t>69.44</t>
         </is>
       </c>
-      <c r="CK9" t="n">
+      <c r="CL9" t="n">
         <v>-0.55</v>
       </c>
-      <c r="CL9" t="n">
+      <c r="CM9" t="n">
         <v>2.5</v>
       </c>
-      <c r="CM9" t="inlineStr">
+      <c r="CN9" t="inlineStr">
         <is>
           <t>1.64</t>
         </is>
       </c>
-      <c r="CN9" t="inlineStr">
+      <c r="CO9" t="inlineStr">
         <is>
           <t>-0.57</t>
         </is>
       </c>
-      <c r="CO9" t="inlineStr">
+      <c r="CP9" t="inlineStr">
         <is>
           <t>144.8</t>
         </is>
       </c>
-      <c r="CP9" t="inlineStr">
+      <c r="CQ9" t="inlineStr">
         <is>
           <t>144.4</t>
         </is>
       </c>
-      <c r="CQ9" t="inlineStr">
+      <c r="CR9" t="inlineStr">
         <is>
           <t>141.28</t>
         </is>
       </c>
-      <c r="CR9" t="inlineStr">
+      <c r="CS9" t="inlineStr">
         <is>
           <t>138.99</t>
         </is>
       </c>
-      <c r="CS9" t="inlineStr">
+      <c r="CT9" t="inlineStr">
         <is>
           <t>139.79</t>
         </is>
       </c>
-      <c r="CT9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="CU9" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CV9" t="inlineStr">
+        <is>
           <t>-0.002067539627842785</t>
         </is>
       </c>
-      <c r="CV9" t="inlineStr">
+      <c r="CW9" t="inlineStr">
         <is>
           <t>0.002429711905588272</t>
         </is>
       </c>
-      <c r="CW9" t="inlineStr">
+      <c r="CX9" t="inlineStr">
         <is>
           <t>0.003017394391196415</t>
         </is>
       </c>
-      <c r="CX9" t="inlineStr">
+      <c r="CY9" t="inlineStr">
         <is>
           <t>0.0008641175199828321</t>
         </is>
       </c>
-      <c r="CY9" t="inlineStr">
+      <c r="CZ9" t="inlineStr">
         <is>
           <t>0.0002683363148479057</t>
         </is>
       </c>
-      <c r="CZ9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="DA9" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="DB9" t="inlineStr">
+        <is>
           <t>17.86</t>
         </is>
       </c>
-      <c r="DB9" t="n">
+      <c r="DC9" t="n">
         <v>2.04</v>
       </c>
-      <c r="DC9" t="n">
+      <c r="DD9" t="n">
         <v>1.73</v>
       </c>
-      <c r="DD9" t="inlineStr">
+      <c r="DE9" t="inlineStr">
         <is>
           <t>1.9</t>
         </is>
       </c>
-      <c r="DE9" t="inlineStr">
+      <c r="DF9" t="inlineStr">
         <is>
           <t>-8.63</t>
         </is>
       </c>
-      <c r="DF9" t="inlineStr">
+      <c r="DG9" t="inlineStr">
         <is>
           <t>2026/08/21</t>
         </is>
       </c>
-      <c r="DG9" t="inlineStr">
+      <c r="DH9" t="inlineStr">
         <is>
           <t>2510241792.666667</t>
         </is>
       </c>
-      <c r="DH9" t="inlineStr">
+      <c r="DI9" t="inlineStr">
         <is>
           <t>1676725028.0</t>
         </is>
       </c>
-      <c r="DI9" t="n">
+      <c r="DJ9" t="n">
         <v>1178675636.2</v>
       </c>
-      <c r="DJ9" t="inlineStr">
+      <c r="DK9" t="inlineStr">
         <is>
           <t>1937528191.3</t>
         </is>
       </c>
-      <c r="DK9" t="inlineStr">
+      <c r="DL9" t="inlineStr">
         <is>
           <t>1486546014.1</t>
         </is>
       </c>
-      <c r="DL9" t="n">
+      <c r="DM9" t="n">
         <v>1735471199.16</v>
       </c>
-      <c r="DM9" t="inlineStr">
+      <c r="DN9" t="inlineStr">
         <is>
           <t>2026673727.9875</t>
         </is>
       </c>
-      <c r="DN9" t="inlineStr">
+      <c r="DO9" t="inlineStr">
         <is>
           <t>44598963.52419861</t>
         </is>
       </c>
-      <c r="DO9" t="inlineStr">
+      <c r="DP9" t="inlineStr">
         <is>
           <t>-45987257.26861119</t>
         </is>
       </c>
-      <c r="DP9" t="inlineStr">
+      <c r="DQ9" t="inlineStr">
         <is>
           <t>1676725028.0</t>
         </is>
       </c>
-      <c r="DQ9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="DR9" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="DS9" t="inlineStr">
+        <is>
           <t>143.5</t>
         </is>
       </c>
-      <c r="DS9" t="inlineStr">
+      <c r="DT9" t="inlineStr">
         <is>
           <t>2026/09/15</t>
         </is>
       </c>
-      <c r="DT9" t="inlineStr">
+      <c r="DU9" t="inlineStr">
         <is>
           <t>0.35</t>
         </is>
       </c>
-      <c r="DU9" t="inlineStr">
+      <c r="DV9" t="inlineStr">
         <is>
           <t>中華電</t>
         </is>
       </c>
-      <c r="DV9" t="inlineStr">
+      <c r="DW9" t="inlineStr">
         <is>
           <t>中華電</t>
         </is>
       </c>
-      <c r="DW9" t="inlineStr">
+      <c r="DX9" t="inlineStr">
         <is>
           <t>通信網路業</t>
         </is>
       </c>
-      <c r="DX9" t="inlineStr">
+      <c r="DY9" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="DY9" t="inlineStr">
+      <c r="DZ9" t="inlineStr">
         <is>
           <t>0.01</t>
         </is>
       </c>
-      <c r="DZ9" t="inlineStr">
+      <c r="EA9" t="inlineStr">
         <is>
           <t>-1.398042523039787</t>
         </is>
       </c>
-      <c r="EA9" t="inlineStr">
+      <c r="EB9" t="inlineStr">
         <is>
           <t>7.608984617555596</t>
         </is>
       </c>
-      <c r="EB9" t="inlineStr">
+      <c r="EC9" t="inlineStr">
         <is>
           <t>7.52024426560034</t>
         </is>
       </c>
-      <c r="EC9" t="inlineStr">
+      <c r="ED9" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
-      <c r="ED9" t="inlineStr">
+      <c r="EE9" t="inlineStr">
         <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="EE9" t="inlineStr">
+      <c r="EF9" t="inlineStr">
         <is>
           <t>3.05</t>
         </is>
       </c>
-      <c r="EF9" t="inlineStr">
+      <c r="EG9" t="inlineStr">
         <is>
           <t>3.55</t>
         </is>
       </c>
-      <c r="EG9" t="inlineStr">
+      <c r="EH9" t="inlineStr">
         <is>
           <t>7.91</t>
         </is>
       </c>
-      <c r="EH9" t="inlineStr">
+      <c r="EI9" t="inlineStr">
         <is>
           <t>28.78</t>
         </is>
       </c>
-      <c r="EI9" t="inlineStr">
+      <c r="EJ9" t="inlineStr">
         <is>
           <t>37.54%</t>
         </is>
       </c>
-      <c r="EJ9" t="inlineStr">
+      <c r="EK9" t="inlineStr">
         <is>
           <t>21.61%</t>
         </is>
       </c>
-      <c r="EK9" t="inlineStr">
+      <c r="EL9" t="inlineStr">
         <is>
           <t>84.4</t>
         </is>
       </c>
-      <c r="EL9" t="inlineStr">
+      <c r="EM9" t="inlineStr">
         <is>
           <t>1136466</t>
         </is>
       </c>
-      <c r="EM9" t="inlineStr">
+      <c r="EN9" t="inlineStr">
         <is>
           <t>個人家庭60.70%、企業客戶32.70%、國際客戶4.00%、其他2.60% (2025年)</t>
         </is>
       </c>
-      <c r="EN9" t="inlineStr">
+      <c r="EO9" t="inlineStr">
         <is>
           <t>中華電-通信網路業-上市</t>
         </is>
       </c>
-      <c r="EO9" t="inlineStr">
+      <c r="EP9" t="inlineStr">
         <is>
           <t>通信網路業右上上市</t>
         </is>
       </c>
-      <c r="EP9" t="inlineStr">
+      <c r="EQ9" t="inlineStr">
         <is>
           <t>146.0</t>
         </is>
       </c>
-      <c r="EQ9" t="inlineStr">
+      <c r="ER9" t="inlineStr">
         <is>
           <t>146.0</t>
         </is>
       </c>
-      <c r="ER9" t="inlineStr">
+      <c r="ES9" t="inlineStr">
         <is>
           <t>143.0</t>
         </is>
       </c>
-      <c r="ES9" t="inlineStr">
+      <c r="ET9" t="inlineStr">
         <is>
           <t>144.0</t>
         </is>
       </c>
-      <c r="ET9" t="inlineStr">
+      <c r="EU9" t="inlineStr">
         <is>
           <t>129.5</t>
         </is>
       </c>
-      <c r="EU9" t="inlineStr">
+      <c r="EV9" t="inlineStr">
         <is>
           <t>47.26</t>
         </is>
       </c>
-      <c r="EV9" t="inlineStr">
+      <c r="EW9" t="inlineStr">
         <is>
           <t>** 通信網路 - 電信服務業** 智慧電網 - 能源管理服務、系統整合服務</t>
         </is>
       </c>
-      <c r="EW9" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
       <c r="EX9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="EY9" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="EZ9" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="EZ9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="FA9" t="inlineStr">
         <is>
           <t>0</t>
@@ -9114,34 +9154,34 @@
       </c>
       <c r="FD9" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="FE9" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="FE9" t="inlineStr">
+      <c r="FF9" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="FF9" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="FG9" t="inlineStr">
         <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="FH9" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="FH9" t="inlineStr">
+      <c r="FI9" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="FI9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="FJ9" t="inlineStr">
         <is>
           <t>0</t>
@@ -9149,170 +9189,175 @@
       </c>
       <c r="FK9" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="FL9" t="inlineStr">
+        <is>
           <t>115.2Q</t>
         </is>
       </c>
-      <c r="FL9" t="inlineStr">
+      <c r="FM9" t="inlineStr">
         <is>
           <t>61363.0</t>
         </is>
       </c>
-      <c r="FM9" t="inlineStr">
+      <c r="FN9" t="inlineStr">
         <is>
           <t>38328.0</t>
         </is>
       </c>
-      <c r="FN9" t="inlineStr">
+      <c r="FO9" t="inlineStr">
         <is>
           <t>23035.0</t>
         </is>
       </c>
-      <c r="FO9" t="inlineStr">
+      <c r="FP9" t="inlineStr">
         <is>
           <t>37.54</t>
         </is>
       </c>
-      <c r="FP9" t="inlineStr">
+      <c r="FQ9" t="inlineStr">
         <is>
           <t>13261.0</t>
         </is>
       </c>
-      <c r="FQ9" t="inlineStr">
+      <c r="FR9" t="inlineStr">
         <is>
           <t>21.61%</t>
         </is>
       </c>
-      <c r="FR9" t="inlineStr">
+      <c r="FS9" t="inlineStr">
         <is>
           <t>691.0</t>
         </is>
       </c>
-      <c r="FS9" t="inlineStr">
+      <c r="FT9" t="inlineStr">
         <is>
           <t>13953.0</t>
         </is>
       </c>
-      <c r="FT9" t="inlineStr">
+      <c r="FU9" t="inlineStr">
         <is>
           <t>10641.0</t>
         </is>
       </c>
-      <c r="FU9" t="inlineStr">
+      <c r="FV9" t="inlineStr">
         <is>
           <t>1.37</t>
         </is>
       </c>
-      <c r="FV9" t="inlineStr">
+      <c r="FW9" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="FW9" t="inlineStr">
+      <c r="FX9" t="inlineStr">
         <is>
           <t>EPS成長 / 毛利率衰退</t>
         </is>
       </c>
-      <c r="FX9" t="inlineStr">
+      <c r="FY9" t="inlineStr">
         <is>
           <t>1.2475</t>
         </is>
       </c>
-      <c r="FY9" t="inlineStr">
+      <c r="FZ9" t="inlineStr">
         <is>
           <t>36.6475</t>
         </is>
       </c>
-      <c r="FZ9" t="inlineStr">
+      <c r="GA9" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="GA9" t="inlineStr">
+      <c r="GB9" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="GB9" t="inlineStr">
+      <c r="GC9" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="GC9" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="GD9" t="inlineStr">
         <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="GE9" t="inlineStr">
+        <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="GE9" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="GF9" t="inlineStr">
         <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="GG9" t="inlineStr">
+        <is>
           <t>0.07000000000000006</t>
         </is>
       </c>
-      <c r="GG9" t="inlineStr">
+      <c r="GH9" t="inlineStr">
         <is>
           <t>0.05384615384615388</t>
         </is>
       </c>
-      <c r="GH9" t="inlineStr">
+      <c r="GI9" t="inlineStr">
         <is>
           <t>-0.3800000000000026</t>
         </is>
       </c>
-      <c r="GI9" t="inlineStr">
+      <c r="GJ9" t="inlineStr">
         <is>
           <t>-0.01002109704641352</t>
         </is>
       </c>
-      <c r="GJ9" t="inlineStr">
+      <c r="GK9" t="inlineStr">
         <is>
           <t>0.06000000000000005</t>
         </is>
       </c>
-      <c r="GK9" t="inlineStr">
+      <c r="GL9" t="inlineStr">
         <is>
           <t>0.04580152671755733</t>
         </is>
       </c>
-      <c r="GL9" t="inlineStr">
+      <c r="GM9" t="inlineStr">
         <is>
           <t>-0.8400000000000034</t>
         </is>
       </c>
-      <c r="GM9" t="inlineStr">
+      <c r="GN9" t="inlineStr">
         <is>
           <t>-0.02188639916623247</t>
         </is>
       </c>
-      <c r="GN9" t="inlineStr">
+      <c r="GO9" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="GO9" t="inlineStr">
+      <c r="GP9" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="GP9" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="GQ9" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
       <c r="GR9" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="GS9" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
@@ -9711,378 +9756,378 @@
       </c>
       <c r="CA10" t="inlineStr">
         <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="CB10" t="inlineStr">
+        <is>
           <t>2026-09-18 00:00:00</t>
         </is>
       </c>
-      <c r="CB10" t="inlineStr">
+      <c r="CC10" t="inlineStr">
         <is>
           <t>2026-09-24</t>
         </is>
       </c>
-      <c r="CC10" t="inlineStr">
+      <c r="CD10" t="inlineStr">
         <is>
           <t>10.53</t>
         </is>
       </c>
-      <c r="CD10" t="inlineStr">
+      <c r="CE10" t="inlineStr">
         <is>
           <t>-0.69</t>
         </is>
       </c>
-      <c r="CE10" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="CF10" t="inlineStr"/>
-      <c r="CG10" t="inlineStr">
+      <c r="CF10" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="CG10" t="inlineStr"/>
+      <c r="CH10" t="inlineStr">
         <is>
           <t>67</t>
         </is>
       </c>
-      <c r="CH10" t="inlineStr">
+      <c r="CI10" t="inlineStr">
         <is>
           <t>9157</t>
         </is>
       </c>
-      <c r="CI10" t="inlineStr">
+      <c r="CJ10" t="inlineStr">
         <is>
           <t>83.33</t>
         </is>
       </c>
-      <c r="CJ10" t="inlineStr">
+      <c r="CK10" t="inlineStr">
         <is>
           <t>91.67</t>
         </is>
       </c>
-      <c r="CK10" t="n">
+      <c r="CL10" t="n">
         <v>-0.07000000000000001</v>
       </c>
-      <c r="CL10" t="n">
+      <c r="CM10" t="n">
         <v>3.02</v>
       </c>
-      <c r="CM10" t="inlineStr">
+      <c r="CN10" t="inlineStr">
         <is>
           <t>1.43</t>
         </is>
       </c>
-      <c r="CN10" t="inlineStr">
+      <c r="CO10" t="inlineStr">
         <is>
           <t>-0.63</t>
         </is>
       </c>
-      <c r="CO10" t="inlineStr">
+      <c r="CP10" t="inlineStr">
         <is>
           <t>145.1</t>
         </is>
       </c>
-      <c r="CP10" t="inlineStr">
+      <c r="CQ10" t="inlineStr">
         <is>
           <t>144.05</t>
         </is>
       </c>
-      <c r="CQ10" t="inlineStr">
+      <c r="CR10" t="inlineStr">
         <is>
           <t>140.85</t>
         </is>
       </c>
-      <c r="CR10" t="inlineStr">
+      <c r="CS10" t="inlineStr">
         <is>
           <t>138.87</t>
         </is>
       </c>
-      <c r="CS10" t="inlineStr">
+      <c r="CT10" t="inlineStr">
         <is>
           <t>139.75</t>
         </is>
       </c>
-      <c r="CT10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="CU10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="CV10" t="inlineStr">
         <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="CW10" t="inlineStr">
+        <is>
           <t>0.003832752613240453</t>
         </is>
       </c>
-      <c r="CW10" t="inlineStr">
+      <c r="CX10" t="inlineStr">
         <is>
           <t>0.00338379341050743</t>
         </is>
       </c>
-      <c r="CX10" t="inlineStr">
+      <c r="CY10" t="inlineStr">
         <is>
           <t>0.001297858533420015</t>
         </is>
       </c>
-      <c r="CY10" t="inlineStr">
+      <c r="CZ10" t="inlineStr">
         <is>
           <t>0.0002684083385522396</t>
         </is>
       </c>
-      <c r="CZ10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="DA10" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="DB10" t="inlineStr">
+        <is>
           <t>29.64</t>
         </is>
       </c>
-      <c r="DB10" t="n">
+      <c r="DC10" t="n">
         <v>2.14</v>
       </c>
-      <c r="DC10" t="n">
+      <c r="DD10" t="n">
         <v>1.65</v>
       </c>
-      <c r="DD10" t="inlineStr">
+      <c r="DE10" t="inlineStr">
         <is>
           <t>1.9</t>
         </is>
       </c>
-      <c r="DE10" t="inlineStr">
+      <c r="DF10" t="inlineStr">
         <is>
           <t>-12.71</t>
         </is>
       </c>
-      <c r="DF10" t="inlineStr">
+      <c r="DG10" t="inlineStr">
         <is>
           <t>2026/08/21</t>
         </is>
       </c>
-      <c r="DG10" t="inlineStr">
+      <c r="DH10" t="inlineStr">
         <is>
           <t>2510241792.666667</t>
         </is>
       </c>
-      <c r="DH10" t="inlineStr">
+      <c r="DI10" t="inlineStr">
         <is>
           <t>918019598.0</t>
         </is>
       </c>
-      <c r="DI10" t="n">
+      <c r="DJ10" t="n">
         <v>1659195852.6</v>
       </c>
-      <c r="DJ10" t="inlineStr">
+      <c r="DK10" t="inlineStr">
         <is>
           <t>1973672854.5</t>
         </is>
       </c>
-      <c r="DK10" t="inlineStr">
+      <c r="DL10" t="inlineStr">
         <is>
           <t>1482010386.8</t>
         </is>
       </c>
-      <c r="DL10" t="n">
+      <c r="DM10" t="n">
         <v>1806077677.02</v>
       </c>
-      <c r="DM10" t="inlineStr">
+      <c r="DN10" t="inlineStr">
         <is>
           <t>2030537576.35</t>
         </is>
       </c>
-      <c r="DN10" t="inlineStr">
+      <c r="DO10" t="inlineStr">
         <is>
           <t>61069185.48652767</t>
         </is>
       </c>
-      <c r="DO10" t="inlineStr">
+      <c r="DP10" t="inlineStr">
         <is>
           <t>-60540988.90541673</t>
         </is>
       </c>
-      <c r="DP10" t="inlineStr">
+      <c r="DQ10" t="inlineStr">
         <is>
           <t>918019598.0</t>
         </is>
       </c>
-      <c r="DQ10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="DR10" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="DS10" t="inlineStr">
+        <is>
           <t>143.5</t>
         </is>
       </c>
-      <c r="DS10" t="inlineStr">
+      <c r="DT10" t="inlineStr">
         <is>
           <t>2026/09/15</t>
         </is>
       </c>
-      <c r="DT10" t="inlineStr">
+      <c r="DU10" t="inlineStr">
         <is>
           <t>1.05</t>
         </is>
       </c>
-      <c r="DU10" t="inlineStr">
+      <c r="DV10" t="inlineStr">
         <is>
           <t>中華電</t>
         </is>
       </c>
-      <c r="DV10" t="inlineStr">
+      <c r="DW10" t="inlineStr">
         <is>
           <t>中華電</t>
         </is>
       </c>
-      <c r="DW10" t="inlineStr">
+      <c r="DX10" t="inlineStr">
         <is>
           <t>通信網路業</t>
         </is>
       </c>
-      <c r="DX10" t="inlineStr">
+      <c r="DY10" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="DY10" t="inlineStr">
+      <c r="DZ10" t="inlineStr">
         <is>
           <t>0.01</t>
         </is>
       </c>
-      <c r="DZ10" t="inlineStr">
+      <c r="EA10" t="inlineStr">
         <is>
           <t>-1.398042523039787</t>
         </is>
       </c>
-      <c r="EA10" t="inlineStr">
+      <c r="EB10" t="inlineStr">
         <is>
           <t>7.608984617555596</t>
         </is>
       </c>
-      <c r="EB10" t="inlineStr">
+      <c r="EC10" t="inlineStr">
         <is>
           <t>7.52024426560034</t>
         </is>
       </c>
-      <c r="EC10" t="inlineStr">
+      <c r="ED10" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
-      <c r="ED10" t="inlineStr">
+      <c r="EE10" t="inlineStr">
         <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="EE10" t="inlineStr">
+      <c r="EF10" t="inlineStr">
         <is>
           <t>3.07</t>
         </is>
       </c>
-      <c r="EF10" t="inlineStr">
+      <c r="EG10" t="inlineStr">
         <is>
           <t>3.55</t>
         </is>
       </c>
-      <c r="EG10" t="inlineStr">
+      <c r="EH10" t="inlineStr">
         <is>
           <t>7.91</t>
         </is>
       </c>
-      <c r="EH10" t="inlineStr">
+      <c r="EI10" t="inlineStr">
         <is>
           <t>28.78</t>
         </is>
       </c>
-      <c r="EI10" t="inlineStr">
+      <c r="EJ10" t="inlineStr">
         <is>
           <t>37.54%</t>
         </is>
       </c>
-      <c r="EJ10" t="inlineStr">
+      <c r="EK10" t="inlineStr">
         <is>
           <t>21.61%</t>
         </is>
       </c>
-      <c r="EK10" t="inlineStr">
+      <c r="EL10" t="inlineStr">
         <is>
           <t>84.4</t>
         </is>
       </c>
-      <c r="EL10" t="inlineStr">
+      <c r="EM10" t="inlineStr">
         <is>
           <t>1136466</t>
         </is>
       </c>
-      <c r="EM10" t="inlineStr">
+      <c r="EN10" t="inlineStr">
         <is>
           <t>個人家庭60.70%、企業客戶32.70%、國際客戶4.00%、其他2.60% (2025年)</t>
         </is>
       </c>
-      <c r="EN10" t="inlineStr">
+      <c r="EO10" t="inlineStr">
         <is>
           <t>中華電-通信網路業-上市</t>
         </is>
       </c>
-      <c r="EO10" t="inlineStr">
+      <c r="EP10" t="inlineStr">
         <is>
           <t>通信網路業右上上市</t>
         </is>
       </c>
-      <c r="EP10" t="inlineStr">
+      <c r="EQ10" t="inlineStr">
         <is>
           <t>145.5</t>
         </is>
       </c>
-      <c r="EQ10" t="inlineStr">
+      <c r="ER10" t="inlineStr">
         <is>
           <t>146.0</t>
         </is>
       </c>
-      <c r="ER10" t="inlineStr">
+      <c r="ES10" t="inlineStr">
         <is>
           <t>145.0</t>
         </is>
       </c>
-      <c r="ES10" t="inlineStr">
+      <c r="ET10" t="inlineStr">
         <is>
           <t>145.0</t>
         </is>
       </c>
-      <c r="ET10" t="inlineStr">
+      <c r="EU10" t="inlineStr">
         <is>
           <t>129.5</t>
         </is>
       </c>
-      <c r="EU10" t="inlineStr">
+      <c r="EV10" t="inlineStr">
         <is>
           <t>47.26</t>
         </is>
       </c>
-      <c r="EV10" t="inlineStr">
+      <c r="EW10" t="inlineStr">
         <is>
           <t>** 通信網路 - 電信服務業** 智慧電網 - 能源管理服務、系統整合服務</t>
         </is>
       </c>
-      <c r="EW10" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
       <c r="EX10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="EY10" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="EZ10" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="EZ10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="FA10" t="inlineStr">
         <is>
           <t>0</t>
@@ -10100,205 +10145,210 @@
       </c>
       <c r="FD10" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="FE10" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="FE10" t="inlineStr">
+      <c r="FF10" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="FF10" t="inlineStr">
+      <c r="FG10" t="inlineStr">
         <is>
           <t>1.119557506059444</t>
         </is>
       </c>
-      <c r="FG10" t="inlineStr">
+      <c r="FH10" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="FH10" t="inlineStr">
+      <c r="FI10" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="FI10" t="inlineStr">
+      <c r="FJ10" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="FJ10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="FK10" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="FL10" t="inlineStr">
+        <is>
           <t>115.2Q</t>
         </is>
       </c>
-      <c r="FL10" t="inlineStr">
+      <c r="FM10" t="inlineStr">
         <is>
           <t>61363.0</t>
         </is>
       </c>
-      <c r="FM10" t="inlineStr">
+      <c r="FN10" t="inlineStr">
         <is>
           <t>38328.0</t>
         </is>
       </c>
-      <c r="FN10" t="inlineStr">
+      <c r="FO10" t="inlineStr">
         <is>
           <t>23035.0</t>
         </is>
       </c>
-      <c r="FO10" t="inlineStr">
+      <c r="FP10" t="inlineStr">
         <is>
           <t>37.54</t>
         </is>
       </c>
-      <c r="FP10" t="inlineStr">
+      <c r="FQ10" t="inlineStr">
         <is>
           <t>13261.0</t>
         </is>
       </c>
-      <c r="FQ10" t="inlineStr">
+      <c r="FR10" t="inlineStr">
         <is>
           <t>21.61%</t>
         </is>
       </c>
-      <c r="FR10" t="inlineStr">
+      <c r="FS10" t="inlineStr">
         <is>
           <t>691.0</t>
         </is>
       </c>
-      <c r="FS10" t="inlineStr">
+      <c r="FT10" t="inlineStr">
         <is>
           <t>13953.0</t>
         </is>
       </c>
-      <c r="FT10" t="inlineStr">
+      <c r="FU10" t="inlineStr">
         <is>
           <t>10641.0</t>
         </is>
       </c>
-      <c r="FU10" t="inlineStr">
+      <c r="FV10" t="inlineStr">
         <is>
           <t>1.37</t>
         </is>
       </c>
-      <c r="FV10" t="inlineStr">
+      <c r="FW10" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="FW10" t="inlineStr">
+      <c r="FX10" t="inlineStr">
         <is>
           <t>EPS成長 / 毛利率衰退</t>
         </is>
       </c>
-      <c r="FX10" t="inlineStr">
+      <c r="FY10" t="inlineStr">
         <is>
           <t>1.2475</t>
         </is>
       </c>
-      <c r="FY10" t="inlineStr">
+      <c r="FZ10" t="inlineStr">
         <is>
           <t>36.6475</t>
         </is>
       </c>
-      <c r="FZ10" t="inlineStr">
+      <c r="GA10" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="GA10" t="inlineStr">
+      <c r="GB10" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="GB10" t="inlineStr">
+      <c r="GC10" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="GC10" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="GD10" t="inlineStr">
         <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="GE10" t="inlineStr">
+        <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="GE10" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="GF10" t="inlineStr">
         <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="GG10" t="inlineStr">
+        <is>
           <t>0.07000000000000006</t>
         </is>
       </c>
-      <c r="GG10" t="inlineStr">
+      <c r="GH10" t="inlineStr">
         <is>
           <t>0.05384615384615388</t>
         </is>
       </c>
-      <c r="GH10" t="inlineStr">
+      <c r="GI10" t="inlineStr">
         <is>
           <t>-0.3800000000000026</t>
         </is>
       </c>
-      <c r="GI10" t="inlineStr">
+      <c r="GJ10" t="inlineStr">
         <is>
           <t>-0.01002109704641352</t>
         </is>
       </c>
-      <c r="GJ10" t="inlineStr">
+      <c r="GK10" t="inlineStr">
         <is>
           <t>0.06000000000000005</t>
         </is>
       </c>
-      <c r="GK10" t="inlineStr">
+      <c r="GL10" t="inlineStr">
         <is>
           <t>0.04580152671755733</t>
         </is>
       </c>
-      <c r="GL10" t="inlineStr">
+      <c r="GM10" t="inlineStr">
         <is>
           <t>-0.8400000000000034</t>
         </is>
       </c>
-      <c r="GM10" t="inlineStr">
+      <c r="GN10" t="inlineStr">
         <is>
           <t>-0.02188639916623247</t>
         </is>
       </c>
-      <c r="GN10" t="inlineStr">
+      <c r="GO10" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="GO10" t="inlineStr">
+      <c r="GP10" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="GP10" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="GQ10" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
       <c r="GR10" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="GS10" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
